--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>408,551</t>
+          <t>406,838</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF FÁCIL RF SIMPLES RESP LTDA</t>
+          <t>CAIXA FIC FIF FÁCIL RF SIMPLES RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.726,533</t>
+          <t>6.646,913</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF MOVIMENTAÇÕES AUTOMÁTICAS RF SIMPLES RESP LTDA</t>
+          <t>CAIXA FIC FIF MOVIMENTAÇÕES AUTOMÁTICAS RF SIMPLES RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>810,624</t>
+          <t>810,007</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>120,092</t>
+          <t>120,091</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>96,153</t>
+          <t>96,136</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>584,603</t>
+          <t>584,596</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>61,658</t>
+          <t>61,657</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1.672,750</t>
+          <t>1.672,699</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,420</t>
+          <t>28,419</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>79,712</t>
+          <t>79,693</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>140,753</t>
+          <t>140,752</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1.756,434</t>
+          <t>1.740,789</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2.192,986</t>
+          <t>2.192,972</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>957,119</t>
+          <t>957,109</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CAIXA EXPERT ARX IPCA DEB INCENTIVADAS FIC FIF RF CRED PRIV - RESP LTDA (1) (2)</t>
+          <t>CAIXA EXPERT ARX IPCA DEB INCENTIVADAS FIC FIF RF CRED PRIV - RESP LTDA (2)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1798,32 +1798,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,10997325</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>2,89</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>219,622</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF FIC EXPERT SULAMERICA RF CRED PRIV LP - RESP LTDA (1)</t>
+          <t>CAIXA FIF FIC EXPERT SULAMERICA RF CRED PRIV LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1851,32 +1851,32 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,22811400</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>0,62</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>4,85</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>14,63</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70,980</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>175,319</t>
+          <t>175,223</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CAIXA EXPERT VOX DESENV SUSTENTAVEL IS RF CRED PRIV LP - RESP LTDA (1) (2)</t>
+          <t>CAIXA EXPERT VOX DESENV SUSTENTAVEL IS RF CRED PRIV LP - RESP LTDA (2)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2014,32 +2014,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,02936900</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>0,52</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>4,97</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21,758</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>CAIXA EXPERT ABSOLUTE CRETA FIC FIF RF CRED PRIV LP - RESP LTDA (1)</t>
+          <t>CAIXA EXPERT ABSOLUTE CRETA FIC FIF RF CRED PRIV LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2067,32 +2067,32 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,15576700</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>0,66</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>4,08</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>13,73</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>66,353</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CAIXA EXPERT RB ASSET CDI DEB INCENTIVADAS FIC FIF RF CRED PRIV RESP LTDA (1) (2)</t>
+          <t>CAIXA EXPERT RB ASSET CDI DEB INCENTIVADAS FIC FIF RF CRED PRIV RESP LTDA (2)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,05776364</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>0,31</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>2,36</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>332,405</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>CAIXA EXPERT VINLAND DEB IN INFRA RF CRED PRIV LP RESP LTDA (1) (2) (3)</t>
+          <t>CAIXA EXPERT VINLAND DEB IN INFRA RF CRED PRIV LP RESP LTDA (2) (3)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>859,898</t>
+          <t>859,833</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.241,411</t>
+          <t>3.241,339</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>3.113,953</t>
+          <t>3.113,942</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>125,145</t>
+          <t>125,015</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>550,004</t>
+          <t>549,999</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>334,888</t>
+          <t>334,883</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2.373,675</t>
+          <t>2.373,657</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>553,400</t>
+          <t>553,399</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15.485,298</t>
+          <t>15.485,082</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>1.383,497</t>
+          <t>1.383,496</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>165,472</t>
+          <t>165,470</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6.013,909</t>
+          <t>5.952,431</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>2.188,952</t>
+          <t>2.188,909</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>839,422</t>
+          <t>839,413</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15.546,151</t>
+          <t>15.545,914</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>9.466,109</t>
+          <t>9.466,015</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>20.846,276</t>
+          <t>20.845,858</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>13.169,981</t>
+          <t>13.169,776</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF RENDA FIXA CURTO PRAZO RESP LTDA</t>
+          <t>CAIXA FIC FIF RENDA FIXA CURTO PRAZO RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>245,548</t>
+          <t>245,520</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF FOF SMART CRED PRIV MM LP RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF FOF SMART CRED PRIV MM LP RESP LTDA</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -3513,32 +3513,32 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,39931700</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>-0,007</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>0,60</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>4,51</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>14,12</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>68,862</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC MULTIGESTOR GLOBAL EQUITIES IE (1)</t>
+          <t>CAIXA FIC MULTIGESTOR GLOBAL EQUITIES IE</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.167,25373800</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>1,55</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>-6,97</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>-2,47</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35,739</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>328,493</t>
+          <t>540,035</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF ESTRATÉGIA LIVRE MULTIMERCADO LP RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF ESTRATÉGIA LIVRE MULTIMERCADO LP RESP LTDA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3684,32 +3684,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.632,15053600</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>-0,006</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>-0,22</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>4,16</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>13,39</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>116,889</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>13,423</t>
+          <t>13,348</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>CAIXA CARTEIRA QUANT DUO FIC FIF MM LP RESP LTDA (1) (2) (3)</t>
+          <t>CAIXA CARTEIRA QUANT DUO FIC FIF MM LP RESP LTDA (2) (3)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF FOF SMART LONG SHORT LP RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF FOF SMART LONG SHORT LP RESP LTDA</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3847,32 +3847,32 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,25018500</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>-0,005</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>-0,44</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>2,36</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>11,60</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6,666</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>CAIXA CARTEIRA QUANT QUALI FIC FIF MM LP RESP LTDA (1) (2) (3)</t>
+          <t>CAIXA CARTEIRA QUANT QUALI FIC FIF MM LP RESP LTDA (2) (3)</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF FOF SMART LONG BIAS MM RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF FOF SMART LONG BIAS MM RESP LTDA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4006,32 +4006,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,44320300</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>-0,004</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>-1,73</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>5,72</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>21,08</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11,970</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>CAIXA CARTEIRA QUANT UNO FIC FIF MM LP RESP LTDA (1) (2) (3)</t>
+          <t>CAIXA CARTEIRA QUANT UNO FIC FIF MM LP RESP LTDA (2) (3)</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF ESTRATÉGICO MULTIMERCADO LP RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF ESTRATÉGICO MULTIMERCADO LP RESP LTDA</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -4169,32 +4169,32 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>5,32047778</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>-0,21</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>3,69</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>13,12</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33,192</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>668,164</t>
+          <t>666,467</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF FOF SMART MULTIESTRATEGIA MM RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF FOF SMART MULTIESTRATEGIA MM RESP LTDA</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>2,85531700</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>-0,004</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>2,22</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>11,44</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>77,229</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>2.330,280</t>
+          <t>2.329,776</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF FUNCIONARIOS ESTRATEGIA LIVRE MULTIMERCADO LP RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF FUNCIONARIOS ESTRATEGIA LIVRE MULTIMERCADO LP RESP LTDA</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -4511,32 +4511,32 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.652,59401600</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>-0,18</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>4,49</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>14,36</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15,317</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>CAIXA HASHDEX NASDAQ CRYPTO INDEX FIC FIF MM RESP LTDA (1) (2)</t>
+          <t>CAIXA HASHDEX NASDAQ CRYPTO INDEX FIC FIF MM RESP LTDA (2)</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4564,32 +4564,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0,57593472</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>-0,007</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>6,16</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>-20,24</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4,200</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF CAPITAL PROTEGIDO CESTA AGRO MM (1)</t>
+          <t>CAIXA FIC FIF CAPITAL PROTEGIDO CESTA AGRO MM</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -4617,32 +4617,32 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,37874300</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>-1,35</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>1,66</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>8,35</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70,771</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>CAIXA CAPITAL PROTEGIDO CÍCLICO III FIC FIF MM LP - RESP LTDA (1)</t>
+          <t>CAIXA CAPITAL PROTEGIDO CÍCLICO III FIC FIF MM LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4670,32 +4670,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,53337400</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>-0,004</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>2,69</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>18,93</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14,513</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>CAIXA CAPITAL PROTEGIDO IBOVESPA CÍCLICO I FIC FIF MM (1)</t>
+          <t>CAIXA CAPITAL PROTEGIDO IBOVESPA CÍCLICO I FIC FIF MM</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -4727,32 +4727,32 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>3,25598300</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>-0,005</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>1,19</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>2,19</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>7,05</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>155,146</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIM CAPITAL PROTEGIDO CICLICO II LP - RL (1)</t>
+          <t>CAIXA FIC FIM CAPITAL PROTEGIDO CICLICO II LP - RL</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4784,32 +4784,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,47220000</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>1,51</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>1,80</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>14,37</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>190,975</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF EXPERT PIMCO INCOME IE MM LP RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF EXPERT PIMCO INCOME IE MM LP RESP LTDA</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -4837,32 +4837,32 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,41230600</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>0,27</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>2,51</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>16,08</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>279,219</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>CAIXA EXPERT GIANT ZARATHUSTRA FIC MULTIMERCADO - RESP LTDA (1)</t>
+          <t>CAIXA EXPERT GIANT ZARATHUSTRA FIC MULTIMERCADO - RESP LTDA</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4894,32 +4894,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,31674000</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>0,57</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>2,59</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>2,78</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13,395</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>898,185</t>
+          <t>898,178</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>748,991</t>
+          <t>748,992</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>FIC FIF CAIXA EXPERT BTG PACTUAL X10 MM LP RESP LTDA (1)</t>
+          <t>FIC FIF CAIXA EXPERT BTG PACTUAL X10 MM LP RESP LTDA</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -5065,32 +5065,32 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>6,78432500</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>-0,004</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>5,48</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>16,73</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>129,587</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF EXPERT SPX NIMITZ MULTIMERCADO RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF EXPERT SPX NIMITZ MULTIMERCADO RESP LTDA</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5122,32 +5122,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,77206600</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>-0,002</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>0,72</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>0,31</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>10,69</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>176,392</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>97,614</t>
+          <t>97,597</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>347,120</t>
+          <t>347,118</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>10,318</t>
+          <t>10,316</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>277,722</t>
+          <t>277,543</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>445,938</t>
+          <t>445,937</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>58,253</t>
+          <t>58,191</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>92,434</t>
+          <t>92,431</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF AÇÕES MULTIGESTOR RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF AÇÕES MULTIGESTOR RESP LTDA</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -5737,32 +5737,32 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,30185000</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>-0,024</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>-4,66</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>10,89</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>295,634</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>114,110</t>
+          <t>114,109</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>133,544</t>
+          <t>133,454</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>47,674</t>
+          <t>47,639</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>129,900</t>
+          <t>129,793</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>41,489</t>
+          <t>41,414</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>677,490</t>
+          <t>677,323</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>440,323</t>
+          <t>440,272</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>30,199</t>
+          <t>30,188</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>1,793</t>
+          <t>1,792</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>44,434</t>
+          <t>44,404</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>36,469</t>
+          <t>36,461</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>910,760</t>
+          <t>910,317</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>2,994</t>
+          <t>2,993</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>19,765</t>
+          <t>19,390</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>269,776</t>
+          <t>269,513</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC ACOES EXPERT VERDE AM LONG BIAS - RESP LTDA (1)</t>
+          <t>CAIXA FIC ACOES EXPERT VERDE AM LONG BIAS - RESP LTDA</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -6731,32 +6731,32 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.017,29224100</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>-4,92</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>3,76</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>19,30</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8,171</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>CAIXA EXPERT CLARITAS VALOR FIC FIF AÇÕES - RESP LTDA (1)</t>
+          <t>CAIXA EXPERT CLARITAS VALOR FIC FIF AÇÕES - RESP LTDA</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6788,32 +6788,32 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.538,75924600</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>-0,002</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>-4,34</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>2,87</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>15,06</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22,409</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>172,97549800</t>
+          <t>172,97549798</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>1.692,073</t>
+          <t>1.691,330</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>730,865</t>
+          <t>730,347</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>797,168</t>
+          <t>796,676</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>633,334</t>
+          <t>632,633</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>477,359</t>
+          <t>476,930</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>728,420</t>
+          <t>727,765</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>CAIXA AZULZINHA FIC FIF RF SIMPLES - RESP LTDA (2)</t>
+          <t>CAIXA AZULZINHA FIC FIF RF SIMPLES - RESP LTDA (2) (8)</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF AMETISTA CORP RF SIMPLES RESP LTDA</t>
+          <t>CAIXA FIC FIF AMETISTA CORP RF SIMPLES RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>278,896</t>
+          <t>210,583</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>41,349</t>
+          <t>41,348</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>7.911,086</t>
+          <t>7.746,819</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>15.188,951</t>
+          <t>15.188,427</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>3.102,003</t>
+          <t>3.101,995</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC INST SOBERANO PLUS RF</t>
+          <t>CAIXA FIC INST SOBERANO PLUS RF (8)</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1,53832400</t>
+          <t>1,53832366</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>351,682</t>
+          <t>349,182</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>13.630,096</t>
+          <t>13.358,530</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>12.332,869</t>
+          <t>12.332,337</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.760,319</t>
+          <t>3.760,105</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF TURQUESA CORPORATIVO RF CP RESP LTDA</t>
+          <t>CAIXA FIC FIF TURQUESA CORPORATIVO RF CP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>1.405,753</t>
+          <t>1.405,645</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF AUTOMATICO POLIS RF CURTO PRAZO RESP LTDA</t>
+          <t>CAIXA FIC FIF AUTOMATICO POLIS RF CURTO PRAZO RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>33.663,684</t>
+          <t>33.436,643</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF PRÁTICO RF CURTO PRAZO RESP LTDA</t>
+          <t>CAIXA FIC FIF PRÁTICO RF CURTO PRAZO RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>2.913,398</t>
+          <t>2.900,764</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF TRANSFERÊNCIA VOLUNTÁRIA RF CP RESP LTDA</t>
+          <t>CAIXA FIC FIF TRANSFERÊNCIA VOLUNTÁRIA RF CP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>14.478,393</t>
+          <t>14.686,376</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>9.177,241</t>
+          <t>9.177,239</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>13.071,443</t>
+          <t>13.071,442</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>1.554,634</t>
+          <t>1.645,842</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>24.730,802</t>
+          <t>24.730,801</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>301,178</t>
+          <t>301,175</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>11,26019000</t>
+          <t>11,26018960</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>3,47467000</t>
+          <t>3,47467001</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>2,54576900</t>
+          <t>2,54576924</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>4.941,247</t>
+          <t>4.940,924</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -703,7 +703,11 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundo-simples/fic-movimentacoes-automaticas-rf-simples/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -870,7 +874,11 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-plus-rf-credito-privado-lp/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1831,7 +1839,11 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/debentures-incentivadas/caixa-expert-arx-ipca-deb-incentivadas-rf-cred-priv-lp/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -1884,7 +1896,11 @@
           <t>PF | PJ | RPPS</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/debentures-incentivadas/caixa-expert-vinlanddebenture-</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1994,7 +2010,11 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fif-inflacao-2027/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2153,7 +2173,11 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/debentures-incentivadas/caixa-expert-rb-asset-deb-incentivadas-cdi-rf-cred-priv/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2259,7 +2283,11 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-plus-qualificado-rf-credito-privado-lp/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -2483,7 +2511,11 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-renda-fixa-ativa-lp/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -2536,7 +2568,11 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/voce/renda-fixa/pos-fixados/ate-100.000/caixa-fic-indexa-tesouro-selic-renda-fixa-lp</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2646,7 +2682,11 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-unique-private-cred-priv-lp/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3493,7 +3533,11 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-automatico-polis-rf-cp/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -3774,7 +3818,11 @@
           <t>GOV | PF | PJ | RPPS</t>
         </is>
       </c>
-      <c r="K59" s="4" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fi-indexa-short-dolar-mult-lp/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3880,7 +3928,11 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="K61" s="4" t="inlineStr"/>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-short-mm/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3933,7 +3985,11 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-bias-mm/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -4039,7 +4095,11 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-bias-mm/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -4650,7 +4710,11 @@
           <t>GOV | PF | PJ | RPPS</t>
         </is>
       </c>
-      <c r="K75" s="4" t="inlineStr"/>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa_fic_fim_cap_protegido_cesta_agro/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5155,7 +5219,11 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fic-caixa-expert-spxmm/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -5322,7 +5390,11 @@
           <t>GOV | PF | PJ</t>
         </is>
       </c>
-      <c r="K87" s="4" t="inlineStr"/>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-brasil-etf-bovespa/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -6051,7 +6123,11 @@
           <t>PF | PJ | RPPS</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/Caixa-FI-Acoes-Banco-do-Brasil-Plus/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -6161,7 +6237,11 @@
           <t>GOV | PF | PJ</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fia-caixa-seguridade/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -6328,7 +6408,11 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="K105" s="4" t="inlineStr"/>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fic-fia-dividendos-quantitativo/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6552,7 +6636,11 @@
           <t>PF | PJ | RPPS</t>
         </is>
       </c>
-      <c r="K109" s="4" t="inlineStr"/>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fia-caixa-indexa-iagro/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6605,7 +6693,11 @@
           <t>PF | PJ | RPPS</t>
         </is>
       </c>
-      <c r="K110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/FIA-Institucional-BDR-nivel-I/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -6658,7 +6750,11 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="K111" s="4" t="inlineStr"/>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fia-caixa-seguridade/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6711,7 +6807,11 @@
           <t>PF | PJ | RPPS</t>
         </is>
       </c>
-      <c r="K112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fia-caixa-eletrobras/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -7412,7 +7512,11 @@
           <t>PJ</t>
         </is>
       </c>
-      <c r="K125" s="4" t="inlineStr"/>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>http://site.extra.caixa.gov.br/fundos-investimento/fundo-simples/fic-azulzinha-rf-simples/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -7864,7 +7968,11 @@
           <t>PJ</t>
         </is>
       </c>
-      <c r="K133" s="4" t="inlineStr"/>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/referenciados/fi-safira-corporativo-rf-lp</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -7917,7 +8025,11 @@
           <t>PJ</t>
         </is>
       </c>
-      <c r="K134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-institucional-soberano-plus-rf-lp/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -8369,7 +8481,11 @@
           <t>GOV</t>
         </is>
       </c>
-      <c r="K142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-automatico-polis-rf-cp/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -8536,7 +8652,11 @@
           <t>RPPS</t>
         </is>
       </c>
-      <c r="K145" s="4" t="inlineStr"/>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-matriz-rf/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -8703,7 +8823,11 @@
           <t>RPPS</t>
         </is>
       </c>
-      <c r="K148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/brasil-IPCA/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -9383,7 +9507,11 @@
           <t>RPPS</t>
         </is>
       </c>
-      <c r="K160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-caixa-brasil-idka-pre2a-rf-lp/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -9607,7 +9735,11 @@
           <t>RPPS</t>
         </is>
       </c>
-      <c r="K164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/estrategia-livre-mm-lp/Paginas/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -3562,7 +3562,7 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>-0,007</t>
+          <t>-0,078</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>-0,003</t>
+          <t>-0,443</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>-0,024</t>
+          <t>-0,035</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF BRASIL ESTRATÉGIA LIVRE MM LP RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF BRASIL ESTRATÉGIA LIVRE MM LP RESP LTDA</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.541,83184800</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="inlineStr">
+        <is>
+          <t>-0,299</t>
+        </is>
+      </c>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>-0,50</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>3,87</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>13,07</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>131,786</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF E-SIMPLES RENDA FIXA LP RESP LTDA</t>
+          <t>CAIXA FIF E-SIMPLES RENDA FIXA LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF GERAÇÃO JOVEM CRED PRIV RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF GERAÇÃO JOVEM CRED PRIV RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF RELACIONAMENTO PERSONAL RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF RELACIONAMENTO PERSONAL RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CAIXA MASTER PLUS FIF RF CRED PRIV LP RESP LTDA</t>
+          <t>CAIXA MASTER PLUS FIF RF CRED PRIV LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF IDEAL RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF IDEAL RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF E-FUNDO RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF E-FUNDO RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF EXCLUSIVO FUNC RF CREDITO PRIVADO LP RESP LTDA</t>
+          <t>CAIXA FIC FIF EXCLUSIVO FUNC RF CREDITO PRIVADO LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF ABSOLUTO PRE RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF ABSOLUTO PRE RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF CAPITAL IND PREÇOS RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF CAPITAL IND PREÇOS RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF EMPREENDER RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF EMPREENDER RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF SOBERANO RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF SOBERANO RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF FOCO IND PREÇOS RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF FOCO IND PREÇOS RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF CLÁSSICO RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF CLÁSSICO RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF DESENVOLVER RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF DESENVOLVER RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF OBJETIVO PRE RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF OBJETIVO PRE RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF OAB RF CRÉD PRIV LP RESP LTDA</t>
+          <t>CAIXA FIC FIF OAB RF CRÉD PRIV LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF EXECUTIVO RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF EXECUTIVO RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC RELACIONAMENTO IDEAL RF LP</t>
+          <t>CAIXA FIC RELACIONAMENTO IDEAL RF LP (8)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF PERFORMANCE IMA-B RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF PERFORMANCE IMA-B RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIFINVESTIDOR RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIFINVESTIDOR RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1806,32 +1806,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,10997325</t>
+          <t>1,10691900</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>-0,001</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
+          <t>-0,276</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>-0,28</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>2,61</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>0,00</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>2,89</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>219,622</t>
+          <t>219,018</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1,22811400</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>-0,001</t>
+          <t>1,22877200</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>4,85</t>
+          <t>4,91</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>14,63</t>
+          <t>14,69</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>70,980</t>
+          <t>71,018</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF PLUS QUALI RF CREDI PRIV LP RESP LTDA</t>
+          <t>CAIXA FIC FIF PLUS QUALI RF CREDI PRIV LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF INFLACAO PRIVATE 2027 RF LONGO PRAZO</t>
+          <t>CAIXA FIF INFLACAO PRIVATE 2027 RF LONGO PRAZO (8)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2034,22 +2034,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,02936900</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>-0,001</t>
+          <t>1,02990900</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>4,97</t>
+          <t>5,03</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,758</t>
+          <t>21,769</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2087,32 +2087,32 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,15576700</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>-0,001</t>
+          <t>1,15651000</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>0,062</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>4,08</t>
+          <t>4,14</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>13,73</t>
+          <t>13,81</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>66,353</t>
+          <t>66,395</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2140,22 +2140,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,05776364</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>-0,001</t>
+          <t>1,05784500</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>0,006</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>332,405</t>
+          <t>332,430</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF QUALIFICADO RF CRED PRIV LP - RESP LTDA</t>
+          <t>CAIXA FIF QUALIFICADO RF CRED PRIV LP - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF EXPERTISE RF CRED PRIV LP RESP LTDA</t>
+          <t>CAIXA FIC FIF EXPERTISE RF CRED PRIV LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF SELEÇÃO RF RESP LTDA</t>
+          <t>CAIXA FIC FIF SELEÇÃO RF RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF PERSONAL RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF PERSONAL RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF RENDA FIXA ATIVA LP RESP LTDA</t>
+          <t>CAIXA FIC FIF RENDA FIXA ATIVA LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>CAIXA INDEXA TESOURO SELIC FIC FIF RF LP - RESP LTDA</t>
+          <t>CAIXA INDEXA TESOURO SELIC FIC FIF RF LP - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF SUPREMO RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF SUPREMO RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF UNIQUE RF CRED PRIV LP - RL</t>
+          <t>CAIXA FIC FIF UNIQUE RF CRED PRIV LP - RL (8)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF ESPECIAL RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF ESPECIAL RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF FIDELIDADE PRIVATE RF LP - RESP LTDA</t>
+          <t>CAIXA FIF FIDELIDADE PRIVATE RF LP - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF MAXI RENDA FIXA CRED PRIV LP - RESP LTDA</t>
+          <t>CAIXA FIC FIF MAXI RENDA FIXA CRED PRIV LP - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF FIDELIDADE II RF CRÉD PRIV LP</t>
+          <t>CAIXA FIF FIDELIDADE II RF CRÉD PRIV LP (8)</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF BETA RF REF DI LP RESP LTDA</t>
+          <t>CAIXA FIC FIF BETA RF REF DI LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>CAIXA SIGMA FUNCIONARIOS FIC FIF RF REF DI LP - RESP LTDA (2) (3)</t>
+          <t>CAIXA SIGMA FUNCIONARIOS FIC FIF RF REF DI LP - RESP LTDA (2) (3) (8)</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF GIRO IMEDIATO RF REF DI LP RESP LTDA</t>
+          <t>CAIXA FIC FIF GIRO IMEDIATO RF REF DI LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF PLENO REF DI LP RESP LTDA</t>
+          <t>CAIXA FIC FIF PLENO REF DI LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC OMEGA REF DI RF LONGO PRAZO</t>
+          <t>CAIXA FIC OMEGA REF DI RF LONGO PRAZO (8)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF PREFERENCIAL REF DI LP RESP LTDA</t>
+          <t>CAIXA FIC FIF PREFERENCIAL REF DI LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF SIGMA RF REF DI LP RESP LTDA</t>
+          <t>CAIXA FIC FIF SIGMA RF REF DI LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF RUBI RF REF DI LP RESP LTDA</t>
+          <t>CAIXA FIC FIF RUBI RF REF DI LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF MEGA RF REFERENC DI LONGO PRAZO - RESP LTDA</t>
+          <t>CAIXA FIC FIF MEGA RF REFERENC DI LONGO PRAZO - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF TOP PRIVATE RF REF DI LP RESP LTDA</t>
+          <t>CAIXA FIC FIF TOP PRIVATE RF REF DI LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -3557,32 +3557,32 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1,39931700</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>-0,078</t>
+          <t>1,40124300</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>0,058</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>4,51</t>
+          <t>4,66</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>14,12</t>
+          <t>14,28</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>68,862</t>
+          <t>68,957</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -3614,32 +3614,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1.167,25373800</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>-0,443</t>
+          <t>1.184,51723600</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>1,028</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>3,05</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>-6,97</t>
+          <t>-5,60</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>-2,47</t>
+          <t>-1,03</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>35,739</t>
+          <t>36,268</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF MULTIMERCADO RV 30 LP RESP LTDA</t>
+          <t>CAIXA FIF MULTIMERCADO RV 30 LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3728,32 +3728,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1.632,15053600</t>
+          <t>1.627,36844900</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>-0,006</t>
+          <t>-0,299</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-0,51</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>4,16</t>
+          <t>3,85</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>13,39</t>
+          <t>13,06</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>116,889</t>
+          <t>116,546</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF INDEXA SHORT DOLAR MM LP RESP LTDA</t>
+          <t>CAIXA FIF INDEXA SHORT DOLAR MM LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3895,32 +3895,32 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1,25018500</t>
+          <t>1,24779700</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>-0,005</t>
+          <t>-0,196</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,63</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>11,60</t>
+          <t>11,39</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>6,666</t>
+          <t>6,654</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC LONG BIAS MM</t>
+          <t>CAIXA FIC LONG BIAS MM (8)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4062,32 +4062,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1,44320300</t>
+          <t>1,43008500</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>-0,004</t>
+          <t>-0,913</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>-1,73</t>
+          <t>-2,62</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>5,72</t>
+          <t>4,76</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>21,08</t>
+          <t>19,98</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>11,970</t>
+          <t>11,861</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF INDEXA EURO MM LONGO PRAZO RESP LTDA</t>
+          <t>CAIXA FIF INDEXA EURO MM LONGO PRAZO RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4229,32 +4229,32 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>5,32047778</t>
+          <t>5,30784700</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>-0,003</t>
+          <t>-0,240</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,44</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>3,69</t>
+          <t>3,44</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>13,12</t>
+          <t>12,85</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>33,192</t>
+          <t>33,114</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF INDEXA OURO MULTIMERCADO LP RESP LTDA</t>
+          <t>CAIXA FIF INDEXA OURO MULTIMERCADO LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4343,32 +4343,32 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>2,85531700</t>
+          <t>2,84411900</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>-0,004</t>
-        </is>
-      </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>0,08</t>
+          <t>-0,396</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>-0,30</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>1,82</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>11,44</t>
+          <t>11,01</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>77,229</t>
+          <t>76,927</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF HEDGE MULTIMERCADO LONGO PRAZO RESP LTDA</t>
+          <t>CAIXA FIC FIF HEDGE MULTIMERCADO LONGO PRAZO RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF INDEXA BOLSA AMERICANA MM LP RESP LTDA</t>
+          <t>CAIXA FIF INDEXA BOLSA AMERICANA MM LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF JUROS E MOEDAS MM PLUS LP RESP LTDA</t>
+          <t>CAIXA FIC FIF JUROS E MOEDAS MM PLUS LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4571,32 +4571,32 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1.652,59401600</t>
+          <t>1.647,85915600</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>-0,003</t>
+          <t>-0,289</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>-0,47</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>4,49</t>
+          <t>4,19</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>14,36</t>
+          <t>14,03</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>15,317</t>
+          <t>15,273</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -4624,22 +4624,22 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>0,57593472</t>
+          <t>0,56806700</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>-0,007</t>
+          <t>-1,373</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>6,16</t>
+          <t>4,71</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>-20,24</t>
+          <t>-21,33</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>4,200</t>
+          <t>4,142</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -4677,32 +4677,32 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>1,37874300</t>
+          <t>1,37535500</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>-0,003</t>
+          <t>-0,249</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>-1,35</t>
+          <t>-1,59</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>1,41</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>8,35</t>
+          <t>8,08</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>70,771</t>
+          <t>70,597</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1,53337400</t>
+          <t>1,53191100</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>-0,004</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
+          <t>-0,100</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>-0,10</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>2,59</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>18,93</t>
+          <t>18,82</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>14,513</t>
+          <t>14,499</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -4791,32 +4791,32 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>3,25598300</t>
+          <t>3,23396800</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>-0,005</t>
+          <t>-0,681</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>0,50</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>1,50</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>7,05</t>
+          <t>6,33</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>155,146</t>
+          <t>154,097</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1,47220000</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>-0,003</t>
+          <t>1,47794200</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>0,386</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>1,90</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>1,80</t>
+          <t>2,19</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>14,37</t>
+          <t>14,82</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>190,975</t>
+          <t>191,720</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -4958,32 +4958,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1,31674000</t>
+          <t>1,30889800</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>-0,001</t>
-        </is>
-      </c>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>0,57</t>
+          <t>-0,597</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>1,97</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>2,78</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>13,395</t>
+          <t>13,313</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF ALOCAÇÃO MACRO MM LONGO PRAZO RESP LTDA</t>
+          <t>CAIXA FIC FIF ALOCAÇÃO MACRO MM LONGO PRAZO RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF JUROS E MOEDAS MM LP RESP LTDA</t>
+          <t>CAIXA FIC FIF JUROS E MOEDAS MM LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,77206600</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>-0,002</t>
+          <t>1,77462000</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>0,142</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>10,69</t>
+          <t>10,85</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>176,392</t>
+          <t>176,646</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF INDEXA DOLAR CAMBIAL RESP LTDA</t>
+          <t>CAIXA FIC FIF INDEXA DOLAR CAMBIAL RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF AÇÕES DIVIDENDOS RESP LTDA</t>
+          <t>CAIXA FIF AÇÕES DIVIDENDOS RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF AÇÕES E-FUNDOS IBOVESPA RESP LTDA</t>
+          <t>CAIXA FIC FIF AÇÕES E-FUNDOS IBOVESPA RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>CAIXA ATENA FIC FIF AÇÕES FUNCIONÁRIOS LIVRE QUANT RESP LTDA</t>
+          <t>CAIXA ATENA FIC FIF AÇÕES FUNCIONÁRIOS LIVRE QUANT RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF AÇÕES BDR NÍVEL I RESP LTDA</t>
+          <t>CAIXA FIF AÇÕES BDR NÍVEL I RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF AÇÕES SMALL CAPS ATIVO RESP LTDA</t>
+          <t>CAIXA FIF AÇÕES SMALL CAPS ATIVO RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF AÇÕES CONSUMO RESP LTDA</t>
+          <t>CAIXA FIF AÇÕES CONSUMO RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF ACOES SUSTENTABILIDADE EMPRESARIAL ISE - IS RESP LTDA</t>
+          <t>CAIXA FIF ACOES SUSTENTABILIDADE EMPRESARIAL ISE - IS RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF ACOES PETROBRAS PLUS RESP LTDA</t>
+          <t>CAIXA FIF ACOES PETROBRAS PLUS RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF AÇÕES IBOVESPA RESP LTDA</t>
+          <t>CAIXA FIC FIF AÇÕES IBOVESPA RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5809,32 +5809,32 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1,30185000</t>
+          <t>1,28764700</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>-0,035</t>
+          <t>-1,125</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>-4,66</t>
+          <t>-5,70</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>10,89</t>
+          <t>9,68</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>295,634</t>
+          <t>292,409</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF AÇÕES CONSTRUÇÃO CIVIL RESP LTDA</t>
+          <t>CAIXA FIF AÇÕES CONSTRUÇÃO CIVIL RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF AÇÕES INFRAESTRUTURA RESP LTDA</t>
+          <t>CAIXA FIF AÇÕES INFRAESTRUTURA RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>CAIXA ATENA FIC FIF AÇÕES LIVRE QUANT RESP LTDA</t>
+          <t>CAIXA ATENA FIC FIF AÇÕES LIVRE QUANT RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF AÇÕES PETROBRAS PRÉ-SAL RESP LTDA</t>
+          <t>CAIXA FIF AÇÕES PETROBRAS PRÉ-SAL RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF ACOES BANCO DO BRASIL PLUS RESP LTDA</t>
+          <t>CAIXA FIF ACOES BANCO DO BRASIL PLUS RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF AÇÕES VALE DO RIO DOCE RESP LTDA</t>
+          <t>CAIXA FIF AÇÕES VALE DO RIO DOCE RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF ACOES SEGURIDADE RESP LTDA</t>
+          <t>CAIXA FIF ACOES SEGURIDADE RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF AÇÕES IBRX ATIVO RESP LTDA</t>
+          <t>CAIXA FIF AÇÕES IBRX ATIVO RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF ACOES INDEXA SETOR FINANCEIRO RESP LTDA</t>
+          <t>CAIXA FIF ACOES INDEXA SETOR FINANCEIRO RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF ACOES DIVIDENDOS QUANTITATIVO RESP LTDA</t>
+          <t>CAIXA FIC FIF ACOES DIVIDENDOS QUANTITATIVO RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF ACOES INDEXA PIBB IBRX 50 RESP LTDA</t>
+          <t>CAIXA FIF ACOES INDEXA PIBB IBRX 50 RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF ACOES IBOVESPA ATIVO RESP LTDA</t>
+          <t>CAIXA FIF ACOES IBOVESPA ATIVO RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF AÇÕES PETROBRÁS RESP LTDA</t>
+          <t>CAIXA FIF AÇÕES PETROBRÁS RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF ACOES INDEXA IAGRO RESP LTDA</t>
+          <t>CAIXA FIF ACOES INDEXA IAGRO RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF ACOES COMPROMISSO BDR NIVEL I RESP LTDA</t>
+          <t>CAIXA FIC FIF ACOES COMPROMISSO BDR NIVEL I RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>CAIXA SEGURIDADE II FIF ACOES - RESP LTDA</t>
+          <t>CAIXA SEGURIDADE II FIF ACOES - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF ACOES ELETROBRAS RESP LTDA</t>
+          <t>CAIXA FIF ACOES ELETROBRAS RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6831,32 +6831,32 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>1.017,29224100</t>
+          <t>1.011,74473600</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>-0,003</t>
+          <t>-0,548</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>-4,92</t>
+          <t>-5,44</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>3,76</t>
+          <t>3,20</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>19,30</t>
+          <t>18,65</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>8,171</t>
+          <t>8,126</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -6888,32 +6888,32 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1.538,75924600</t>
+          <t>1.528,30147000</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>-0,002</t>
+          <t>-0,682</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>-4,34</t>
+          <t>-4,99</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2,87</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>15,06</t>
+          <t>14,28</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>22,409</t>
+          <t>22,256</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>CAIXA ETF IBOVESPA FUNDO DE ÍNDICE RESP LTDA</t>
+          <t>CAIXA ETF IBOVESPA FUNDO DE ÍNDICE RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FMP-FGTS ELETROBRAS MIGRACAO</t>
+          <t>CAIXA FMP-FGTS ELETROBRAS MIGRACAO (8)</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FMP-FGTS ELETROBRAS RESP LTDA</t>
+          <t>CAIXA FMP-FGTS ELETROBRAS RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FMP-FGTS PETROBRÁS IV RESP LTDA</t>
+          <t>CAIXA FMP-FGTS PETROBRÁS IV RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FMP-FGTS VALE RIO DOCE II RESP LTDA</t>
+          <t>CAIXA FMP-FGTS VALE RIO DOCE II RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FMP-FGTS CL ABSOLUTO RESP LTDA</t>
+          <t>CAIXA FMP-FGTS CL ABSOLUTO RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FMP-FGTS VALE RIO DOCE MIGRAÇÃO RESP LTDA</t>
+          <t>CAIXA FMP-FGTS VALE RIO DOCE MIGRAÇÃO RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FMP-FGTS PETROBRÁS II RESP LTDA</t>
+          <t>CAIXA FMP-FGTS PETROBRÁS II RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FMP-FGTS VALE RIO DOCE I RESP LTDA</t>
+          <t>CAIXA FMP-FGTS VALE RIO DOCE I RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FMP-FGTS PETROBRÁS III RESP LTDA</t>
+          <t>CAIXA FMP-FGTS PETROBRÁS III RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF EQUILIBRIO MPE RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF EQUILIBRIO MPE RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF SAUDE SUPLEMENTAR ANS RF LP - RESP LTDA</t>
+          <t>CAIXA FIF SAUDE SUPLEMENTAR ANS RF LP - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF TITULO PUBLICO MPE RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF TITULO PUBLICO MPE RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF PATRIMONIO IND.DE PRECOS RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF PATRIMONIO IND.DE PRECOS RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>CAIXA GIRO EMPRESAS FIC FIF RF REF DI LP RESP LTDA</t>
+          <t>CAIXA GIRO EMPRESAS FIC FIF RF REF DI LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF DIAMANTE CORP RF CRED PRIV LP - RESP LTDA</t>
+          <t>CAIXA FIF DIAMANTE CORP RF CRED PRIV LP - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF SAFIRA CORPORATIVO RF LP - RESP LTDA</t>
+          <t>CAIXA FIF SAFIRA CORPORATIVO RF LP - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF SAUDE SUPLEMENTAR ANS II RF LP - RESP LTDA</t>
+          <t>CAIXA FIF SAUDE SUPLEMENTAR ANS II RF LP - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF CNI RF LP - RESP LTDA</t>
+          <t>CAIXA FIF CNI RF LP - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF SEBRAE RF LP RESP LTDA</t>
+          <t>CAIXA FIF SEBRAE RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF GIRO MPE REF DI LP RESP LTDA</t>
+          <t>CAIXA FIC FIF GIRO MPE REF DI LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF TOPAZIO CORP RF REFERENC DI - RESP LTDA</t>
+          <t>CAIXA FIF TOPAZIO CORP RF REFERENC DI - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC ESMERALDA CORP RF REF DI CRED PRIV LP - RESP LTDA</t>
+          <t>CAIXA FIC ESMERALDA CORP RF REF DI CRED PRIV LP - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF BRASIL MATRIZ RF RESP LTDA</t>
+          <t>CAIXA FIF BRASIL MATRIZ RF RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF BRASIL GESTÃO ESTRATÉGICA RF RESP LTDA</t>
+          <t>CAIXA FIC FIF BRASIL GESTÃO ESTRATÉGICA RF RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL INFLAÇÃO ATIVA FIF RF CRED PRIV RESP LTDA</t>
+          <t>CAIXA BRASIL INFLAÇÃO ATIVA FIF RF CRED PRIV RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF BRASIL RENDA FIXA ATIVA LP RESP LTDA</t>
+          <t>CAIXA FIC FIF BRASIL RENDA FIXA ATIVA LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FI BRASIL IRF-M 1 TP RF</t>
+          <t>CAIXA FI BRASIL IRF-M 1 TP RF (8)</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF BRASIL IDKA IPCA 2A TIT PUB RF LP RESP LTDA</t>
+          <t>CAIXA FIF BRASIL IDKA IPCA 2A TIT PUB RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF BRASIL IRF-M TP RF LP - RESP LTDA</t>
+          <t>CAIXA FIF BRASIL IRF-M TP RF LP - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FI BRASIL IMA-B TP RF LP</t>
+          <t>CAIXA FI BRASIL IMA-B TP RF LP (8)</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF BRASIL IMA-B 5 TP RF LP - RESP LTDA</t>
+          <t>CAIXA FIF BRASIL IMA-B 5 TP RF LP - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF BRASIL IMA GERAL TP RF LP - RESP LTDA</t>
+          <t>CAIXA FIF BRASIL IMA GERAL TP RF LP - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF RS TITULOS PUBLICOS RF LP - RESP LTDA</t>
+          <t>CAIXA FIF RS TITULOS PUBLICOS RF LP - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF BRASIL IMA-B 5+ TP RF LP - RESP LTDA</t>
+          <t>CAIXA FIF BRASIL IMA-B 5+ TP RF LP - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FI BRASIL IRF-M 1+ TP RF LP</t>
+          <t>CAIXA FI BRASIL IRF-M 1+ TP RF LP (8)</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF BRASIL TITULOS PUBLICOS RF LP - RESP LTDA</t>
+          <t>CAIXA FIF BRASIL TITULOS PUBLICOS RF LP - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF ALIANÇA TP RF CURTO PRAZO - RESP LTDA</t>
+          <t>CAIXA FIF ALIANÇA TP RF CURTO PRAZO - RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF BRASIL IDKA PRE 2A RF LP RESP LTDA</t>
+          <t>CAIXA FIC FIF BRASIL IDKA PRE 2A RF LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF BRASIL DISPONIBILIDADES SIMPLES RF RESP LTDA</t>
+          <t>CAIXA FIC FIF BRASIL DISPONIBILIDADES SIMPLES RF RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF BRASIL RF REFER DI LONGO PRAZO RESP LTDA</t>
+          <t>CAIXA FIC FIF BRASIL RF REFER DI LONGO PRAZO RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF NOVO BRASIL RF IMA-B LP RESP LTDA</t>
+          <t>CAIXA FIC FIF NOVO BRASIL RF IMA-B LP RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF AÇOES BRASIL IBOVESPA RESP LTDA</t>
+          <t>CAIXA FIF AÇOES BRASIL IBOVESPA RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF AÇÕES BRASIL ETF IBOVESPA RESP LTDA</t>
+          <t>CAIXA FIF AÇÕES BRASIL ETF IBOVESPA RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF AÇÕES INSTITUCIONAL BDR NIVEL I RESP LTDA</t>
+          <t>CAIXA FIF AÇÕES INSTITUCIONAL BDR NIVEL I RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF ACOES BRASIL IBX-50 RESP LTDA</t>
+          <t>CAIXA FIF ACOES BRASIL IBX-50 RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>CAIXA ATENA FIC FIF AÇÕES BRASIL LIVRE QUANT RESP LTDA</t>
+          <t>CAIXA ATENA FIC FIF AÇÕES BRASIL LIVRE QUANT RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC ACOES EXPERT VINCI VALOR DIVIDENDOS RPPS RESP LTDA</t>
+          <t>CAIXA FIC ACOES EXPERT VINCI VALOR DIVIDENDOS RPPS RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC ACOES EXPERT VINCI VALOR RPPS RESP LTDA</t>
+          <t>CAIXA FIC ACOES EXPERT VINCI VALOR RPPS RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF EXTRAMERCADO COMUM IRFM-1 RF RESP LTDA</t>
+          <t>CAIXA FIF EXTRAMERCADO COMUM IRFM-1 RF RESP LTDA (8)</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -1944,11 +1944,7 @@
           <t>PF | PJ | TODOS</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-investidor-rf-longo-prazo</t>
-        </is>
-      </c>
+      <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="4" t="inlineStr"/>
       <c r="M23" s="4" t="inlineStr"/>
       <c r="N23" s="4" t="inlineStr"/>
@@ -1964,7 +1960,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CAIXA EXPERT ARX IPCA DEB INCENTIVADAS FIC FIF RF CRED PRIV - RESP LTDA (1) (2)</t>
+          <t>CAIXA EXPERT ARX IPCA DEB INCENTIVADAS FIC FIF RF CRED PRIV - RESP LTDA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2027,7 +2023,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF FIC EXPERT SULAMERICA RF CRED PRIV LP - RESP LTDA (1)</t>
+          <t>CAIXA FIF FIC EXPERT SULAMERICA RF CRED PRIV LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2216,7 +2212,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CAIXA EXPERT VOX DESENV SUSTENTAVEL IS RF CRED PRIV LP - RESP LTDA (1) (2)</t>
+          <t>CAIXA EXPERT VOX DESENV SUSTENTAVEL IS RF CRED PRIV LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2275,7 +2271,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>CAIXA EXPERT ABSOLUTE CRETA FIC FIF RF CRED PRIV LP - RESP LTDA (1)</t>
+          <t>CAIXA EXPERT ABSOLUTE CRETA FIC FIF RF CRED PRIV LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2334,7 +2330,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CAIXA EXPERT RB ASSET CDI DEB INCENTIVADAS FIC FIF RF CRED PRIV RESP LTDA (1) (2)</t>
+          <t>CAIXA EXPERT RB ASSET CDI DEB INCENTIVADAS FIC FIF RF CRED PRIV RESP LTDA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2397,7 +2393,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>CAIXA EXPERT VINLAND DEB IN INFRA RF CRED PRIV LP RESP LTDA (1) (2) (3)</t>
+          <t>CAIXA EXPERT VINLAND DEB IN INFRA RF CRED PRIV LP RESP LTDA</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3275,7 +3271,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>CAIXA SIGMA FUNCIONARIOS FIC FIF RF REF DI LP - RESP LTDA (2) (3)</t>
+          <t>CAIXA SIGMA FUNCIONARIOS FIC FIF RF REF DI LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3901,7 +3897,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF FOF SMART CRED PRIV MM LP RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF FOF SMART CRED PRIV MM LP RESP LTDA</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -3964,7 +3960,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC MULTIGESTOR GLOBAL EQUITIES IE (1)</t>
+          <t>CAIXA FIC MULTIGESTOR GLOBAL EQUITIES IE</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4090,7 +4086,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF ESTRATÉGIA LIVRE MULTIMERCADO LP RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF ESTRATÉGIA LIVRE MULTIMERCADO LP RESP LTDA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4216,7 +4212,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>CAIXA CARTEIRA QUANT DUO FIC FIF MM LP RESP LTDA (1) (2) (3)</t>
+          <t>CAIXA CARTEIRA QUANT DUO FIC FIF MM LP RESP LTDA</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4275,7 +4271,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF FOF SMART LONG SHORT LP RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF FOF SMART LONG SHORT LP RESP LTDA</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -4401,7 +4397,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>CAIXA CARTEIRA QUANT QUALI FIC FIF MM LP RESP LTDA (1) (2) (3)</t>
+          <t>CAIXA CARTEIRA QUANT QUALI FIC FIF MM LP RESP LTDA</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -4460,7 +4456,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF FOF SMART LONG BIAS MM RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF FOF SMART LONG BIAS MM RESP LTDA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4523,7 +4519,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>CAIXA CARTEIRA QUANT UNO FIC FIF MM LP RESP LTDA (1) (2) (3)</t>
+          <t>CAIXA CARTEIRA QUANT UNO FIC FIF MM LP RESP LTDA</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -4645,7 +4641,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF ESTRATÉGICO MULTIMERCADO LP RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF ESTRATÉGICO MULTIMERCADO LP RESP LTDA</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -4771,7 +4767,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF FOF SMART MULTIESTRATEGIA MM RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF FOF SMART MULTIESTRATEGIA MM RESP LTDA</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -5023,7 +5019,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF FUNCIONARIOS ESTRATEGIA LIVRE MULTIMERCADO LP RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF FUNCIONARIOS ESTRATEGIA LIVRE MULTIMERCADO LP RESP LTDA</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -5082,7 +5078,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>CAIXA HASHDEX NASDAQ CRYPTO INDEX FIC FIF MM RESP LTDA (1) (2)</t>
+          <t>CAIXA HASHDEX NASDAQ CRYPTO INDEX FIC FIF MM RESP LTDA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5141,7 +5137,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF CAPITAL PROTEGIDO CESTA AGRO MM (1)</t>
+          <t>CAIXA FIC FIF CAPITAL PROTEGIDO CESTA AGRO MM</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -5204,7 +5200,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>CAIXA CAPITAL PROTEGIDO CÍCLICO III FIC FIF MM LP - RESP LTDA (1)</t>
+          <t>CAIXA CAPITAL PROTEGIDO CÍCLICO III FIC FIF MM LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5267,7 +5263,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>CAIXA CAPITAL PROTEGIDO IBOVESPA CÍCLICO I FIC FIF MM (1)</t>
+          <t>CAIXA CAPITAL PROTEGIDO IBOVESPA CÍCLICO I FIC FIF MM</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -5330,7 +5326,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIM CAPITAL PROTEGIDO CICLICO II LP - RL (1)</t>
+          <t>CAIXA FIC FIM CAPITAL PROTEGIDO CICLICO II LP - RL</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5393,7 +5389,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF EXPERT PIMCO INCOME IE MM LP RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF EXPERT PIMCO INCOME IE MM LP RESP LTDA</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -5456,7 +5452,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>CAIXA EXPERT GIANT ZARATHUSTRA FIC MULTIMERCADO - RESP LTDA (1)</t>
+          <t>CAIXA EXPERT GIANT ZARATHUSTRA FIC MULTIMERCADO - RESP LTDA</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5645,7 +5641,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>FIC FIF CAIXA EXPERT BTG PACTUAL X10 MM LP RESP LTDA (1)</t>
+          <t>FIC FIF CAIXA EXPERT BTG PACTUAL X10 MM LP RESP LTDA</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -5708,7 +5704,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF EXPERT SPX NIMITZ MULTIMERCADO RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF EXPERT SPX NIMITZ MULTIMERCADO RESP LTDA</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6397,7 +6393,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF AÇÕES MULTIGESTOR RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF AÇÕES MULTIGESTOR RESP LTDA</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -7381,11 +7377,7 @@
           <t>PF | PJ | RPPS</t>
         </is>
       </c>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/FIA-Institucional-BDR-nivel-I/Paginas/default.aspx</t>
-        </is>
-      </c>
+      <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr"/>
       <c r="M110" s="2" t="inlineStr"/>
       <c r="N110" s="2" t="inlineStr"/>
@@ -7527,7 +7519,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC ACOES EXPERT VERDE AM LONG BIAS - RESP LTDA (1)</t>
+          <t>CAIXA FIC ACOES EXPERT VERDE AM LONG BIAS - RESP LTDA</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -7590,7 +7582,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>CAIXA EXPERT CLARITAS VALOR FIC FIF AÇÕES - RESP LTDA (1)</t>
+          <t>CAIXA EXPERT CLARITAS VALOR FIC FIF AÇÕES - RESP LTDA</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8247,7 +8239,7 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>CAIXA AZULZINHA FIC FIF RF SIMPLES - RESP LTDA (2)</t>
+          <t>CAIXA AZULZINHA FIC FIF RF SIMPLES - RESP LTDA</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -10704,7 +10696,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF BRASIL ESTRATÉGIA LIVRE MM LP RESP LTDA (1)</t>
+          <t>CAIXA FIC FIF BRASIL ESTRATÉGIA LIVRE MM LP RESP LTDA</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -479,8 +479,8 @@
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
@@ -882,12 +882,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-relacionamento-personal-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>10.577.509/0001-55</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1071,12 +1095,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/e-fundos/renda-fixa-longo-prazo</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
-      <c r="O9" s="4" t="inlineStr"/>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>15.154.422/0001-99</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1319,12 +1367,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-empreender-rf-longo-prazo/</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="4" t="inlineStr"/>
-      <c r="N13" s="4" t="inlineStr"/>
-      <c r="O13" s="4" t="inlineStr"/>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>00.068.305/0001-35</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1571,12 +1643,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-desenvolver-rf-longo-prazo/</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr"/>
-      <c r="N17" s="4" t="inlineStr"/>
-      <c r="O17" s="4" t="inlineStr"/>
-      <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="4" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>16.877.609/0001-83</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1634,12 +1730,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-objetivo-pre-rf-longo-prazo/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>14.120.511/0001-51</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1886,12 +2006,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-performance-ima-b-renda-fixa-longo-prazo/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr"/>
-      <c r="P22" s="2" t="inlineStr"/>
-      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>10.577.516/0001-57</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -2500,12 +2644,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-plus-qualificado-rf-credito-privado-lp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr"/>
-      <c r="P32" s="2" t="inlineStr"/>
-      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>10.551.353/0001-33</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>20000.0</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>D+04 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -2563,12 +2731,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-expertise-rf-credito-privado-longo-prazo</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr"/>
-      <c r="M33" s="4" t="inlineStr"/>
-      <c r="N33" s="4" t="inlineStr"/>
-      <c r="O33" s="4" t="inlineStr"/>
-      <c r="P33" s="4" t="inlineStr"/>
-      <c r="Q33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>10.646.888/0001-98</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>20000.0</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2626,12 +2818,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-selecao-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" s="2" t="inlineStr"/>
-      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>03.737.207/0001-31</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>30000.0</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -2815,12 +3031,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/voce/renda-fixa/pos-fixados/ate-100.000/caixa-fic-indexa-tesouro-selic-renda-fixa-lp</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr"/>
-      <c r="M37" s="4" t="inlineStr"/>
-      <c r="N37" s="4" t="inlineStr"/>
-      <c r="O37" s="4" t="inlineStr"/>
-      <c r="P37" s="4" t="inlineStr"/>
-      <c r="Q37" s="4" t="inlineStr"/>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>17.687.735/0001-38</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>50000.0</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3130,12 +3370,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-maxi-rf-credito-privado-longo-prazo/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr"/>
-      <c r="O42" s="2" t="inlineStr"/>
-      <c r="P42" s="2" t="inlineStr"/>
-      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>17.322.725/0001-07</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>50000.0</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -3441,12 +3705,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-pleno-ref-di-longo-prazo</t>
         </is>
       </c>
-      <c r="L47" s="4" t="inlineStr"/>
-      <c r="M47" s="4" t="inlineStr"/>
-      <c r="N47" s="4" t="inlineStr"/>
-      <c r="O47" s="4" t="inlineStr"/>
-      <c r="P47" s="4" t="inlineStr"/>
-      <c r="Q47" s="4" t="inlineStr"/>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>10.740.508/0001-80</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="P47" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3567,12 +3855,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-preferencial-ref-di-longo-prazo</t>
         </is>
       </c>
-      <c r="L49" s="4" t="inlineStr"/>
-      <c r="M49" s="4" t="inlineStr"/>
-      <c r="N49" s="4" t="inlineStr"/>
-      <c r="O49" s="4" t="inlineStr"/>
-      <c r="P49" s="4" t="inlineStr"/>
-      <c r="Q49" s="4" t="inlineStr"/>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>03.737.211/0001-08</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="O49" s="4" t="inlineStr">
+        <is>
+          <t>30000.0</t>
+        </is>
+      </c>
+      <c r="P49" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3882,12 +4194,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-automatico-polis-rf-cp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr"/>
-      <c r="O54" s="2" t="inlineStr"/>
-      <c r="P54" s="2" t="inlineStr"/>
-      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>39.594.941/0001-36</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -4197,12 +4533,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fi-indexa-short-dolar-mult-lp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L59" s="4" t="inlineStr"/>
-      <c r="M59" s="4" t="inlineStr"/>
-      <c r="N59" s="4" t="inlineStr"/>
-      <c r="O59" s="4" t="inlineStr"/>
-      <c r="P59" s="4" t="inlineStr"/>
-      <c r="Q59" s="4" t="inlineStr"/>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>29.157.511/0001-01</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="O59" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P59" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q59" s="4" t="inlineStr">
+        <is>
+          <t>D+01 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4752,12 +5112,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fi-ouro-multimercado-longo-prazo</t>
         </is>
       </c>
-      <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="inlineStr"/>
-      <c r="N68" s="2" t="inlineStr"/>
-      <c r="O68" s="2" t="inlineStr"/>
-      <c r="P68" s="2" t="inlineStr"/>
-      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>16.916.060/0001-99</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>D+02 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -4878,12 +5262,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-hedge-multimercado-lp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr"/>
-      <c r="O70" s="2" t="inlineStr"/>
-      <c r="P70" s="2" t="inlineStr"/>
-      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>30.068.135/0001-50</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>D+01 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -5626,12 +6034,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fi-juros-moedas-multimercado-longo-prazo</t>
         </is>
       </c>
-      <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr"/>
-      <c r="N82" s="2" t="inlineStr"/>
-      <c r="O82" s="2" t="inlineStr"/>
-      <c r="P82" s="2" t="inlineStr"/>
-      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>14.120.520/0001-42</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -5815,12 +6247,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/cambiais/fic-cambial-dolar/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L85" s="4" t="inlineStr"/>
-      <c r="M85" s="4" t="inlineStr"/>
-      <c r="N85" s="4" t="inlineStr"/>
-      <c r="O85" s="4" t="inlineStr"/>
-      <c r="P85" s="4" t="inlineStr"/>
-      <c r="Q85" s="4" t="inlineStr"/>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>05.114.733/0001-70</t>
+        </is>
+      </c>
+      <c r="M85" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N85" s="4" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="O85" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P85" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q85" s="4" t="inlineStr">
+        <is>
+          <t>D+01 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5878,12 +6334,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-dividendos</t>
         </is>
       </c>
-      <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr"/>
-      <c r="N86" s="2" t="inlineStr"/>
-      <c r="O86" s="2" t="inlineStr"/>
-      <c r="P86" s="2" t="inlineStr"/>
-      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>05.900.798/0001-41</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -6063,12 +6543,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-bdr-nivel-1</t>
         </is>
       </c>
-      <c r="L89" s="4" t="inlineStr"/>
-      <c r="M89" s="4" t="inlineStr"/>
-      <c r="N89" s="4" t="inlineStr"/>
-      <c r="O89" s="4" t="inlineStr"/>
-      <c r="P89" s="4" t="inlineStr"/>
-      <c r="Q89" s="4" t="inlineStr"/>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>17.503.172/0001-80</t>
+        </is>
+      </c>
+      <c r="M89" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N89" s="4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="O89" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P89" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q89" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -6126,12 +6630,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-small-caps-ativo</t>
         </is>
       </c>
-      <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="2" t="inlineStr"/>
-      <c r="N90" s="2" t="inlineStr"/>
-      <c r="O90" s="2" t="inlineStr"/>
-      <c r="P90" s="2" t="inlineStr"/>
-      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>15.154.220/0001-47</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -6189,12 +6717,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-consumo</t>
         </is>
       </c>
-      <c r="L91" s="4" t="inlineStr"/>
-      <c r="M91" s="4" t="inlineStr"/>
-      <c r="N91" s="4" t="inlineStr"/>
-      <c r="O91" s="4" t="inlineStr"/>
-      <c r="P91" s="4" t="inlineStr"/>
-      <c r="Q91" s="4" t="inlineStr"/>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>10.577.512/0001-79</t>
+        </is>
+      </c>
+      <c r="M91" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="O91" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P91" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q91" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -6252,12 +6804,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-ise</t>
         </is>
       </c>
-      <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="2" t="inlineStr"/>
-      <c r="O92" s="2" t="inlineStr"/>
-      <c r="P92" s="2" t="inlineStr"/>
-      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>08.070.838/0001-63</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -6315,12 +6891,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fia-caixa-petrobras-plus/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L93" s="4" t="inlineStr"/>
-      <c r="M93" s="4" t="inlineStr"/>
-      <c r="N93" s="4" t="inlineStr"/>
-      <c r="O93" s="4" t="inlineStr"/>
-      <c r="P93" s="4" t="inlineStr"/>
-      <c r="Q93" s="4" t="inlineStr"/>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>30.068.205/0001-70</t>
+        </is>
+      </c>
+      <c r="M93" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N93" s="4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="O93" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P93" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q93" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -6378,12 +6978,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-ibovespa</t>
         </is>
       </c>
-      <c r="L94" s="2" t="inlineStr"/>
-      <c r="M94" s="2" t="inlineStr"/>
-      <c r="N94" s="2" t="inlineStr"/>
-      <c r="O94" s="2" t="inlineStr"/>
-      <c r="P94" s="2" t="inlineStr"/>
-      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>01.525.057/0001-77</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -6504,12 +7128,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-construcao-civil</t>
         </is>
       </c>
-      <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr"/>
-      <c r="N96" s="2" t="inlineStr"/>
-      <c r="O96" s="2" t="inlineStr"/>
-      <c r="P96" s="2" t="inlineStr"/>
-      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>10.551.375/0001-01</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -6567,12 +7215,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-infraestrutura</t>
         </is>
       </c>
-      <c r="L97" s="4" t="inlineStr"/>
-      <c r="M97" s="4" t="inlineStr"/>
-      <c r="N97" s="4" t="inlineStr"/>
-      <c r="O97" s="4" t="inlineStr"/>
-      <c r="P97" s="4" t="inlineStr"/>
-      <c r="Q97" s="4" t="inlineStr"/>
+      <c r="L97" s="4" t="inlineStr">
+        <is>
+          <t>10.551.382/0001-03</t>
+        </is>
+      </c>
+      <c r="M97" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O97" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P97" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q97" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6625,13 +7297,41 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr"/>
-      <c r="O98" s="2" t="inlineStr"/>
-      <c r="P98" s="2" t="inlineStr"/>
-      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/FIC-FIA-acoes-livres/Paginas/default.aspx</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>22.791.154/0001-81</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>D+13 (du)</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>D+15 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -6689,12 +7389,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-petrobras-pre-sal</t>
         </is>
       </c>
-      <c r="L99" s="4" t="inlineStr"/>
-      <c r="M99" s="4" t="inlineStr"/>
-      <c r="N99" s="4" t="inlineStr"/>
-      <c r="O99" s="4" t="inlineStr"/>
-      <c r="P99" s="4" t="inlineStr"/>
-      <c r="Q99" s="4" t="inlineStr"/>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>11.060.594/0001-42</t>
+        </is>
+      </c>
+      <c r="M99" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N99" s="4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O99" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P99" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q99" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6752,12 +7476,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/Caixa-FI-Acoes-Banco-do-Brasil-Plus/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr"/>
-      <c r="N100" s="2" t="inlineStr"/>
-      <c r="O100" s="2" t="inlineStr"/>
-      <c r="P100" s="2" t="inlineStr"/>
-      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>30.068.271/0001-40</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -6815,12 +7563,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-vale-rio-doce</t>
         </is>
       </c>
-      <c r="L101" s="4" t="inlineStr"/>
-      <c r="M101" s="4" t="inlineStr"/>
-      <c r="N101" s="4" t="inlineStr"/>
-      <c r="O101" s="4" t="inlineStr"/>
-      <c r="P101" s="4" t="inlineStr"/>
-      <c r="Q101" s="4" t="inlineStr"/>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>04.885.820/0001-69</t>
+        </is>
+      </c>
+      <c r="M101" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N101" s="4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O101" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P101" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q101" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6941,12 +7713,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-ibrx-ativo</t>
         </is>
       </c>
-      <c r="L103" s="4" t="inlineStr"/>
-      <c r="M103" s="4" t="inlineStr"/>
-      <c r="N103" s="4" t="inlineStr"/>
-      <c r="O103" s="4" t="inlineStr"/>
-      <c r="P103" s="4" t="inlineStr"/>
-      <c r="Q103" s="4" t="inlineStr"/>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>05.164.370/0001-88</t>
+        </is>
+      </c>
+      <c r="M103" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N103" s="4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="O103" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P103" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q103" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -7004,12 +7800,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/caixa-fia-indexa-setor-financeiro/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L104" s="2" t="inlineStr"/>
-      <c r="M104" s="2" t="inlineStr"/>
-      <c r="N104" s="2" t="inlineStr"/>
-      <c r="O104" s="2" t="inlineStr"/>
-      <c r="P104" s="2" t="inlineStr"/>
-      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>40.209.029/0001-00</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -7067,12 +7887,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fic-fia-dividendos-quantitativo/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L105" s="4" t="inlineStr"/>
-      <c r="M105" s="4" t="inlineStr"/>
-      <c r="N105" s="4" t="inlineStr"/>
-      <c r="O105" s="4" t="inlineStr"/>
-      <c r="P105" s="4" t="inlineStr"/>
-      <c r="Q105" s="4" t="inlineStr"/>
+      <c r="L105" s="4" t="inlineStr">
+        <is>
+          <t>42.120.405/0001-03</t>
+        </is>
+      </c>
+      <c r="M105" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N105" s="4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O105" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P105" s="4" t="inlineStr">
+        <is>
+          <t>D+13 (du)</t>
+        </is>
+      </c>
+      <c r="Q105" s="4" t="inlineStr">
+        <is>
+          <t>D+15 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -7130,12 +7974,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-pibb-sem-opcao-de-venda</t>
         </is>
       </c>
-      <c r="L106" s="2" t="inlineStr"/>
-      <c r="M106" s="2" t="inlineStr"/>
-      <c r="N106" s="2" t="inlineStr"/>
-      <c r="O106" s="2" t="inlineStr"/>
-      <c r="P106" s="2" t="inlineStr"/>
-      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>05.164.361/0001-97</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -7193,12 +8061,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-ibovespa-ativo</t>
         </is>
       </c>
-      <c r="L107" s="4" t="inlineStr"/>
-      <c r="M107" s="4" t="inlineStr"/>
-      <c r="N107" s="4" t="inlineStr"/>
-      <c r="O107" s="4" t="inlineStr"/>
-      <c r="P107" s="4" t="inlineStr"/>
-      <c r="Q107" s="4" t="inlineStr"/>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>08.046.355/0001-23</t>
+        </is>
+      </c>
+      <c r="M107" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N107" s="4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O107" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P107" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q107" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -7256,12 +8148,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-petrobras</t>
         </is>
       </c>
-      <c r="L108" s="2" t="inlineStr"/>
-      <c r="M108" s="2" t="inlineStr"/>
-      <c r="N108" s="2" t="inlineStr"/>
-      <c r="O108" s="2" t="inlineStr"/>
-      <c r="P108" s="2" t="inlineStr"/>
-      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>03.914.671/0001-56</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -7319,12 +8235,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fia-caixa-indexa-iagro/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L109" s="4" t="inlineStr"/>
-      <c r="M109" s="4" t="inlineStr"/>
-      <c r="N109" s="4" t="inlineStr"/>
-      <c r="O109" s="4" t="inlineStr"/>
-      <c r="P109" s="4" t="inlineStr"/>
-      <c r="Q109" s="4" t="inlineStr"/>
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>45.443.601/0001-07</t>
+        </is>
+      </c>
+      <c r="M109" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N109" s="4" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="O109" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P109" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q109" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -7377,13 +8317,41 @@
           <t>PF | PJ | RPPS</t>
         </is>
       </c>
-      <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="inlineStr"/>
-      <c r="M110" s="2" t="inlineStr"/>
-      <c r="N110" s="2" t="inlineStr"/>
-      <c r="O110" s="2" t="inlineStr"/>
-      <c r="P110" s="2" t="inlineStr"/>
-      <c r="Q110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/FIA-Institucional-BDR-nivel-I/Paginas/default.aspx</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>43.760.251/0001-87</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -7441,12 +8409,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fia-caixa-seguridade/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L111" s="4" t="inlineStr"/>
-      <c r="M111" s="4" t="inlineStr"/>
-      <c r="N111" s="4" t="inlineStr"/>
-      <c r="O111" s="4" t="inlineStr"/>
-      <c r="P111" s="4" t="inlineStr"/>
-      <c r="Q111" s="4" t="inlineStr"/>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>59.815.671/0001-53</t>
+        </is>
+      </c>
+      <c r="M111" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N111" s="4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O111" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P111" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q111" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -7504,12 +8496,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fia-caixa-eletrobras/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L112" s="2" t="inlineStr"/>
-      <c r="M112" s="2" t="inlineStr"/>
-      <c r="N112" s="2" t="inlineStr"/>
-      <c r="O112" s="2" t="inlineStr"/>
-      <c r="P112" s="2" t="inlineStr"/>
-      <c r="Q112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>45.443.475/0001-90</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -7810,13 +8826,41 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="K117" s="4" t="inlineStr"/>
-      <c r="L117" s="4" t="inlineStr"/>
-      <c r="M117" s="4" t="inlineStr"/>
-      <c r="N117" s="4" t="inlineStr"/>
-      <c r="O117" s="4" t="inlineStr"/>
-      <c r="P117" s="4" t="inlineStr"/>
-      <c r="Q117" s="4" t="inlineStr"/>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-eletrobras</t>
+        </is>
+      </c>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>45.160.183/0001-40</t>
+        </is>
+      </c>
+      <c r="M117" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N117" s="4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O117" s="4" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="P117" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q117" s="4" t="inlineStr">
+        <is>
+          <t>D+05 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -7869,13 +8913,41 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="2" t="inlineStr"/>
-      <c r="M118" s="2" t="inlineStr"/>
-      <c r="N118" s="2" t="inlineStr"/>
-      <c r="O118" s="2" t="inlineStr"/>
-      <c r="P118" s="2" t="inlineStr"/>
-      <c r="Q118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-petrobas-4</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>03.555.959/0001-81</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>D+05 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -7987,13 +9059,41 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="2" t="inlineStr"/>
-      <c r="M120" s="2" t="inlineStr"/>
-      <c r="N120" s="2" t="inlineStr"/>
-      <c r="O120" s="2" t="inlineStr"/>
-      <c r="P120" s="2" t="inlineStr"/>
-      <c r="Q120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-cl-absoluto</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>04.602.186/0001-00</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>D+05 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -8105,13 +9205,41 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="2" t="inlineStr"/>
-      <c r="M122" s="2" t="inlineStr"/>
-      <c r="N122" s="2" t="inlineStr"/>
-      <c r="O122" s="2" t="inlineStr"/>
-      <c r="P122" s="2" t="inlineStr"/>
-      <c r="Q122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-petrobas-2</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>03.915.910/0001-92</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>D+05 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -8223,13 +9351,41 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="2" t="inlineStr"/>
-      <c r="M124" s="2" t="inlineStr"/>
-      <c r="N124" s="2" t="inlineStr"/>
-      <c r="O124" s="2" t="inlineStr"/>
-      <c r="P124" s="2" t="inlineStr"/>
-      <c r="Q124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-petrobas-3</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>03.915.903/0001-90</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>D+05 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -8413,12 +9569,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-equilibrio-mpe-rf-lp/</t>
         </is>
       </c>
-      <c r="L127" s="4" t="inlineStr"/>
-      <c r="M127" s="4" t="inlineStr"/>
-      <c r="N127" s="4" t="inlineStr"/>
-      <c r="O127" s="4" t="inlineStr"/>
-      <c r="P127" s="4" t="inlineStr"/>
-      <c r="Q127" s="4" t="inlineStr"/>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>07.986.172/0001-25</t>
+        </is>
+      </c>
+      <c r="M127" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N127" s="4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O127" s="4" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="P127" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q127" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -8476,12 +9656,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-saude-suplementar-anf-rf</t>
         </is>
       </c>
-      <c r="L128" s="2" t="inlineStr"/>
-      <c r="M128" s="2" t="inlineStr"/>
-      <c r="N128" s="2" t="inlineStr"/>
-      <c r="O128" s="2" t="inlineStr"/>
-      <c r="P128" s="2" t="inlineStr"/>
-      <c r="Q128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>09.181.268/0001-41</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -8539,12 +9743,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-tp-mpe-rf-lp/</t>
         </is>
       </c>
-      <c r="L129" s="4" t="inlineStr"/>
-      <c r="M129" s="4" t="inlineStr"/>
-      <c r="N129" s="4" t="inlineStr"/>
-      <c r="O129" s="4" t="inlineStr"/>
-      <c r="P129" s="4" t="inlineStr"/>
-      <c r="Q129" s="4" t="inlineStr"/>
+      <c r="L129" s="4" t="inlineStr">
+        <is>
+          <t>15.154.429/0001-00</t>
+        </is>
+      </c>
+      <c r="M129" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N129" s="4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O129" s="4" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="P129" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q129" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -8602,12 +9830,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-patrimonio-indice-precos-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L130" s="2" t="inlineStr"/>
-      <c r="M130" s="2" t="inlineStr"/>
-      <c r="N130" s="2" t="inlineStr"/>
-      <c r="O130" s="2" t="inlineStr"/>
-      <c r="P130" s="2" t="inlineStr"/>
-      <c r="Q130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>03.191.874/0001-61</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>100000.0</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>D+3 (du)</t>
+        </is>
+      </c>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -8665,12 +9917,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-giro-empresas-ref-di-longo-prazo/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L131" s="4" t="inlineStr"/>
-      <c r="M131" s="4" t="inlineStr"/>
-      <c r="N131" s="4" t="inlineStr"/>
-      <c r="O131" s="4" t="inlineStr"/>
-      <c r="P131" s="4" t="inlineStr"/>
-      <c r="Q131" s="4" t="inlineStr"/>
+      <c r="L131" s="4" t="inlineStr">
+        <is>
+          <t>16.916.063/0001-22</t>
+        </is>
+      </c>
+      <c r="M131" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N131" s="4" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="O131" s="4" t="inlineStr">
+        <is>
+          <t>500000.0</t>
+        </is>
+      </c>
+      <c r="P131" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q131" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -8791,12 +10067,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/referenciados/fi-safira-corporativo-rf-lp</t>
         </is>
       </c>
-      <c r="L133" s="4" t="inlineStr"/>
-      <c r="M133" s="4" t="inlineStr"/>
-      <c r="N133" s="4" t="inlineStr"/>
-      <c r="O133" s="4" t="inlineStr"/>
-      <c r="P133" s="4" t="inlineStr"/>
-      <c r="Q133" s="4" t="inlineStr"/>
+      <c r="L133" s="4" t="inlineStr">
+        <is>
+          <t>10.384.413/0001-70</t>
+        </is>
+      </c>
+      <c r="M133" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N133" s="4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="O133" s="4" t="inlineStr">
+        <is>
+          <t>1000000.0</t>
+        </is>
+      </c>
+      <c r="P133" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q133" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -8917,12 +10217,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-saude-suplementar-ans-ii-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L135" s="4" t="inlineStr"/>
-      <c r="M135" s="4" t="inlineStr"/>
-      <c r="N135" s="4" t="inlineStr"/>
-      <c r="O135" s="4" t="inlineStr"/>
-      <c r="P135" s="4" t="inlineStr"/>
-      <c r="Q135" s="4" t="inlineStr"/>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>09.548.725/0001-93</t>
+        </is>
+      </c>
+      <c r="M135" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N135" s="4" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="O135" s="4" t="inlineStr">
+        <is>
+          <t>10000000.0</t>
+        </is>
+      </c>
+      <c r="P135" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q135" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -9043,12 +10367,32 @@
           <t>https://www.caixa.gov.br/fundos-investimento/empresa/renda-fixa/fi-sebrae-rf-longo-prazo/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L137" s="4" t="inlineStr"/>
-      <c r="M137" s="4" t="inlineStr"/>
+      <c r="L137" s="4" t="inlineStr">
+        <is>
+          <t>03.737.227/0001-02</t>
+        </is>
+      </c>
+      <c r="M137" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
       <c r="N137" s="4" t="inlineStr"/>
-      <c r="O137" s="4" t="inlineStr"/>
-      <c r="P137" s="4" t="inlineStr"/>
-      <c r="Q137" s="4" t="inlineStr"/>
+      <c r="O137" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P137" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q137" s="4" t="inlineStr">
+        <is>
+          <t>D+01 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -9673,12 +11017,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/brasil-IPCA</t>
         </is>
       </c>
-      <c r="L147" s="4" t="inlineStr"/>
-      <c r="M147" s="4" t="inlineStr"/>
-      <c r="N147" s="4" t="inlineStr"/>
-      <c r="O147" s="4" t="inlineStr"/>
-      <c r="P147" s="4" t="inlineStr"/>
-      <c r="Q147" s="4" t="inlineStr"/>
+      <c r="L147" s="4" t="inlineStr">
+        <is>
+          <t>21.918.896/0001-62</t>
+        </is>
+      </c>
+      <c r="M147" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N147" s="4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O147" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P147" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q147" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -10492,12 +11860,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-caixa-brasil-idka-pre2a-rf-lp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L160" s="2" t="inlineStr"/>
-      <c r="M160" s="2" t="inlineStr"/>
-      <c r="N160" s="2" t="inlineStr"/>
-      <c r="O160" s="2" t="inlineStr"/>
-      <c r="P160" s="2" t="inlineStr"/>
-      <c r="Q160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>45.163.710/0001-70</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -11244,12 +12636,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-extramercado-comum-irfm-1-rf/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L172" s="2" t="inlineStr"/>
-      <c r="M172" s="2" t="inlineStr"/>
-      <c r="N172" s="2" t="inlineStr"/>
-      <c r="O172" s="2" t="inlineStr"/>
-      <c r="P172" s="2" t="inlineStr"/>
-      <c r="Q172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>14.507.897/0001-59</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -693,12 +693,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundo-simples/fic-facil-rf-simples</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr"/>
-      <c r="N3" s="4" t="inlineStr"/>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>05.114.716/0001-33</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -756,12 +780,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundo-simples/fic-movimentacoes-automaticas-rf-simples/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14.508.652/0001-46</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -969,12 +1017,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-plus-rf-credito-privado-lp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="4" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>40.194.309/0001-84</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>D+14 (du)</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>D+15 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1032,12 +1104,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-ideal-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>68.623.479/0001-56</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1241,12 +1337,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-absoluto-pre-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="inlineStr"/>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>02.201.164/0001-02</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1304,12 +1424,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-capital-indice-de-precos-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>03.218.183/0001-04</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>D+3 (du)</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1454,12 +1598,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-soberano-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>02.323.746/0001-61</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1517,12 +1685,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-foco-indice-precos-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr"/>
-      <c r="N15" s="4" t="inlineStr"/>
-      <c r="O15" s="4" t="inlineStr"/>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>09.548.729/0001-71</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>D+3 (du)</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1580,12 +1772,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-classico-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>01.165.796/0001-03</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1817,12 +2033,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-oab-rf-credito-privado-longo-prazo</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr"/>
-      <c r="N19" s="4" t="inlineStr"/>
-      <c r="O19" s="4" t="inlineStr"/>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>14.120.488/0001-03</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1880,12 +2120,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-executivo-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>01.165.781/0001-37</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1943,12 +2207,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-relacionamento-ideal-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr"/>
-      <c r="M21" s="4" t="inlineStr"/>
-      <c r="N21" s="4" t="inlineStr"/>
-      <c r="O21" s="4" t="inlineStr"/>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>10.577.505/0001-77</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2152,12 +2440,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/debentures-incentivadas/caixa-expert-arx-ipca-deb-incentivadas-rf-cred-priv-lp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>60.138.811/0001-85</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>D+14 (du)</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>D+16 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2215,12 +2527,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/debentures-incentivadas/caixa-expert-vinlanddebenture-</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr"/>
-      <c r="M25" s="4" t="inlineStr"/>
-      <c r="N25" s="4" t="inlineStr"/>
-      <c r="O25" s="4" t="inlineStr"/>
-      <c r="P25" s="4" t="inlineStr"/>
-      <c r="Q25" s="4" t="inlineStr"/>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>58.113.332/0001-62</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="inlineStr">
+        <is>
+          <t>D+13 (du)</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>D+15 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2341,12 +2677,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fif-inflacao-2027/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr"/>
-      <c r="M27" s="4" t="inlineStr"/>
-      <c r="N27" s="4" t="inlineStr"/>
-      <c r="O27" s="4" t="inlineStr"/>
-      <c r="P27" s="4" t="inlineStr"/>
-      <c r="Q27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>56.349.290/0001-38</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2400,12 +2760,36 @@
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr"/>
-      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>63.455.348/0001-93</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>D+5 (du)</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>D+07 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2459,12 +2843,36 @@
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr"/>
-      <c r="L29" s="4" t="inlineStr"/>
-      <c r="M29" s="4" t="inlineStr"/>
-      <c r="N29" s="4" t="inlineStr"/>
-      <c r="O29" s="4" t="inlineStr"/>
-      <c r="P29" s="4" t="inlineStr"/>
-      <c r="Q29" s="4" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>59.861.817/0001-05</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>D+22 (du)</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>D+24 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2522,12 +2930,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/debentures-incentivadas/caixa-expert-rb-asset-deb-incentivadas-cdi-rf-cred-priv/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
-      <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>62.890.286/0001-85</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>D+14 (du)</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>D+16 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2581,12 +3013,32 @@
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr"/>
-      <c r="L31" s="4" t="inlineStr"/>
-      <c r="M31" s="4" t="inlineStr"/>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>65.789.297/0001-61</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
       <c r="N31" s="4" t="inlineStr"/>
-      <c r="O31" s="4" t="inlineStr"/>
-      <c r="P31" s="4" t="inlineStr"/>
-      <c r="Q31" s="4" t="inlineStr"/>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>D+21 (du)</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>D+23 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2905,12 +3357,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-personal-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr"/>
-      <c r="M35" s="4" t="inlineStr"/>
-      <c r="N35" s="4" t="inlineStr"/>
-      <c r="O35" s="4" t="inlineStr"/>
-      <c r="P35" s="4" t="inlineStr"/>
-      <c r="Q35" s="4" t="inlineStr"/>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>02.201.163/0001-68</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>50000.0</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2968,12 +3444,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-renda-fixa-ativa-lp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
-      <c r="P36" s="2" t="inlineStr"/>
-      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>35.536.542/0001-68</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>50000.0</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>D+01 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -3118,12 +3618,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-supremo-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr"/>
-      <c r="P38" s="2" t="inlineStr"/>
-      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>07.986.178/0001-00</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>70000.0</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -3181,12 +3705,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-unique-private-cred-priv-lp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L39" s="4" t="inlineStr"/>
-      <c r="M39" s="4" t="inlineStr"/>
-      <c r="N39" s="4" t="inlineStr"/>
-      <c r="O39" s="4" t="inlineStr"/>
-      <c r="P39" s="4" t="inlineStr"/>
-      <c r="Q39" s="4" t="inlineStr"/>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>55.986.292/0001-75</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>100000.0</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3244,12 +3792,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-especial-rf-longo-prazo/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr"/>
-      <c r="O40" s="2" t="inlineStr"/>
-      <c r="P40" s="2" t="inlineStr"/>
-      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>03.737.190/0001-12</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>100000.0</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -3307,12 +3879,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-fidelidade-private-rf-longo-prazo/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr"/>
-      <c r="M41" s="4" t="inlineStr"/>
-      <c r="N41" s="4" t="inlineStr"/>
-      <c r="O41" s="4" t="inlineStr"/>
-      <c r="P41" s="4" t="inlineStr"/>
-      <c r="Q41" s="4" t="inlineStr"/>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>09.181.287/0001-78</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>200000.0</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3457,12 +4053,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-fidelidade-ii-rf-credito-privado-longo-prazo/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L43" s="4" t="inlineStr"/>
-      <c r="M43" s="4" t="inlineStr"/>
-      <c r="N43" s="4" t="inlineStr"/>
-      <c r="O43" s="4" t="inlineStr"/>
-      <c r="P43" s="4" t="inlineStr"/>
-      <c r="Q43" s="4" t="inlineStr"/>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>10.322.668/0001-09</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>1000000.0</t>
+        </is>
+      </c>
+      <c r="P43" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3520,12 +4140,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-beta-ref-di-lp</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr"/>
-      <c r="O44" s="2" t="inlineStr"/>
-      <c r="P44" s="2" t="inlineStr"/>
-      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>00.834.072/0001-34</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -3579,12 +4223,36 @@
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr"/>
-      <c r="L45" s="4" t="inlineStr"/>
-      <c r="M45" s="4" t="inlineStr"/>
-      <c r="N45" s="4" t="inlineStr"/>
-      <c r="O45" s="4" t="inlineStr"/>
-      <c r="P45" s="4" t="inlineStr"/>
-      <c r="Q45" s="4" t="inlineStr"/>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>66.034.762/0001-17</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P45" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3642,12 +4310,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-giro-imediato-ref-di-longo-prazo</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="2" t="inlineStr"/>
-      <c r="P46" s="2" t="inlineStr"/>
-      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>17.502.869/0001-37</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -3792,12 +4484,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-omega-ref-di-longo-prazo/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr"/>
-      <c r="O48" s="2" t="inlineStr"/>
-      <c r="P48" s="2" t="inlineStr"/>
-      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>55.036.101/0001-04</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -3942,12 +4658,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-sigma-ref-di-longo-prazo</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr"/>
-      <c r="P50" s="2" t="inlineStr"/>
-      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>10.731.794/0001-17</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -4005,12 +4745,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-rubi-ref-di-longo-prazo/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L51" s="4" t="inlineStr"/>
-      <c r="M51" s="4" t="inlineStr"/>
-      <c r="N51" s="4" t="inlineStr"/>
-      <c r="O51" s="4" t="inlineStr"/>
-      <c r="P51" s="4" t="inlineStr"/>
-      <c r="Q51" s="4" t="inlineStr"/>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>10.646.885/0001-54</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t>100000.0</t>
+        </is>
+      </c>
+      <c r="P51" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4131,12 +4895,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-top-private-ref-di-longo-prazo/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L53" s="4" t="inlineStr"/>
-      <c r="M53" s="4" t="inlineStr"/>
-      <c r="N53" s="4" t="inlineStr"/>
-      <c r="O53" s="4" t="inlineStr"/>
-      <c r="P53" s="4" t="inlineStr"/>
-      <c r="Q53" s="4" t="inlineStr"/>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>19.769.018/0001-80</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="O53" s="4" t="inlineStr">
+        <is>
+          <t>100000.0</t>
+        </is>
+      </c>
+      <c r="P53" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q53" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4281,12 +5069,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fic-fof-smart-credito-privado-multimercado-longo-prazo/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L55" s="4" t="inlineStr"/>
-      <c r="M55" s="4" t="inlineStr"/>
-      <c r="N55" s="4" t="inlineStr"/>
-      <c r="O55" s="4" t="inlineStr"/>
-      <c r="P55" s="4" t="inlineStr"/>
-      <c r="Q55" s="4" t="inlineStr"/>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>51.943.346/0001-64</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="O55" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P55" s="4" t="inlineStr">
+        <is>
+          <t>D+46 (du)</t>
+        </is>
+      </c>
+      <c r="Q55" s="4" t="inlineStr">
+        <is>
+          <t>D+48 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4344,12 +5156,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-multigestor-global-equities-invest-ext/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr"/>
-      <c r="O56" s="2" t="inlineStr"/>
-      <c r="P56" s="2" t="inlineStr"/>
-      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>39.528.038/0001-77</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>D+7 (du)</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>D+12 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -4470,12 +5306,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/estrategia-livre-mm-lp</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr"/>
-      <c r="O58" s="2" t="inlineStr"/>
-      <c r="P58" s="2" t="inlineStr"/>
-      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>34.660.276/0001-18</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>D+13 (du)</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>D+15 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -4616,12 +5476,36 @@
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr"/>
-      <c r="O60" s="2" t="inlineStr"/>
-      <c r="P60" s="2" t="inlineStr"/>
-      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>65.795.043/0001-56</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>D+8 (du)</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>D+10 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -4679,12 +5563,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-short-mm/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L61" s="4" t="inlineStr"/>
-      <c r="M61" s="4" t="inlineStr"/>
-      <c r="N61" s="4" t="inlineStr"/>
-      <c r="O61" s="4" t="inlineStr"/>
-      <c r="P61" s="4" t="inlineStr"/>
-      <c r="Q61" s="4" t="inlineStr"/>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>51.408.738/0001-23</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P61" s="4" t="inlineStr">
+        <is>
+          <t>D+24 (du)</t>
+        </is>
+      </c>
+      <c r="Q61" s="4" t="inlineStr">
+        <is>
+          <t>D+26 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4742,12 +5650,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-bias-mm/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr"/>
-      <c r="N62" s="2" t="inlineStr"/>
-      <c r="O62" s="2" t="inlineStr"/>
-      <c r="P62" s="2" t="inlineStr"/>
-      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>54.439.846/0001-51</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>D+13 (du)</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>D+15 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -4801,12 +5733,36 @@
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr"/>
-      <c r="L63" s="4" t="inlineStr"/>
-      <c r="M63" s="4" t="inlineStr"/>
-      <c r="N63" s="4" t="inlineStr"/>
-      <c r="O63" s="4" t="inlineStr"/>
-      <c r="P63" s="4" t="inlineStr"/>
-      <c r="Q63" s="4" t="inlineStr"/>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>65.795.384/0001-21</t>
+        </is>
+      </c>
+      <c r="M63" s="4" t="inlineStr">
+        <is>
+          <t>Agressivo</t>
+        </is>
+      </c>
+      <c r="N63" s="4" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="O63" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P63" s="4" t="inlineStr">
+        <is>
+          <t>D+14 (du)</t>
+        </is>
+      </c>
+      <c r="Q63" s="4" t="inlineStr">
+        <is>
+          <t>D+16 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4864,12 +5820,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-bias-mm/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr"/>
-      <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr"/>
-      <c r="O64" s="2" t="inlineStr"/>
-      <c r="P64" s="2" t="inlineStr"/>
-      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>51.408.950/0001-90</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>D+24 (du)</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>D+26 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -4923,12 +5903,36 @@
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr"/>
-      <c r="L65" s="4" t="inlineStr"/>
-      <c r="M65" s="4" t="inlineStr"/>
-      <c r="N65" s="4" t="inlineStr"/>
-      <c r="O65" s="4" t="inlineStr"/>
-      <c r="P65" s="4" t="inlineStr"/>
-      <c r="Q65" s="4" t="inlineStr"/>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>65.794.476/0001-97</t>
+        </is>
+      </c>
+      <c r="M65" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="O65" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P65" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q65" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4986,12 +5990,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fi-euro-multimercado-longo-prazo/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr"/>
-      <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr"/>
-      <c r="O66" s="2" t="inlineStr"/>
-      <c r="P66" s="2" t="inlineStr"/>
-      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>54.483.566/0001-40</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -5049,12 +6077,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fic-estrategico-multimercado-longo-prazo</t>
         </is>
       </c>
-      <c r="L67" s="4" t="inlineStr"/>
-      <c r="M67" s="4" t="inlineStr"/>
-      <c r="N67" s="4" t="inlineStr"/>
-      <c r="O67" s="4" t="inlineStr"/>
-      <c r="P67" s="4" t="inlineStr"/>
-      <c r="Q67" s="4" t="inlineStr"/>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>03.737.200/0001-10</t>
+        </is>
+      </c>
+      <c r="M67" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="O67" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P67" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q67" s="4" t="inlineStr">
+        <is>
+          <t>D+01 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -5199,12 +6251,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fic-multigestor</t>
         </is>
       </c>
-      <c r="L69" s="4" t="inlineStr"/>
-      <c r="M69" s="4" t="inlineStr"/>
-      <c r="N69" s="4" t="inlineStr"/>
-      <c r="O69" s="4" t="inlineStr"/>
-      <c r="P69" s="4" t="inlineStr"/>
-      <c r="Q69" s="4" t="inlineStr"/>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>18.007.710/0001-09</t>
+        </is>
+      </c>
+      <c r="M69" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="O69" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P69" s="4" t="inlineStr">
+        <is>
+          <t>D+24 (du)</t>
+        </is>
+      </c>
+      <c r="Q69" s="4" t="inlineStr">
+        <is>
+          <t>D+26 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -5349,12 +6425,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fi-bolsa-americana-multimercado-lp</t>
         </is>
       </c>
-      <c r="L71" s="4" t="inlineStr"/>
-      <c r="M71" s="4" t="inlineStr"/>
-      <c r="N71" s="4" t="inlineStr"/>
-      <c r="O71" s="4" t="inlineStr"/>
-      <c r="P71" s="4" t="inlineStr"/>
-      <c r="Q71" s="4" t="inlineStr"/>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>30.036.235/0001-02</t>
+        </is>
+      </c>
+      <c r="M71" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P71" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q71" s="4" t="inlineStr">
+        <is>
+          <t>D+01 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -5412,12 +6512,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-juros-e-moedas-multimercado-plus-lp/</t>
         </is>
       </c>
-      <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr"/>
-      <c r="N72" s="2" t="inlineStr"/>
-      <c r="O72" s="2" t="inlineStr"/>
-      <c r="P72" s="2" t="inlineStr"/>
-      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>29.157.485/0001-03</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -5471,12 +6595,36 @@
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr"/>
-      <c r="L73" s="4" t="inlineStr"/>
-      <c r="M73" s="4" t="inlineStr"/>
-      <c r="N73" s="4" t="inlineStr"/>
-      <c r="O73" s="4" t="inlineStr"/>
-      <c r="P73" s="4" t="inlineStr"/>
-      <c r="Q73" s="4" t="inlineStr"/>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>35.536.472/0001-48</t>
+        </is>
+      </c>
+      <c r="M73" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="O73" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P73" s="4" t="inlineStr">
+        <is>
+          <t>D+13 (du)</t>
+        </is>
+      </c>
+      <c r="Q73" s="4" t="inlineStr">
+        <is>
+          <t>D+15 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5529,13 +6677,41 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr"/>
-      <c r="O74" s="2" t="inlineStr"/>
-      <c r="P74" s="2" t="inlineStr"/>
-      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-hashdex-nasdaq-crypto-fic-fif-mm</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>62.769.135/0001-73</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>Agressivo</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>D+3 (du)</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>D+08 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -5593,12 +6769,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa_fic_fim_cap_protegido_cesta_agro/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L75" s="4" t="inlineStr"/>
-      <c r="M75" s="4" t="inlineStr"/>
-      <c r="N75" s="4" t="inlineStr"/>
-      <c r="O75" s="4" t="inlineStr"/>
-      <c r="P75" s="4" t="inlineStr"/>
-      <c r="Q75" s="4" t="inlineStr"/>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>42.229.068/0001-97</t>
+        </is>
+      </c>
+      <c r="M75" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="O75" s="4" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="P75" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q75" s="4" t="inlineStr">
+        <is>
+          <t>D+02 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5656,12 +6856,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fic-capital-protegido-ciclico-iii-multimercado-lp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr"/>
-      <c r="O76" s="2" t="inlineStr"/>
-      <c r="P76" s="2" t="inlineStr"/>
-      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>44.683.343/0001-73</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>D+02 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -5719,12 +6943,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fic-capital-protegido-ibovespa-ciclico-1-multimercado</t>
         </is>
       </c>
-      <c r="L77" s="4" t="inlineStr"/>
-      <c r="M77" s="4" t="inlineStr"/>
-      <c r="N77" s="4" t="inlineStr"/>
-      <c r="O77" s="4" t="inlineStr"/>
-      <c r="P77" s="4" t="inlineStr"/>
-      <c r="Q77" s="4" t="inlineStr"/>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>14.239.659/0001-00</t>
+        </is>
+      </c>
+      <c r="M77" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="O77" s="4" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="P77" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q77" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5782,12 +7030,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fic-capital-protegido-ciclico-ii-multimercado-lp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr"/>
-      <c r="O78" s="2" t="inlineStr"/>
-      <c r="P78" s="2" t="inlineStr"/>
-      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>45.443.651/0001-94</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>D+02 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -5845,12 +7117,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-expert-pimco-income-ie-fic-multimercado/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L79" s="4" t="inlineStr"/>
-      <c r="M79" s="4" t="inlineStr"/>
-      <c r="N79" s="4" t="inlineStr"/>
-      <c r="O79" s="4" t="inlineStr"/>
-      <c r="P79" s="4" t="inlineStr"/>
-      <c r="Q79" s="4" t="inlineStr"/>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>51.659.921/0001-00</t>
+        </is>
+      </c>
+      <c r="M79" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="O79" s="4" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P79" s="4" t="inlineStr">
+        <is>
+          <t>D+3 (du)</t>
+        </is>
+      </c>
+      <c r="Q79" s="4" t="inlineStr">
+        <is>
+          <t>D+08 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -5908,12 +7204,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/expert-giant-zarathustra-fic-multimercado</t>
         </is>
       </c>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr"/>
-      <c r="O80" s="2" t="inlineStr"/>
-      <c r="P80" s="2" t="inlineStr"/>
-      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>40.209.061/0001-88</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>D+22 (du)</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>D+25 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -5971,12 +7291,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fic-alocacao-macro-multimercado-longo-prazo/</t>
         </is>
       </c>
-      <c r="L81" s="4" t="inlineStr"/>
-      <c r="M81" s="4" t="inlineStr"/>
-      <c r="N81" s="4" t="inlineStr"/>
-      <c r="O81" s="4" t="inlineStr"/>
-      <c r="P81" s="4" t="inlineStr"/>
-      <c r="Q81" s="4" t="inlineStr"/>
+      <c r="L81" s="4" t="inlineStr">
+        <is>
+          <t>08.070.841/0001-87</t>
+        </is>
+      </c>
+      <c r="M81" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N81" s="4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O81" s="4" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P81" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q81" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -6121,12 +7465,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/btg-pactual-x10-multimercado-longo-prazo/</t>
         </is>
       </c>
-      <c r="L83" s="4" t="inlineStr"/>
-      <c r="M83" s="4" t="inlineStr"/>
-      <c r="N83" s="4" t="inlineStr"/>
-      <c r="O83" s="4" t="inlineStr"/>
-      <c r="P83" s="4" t="inlineStr"/>
-      <c r="Q83" s="4" t="inlineStr"/>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>17.433.039/0001-03</t>
+        </is>
+      </c>
+      <c r="M83" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N83" s="4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O83" s="4" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P83" s="4" t="inlineStr">
+        <is>
+          <t>D+8 (du)</t>
+        </is>
+      </c>
+      <c r="Q83" s="4" t="inlineStr">
+        <is>
+          <t>D+10 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -6184,12 +7552,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fic-caixa-expert-spxmm/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr"/>
-      <c r="O84" s="2" t="inlineStr"/>
-      <c r="P84" s="2" t="inlineStr"/>
-      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>34.660.453/0001-66</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>D+22 (du)</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>D+24 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -6421,12 +7813,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-brasil-etf-bovespa/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L87" s="4" t="inlineStr"/>
-      <c r="M87" s="4" t="inlineStr"/>
-      <c r="N87" s="4" t="inlineStr"/>
-      <c r="O87" s="4" t="inlineStr"/>
-      <c r="P87" s="4" t="inlineStr"/>
-      <c r="Q87" s="4" t="inlineStr"/>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>01.525.057/0001-77</t>
+        </is>
+      </c>
+      <c r="M87" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N87" s="4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O87" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P87" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q87" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -6480,12 +7896,36 @@
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
-      <c r="N88" s="2" t="inlineStr"/>
-      <c r="O88" s="2" t="inlineStr"/>
-      <c r="P88" s="2" t="inlineStr"/>
-      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>35.536.497/0001-41</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>D+13 (du)</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>D+15 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -7065,12 +8505,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fic-fia-multigestor/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L95" s="4" t="inlineStr"/>
-      <c r="M95" s="4" t="inlineStr"/>
-      <c r="N95" s="4" t="inlineStr"/>
-      <c r="O95" s="4" t="inlineStr"/>
-      <c r="P95" s="4" t="inlineStr"/>
-      <c r="Q95" s="4" t="inlineStr"/>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>30.068.224/0001-04</t>
+        </is>
+      </c>
+      <c r="M95" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N95" s="4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="O95" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P95" s="4" t="inlineStr">
+        <is>
+          <t>D+23 (du)</t>
+        </is>
+      </c>
+      <c r="Q95" s="4" t="inlineStr">
+        <is>
+          <t>D+25 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -7650,12 +9114,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fia-caixa-seguridade/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="2" t="inlineStr"/>
-      <c r="N102" s="2" t="inlineStr"/>
-      <c r="O102" s="2" t="inlineStr"/>
-      <c r="P102" s="2" t="inlineStr"/>
-      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>30.068.049/0001-47</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -8583,12 +10071,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/CAIXA-Expert-Verde-Am-Long-Bias-FIC-Acoes/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L113" s="4" t="inlineStr"/>
-      <c r="M113" s="4" t="inlineStr"/>
-      <c r="N113" s="4" t="inlineStr"/>
-      <c r="O113" s="4" t="inlineStr"/>
-      <c r="P113" s="4" t="inlineStr"/>
-      <c r="Q113" s="4" t="inlineStr"/>
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>30.068.071/0001-97</t>
+        </is>
+      </c>
+      <c r="M113" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N113" s="4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="O113" s="4" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P113" s="4" t="inlineStr">
+        <is>
+          <t>D+22 (du)</t>
+        </is>
+      </c>
+      <c r="Q113" s="4" t="inlineStr">
+        <is>
+          <t>D+24 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -8646,12 +10158,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/caixa-expert-claritas-valor-fic-acoes/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L114" s="2" t="inlineStr"/>
-      <c r="M114" s="2" t="inlineStr"/>
-      <c r="N114" s="2" t="inlineStr"/>
-      <c r="O114" s="2" t="inlineStr"/>
-      <c r="P114" s="2" t="inlineStr"/>
-      <c r="Q114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>30.068.060/0001-07</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>D+23 (du)</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>D+25 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -8767,13 +10303,41 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="2" t="inlineStr"/>
-      <c r="M116" s="2" t="inlineStr"/>
-      <c r="N116" s="2" t="inlineStr"/>
-      <c r="O116" s="2" t="inlineStr"/>
-      <c r="P116" s="2" t="inlineStr"/>
-      <c r="Q116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-eletrobras-migracao</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>45.443.366/0001-73</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>D+05 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -9000,13 +10564,41 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="K119" s="4" t="inlineStr"/>
-      <c r="L119" s="4" t="inlineStr"/>
-      <c r="M119" s="4" t="inlineStr"/>
-      <c r="N119" s="4" t="inlineStr"/>
-      <c r="O119" s="4" t="inlineStr"/>
-      <c r="P119" s="4" t="inlineStr"/>
-      <c r="Q119" s="4" t="inlineStr"/>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-2</t>
+        </is>
+      </c>
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>04.885.824/0001-47</t>
+        </is>
+      </c>
+      <c r="M119" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N119" s="4" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="O119" s="4" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P119" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q119" s="4" t="inlineStr">
+        <is>
+          <t>D+05 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -9146,13 +10738,41 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="K121" s="4" t="inlineStr"/>
-      <c r="L121" s="4" t="inlineStr"/>
-      <c r="M121" s="4" t="inlineStr"/>
-      <c r="N121" s="4" t="inlineStr"/>
-      <c r="O121" s="4" t="inlineStr"/>
-      <c r="P121" s="4" t="inlineStr"/>
-      <c r="Q121" s="4" t="inlineStr"/>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-migracao</t>
+        </is>
+      </c>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>04.885.832/0001-93</t>
+        </is>
+      </c>
+      <c r="M121" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N121" s="4" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="O121" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P121" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q121" s="4" t="inlineStr">
+        <is>
+          <t>D+05 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -9292,13 +10912,41 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="K123" s="4" t="inlineStr"/>
-      <c r="L123" s="4" t="inlineStr"/>
-      <c r="M123" s="4" t="inlineStr"/>
-      <c r="N123" s="4" t="inlineStr"/>
-      <c r="O123" s="4" t="inlineStr"/>
-      <c r="P123" s="4" t="inlineStr"/>
-      <c r="Q123" s="4" t="inlineStr"/>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-2</t>
+        </is>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>04.885.824/0001-47</t>
+        </is>
+      </c>
+      <c r="M123" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N123" s="4" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="O123" s="4" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P123" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q123" s="4" t="inlineStr">
+        <is>
+          <t>D+05 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -9443,12 +11091,36 @@
           <t>http://site.extra.caixa.gov.br/fundos-investimento/fundo-simples/fic-azulzinha-rf-simples/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L125" s="4" t="inlineStr"/>
-      <c r="M125" s="4" t="inlineStr"/>
-      <c r="N125" s="4" t="inlineStr"/>
-      <c r="O125" s="4" t="inlineStr"/>
-      <c r="P125" s="4" t="inlineStr"/>
-      <c r="Q125" s="4" t="inlineStr"/>
+      <c r="L125" s="4" t="inlineStr">
+        <is>
+          <t>61.160.298/0001-91</t>
+        </is>
+      </c>
+      <c r="M125" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N125" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="O125" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P125" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q125" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -10004,12 +11676,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/empresa/renda-fixa/credito-privado/caixa-fi-diamante-corporativo-rf-cred-priv-lp</t>
         </is>
       </c>
-      <c r="L132" s="2" t="inlineStr"/>
-      <c r="M132" s="2" t="inlineStr"/>
-      <c r="N132" s="2" t="inlineStr"/>
-      <c r="O132" s="2" t="inlineStr"/>
-      <c r="P132" s="2" t="inlineStr"/>
-      <c r="Q132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>29.157.520/0001-94</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>1000000.0</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -10154,12 +11850,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-institucional-soberano-plus-rf-lp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L134" s="2" t="inlineStr"/>
-      <c r="M134" s="2" t="inlineStr"/>
-      <c r="N134" s="2" t="inlineStr"/>
-      <c r="O134" s="2" t="inlineStr"/>
-      <c r="P134" s="2" t="inlineStr"/>
-      <c r="Q134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>42.196.029/0001-30</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>5000000.0</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -10304,12 +12024,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/empresa/renda-fixa/fi-cni-rf-longo-prazo/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L136" s="2" t="inlineStr"/>
-      <c r="M136" s="2" t="inlineStr"/>
-      <c r="N136" s="2" t="inlineStr"/>
-      <c r="O136" s="2" t="inlineStr"/>
-      <c r="P136" s="2" t="inlineStr"/>
-      <c r="Q136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>05.164.366/0001-10</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -10450,12 +12194,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-giro-mpe-ref-di-longo-prazo/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L138" s="2" t="inlineStr"/>
-      <c r="M138" s="2" t="inlineStr"/>
-      <c r="N138" s="2" t="inlineStr"/>
-      <c r="O138" s="2" t="inlineStr"/>
-      <c r="P138" s="2" t="inlineStr"/>
-      <c r="Q138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>10.551.370/0001-70</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -10513,12 +12281,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/referenciados/fic-topazio-rf-ref-di-lp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L139" s="4" t="inlineStr"/>
-      <c r="M139" s="4" t="inlineStr"/>
-      <c r="N139" s="4" t="inlineStr"/>
-      <c r="O139" s="4" t="inlineStr"/>
-      <c r="P139" s="4" t="inlineStr"/>
-      <c r="Q139" s="4" t="inlineStr"/>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>11.061.230/0001-87</t>
+        </is>
+      </c>
+      <c r="M139" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N139" s="4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="O139" s="4" t="inlineStr">
+        <is>
+          <t>1000000.0</t>
+        </is>
+      </c>
+      <c r="P139" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q139" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -10576,12 +12368,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-esmeralda-corp-ref-di/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L140" s="2" t="inlineStr"/>
-      <c r="M140" s="2" t="inlineStr"/>
-      <c r="N140" s="2" t="inlineStr"/>
-      <c r="O140" s="2" t="inlineStr"/>
-      <c r="P140" s="2" t="inlineStr"/>
-      <c r="Q140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>52.699.555/0001-77</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>1000000.0</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -10639,12 +12455,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/voce/renda-fixa/fic-turquesa-corporativo-curto-prazo</t>
         </is>
       </c>
-      <c r="L141" s="4" t="inlineStr"/>
-      <c r="M141" s="4" t="inlineStr"/>
-      <c r="N141" s="4" t="inlineStr"/>
-      <c r="O141" s="4" t="inlineStr"/>
-      <c r="P141" s="4" t="inlineStr"/>
-      <c r="Q141" s="4" t="inlineStr"/>
+      <c r="L141" s="4" t="inlineStr">
+        <is>
+          <t>30.068.141/0001-07</t>
+        </is>
+      </c>
+      <c r="M141" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N141" s="4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="O141" s="4" t="inlineStr">
+        <is>
+          <t>3000000.0</t>
+        </is>
+      </c>
+      <c r="P141" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q141" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -10702,12 +12542,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-automatico-polis-rf-cp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L142" s="2" t="inlineStr"/>
-      <c r="M142" s="2" t="inlineStr"/>
-      <c r="N142" s="2" t="inlineStr"/>
-      <c r="O142" s="2" t="inlineStr"/>
-      <c r="P142" s="2" t="inlineStr"/>
-      <c r="Q142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>50.803.936/0001-29</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -10765,12 +12629,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-pratico-curto-prazo</t>
         </is>
       </c>
-      <c r="L143" s="4" t="inlineStr"/>
-      <c r="M143" s="4" t="inlineStr"/>
-      <c r="N143" s="4" t="inlineStr"/>
-      <c r="O143" s="4" t="inlineStr"/>
-      <c r="P143" s="4" t="inlineStr"/>
-      <c r="Q143" s="4" t="inlineStr"/>
+      <c r="L143" s="4" t="inlineStr">
+        <is>
+          <t>00.834.074/0001-23</t>
+        </is>
+      </c>
+      <c r="M143" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N143" s="4" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="O143" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P143" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q143" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -10891,12 +12779,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-matriz-rf/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L145" s="4" t="inlineStr"/>
-      <c r="M145" s="4" t="inlineStr"/>
-      <c r="N145" s="4" t="inlineStr"/>
-      <c r="O145" s="4" t="inlineStr"/>
-      <c r="P145" s="4" t="inlineStr"/>
-      <c r="Q145" s="4" t="inlineStr"/>
+      <c r="L145" s="4" t="inlineStr">
+        <is>
+          <t>23.215.008/0001-70</t>
+        </is>
+      </c>
+      <c r="M145" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N145" s="4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O145" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P145" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q145" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -10954,12 +12866,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-brasil-gestao-estrategica-rf</t>
         </is>
       </c>
-      <c r="L146" s="2" t="inlineStr"/>
-      <c r="M146" s="2" t="inlineStr"/>
-      <c r="N146" s="2" t="inlineStr"/>
-      <c r="O146" s="2" t="inlineStr"/>
-      <c r="P146" s="2" t="inlineStr"/>
-      <c r="Q146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>23.215.097/0001-55</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -11104,12 +13040,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/brasil-IPCA/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L148" s="2" t="inlineStr"/>
-      <c r="M148" s="2" t="inlineStr"/>
-      <c r="N148" s="2" t="inlineStr"/>
-      <c r="O148" s="2" t="inlineStr"/>
-      <c r="P148" s="2" t="inlineStr"/>
-      <c r="Q148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>35.536.532/0001-22</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>D+01 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -11167,12 +13127,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-irfm-1-titulos-publicos-rf</t>
         </is>
       </c>
-      <c r="L149" s="4" t="inlineStr"/>
-      <c r="M149" s="4" t="inlineStr"/>
-      <c r="N149" s="4" t="inlineStr"/>
-      <c r="O149" s="4" t="inlineStr"/>
-      <c r="P149" s="4" t="inlineStr"/>
-      <c r="Q149" s="4" t="inlineStr"/>
+      <c r="L149" s="4" t="inlineStr">
+        <is>
+          <t>10.740.670/0001-06</t>
+        </is>
+      </c>
+      <c r="M149" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N149" s="4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O149" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P149" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q149" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -11293,12 +13277,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/brasil-irf-m-titulos-publicos-renda-fixa-longo-prazo</t>
         </is>
       </c>
-      <c r="L151" s="4" t="inlineStr"/>
-      <c r="M151" s="4" t="inlineStr"/>
-      <c r="N151" s="4" t="inlineStr"/>
-      <c r="O151" s="4" t="inlineStr"/>
-      <c r="P151" s="4" t="inlineStr"/>
-      <c r="Q151" s="4" t="inlineStr"/>
+      <c r="L151" s="4" t="inlineStr">
+        <is>
+          <t>10.740.670/0001-06</t>
+        </is>
+      </c>
+      <c r="M151" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N151" s="4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O151" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P151" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q151" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -11356,12 +13364,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-ima-b-titulos-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L152" s="2" t="inlineStr"/>
-      <c r="M152" s="2" t="inlineStr"/>
-      <c r="N152" s="2" t="inlineStr"/>
-      <c r="O152" s="2" t="inlineStr"/>
-      <c r="P152" s="2" t="inlineStr"/>
-      <c r="Q152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>10.740.658/0001-93</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -11419,12 +13451,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-ima-b-5-titulos-publicos-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L153" s="4" t="inlineStr"/>
-      <c r="M153" s="4" t="inlineStr"/>
-      <c r="N153" s="4" t="inlineStr"/>
-      <c r="O153" s="4" t="inlineStr"/>
-      <c r="P153" s="4" t="inlineStr"/>
-      <c r="Q153" s="4" t="inlineStr"/>
+      <c r="L153" s="4" t="inlineStr">
+        <is>
+          <t>10.740.658/0001-93</t>
+        </is>
+      </c>
+      <c r="M153" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N153" s="4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O153" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P153" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q153" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -11482,12 +13538,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-ima-geral-tp-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L154" s="2" t="inlineStr"/>
-      <c r="M154" s="2" t="inlineStr"/>
-      <c r="N154" s="2" t="inlineStr"/>
-      <c r="O154" s="2" t="inlineStr"/>
-      <c r="P154" s="2" t="inlineStr"/>
-      <c r="Q154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>11.061.217/0001-28</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -11608,12 +13688,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-ima-b-5_mais-titulos-publicos-rf-lp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L156" s="2" t="inlineStr"/>
-      <c r="M156" s="2" t="inlineStr"/>
-      <c r="N156" s="2" t="inlineStr"/>
-      <c r="O156" s="2" t="inlineStr"/>
-      <c r="P156" s="2" t="inlineStr"/>
-      <c r="Q156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>10.740.658/0001-93</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -11671,12 +13775,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-irfm-1-titulos-publicos-rf-longo-prazo/</t>
         </is>
       </c>
-      <c r="L157" s="4" t="inlineStr"/>
-      <c r="M157" s="4" t="inlineStr"/>
-      <c r="N157" s="4" t="inlineStr"/>
-      <c r="O157" s="4" t="inlineStr"/>
-      <c r="P157" s="4" t="inlineStr"/>
-      <c r="Q157" s="4" t="inlineStr"/>
+      <c r="L157" s="4" t="inlineStr">
+        <is>
+          <t>10.740.670/0001-06</t>
+        </is>
+      </c>
+      <c r="M157" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N157" s="4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O157" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P157" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q157" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -11734,12 +13862,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-titulos-publicos-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L158" s="2" t="inlineStr"/>
-      <c r="M158" s="2" t="inlineStr"/>
-      <c r="N158" s="2" t="inlineStr"/>
-      <c r="O158" s="2" t="inlineStr"/>
-      <c r="P158" s="2" t="inlineStr"/>
-      <c r="Q158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>05.164.356/0001-84</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -11797,12 +13949,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-alianca-rf</t>
         </is>
       </c>
-      <c r="L159" s="4" t="inlineStr"/>
-      <c r="M159" s="4" t="inlineStr"/>
-      <c r="N159" s="4" t="inlineStr"/>
-      <c r="O159" s="4" t="inlineStr"/>
-      <c r="P159" s="4" t="inlineStr"/>
-      <c r="Q159" s="4" t="inlineStr"/>
+      <c r="L159" s="4" t="inlineStr">
+        <is>
+          <t>05.164.358/0001-73</t>
+        </is>
+      </c>
+      <c r="M159" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N159" s="4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O159" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P159" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q159" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -11947,12 +14123,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/brasil-disponibilidades</t>
         </is>
       </c>
-      <c r="L161" s="4" t="inlineStr"/>
-      <c r="M161" s="4" t="inlineStr"/>
-      <c r="N161" s="4" t="inlineStr"/>
-      <c r="O161" s="4" t="inlineStr"/>
-      <c r="P161" s="4" t="inlineStr"/>
-      <c r="Q161" s="4" t="inlineStr"/>
+      <c r="L161" s="4" t="inlineStr">
+        <is>
+          <t>14.508.643/0001-55</t>
+        </is>
+      </c>
+      <c r="M161" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N161" s="4" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="O161" s="4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="P161" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q161" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -12073,12 +14273,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-novo-brasil-ima-b-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L163" s="4" t="inlineStr"/>
-      <c r="M163" s="4" t="inlineStr"/>
-      <c r="N163" s="4" t="inlineStr"/>
-      <c r="O163" s="4" t="inlineStr"/>
-      <c r="P163" s="4" t="inlineStr"/>
-      <c r="Q163" s="4" t="inlineStr"/>
+      <c r="L163" s="4" t="inlineStr">
+        <is>
+          <t>10.646.895/0001-90</t>
+        </is>
+      </c>
+      <c r="M163" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N163" s="4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O163" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P163" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q163" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -12136,12 +14360,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/estrategia-livre-mm-lp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L164" s="2" t="inlineStr"/>
-      <c r="M164" s="2" t="inlineStr"/>
-      <c r="N164" s="2" t="inlineStr"/>
-      <c r="O164" s="2" t="inlineStr"/>
-      <c r="P164" s="2" t="inlineStr"/>
-      <c r="Q164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>34.660.276/0001-18</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr">
+        <is>
+          <t>D+13 (du)</t>
+        </is>
+      </c>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>D+15 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -12199,12 +14447,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-brasil-ibovespa/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L165" s="4" t="inlineStr"/>
-      <c r="M165" s="4" t="inlineStr"/>
-      <c r="N165" s="4" t="inlineStr"/>
-      <c r="O165" s="4" t="inlineStr"/>
-      <c r="P165" s="4" t="inlineStr"/>
-      <c r="Q165" s="4" t="inlineStr"/>
+      <c r="L165" s="4" t="inlineStr">
+        <is>
+          <t>13.058.816/0001-18</t>
+        </is>
+      </c>
+      <c r="M165" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N165" s="4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O165" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P165" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q165" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -12262,12 +14534,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-brasil-etf-bovespa</t>
         </is>
       </c>
-      <c r="L166" s="2" t="inlineStr"/>
-      <c r="M166" s="2" t="inlineStr"/>
-      <c r="N166" s="2" t="inlineStr"/>
-      <c r="O166" s="2" t="inlineStr"/>
-      <c r="P166" s="2" t="inlineStr"/>
-      <c r="Q166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>15.154.236/0001-50</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -12325,12 +14621,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/FIA-Institucional-BDR-nivel-I/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L167" s="4" t="inlineStr"/>
-      <c r="M167" s="4" t="inlineStr"/>
-      <c r="N167" s="4" t="inlineStr"/>
-      <c r="O167" s="4" t="inlineStr"/>
-      <c r="P167" s="4" t="inlineStr"/>
-      <c r="Q167" s="4" t="inlineStr"/>
+      <c r="L167" s="4" t="inlineStr">
+        <is>
+          <t>17.502.937/0001-68</t>
+        </is>
+      </c>
+      <c r="M167" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N167" s="4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="O167" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P167" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q167" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -12388,12 +14708,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-brasil-ibx-50</t>
         </is>
       </c>
-      <c r="L168" s="2" t="inlineStr"/>
-      <c r="M168" s="2" t="inlineStr"/>
-      <c r="N168" s="2" t="inlineStr"/>
-      <c r="O168" s="2" t="inlineStr"/>
-      <c r="P168" s="2" t="inlineStr"/>
-      <c r="Q168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>03.737.217/0001-77</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -12446,13 +14790,41 @@
           <t>RPPS</t>
         </is>
       </c>
-      <c r="K169" s="4" t="inlineStr"/>
-      <c r="L169" s="4" t="inlineStr"/>
-      <c r="M169" s="4" t="inlineStr"/>
-      <c r="N169" s="4" t="inlineStr"/>
-      <c r="O169" s="4" t="inlineStr"/>
-      <c r="P169" s="4" t="inlineStr"/>
-      <c r="Q169" s="4" t="inlineStr"/>
+      <c r="K169" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/FIC-FIA-Brasil-Acoes-Livres/Paginas/default.aspx</t>
+        </is>
+      </c>
+      <c r="L169" s="4" t="inlineStr">
+        <is>
+          <t>30.068.169/0001-44</t>
+        </is>
+      </c>
+      <c r="M169" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="N169" s="4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O169" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P169" s="4" t="inlineStr">
+        <is>
+          <t>D+13 (du)</t>
+        </is>
+      </c>
+      <c r="Q169" s="4" t="inlineStr">
+        <is>
+          <t>D+15 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -12510,12 +14882,32 @@
           <t>https://www.caixa.gov.br/fundos-investimento/rpps/caixa-fic-acoes-vinci-valor-dividendos-rpps</t>
         </is>
       </c>
-      <c r="L170" s="2" t="inlineStr"/>
-      <c r="M170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>15.154.441/0001-15</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
       <c r="N170" s="2" t="inlineStr"/>
-      <c r="O170" s="2" t="inlineStr"/>
-      <c r="P170" s="2" t="inlineStr"/>
-      <c r="Q170" s="2" t="inlineStr"/>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>D+30 (du)</t>
+        </is>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>D+32 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -12573,12 +14965,32 @@
           <t>https://www.caixa.gov.br/fundos-investimento/rpps/caixa-fic-acoes-vinci-valor-rpps</t>
         </is>
       </c>
-      <c r="L171" s="4" t="inlineStr"/>
-      <c r="M171" s="4" t="inlineStr"/>
+      <c r="L171" s="4" t="inlineStr">
+        <is>
+          <t>14.507.699/0001-95</t>
+        </is>
+      </c>
+      <c r="M171" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
       <c r="N171" s="4" t="inlineStr"/>
-      <c r="O171" s="4" t="inlineStr"/>
-      <c r="P171" s="4" t="inlineStr"/>
-      <c r="Q171" s="4" t="inlineStr"/>
+      <c r="O171" s="4" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P171" s="4" t="inlineStr">
+        <is>
+          <t>D+21 (du)</t>
+        </is>
+      </c>
+      <c r="Q171" s="4" t="inlineStr">
+        <is>
+          <t>D+23 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,24556000</t>
+          <t>2,24764800</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -602,22 +602,22 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,60</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>4,50</t>
+          <t>4,60</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>12,87</t>
+          <t>12,86</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>406,837</t>
+          <t>408,767</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,45820400</t>
+          <t>5,46319100</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -665,12 +665,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>4,51</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.629,297</t>
+          <t>6.700,549</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,75595500</t>
+          <t>2,75847300</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>4,50</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>811,787</t>
+          <t>845,264</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -829,32 +829,32 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>3,30389000</t>
+          <t>3,30754800</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>4,85</t>
+          <t>4,97</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>14,06</t>
+          <t>14,07</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>11,439</t>
+          <t>11,463</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -892,32 +892,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,45704200</t>
+          <t>3,46093600</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>4,97</t>
+          <t>5,09</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>14,33</t>
+          <t>14,34</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>120,094</t>
+          <t>120,201</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -979,32 +979,32 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1.819,03255500</t>
+          <t>1.821,34614500</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,067</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>4,97</t>
+          <t>5,10</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>14,63</t>
+          <t>14,64</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>96,187</t>
+          <t>96,311</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>40.194.309/0001-84</t>
+          <t>40.194.314/0001-97</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,62709400</t>
+          <t>9,63708600</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>4,65</t>
+          <t>4,76</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>584,771</t>
+          <t>584,748</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3,32772600</t>
+          <t>3,33138500</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>4,95</t>
+          <t>5,06</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>61,791</t>
+          <t>61,782</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,97017700</t>
+          <t>2,97371100</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1250,22 +1250,22 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>5,10</t>
+          <t>5,22</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>14,80</t>
+          <t>14,81</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1.670,827</t>
+          <t>1.675,653</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1299,32 +1299,32 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>19,68278100</t>
+          <t>19,75538100</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>0,196</t>
+          <t>0,489</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>-0,45</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>11,36</t>
+          <t>11,60</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>125,061</t>
+          <t>123,200</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1386,32 +1386,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,43352200</t>
+          <t>13,45298300</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>0,154</t>
+          <t>0,152</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>4,46</t>
+          <t>4,61</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>9,45</t>
+          <t>9,42</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,463</t>
+          <t>28,390</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>45,78701200</t>
+          <t>45,83440800</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>4,64</t>
+          <t>4,75</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>40,607</t>
+          <t>40,639</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20,05782200</t>
+          <t>20,07688500</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>4,57</t>
+          <t>4,67</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,649</t>
+          <t>64,695</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1647,22 +1647,22 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>3,12688100</t>
+          <t>3,13162100</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>0,138</t>
+          <t>0,139</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>5,43</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>79,801</t>
+          <t>79,934</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14,83252100</t>
+          <t>14,84797200</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>4,67</t>
+          <t>4,78</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,903</t>
+          <t>27,928</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1821,22 +1821,22 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2,97621300</t>
+          <t>2,97922700</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>4,54</t>
+          <t>4,64</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>1,653</t>
+          <t>1,654</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1908,32 +1908,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,28286000</t>
+          <t>3,29411600</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>0,189</t>
+          <t>0,461</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>3,00</t>
+          <t>3,35</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>11,90</t>
+          <t>12,14</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>140,482</t>
+          <t>139,590</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1995,32 +1995,32 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,01269400</t>
+          <t>3,01613500</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>5,10</t>
+          <t>5,22</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>14,75</t>
+          <t>14,76</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1.734,896</t>
+          <t>1.767,260</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2082,22 +2082,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32,51576800</t>
+          <t>32,55052300</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>4,80</t>
+          <t>4,91</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2.196,070</t>
+          <t>2.185,792</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2169,22 +2169,22 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,27794600</t>
+          <t>3,28145400</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>4,81</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>13,219</t>
+          <t>13,222</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2256,32 +2256,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3,33051200</t>
+          <t>3,32718700</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0,170</t>
+          <t>0,179</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,34</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>4,50</t>
+          <t>4,39</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>9,88</t>
+          <t>9,63</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,680</t>
+          <t>66,794</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>18,87399600</t>
+          <t>18,89505900</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2353,22 +2353,22 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>4,92</t>
+          <t>5,03</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>14,18</t>
+          <t>14,19</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>957,116</t>
+          <t>957,765</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2402,32 +2402,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,10690359</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>-0,001</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>-0,28</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>2,61</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>219,015</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2489,32 +2489,32 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1,22875500</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>-0,001</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>0,67</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>4,91</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>14,63</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>71,020</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1.815,33357400</t>
+          <t>1.817,55644800</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0,065</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>5,05</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>14,77</t>
+          <t>14,79</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>175,289</t>
+          <t>175,416</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2639,32 +2639,32 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1,19389700</t>
+          <t>1,19523300</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>0,095</t>
+          <t>0,064</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>6,23</t>
+          <t>6,35</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>12,53</t>
+          <t>12,51</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>40,101</t>
+          <t>40,146</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2726,32 +2726,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,02989600</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>-0,001</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>0,57</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>5,03</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,779</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2809,32 +2809,32 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,15649400</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>-0,001</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>4,14</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>13,74</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>66,386</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2892,32 +2892,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,05921761</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>0,129</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>0,45</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>2,50</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>333,022</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3058,32 +3058,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>5,09466900</t>
+          <t>5,10086800</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,065</t>
+          <t>0,058</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>5,21</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>14,82</t>
+          <t>14,83</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>860,185</t>
+          <t>860,762</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>4,90222200</t>
+          <t>4,90789100</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>0,057</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>5,09</t>
+          <t>5,21</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>14,74</t>
+          <t>14,75</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.240,628</t>
+          <t>3.242,462</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>29,02485300</t>
+          <t>29,05288200</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>4,66</t>
+          <t>4,76</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,206</t>
+          <t>21,210</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>30,35428000</t>
+          <t>30,38876700</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -3329,22 +3329,22 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>5,13</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>14,47</t>
+          <t>14,48</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>3.115,478</t>
+          <t>3.114,068</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1.758,84767700</t>
+          <t>1.762,02763700</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0,082</t>
+          <t>0,138</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>4,60</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>13,58</t>
+          <t>13,60</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>124,785</t>
+          <t>126,456</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>3,19549800</t>
+          <t>3,19891800</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>5,15</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>554,168</t>
+          <t>563,619</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>6,13751100</t>
+          <t>6,14437600</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -3590,22 +3590,22 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>4,93</t>
+          <t>5,05</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>14,22</t>
+          <t>14,23</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>123,303</t>
+          <t>123,323</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -3667,32 +3667,32 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1,25812300</t>
+          <t>1,25960200</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>0,058</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>5,30</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>14,99</t>
+          <t>15,00</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>334,883</t>
+          <t>334,495</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>10,50456600</t>
+          <t>10,51665300</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -3764,22 +3764,22 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>5,21</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>14,68</t>
+          <t>14,69</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2.379,736</t>
+          <t>2.385,058</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -3841,22 +3841,22 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>5,47049600</t>
+          <t>5,47678100</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>5,30</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>553,638</t>
+          <t>554,857</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -3928,32 +3928,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3,53695200</t>
+          <t>3,54109800</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0,057</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>14,97</t>
+          <t>14,99</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15.496,701</t>
+          <t>15.512,915</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>5,25618000</t>
+          <t>5,26290800</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -4025,22 +4025,22 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>5,21</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>15,20</t>
+          <t>15,21</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>1.384,319</t>
+          <t>1.385,487</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>30,10569200</t>
+          <t>30,13470100</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>4,62</t>
+          <t>4,72</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>165,499</t>
+          <t>165,497</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2,78811100</t>
+          <t>2,79074300</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>4,56</t>
+          <t>4,66</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5.924,364</t>
+          <t>5.972,051</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>3,57547900</t>
+          <t>3,57938200</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -4369,22 +4369,22 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>4,97</t>
+          <t>5,09</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>14,32</t>
+          <t>14,33</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>2.188,366</t>
+          <t>2.188,933</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -4446,22 +4446,22 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1,27999600</t>
+          <t>1,28136400</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>5,12</t>
+          <t>5,24</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>66,576</t>
+          <t>66,490</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>9,60521600</t>
+          <t>9,61577000</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -4543,22 +4543,22 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>14,42</t>
+          <t>14,43</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>839,055</t>
+          <t>839,017</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -4620,32 +4620,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>4,42035900</t>
+          <t>4,42503000</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>5,07</t>
+          <t>5,18</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>14,54</t>
+          <t>14,53</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15.604,543</t>
+          <t>15.699,666</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -4707,32 +4707,32 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>4,73417400</t>
+          <t>4,73949100</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>5,12</t>
+          <t>5,24</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>14,77</t>
+          <t>14,78</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>9.458,177</t>
+          <t>9.461,521</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>5,05880200</t>
+          <t>5,06445200</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>5,14</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>20.871,193</t>
+          <t>20.901,433</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>3,15949900</t>
+          <t>3,16308500</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>5,30</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>13.180,422</t>
+          <t>13.242,121</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1.716,23166900</t>
+          <t>1.717,99116900</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>4,94</t>
+          <t>5,05</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>247,593</t>
+          <t>250,114</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -4982,12 +4982,36 @@
           <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-automatico-polis-rf-cp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr"/>
-      <c r="O54" s="2" t="inlineStr"/>
-      <c r="P54" s="2" t="inlineStr"/>
-      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>39.594.941/0001-36</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -5007,32 +5031,32 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1,40124000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>0,000</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>4,65</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>14,20</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>68,957</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -5094,32 +5118,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1.184,48070500</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>-0,003</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>3,05</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>-5,60</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>-1,37</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>36,286</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -5181,32 +5205,32 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>12,57805500</t>
+          <t>12,61200400</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>0,117</t>
+          <t>0,714</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>-1,27</t>
+          <t>-1,00</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>5,96</t>
+          <t>6,24</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>17,33</t>
+          <t>17,32</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>540,035</t>
+          <t>328,777</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -5244,32 +5268,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1.629,68841700</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>0,142</t>
-        </is>
-      </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>-0,37</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>13,03</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>116,615</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -5284,7 +5308,7 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>34.660.276/0001-18</t>
+          <t>34.660.333/0001-69</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -5331,32 +5355,32 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>2.418,57883500</t>
+          <t>2.428,02903800</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>1,196</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>-0,26</t>
+          <t>0,839</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>0,12</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>17,74</t>
+          <t>18,20</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>38,11</t>
+          <t>38,71</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>13,479</t>
+          <t>13,602</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -5501,32 +5525,32 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1,24772700</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>-0,005</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>-0,63</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>2,16</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>11,12</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>6,403</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -5588,32 +5612,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1,12991900</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>-0,274</t>
+          <t>1,15213700</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>2,644</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>-6,62</t>
+          <t>-4,78</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>-2,54</t>
+          <t>-0,63</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>13,70</t>
+          <t>15,13</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>3,423</t>
+          <t>3,496</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -5758,32 +5782,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1,43001400</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>-0,004</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>-2,63</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>4,75</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>19,49</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>11,883</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -5928,32 +5952,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1,10072200</t>
+          <t>1,09835000</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>-0,989</t>
+          <t>-0,511</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>-8,70</t>
+          <t>-8,90</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>-6,09</t>
+          <t>-7,43</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>3,163</t>
+          <t>3,682</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -6015,32 +6039,32 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>5,31548829</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>0,143</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>-0,30</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>3,59</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>12,87</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>33,112</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -6102,32 +6126,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>4,74467200</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>-0,036</t>
+          <t>4,72624300</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>0,582</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>-0,97</t>
+          <t>-1,36</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>6,78</t>
+          <t>6,37</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>50,60</t>
+          <t>45,45</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>665,006</t>
+          <t>661,651</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -6189,32 +6213,32 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>2,84399200</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>-0,004</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>-0,30</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>10,78</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>76,852</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -6276,32 +6300,32 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1.655,00410000</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>0,190</t>
+          <t>1.658,58650000</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>-0,590</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>11,68</t>
+          <t>11,71</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>32,160</t>
+          <t>32,246</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -6363,32 +6387,32 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>3,72710300</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>-0,045</t>
+          <t>3,74402200</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>1,080</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>3,00</t>
+          <t>3,46</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>10,79</t>
+          <t>11,29</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>35,62</t>
+          <t>36,47</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>2.329,591</t>
+          <t>2.341,201</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -6450,32 +6474,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1,89457400</t>
+          <t>1,89794100</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>0,101</t>
+          <t>0,148</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>4,40</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>12,93</t>
+          <t>12,97</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>21,810</t>
+          <t>21,918</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -6537,32 +6561,32 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1.650,19240600</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>0,141</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>-0,32</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>4,34</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>13,99</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>14,891</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -6620,32 +6644,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>0,56802624</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>-0,007</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>4,70</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr">
-        <is>
-          <t>-21,33</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>4,140</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -6707,32 +6731,32 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>3,23930700</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>0,165</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>0,67</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>1,66</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>6,61</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>154,351</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -6747,7 +6771,7 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>14.239.659/0001-00</t>
+          <t>45.443.651/0001-94</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
@@ -6757,7 +6781,7 @@
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
@@ -6767,12 +6791,12 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>D+1 (du)</t>
+          <t>D+0 (du)</t>
         </is>
       </c>
       <c r="Q75" s="4" t="inlineStr">
         <is>
-          <t>D+03 (du)</t>
+          <t>D+02 (du)</t>
         </is>
       </c>
     </row>
@@ -6794,32 +6818,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1,53509800</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>0,208</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>0,10</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t>2,81</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>19,12</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>14,530</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -6881,32 +6905,32 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1,37606700</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>0,051</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>-1,54</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>1,46</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>8,02</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>70,634</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -6968,32 +6992,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1,47262900</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>-0,359</t>
-        </is>
-      </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>1,54</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>14,29</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>191,031</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -7003,7 +7027,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fim-cap-protegido-ciclico-ii</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fic-capital-protegido-ciclico-ii-multimercado-lp/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -7055,32 +7079,32 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1,77458400</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>-0,002</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>0,45</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>10,71</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>176,645</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -7142,32 +7166,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>5,58029600</t>
+          <t>5,59555300</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>0,114</t>
+          <t>0,407</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>5,01</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>14,46</t>
+          <t>14,63</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>899,316</t>
+          <t>901,638</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -7229,32 +7253,32 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>3,62987100</t>
+          <t>3,63643100</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>0,102</t>
+          <t>0,150</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,60</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>4,55</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>13,34</t>
+          <t>13,38</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>749,433</t>
+          <t>750,198</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -7316,32 +7340,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>6,78407000</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>-0,003</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="inlineStr">
-        <is>
-          <t>5,48</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>16,67</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>129,574</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -7403,32 +7427,32 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>1,40154200</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>-0,003</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>15,08</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>277,091</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -7490,32 +7514,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,30887200</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>-0,001</t>
-        </is>
-      </c>
-      <c r="F84" s="7" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>1,97</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>2,02</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>13,313</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -7577,32 +7601,32 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>3,73135500</t>
+          <t>3,72402400</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>-1,100</t>
+          <t>-0,737</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>1,27</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>-7,17</t>
+          <t>-7,35</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>-7,39</t>
+          <t>-7,81</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>96,463</t>
+          <t>96,249</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -7664,32 +7688,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>6,74316500</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>-0,193</t>
+          <t>6,77843700</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>1,910</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>-5,71</t>
+          <t>-5,22</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>6,31</t>
+          <t>6,87</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>21,35</t>
+          <t>20,94</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>346,462</t>
+          <t>348,240</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -7751,32 +7775,32 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>2,63050200</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>-0,192</t>
+          <t>2,63642800</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>1,754</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>-5,44</t>
+          <t>-5,23</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>9,32</t>
+          <t>9,57</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>25,94</t>
+          <t>25,43</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>13,657</t>
+          <t>13,700</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -7838,32 +7862,32 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1.923,33015000</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>-0,323</t>
+          <t>1.965,52409700</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>3,824</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>-7,52</t>
+          <t>-5,49</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>-3,11</t>
+          <t>-0,98</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>14,16</t>
+          <t>15,50</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>10,257</t>
+          <t>10,477</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -7921,32 +7945,32 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>9,87331500</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>-1,741</t>
+          <t>9,94323300</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>0,409</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>4,79</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>-0,28</t>
+          <t>5,53</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>0,41</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>18,01</t>
+          <t>18,88</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>272,499</t>
+          <t>273,943</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -8008,32 +8032,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1,46431500</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>-0,230</t>
+          <t>1,49434700</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>3,862</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>-4,35</t>
+          <t>-2,39</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>-3,94</t>
+          <t>-1,97</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>444,892</t>
+          <t>453,998</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -8095,32 +8119,32 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1,10617000</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>-0,446</t>
+          <t>1,13223300</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>3,937</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>-3,63</t>
+          <t>-1,36</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>-4,96</t>
+          <t>-2,72</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-0,31</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>57,923</t>
+          <t>59,264</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -8182,32 +8206,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1,73227600</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>-0,367</t>
+          <t>1,75185800</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>2,937</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>-6,71</t>
+          <t>-5,66</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>2,77</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>12,07</t>
+          <t>12,56</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2,275</t>
+          <t>2,198</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -8269,32 +8293,32 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>4,99885300</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>2,607</t>
+          <t>4,79629500</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>-3,825</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>-5,34</t>
+          <t>-9,17</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>58,73</t>
+          <t>52,30</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>61,52</t>
+          <t>54,90</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>85,299</t>
+          <t>81,643</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -8356,32 +8380,32 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>8,81868300</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>-0,197</t>
+          <t>8,83778400</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>1,749</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>-5,48</t>
+          <t>-5,28</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>8,91</t>
+          <t>9,15</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>24,59</t>
+          <t>24,08</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>92,212</t>
+          <t>92,330</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -8443,32 +8467,32 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1,28730000</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>-0,026</t>
-        </is>
-      </c>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>-5,73</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="H95" s="5" t="inlineStr">
-        <is>
-          <t>9,44</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>292,330</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -8530,32 +8554,32 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>1,82255400</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>-0,553</t>
+          <t>1,87928700</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>4,435</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>-5,02</t>
+          <t>-2,06</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>-4,14</t>
+          <t>-1,16</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>16,36</t>
+          <t>18,29</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>113,388</t>
+          <t>116,775</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -8617,32 +8641,32 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>2,99704100</t>
+          <t>3,02099200</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>0,175</t>
+          <t>2,082</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>-6,92</t>
+          <t>-6,18</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>9,96</t>
+          <t>10,84</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>23,08</t>
+          <t>22,94</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>133,683</t>
+          <t>134,718</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -8704,32 +8728,32 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1,86995400</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>-0,327</t>
+          <t>1,91075600</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>3,814</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>-7,55</t>
+          <t>-5,54</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>-3,49</t>
+          <t>-1,38</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>12,92</t>
+          <t>14,21</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>47,483</t>
+          <t>48,519</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -8791,32 +8815,32 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>7,09103500</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>2,090</t>
+          <t>6,81300400</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>-3,198</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>-5,29</t>
+          <t>-9,01</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>51,18</t>
+          <t>45,25</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>57,06</t>
+          <t>50,49</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>132,545</t>
+          <t>127,490</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -8878,32 +8902,32 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>1.281,15013800</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>-1,352</t>
+          <t>1.298,50084500</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>2,307</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>-8,08</t>
+          <t>-6,83</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>-6,28</t>
+          <t>-5,01</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>-18,67</t>
+          <t>-17,01</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>40,878</t>
+          <t>41,697</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -8965,32 +8989,32 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>38,76144700</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>-2,000</t>
+          <t>38,83590000</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>1,198</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>12,19</t>
+          <t>12,41</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>55,90</t>
+          <t>56,62</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>663,484</t>
+          <t>664,541</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -9052,32 +9076,32 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2,67079200</t>
+          <t>2,71903500</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>1,315</t>
-        </is>
-      </c>
-      <c r="F102" s="7" t="inlineStr">
-        <is>
-          <t>-0,76</t>
+          <t>2,326</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>1,03</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>12,24</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>24,41</t>
+          <t>25,44</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>446,133</t>
+          <t>454,125</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -9139,32 +9163,32 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>4,85455100</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>-0,240</t>
+          <t>4,87282400</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>2,056</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>-5,58</t>
+          <t>-5,22</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>8,17</t>
+          <t>8,58</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>25,74</t>
+          <t>25,39</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>23,548</t>
+          <t>23,637</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -9226,32 +9250,32 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>1.503,93690500</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>-0,265</t>
+          <t>1.514,92425700</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>2,952</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>-7,23</t>
+          <t>-6,55</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>3,34</t>
+          <t>4,09</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>14,27</t>
+          <t>14,11</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>30,100</t>
+          <t>30,313</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -9313,32 +9337,32 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>1,94571700</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>-0,416</t>
+          <t>1,97421400</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>3,117</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>-5,07</t>
+          <t>-3,68</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>-4,36</t>
+          <t>-2,95</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>10,16</t>
+          <t>10,96</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>1,785</t>
+          <t>1,811</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -9400,32 +9424,32 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>5,96780200</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>-0,172</t>
+          <t>5,98843100</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>1,686</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>-5,61</t>
+          <t>-5,29</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>10,93</t>
+          <t>11,32</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>28,01</t>
+          <t>27,44</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>44,328</t>
+          <t>44,492</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -9487,32 +9511,32 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>2,25669400</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>-0,342</t>
+          <t>2,26435400</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>2,012</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>-4,01</t>
+          <t>-3,68</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>7,55</t>
+          <t>7,91</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>24,76</t>
+          <t>24,39</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>36,357</t>
+          <t>36,459</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -9574,32 +9598,32 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>46,35504100</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>2,604</t>
+          <t>44,48042100</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>-3,817</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>-5,34</t>
+          <t>-9,17</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>58,77</t>
+          <t>52,35</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>61,63</t>
+          <t>55,02</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>933,285</t>
+          <t>895,431</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -9661,32 +9685,32 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>0,88476400</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>-0,431</t>
+          <t>0,89138100</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>2,801</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>-3,72</t>
+          <t>-3,00</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>-8,08</t>
+          <t>-7,39</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>-15,85</t>
+          <t>-15,50</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>2,980</t>
+          <t>3,004</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -9748,32 +9772,32 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>1,18091200</t>
-        </is>
-      </c>
-      <c r="E110" s="7" t="inlineStr">
-        <is>
-          <t>-1,349</t>
+          <t>1,19678200</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>1,872</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>-1,37</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>-2,41</t>
+          <t>-1,10</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>11,92</t>
+          <t>13,12</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>3,852</t>
+          <t>3,903</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -9835,32 +9859,32 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>1,31951300</t>
+          <t>1,34335600</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>1,316</t>
-        </is>
-      </c>
-      <c r="F111" s="6" t="inlineStr">
-        <is>
-          <t>-0,76</t>
+          <t>2,328</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>1,02</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>10,19</t>
+          <t>12,18</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>24,24</t>
+          <t>25,27</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>19,645</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -9922,32 +9946,32 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1,83882700</t>
-        </is>
-      </c>
-      <c r="E112" s="7" t="inlineStr">
-        <is>
-          <t>-0,669</t>
+          <t>1,86202400</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>2,189</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>-12,43</t>
+          <t>-11,33</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>6,96</t>
+          <t>8,31</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>73,37</t>
+          <t>75,72</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>267,114</t>
+          <t>270,616</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -10009,32 +10033,32 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>1.011,71107700</t>
-        </is>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
-        <is>
-          <t>-0,003</t>
-        </is>
-      </c>
-      <c r="F113" s="6" t="inlineStr">
-        <is>
-          <t>-5,44</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>3,19</t>
-        </is>
-      </c>
-      <c r="H113" s="5" t="inlineStr">
-        <is>
-          <t>18,63</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>8,117</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -10096,32 +10120,32 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1.528,26037500</t>
-        </is>
-      </c>
-      <c r="E114" s="7" t="inlineStr">
-        <is>
-          <t>-0,002</t>
-        </is>
-      </c>
-      <c r="F114" s="7" t="inlineStr">
-        <is>
-          <t>-5,00</t>
-        </is>
-      </c>
-      <c r="G114" s="3" t="inlineStr">
-        <is>
-          <t>2,17</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>14,02</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>22,256</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -10183,32 +10207,32 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>172,64302960</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>-0,192</t>
+          <t>173,00144700</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>1,730</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>-5,42</t>
+          <t>-5,22</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>9,56</t>
+          <t>9,78</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>26,59</t>
+          <t>26,04</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>43,162</t>
+          <t>43,252</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -10246,32 +10270,32 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1,87984000</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="inlineStr">
-        <is>
-          <t>-0,654</t>
+          <t>1,90346500</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>2,172</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>-12,39</t>
+          <t>-11,28</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>7,06</t>
+          <t>8,41</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>73,73</t>
+          <t>76,09</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>5,110</t>
+          <t>5,174</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -10333,32 +10357,32 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1,83352000</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>-0,656</t>
+          <t>1,85673400</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>2,185</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>-12,44</t>
+          <t>-11,33</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>7,10</t>
+          <t>8,46</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>73,83</t>
+          <t>76,20</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>1.679,222</t>
+          <t>1.699,797</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -10420,32 +10444,32 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>51,56080700</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>2,614</t>
+          <t>49,47753300</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>-3,816</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>-5,33</t>
+          <t>-9,15</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>59,20</t>
+          <t>52,76</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>62,57</t>
+          <t>55,92</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>749,041</t>
+          <t>718,564</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -10507,32 +10531,32 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>42,93658200</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>-2,001</t>
+          <t>43,02165500</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>1,203</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>12,41</t>
+          <t>12,63</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>56,76</t>
+          <t>57,48</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>780,554</t>
+          <t>780,981</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -10594,32 +10618,32 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>16,46934500</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="inlineStr">
-        <is>
-          <t>-0,285</t>
+          <t>16,82967500</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>3,786</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>-7,12</t>
+          <t>-5,09</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>-2,35</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>15,55</t>
+          <t>17,21</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>114,165</t>
+          <t>116,640</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -10681,32 +10705,32 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>36,00806200</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>-1,992</t>
+          <t>36,07689700</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>1,194</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>0,70</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>12,21</t>
+          <t>12,43</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>55,66</t>
+          <t>56,37</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>11,781</t>
+          <t>11,803</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
@@ -10768,32 +10792,32 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>45,56491500</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>2,611</t>
+          <t>43,72069300</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>-3,821</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>-5,34</t>
+          <t>-9,17</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>58,92</t>
+          <t>52,49</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>61,82</t>
+          <t>55,20</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>648,868</t>
+          <t>622,111</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -10855,32 +10879,32 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>36,97364600</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
-          <t>-2,003</t>
+          <t>37,04497900</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>1,200</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>12,20</t>
+          <t>12,42</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>55,91</t>
+          <t>56,63</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>467,099</t>
+          <t>467,903</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -10942,32 +10966,32 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>48,44390500</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>2,613</t>
+          <t>46,48517400</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>-3,818</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>-5,32</t>
+          <t>-9,15</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>59,08</t>
+          <t>52,65</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>62,19</t>
+          <t>55,56</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>746,715</t>
+          <t>715,726</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -11029,7 +11053,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>1,11811700</t>
+          <t>1,11916800</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -11039,12 +11063,12 @@
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>4,50</t>
+          <t>4,60</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -11054,7 +11078,7 @@
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>52,259</t>
+          <t>55,647</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
@@ -11116,7 +11140,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>1,34935900</t>
+          <t>1,35063300</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -11126,22 +11150,22 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>4,65</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>13,05</t>
+          <t>13,04</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>201,906</t>
+          <t>259,442</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -11179,22 +11203,22 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>5,84855000</t>
+          <t>5,85498700</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>4,96</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -11204,7 +11228,7 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>41,420</t>
+          <t>41,501</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -11266,7 +11290,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>5,09001200</t>
+          <t>5,09536000</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -11276,22 +11300,22 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>5,07</t>
+          <t>5,18</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>14,52</t>
+          <t>14,51</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>788,405</t>
+          <t>789,234</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -11353,22 +11377,22 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>3,19799800</t>
+          <t>3,20128000</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>4,93</t>
+          <t>5,04</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -11378,7 +11402,7 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>18,060</t>
+          <t>18,648</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -11440,32 +11464,32 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>23,63009800</t>
+          <t>23,66721400</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>0,140</t>
+          <t>0,142</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>5,71</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>11,38</t>
+          <t>11,39</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>94,520</t>
+          <t>94,669</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -11527,7 +11551,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>3,25229500</t>
+          <t>3,25564800</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -11537,22 +11561,22 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>4,98</t>
+          <t>5,08</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>14,28</t>
+          <t>14,27</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>7.774,671</t>
+          <t>7.835,830</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -11614,32 +11638,32 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>1.872,93507200</t>
+          <t>1.875,19334500</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>5,21</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>15,11</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>15.212,879</t>
+          <t>15.313,366</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -11701,22 +11725,22 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>4,84743600</t>
+          <t>4,85296300</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,061</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -11726,7 +11750,7 @@
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>3.069,410</t>
+          <t>3.070,621</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -11788,7 +11812,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1,53913499</t>
+          <t>1,54075600</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -11798,22 +11822,22 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>5,14</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>14,77</t>
+          <t>14,76</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>339,466</t>
+          <t>339,824</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -11875,7 +11899,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>5,09124400</t>
+          <t>5,09668800</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -11885,12 +11909,12 @@
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>5,28</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -11900,7 +11924,7 @@
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>283,780</t>
+          <t>284,084</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -11962,22 +11986,22 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>8,65382400</t>
+          <t>8,66379100</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,062</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>5,20</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
@@ -11987,7 +12011,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>3.989,571</t>
+          <t>3.992,325</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -12049,22 +12073,22 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>17,79990200</t>
+          <t>17,82024600</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,061</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -12074,7 +12098,7 @@
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>4.808,036</t>
+          <t>4.804,684</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -12132,22 +12156,22 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>2,80856600</t>
+          <t>2,81126200</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>4,63</t>
+          <t>4,74</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
@@ -12157,7 +12181,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>13.360,062</t>
+          <t>13.566,613</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -12219,22 +12243,22 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>4,39983400</t>
+          <t>4,40457400</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>5,17</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -12244,7 +12268,7 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>12.332,325</t>
+          <t>12.375,346</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -12306,22 +12330,22 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>1,36516000</t>
+          <t>1,36662300</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>5,23</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
@@ -12331,7 +12355,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.786,443</t>
+          <t>3.666,369</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -12393,7 +12417,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>1.761,17403600</t>
+          <t>1.763,03462300</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -12403,12 +12427,12 @@
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>5,09</t>
+          <t>5,20</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -12418,7 +12442,7 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>1.429,917</t>
+          <t>1.430,664</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -12480,7 +12504,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>1,30118900</t>
+          <t>1,30231400</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -12490,12 +12514,12 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>4,16</t>
+          <t>4,25</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
@@ -12505,7 +12529,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>33.651,181</t>
+          <t>33.953,808</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -12567,7 +12591,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>9,35110000</t>
+          <t>9,35977100</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -12577,12 +12601,12 @@
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,60</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>4,47</t>
+          <t>4,56</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
@@ -12592,7 +12616,7 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>2.890,863</t>
+          <t>2.916,225</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
@@ -12654,22 +12678,22 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>2,46274400</t>
+          <t>2,46500500</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>4,47</t>
+          <t>4,56</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
@@ -12679,7 +12703,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>15.151,461</t>
+          <t>15.132,079</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -12717,32 +12741,32 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>2,58940600</t>
+          <t>2,59243400</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,059</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>5,14</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>14,80</t>
+          <t>14,81</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>9.188,681</t>
+          <t>9.333,484</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
@@ -12804,32 +12828,32 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>2,38780600</t>
+          <t>2,39502700</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>0,168</t>
+          <t>0,340</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>3,99</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>12,29</t>
+          <t>12,43</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>3.754,188</t>
+          <t>3.769,405</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -12891,32 +12915,32 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>2,97184700</t>
+          <t>2,97646000</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>0,163</t>
+          <t>0,160</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>11,46</t>
+          <t>11,43</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>41,613</t>
+          <t>41,678</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
@@ -12978,32 +13002,32 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1.631,89638200</t>
+          <t>1.635,30747600</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>0,107</t>
+          <t>0,186</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>3,98</t>
+          <t>4,19</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>11,16</t>
+          <t>11,21</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>457,773</t>
+          <t>458,730</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -13065,32 +13089,32 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>4,44847900</t>
+          <t>4,45461800</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>0,075</t>
+          <t>0,084</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>4,98</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>14,22</t>
+          <t>14,25</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>11.007,969</t>
+          <t>11.083,199</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
@@ -13105,7 +13129,7 @@
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t>10.740.670/0001-06</t>
+          <t>14.508.605/0001-00</t>
         </is>
       </c>
       <c r="M149" s="4" t="inlineStr">
@@ -13152,32 +13176,32 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>3,80211600</t>
+          <t>3,80968400</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>0,135</t>
+          <t>0,157</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>5,62</t>
+          <t>5,83</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>11,73</t>
+          <t>11,78</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2.961,910</t>
+          <t>2.967,990</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -13215,32 +13239,32 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>3,60143300</t>
+          <t>3,61394200</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>0,191</t>
+          <t>0,462</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-0,01</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>3,16</t>
+          <t>3,52</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>12,46</t>
+          <t>12,69</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>1.726,187</t>
+          <t>1.733,233</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
@@ -13255,7 +13279,7 @@
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t>10.740.670/0001-06</t>
+          <t>14.508.605/0001-00</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
@@ -13302,32 +13326,32 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>5,13759900</t>
+          <t>5,13246600</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>0,153</t>
+          <t>0,171</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,37</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>4,48</t>
+          <t>4,38</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>10,12</t>
+          <t>9,81</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2.561,152</t>
+          <t>2.560,830</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -13342,7 +13366,7 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>10.740.658/0001-93</t>
+          <t>10.577.503/0001-88</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
@@ -13389,22 +13413,22 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>5,15550800</t>
+          <t>5,16358400</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>0,149</t>
+          <t>0,142</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>5,60</t>
+          <t>5,77</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
@@ -13414,7 +13438,7 @@
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>5.434,253</t>
+          <t>5.445,155</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
@@ -13429,7 +13453,7 @@
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
-          <t>10.740.658/0001-93</t>
+          <t>10.577.503/0001-88</t>
         </is>
       </c>
       <c r="M153" s="4" t="inlineStr">
@@ -13476,32 +13500,32 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>4,71913100</t>
+          <t>4,72426000</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>0,108</t>
+          <t>0,173</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>4,66</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>13,12</t>
+          <t>13,08</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>512,895</t>
+          <t>513,753</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -13563,22 +13587,22 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>7,89629100</t>
+          <t>7,90550900</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>0,057</t>
+          <t>0,064</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>5,09</t>
+          <t>5,21</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
@@ -13588,7 +13612,7 @@
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>166,066</t>
+          <t>166,555</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
@@ -13626,32 +13650,32 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>3,45583300</t>
+          <t>3,44574300</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>0,146</t>
+          <t>0,209</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>-0,82</t>
+          <t>-1,10</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>3,58</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>8,98</t>
+          <t>8,45</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>824,894</t>
+          <t>822,485</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -13666,7 +13690,7 @@
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>10.740.658/0001-93</t>
+          <t>10.577.503/0001-88</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
@@ -13713,32 +13737,32 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>3,72953400</t>
+          <t>3,74554900</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>0,236</t>
+          <t>0,611</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>-0,70</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>2,55</t>
+          <t>2,99</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>11,77</t>
+          <t>12,08</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>713,304</t>
+          <t>716,984</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
@@ -13753,7 +13777,7 @@
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>10.740.670/0001-06</t>
+          <t>14.508.605/0001-00</t>
         </is>
       </c>
       <c r="M157" s="4" t="inlineStr">
@@ -13800,22 +13824,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>7,12662600</t>
+          <t>7,13459000</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,058</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>5,11</t>
+          <t>5,23</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
@@ -13825,7 +13849,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>12.892,224</t>
+          <t>12.881,048</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -13887,7 +13911,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>7,44359700</t>
+          <t>7,45141800</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -13897,22 +13921,22 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>5,06</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>14,56</t>
+          <t>14,55</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>5.099,311</t>
+          <t>5.070,946</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -13974,32 +13998,32 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>1,43573400</t>
+          <t>1,44138200</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>0,212</t>
-        </is>
-      </c>
-      <c r="F160" s="7" t="inlineStr">
-        <is>
-          <t>-0,01</t>
+          <t>0,411</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>3,37</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>12,00</t>
+          <t>12,18</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>171,517</t>
+          <t>172,083</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
@@ -14061,32 +14085,32 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>3,12007400</t>
+          <t>3,12316000</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>4,80</t>
+          <t>4,91</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>13,68</t>
+          <t>13,67</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>1.891,061</t>
+          <t>1.834,399</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
@@ -14148,7 +14172,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>6,67411200</t>
+          <t>6,68165700</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
@@ -14158,12 +14182,12 @@
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>5,28</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
@@ -14173,7 +14197,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>24.728,488</t>
+          <t>24.576,641</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -14211,32 +14235,32 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>5,50531800</t>
+          <t>5,50009600</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>0,172</t>
+          <t>0,182</t>
         </is>
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,31</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>4,74</t>
+          <t>4,64</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>10,56</t>
+          <t>10,31</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>597,210</t>
+          <t>596,643</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
@@ -14385,32 +14409,32 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>3,96611200</t>
-        </is>
-      </c>
-      <c r="E165" s="6" t="inlineStr">
-        <is>
-          <t>-0,192</t>
+          <t>3,97519600</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>1,763</t>
         </is>
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>-5,45</t>
+          <t>-5,23</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>9,54</t>
+          <t>9,79</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>26,55</t>
+          <t>26,04</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>300,576</t>
+          <t>301,202</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
@@ -14425,7 +14449,7 @@
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
-          <t>13.058.816/0001-18</t>
+          <t>15.154.236/0001-50</t>
         </is>
       </c>
       <c r="M165" s="4" t="inlineStr">
@@ -14472,32 +14496,32 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>3,64690500</t>
-        </is>
-      </c>
-      <c r="E166" s="7" t="inlineStr">
-        <is>
-          <t>-0,138</t>
+          <t>3,65668000</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>1,787</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>-5,38</t>
+          <t>-5,13</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>9,38</t>
+          <t>9,67</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>26,16</t>
+          <t>25,67</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>9,228</t>
+          <t>9,253</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -14559,32 +14583,32 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>11,06429690</t>
-        </is>
-      </c>
-      <c r="E167" s="6" t="inlineStr">
-        <is>
-          <t>-1,739</t>
+          <t>11,14343300</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>0,412</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>4,83</t>
-        </is>
-      </c>
-      <c r="G167" s="6" t="inlineStr">
-        <is>
-          <t>-0,02</t>
+          <t>5,58</t>
+        </is>
+      </c>
+      <c r="G167" s="5" t="inlineStr">
+        <is>
+          <t>0,69</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
         <is>
-          <t>18,98</t>
+          <t>19,86</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>2.289,783</t>
+          <t>2.304,846</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
@@ -14646,32 +14670,32 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>2,04189200</t>
-        </is>
-      </c>
-      <c r="E168" s="7" t="inlineStr">
-        <is>
-          <t>-0,237</t>
+          <t>2,04993200</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>1,883</t>
         </is>
       </c>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>-5,11</t>
+          <t>-4,74</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>7,72</t>
+          <t>8,15</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>23,41</t>
+          <t>23,09</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>201,562</t>
+          <t>202,356</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -14733,32 +14757,32 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>2,00109800</t>
-        </is>
-      </c>
-      <c r="E169" s="6" t="inlineStr">
-        <is>
-          <t>-0,327</t>
+          <t>2,04482500</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>3,820</t>
         </is>
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>-7,56</t>
+          <t>-5,54</t>
         </is>
       </c>
       <c r="G169" s="6" t="inlineStr">
         <is>
-          <t>-3,48</t>
+          <t>-1,37</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
         <is>
-          <t>13,76</t>
+          <t>14,99</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>764,310</t>
+          <t>777,897</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
@@ -14820,32 +14844,32 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>3,47253284</t>
-        </is>
-      </c>
-      <c r="E170" s="7" t="inlineStr">
-        <is>
-          <t>-0,061</t>
+          <t>3,48283800</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>1,562</t>
         </is>
       </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>-5,80</t>
+          <t>-5,52</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>6,73</t>
+          <t>7,05</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>21,80</t>
+          <t>20,99</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>1.331,637</t>
+          <t>1.335,588</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -14903,32 +14927,32 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>2,54263103</t>
-        </is>
-      </c>
-      <c r="E171" s="6" t="inlineStr">
-        <is>
-          <t>-0,123</t>
+          <t>2,54853900</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>1,703</t>
         </is>
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>-6,39</t>
+          <t>-6,17</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>7,57</t>
+          <t>7,82</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>23,53</t>
+          <t>22,68</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>786,997</t>
+          <t>788,825</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
@@ -14986,32 +15010,32 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>3,72253400</t>
+          <t>3,72791800</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>0,083</t>
+          <t>0,089</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>4,83</t>
+          <t>4,99</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>14,26</t>
+          <t>14,30</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>4.934,360</t>
+          <t>5.044,594</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -94,10 +94,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -628,7 +628,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,25079100</t>
+          <t>2,25184400</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>4,74</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>12,86</t>
+          <t>12,85</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>406,754</t>
+          <t>407,232</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,47068900</t>
+          <t>5,47319100</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>4,65</t>
+          <t>4,70</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.590,423</t>
+          <t>6.603,336</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,76225700</t>
+          <t>2,76352100</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -824,22 +824,22 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>4,64</t>
+          <t>4,69</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>12,61</t>
+          <t>12,60</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>829,136</t>
+          <t>861,740</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -931,22 +931,22 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>3,31289400</t>
+          <t>3,31460400</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>5,14</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>11,489</t>
+          <t>11,569</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -1000,22 +1000,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,46649000</t>
+          <t>3,46828400</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>120,255</t>
+          <t>120,005</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1117,32 +1117,32 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1.824,50240700</t>
+          <t>1.825,48334600</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>5,28</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>14,67</t>
+          <t>14,66</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>96,475</t>
+          <t>97,079</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1234,22 +1234,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,65184500</t>
+          <t>9,65656300</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>4,92</t>
+          <t>4,97</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>585,353</t>
+          <t>584,983</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1351,22 +1351,22 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3,33679400</t>
+          <t>3,33852800</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>5,24</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>61,272</t>
+          <t>61,284</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1468,32 +1468,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,97883300</t>
+          <t>2,98041100</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>5,40</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>14,84</t>
+          <t>14,83</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1.672,391</t>
+          <t>1.674,277</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1533,32 +1533,32 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>19,88931100</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>0,409</t>
+          <t>19,85273400</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>-0,183</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>3,76</t>
+          <t>3,57</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>12,32</t>
+          <t>12,01</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>123,550</t>
+          <t>123,270</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,49370500</t>
+          <t>13,49435700</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>0,160</t>
+          <t>0,004</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>10,00</t>
+          <t>10,04</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,449</t>
+          <t>28,433</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1767,32 +1767,32 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>45,90441200</t>
+          <t>45,92679000</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0,80</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>4,91</t>
+          <t>4,96</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>13,35</t>
+          <t>13,34</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>40,677</t>
+          <t>40,697</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1884,22 +1884,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20,10582000</t>
+          <t>20,11546900</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>4,82</t>
+          <t>4,87</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,763</t>
+          <t>64,794</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>3,14039100</t>
+          <t>3,14104800</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>0,141</t>
+          <t>0,020</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>5,73</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>11,11</t>
+          <t>11,17</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>79,826</t>
+          <t>79,845</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -2118,22 +2118,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14,87079700</t>
+          <t>14,87809500</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>4,94</t>
+          <t>4,99</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,968</t>
+          <t>27,942</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2235,22 +2235,22 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2,98367600</t>
+          <t>2,98509700</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>4,80</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>1,657</t>
+          <t>1,658</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -2352,32 +2352,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,31561300</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>0,387</t>
+          <t>3,31019800</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>-0,163</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>4,03</t>
+          <t>3,86</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>12,80</t>
+          <t>12,52</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>139,951</t>
+          <t>139,764</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2469,22 +2469,22 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,02119200</t>
+          <t>3,02282300</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>5,40</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1.760,529</t>
+          <t>1.761,317</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2586,32 +2586,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32,60188400</t>
+          <t>32,61832600</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>5,13</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>13,83</t>
+          <t>13,82</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2.188,847</t>
+          <t>2.187,597</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2703,22 +2703,22 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,28663800</t>
+          <t>3,28829700</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>5,09</t>
+          <t>5,14</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>13,229</t>
+          <t>13,236</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2820,22 +2820,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3,33897500</t>
+          <t>3,34249700</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0,149</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
+          <t>0,105</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>0,11</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>4,76</t>
+          <t>4,88</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,838</t>
+          <t>66,983</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>18,92508400</t>
+          <t>18,93477900</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>5,20</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>958,155</t>
+          <t>958,430</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -3002,22 +3002,22 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,10981982</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
+          <t>1,11182293</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>-0,001</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>-0,01</t>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2,88</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>210,334</t>
+          <t>212,497</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3119,22 +3119,22 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1,23272700</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
+          <t>1,23340200</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>-0,001</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>1,00</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>70,786</t>
+          <t>70,866</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -3236,32 +3236,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1.820,75933100</t>
+          <t>1.821,75907000</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>5,42</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>14,82</t>
+          <t>14,81</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>175,373</t>
+          <t>175,323</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3305,32 +3305,32 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1,19693800</t>
+          <t>1,19801900</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,090</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>1,00</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>6,50</t>
+          <t>6,60</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>12,82</t>
+          <t>12,96</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>40,203</t>
+          <t>40,239</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -3422,22 +3422,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,03303600</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,000</t>
+          <t>1,03359700</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>5,35</t>
+          <t>5,41</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,839</t>
+          <t>21,851</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3535,32 +3535,32 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,16099200</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>0,000</t>
+          <t>1,16170700</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>4,61</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>13,84</t>
+          <t>13,85</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>66,519</t>
+          <t>66,562</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,06193675</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
+          <t>1,06332986</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>-0,001</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2,77</t>
+          <t>2,90</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>321,125</t>
+          <t>319,464</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3874,32 +3874,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>5,10959100</t>
+          <t>5,11230800</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>5,44</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>14,85</t>
+          <t>14,84</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>861,741</t>
+          <t>860,938</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>4,91618500</t>
+          <t>4,91884200</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>5,44</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.246,101</t>
+          <t>3.247,276</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>29,09497800</t>
+          <t>29,10902400</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -4118,12 +4118,12 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>4,91</t>
+          <t>4,96</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,240</t>
+          <t>21,251</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4225,22 +4225,22 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>30,43797500</t>
+          <t>30,45387500</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>5,30</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>3.114,179</t>
+          <t>3.116,203</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -4342,32 +4342,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1.765,93907400</t>
+          <t>1.766,25761100</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0,096</t>
+          <t>0,018</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>4,83</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>13,70</t>
+          <t>13,64</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>125,911</t>
+          <t>125,896</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4459,22 +4459,22 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>3,20410400</t>
+          <t>3,20583400</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>5,49</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>578,670</t>
+          <t>581,881</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -4576,32 +4576,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>6,15416300</t>
+          <t>6,15732400</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>5,21</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>14,24</t>
+          <t>14,23</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>122,530</t>
+          <t>122,585</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1,26176600</t>
+          <t>1,26246000</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>338,194</t>
+          <t>337,787</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -4810,22 +4810,22 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>10,53391300</t>
+          <t>10,53949200</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>5,43</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2.385,810</t>
+          <t>2.387,796</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4927,22 +4927,22 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>5,48572700</t>
+          <t>5,48875200</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>555,617</t>
+          <t>555,566</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -5044,32 +5044,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3,54716600</t>
+          <t>3,54911200</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>15,01</t>
+          <t>15,00</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15.528,207</t>
+          <t>15.556,492</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5161,32 +5161,32 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>5,27239100</t>
+          <t>5,27513100</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>0,060</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>5,59</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>15,23</t>
+          <t>15,22</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>1.388,431</t>
+          <t>1.388,284</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>30,17881300</t>
+          <t>30,19351400</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -5288,12 +5288,12 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>4,88</t>
+          <t>4,93</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>166,020</t>
+          <t>165,888</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2,79472600</t>
+          <t>2,79605200</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>4,81</t>
+          <t>4,86</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5.917,642</t>
+          <t>5.919,794</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5625,22 +5625,22 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>3,58503100</t>
+          <t>3,58689400</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>2.189,075</t>
+          <t>2.188,811</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -5742,22 +5742,22 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1,28344200</t>
+          <t>1,28413400</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>5,41</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>65,202</t>
+          <t>65,209</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>9,63105600</t>
+          <t>9,63609500</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>838,646</t>
+          <t>838,876</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>4,43212700</t>
+          <t>4,43449200</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>5,35</t>
+          <t>5,40</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15.735,976</t>
+          <t>15.784,652</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>4,74719600</t>
+          <t>4,74973600</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>5,41</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>9.455,265</t>
+          <t>9.431,611</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>5,07270700</t>
+          <t>5,07543200</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -6220,22 +6220,22 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>5,49</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>14,84</t>
+          <t>14,83</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>20.991,279</t>
+          <t>21.035,911</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>3,16828400</t>
+          <t>3,16999900</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -6289,22 +6289,22 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>14,96</t>
+          <t>14,95</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>13.351,574</t>
+          <t>13.325,941</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1.720,63337200</t>
+          <t>1.721,51500400</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>5,21</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>248,106</t>
+          <t>247,691</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6465,32 +6465,32 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1,40585300</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>0,000</t>
+          <t>1,40566100</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>-0,080</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>5,00</t>
+          <t>4,99</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>14,28</t>
+          <t>14,20</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>68,281</t>
+          <t>68,272</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1.188,55802500</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
+          <t>1.187,95469000</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>-0,003</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>3,40</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>-5,27</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>0,21</t>
+          <t>3,35</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>-5,32</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>36,424</t>
+          <t>36,405</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6699,27 +6699,27 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>12,65058600</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>0,365</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>-0,70</t>
+          <t>12,62034000</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>-0,239</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>-0,93</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>6,57</t>
+          <t>6,31</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>18,08</t>
+          <t>17,63</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -6768,32 +6768,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1.635,49048400</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>-0,006</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>-0,01</t>
+          <t>1.637,55822600</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>-0,163</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>4,37</t>
+          <t>4,50</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>13,27</t>
+          <t>13,26</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>116,929</t>
+          <t>115,457</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6885,32 +6885,32 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>2.427,83792800</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>0,152</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>0,12</t>
+          <t>2.422,49728200</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>-0,219</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>18,19</t>
+          <t>17,93</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>37,69</t>
+          <t>37,71</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>13,570</t>
+          <t>13,405</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -7115,32 +7115,32 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1,24900300</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>-0,005</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>-0,53</t>
+          <t>1,24854500</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>-0,332</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>-0,57</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>2,22</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>10,84</t>
+          <t>10,72</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>6,407</t>
+          <t>6,410</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -7232,32 +7232,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1,15806600</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>1,452</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>-4,29</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>-0,12</t>
+          <t>1,14894900</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>-0,787</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>-5,05</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>-0,90</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>16,72</t>
+          <t>15,21</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>3,508</t>
+          <t>3,481</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1,41975100</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>-0,004</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>-3,33</t>
+          <t>1,41938200</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>-0,729</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>-3,35</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>4,00</t>
+          <t>3,97</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>18,88</t>
+          <t>18,35</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>11,810</t>
+          <t>11,807</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7692,32 +7692,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1,10245300</t>
+          <t>1,10437600</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>0,193</t>
+          <t>0,174</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>-8,56</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>-7,43</t>
+          <t>0,61</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>-8,40</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>-7,75</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>3,702</t>
+          <t>3,738</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7809,32 +7809,32 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>5,33291181</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>-0,003</t>
+          <t>5,33930383</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>-0,121</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>3,93</t>
+          <t>4,05</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>13,02</t>
+          <t>13,04</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>33,078</t>
+          <t>33,106</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -7926,32 +7926,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>4,72104000</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>0,053</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>-1,47</t>
+          <t>4,69555700</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>-0,539</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>-2,00</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>5,67</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>41,55</t>
+          <t>40,77</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>639,349</t>
+          <t>632,603</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8043,32 +8043,32 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>2,84761300</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>0,000</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>-0,18</t>
+          <t>2,84704900</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>-0,401</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>-0,20</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>10,43</t>
+          <t>10,30</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>76,636</t>
+          <t>76,621</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -8160,32 +8160,32 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1.651,42905900</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>-0,458</t>
+          <t>1.656,65385700</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>0,316</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>1,92</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>4,82</t>
+          <t>5,15</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>10,90</t>
+          <t>11,23</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>29,267</t>
+          <t>29,357</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8277,32 +8277,32 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>3,79859100</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>0,814</t>
+          <t>3,79340800</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>-0,136</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>4,97</t>
+          <t>4,83</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>12,92</t>
+          <t>12,76</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>41,56</t>
+          <t>39,74</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>2.377,622</t>
+          <t>2.374,711</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -8394,32 +8394,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1,90203900</t>
+          <t>1,90226100</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>0,096</t>
+          <t>0,011</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>0,80</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>4,63</t>
+          <t>4,64</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>13,07</t>
+          <t>13,01</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>21,987</t>
+          <t>21,922</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1.656,37276600</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>-0,003</t>
+          <t>1.658,55978400</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>-0,158</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>4,87</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>14,845</t>
+          <t>14,836</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -8624,22 +8624,22 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>0,53565193</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>-0,006</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>-1,26</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>-25,81</t>
+          <t>0,55118618</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>0,000</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>1,60</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>-23,66</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>3,926</t>
+          <t>4,039</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8741,32 +8741,32 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>3,26250100</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>-0,005</t>
+          <t>3,25686300</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>-0,541</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>1,39</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>2,39</t>
+          <t>2,22</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>8,41</t>
+          <t>8,06</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>155,456</t>
+          <t>155,188</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -8858,32 +8858,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1,54371700</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>-0,004</t>
+          <t>1,54597100</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>-0,198</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>3,38</t>
+          <t>3,53</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>20,32</t>
+          <t>20,28</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>14,611</t>
+          <t>14,633</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8975,32 +8975,32 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1,38222400</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>-0,003</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>-1,10</t>
+          <t>1,38073200</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>-0,220</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>-1,21</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>1,92</t>
+          <t>1,81</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>8,01</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>70,950</t>
+          <t>70,873</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -9092,32 +9092,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1,48472000</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>-0,003</t>
+          <t>1,48741900</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>-0,061</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2,37</t>
+          <t>2,55</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>2,85</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>15,53</t>
+          <t>15,55</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>192,600</t>
+          <t>192,950</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9209,12 +9209,12 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1,77265100</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>-0,001</t>
+          <t>1,77271200</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>-0,002</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -9224,17 +9224,17 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>9,45</t>
+          <t>9,37</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>176,190</t>
+          <t>176,087</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -9326,32 +9326,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>5,61269600</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>0,228</t>
+          <t>5,60811300</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>-0,081</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>14,90</t>
+          <t>14,70</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>903,547</t>
+          <t>902,645</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9443,32 +9443,32 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>3,64444400</t>
+          <t>3,64492300</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>0,098</t>
+          <t>0,013</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>13,48</t>
+          <t>13,42</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>752,359</t>
+          <t>751,725</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -9560,32 +9560,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>6,79311100</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>-0,003</t>
+          <t>6,82039100</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>-0,005</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>5,62</t>
+          <t>6,04</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>16,19</t>
+          <t>16,60</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>129,652</t>
+          <t>130,173</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9677,17 +9677,17 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>1,41388200</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
+          <t>1,41382700</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>-0,003</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>279,675</t>
+          <t>279,703</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -9794,32 +9794,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,31680300</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
+          <t>1,32365200</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t>-0,001</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>1,10</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>3,12</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>1,64</t>
+          <t>2,53</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>13,317</t>
+          <t>13,386</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9911,32 +9911,32 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>3,73560200</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>-0,051</t>
+          <t>3,74765400</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>0,322</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>1,39</t>
-        </is>
-      </c>
-      <c r="G85" s="7" t="inlineStr">
-        <is>
-          <t>-7,07</t>
-        </is>
-      </c>
-      <c r="H85" s="7" t="inlineStr">
-        <is>
-          <t>-7,12</t>
+          <t>1,71</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>-6,77</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>-7,14</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>96,385</t>
+          <t>96,673</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -10028,32 +10028,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>6,76577100</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>0,818</t>
-        </is>
-      </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>-5,40</t>
+          <t>6,73248300</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>-0,492</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>-5,86</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>6,67</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>22,36</t>
+          <t>21,39</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>347,505</t>
+          <t>345,724</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10145,32 +10145,32 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>2,64365400</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>0,914</t>
-        </is>
-      </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>-4,97</t>
+          <t>2,62560600</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>-0,682</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>-5,62</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>9,87</t>
+          <t>9,12</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>27,82</t>
+          <t>26,67</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>13,751</t>
+          <t>13,655</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -10262,32 +10262,32 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1.980,77142200</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>2,265</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>-4,76</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>-0,21</t>
+          <t>1.958,07515100</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>-1,145</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>-5,85</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>-1,36</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>17,56</t>
+          <t>15,59</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>10,578</t>
+          <t>10,461</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10375,32 +10375,32 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>10,05486600</t>
+          <t>10,08273100</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>0,513</t>
+          <t>0,277</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>6,72</t>
+          <t>7,01</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>1,54</t>
+          <t>1,82</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>23,13</t>
+          <t>22,50</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>276,621</t>
+          <t>277,347</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -10492,32 +10492,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1,50729200</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>2,645</t>
-        </is>
-      </c>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>-1,54</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>-1,12</t>
+          <t>1,49314600</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>-0,938</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>-2,46</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>-2,05</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>6,26</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>457,536</t>
+          <t>453,224</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10609,32 +10609,32 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1,13695100</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>2,507</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="inlineStr">
-        <is>
-          <t>-2,31</t>
+          <t>1,13007300</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>-0,604</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>-1,55</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>-2,90</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>59,432</t>
+          <t>58,398</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1,75482400</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>1,686</t>
-        </is>
-      </c>
-      <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>-5,50</t>
+          <t>1,73881100</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>-0,912</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>-6,36</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>2,00</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>14,32</t>
+          <t>12,52</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2,187</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10843,32 +10843,32 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>4,70066300</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>-2,893</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="inlineStr">
-        <is>
-          <t>-10,98</t>
+          <t>4,71952900</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>0,401</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>-10,63</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>49,27</t>
+          <t>49,86</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>54,93</t>
+          <t>55,51</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>80,015</t>
+          <t>80,325</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -10960,32 +10960,32 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>8,86083200</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>0,910</t>
-        </is>
-      </c>
-      <c r="F94" s="6" t="inlineStr">
-        <is>
-          <t>-5,03</t>
+          <t>8,79993100</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>-0,687</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>-5,68</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>9,44</t>
+          <t>8,68</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>26,46</t>
+          <t>25,32</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>92,539</t>
+          <t>91,898</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -11077,32 +11077,32 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1,28503400</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>0,128</t>
-        </is>
-      </c>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>-5,89</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>-0,15</t>
+          <t>1,30250700</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>-0,036</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>-4,61</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>1,19</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>10,16</t>
+          <t>11,11</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>291,056</t>
+          <t>295,008</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -11194,32 +11194,32 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>1,89035900</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>3,832</t>
-        </is>
-      </c>
-      <c r="F96" s="6" t="inlineStr">
-        <is>
-          <t>-1,48</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>-0,58</t>
+          <t>1,88061600</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>-0,515</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>-1,99</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>-1,09</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>21,61</t>
+          <t>20,59</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>116,746</t>
+          <t>116,098</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11311,32 +11311,32 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>2,97478000</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>0,513</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>-7,61</t>
+          <t>2,95071100</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>-0,809</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>-8,36</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>9,14</t>
+          <t>8,26</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>22,99</t>
+          <t>21,13</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>132,589</t>
+          <t>129,845</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -11428,32 +11428,32 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1,92531400</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>2,258</t>
-        </is>
-      </c>
-      <c r="F98" s="6" t="inlineStr">
-        <is>
-          <t>-4,82</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>-0,63</t>
+          <t>1,90320000</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>-1,148</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>-5,91</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>-1,77</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>16,24</t>
+          <t>14,30</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>49,373</t>
+          <t>48,800</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11545,32 +11545,32 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>6,63129900</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>-2,403</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>-11,43</t>
+          <t>6,63721700</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>0,089</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>-11,35</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>41,38</t>
+          <t>41,50</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>49,74</t>
+          <t>50,35</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>123,773</t>
+          <t>123,858</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -11662,32 +11662,32 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>1.357,58309200</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>3,368</t>
-        </is>
-      </c>
-      <c r="F100" s="6" t="inlineStr">
-        <is>
-          <t>-2,59</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>-0,68</t>
-        </is>
-      </c>
-      <c r="H100" s="6" t="inlineStr">
-        <is>
-          <t>-9,40</t>
+          <t>1.323,79335000</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>-2,488</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>-5,02</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>-3,16</t>
+        </is>
+      </c>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>-12,54</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>43,611</t>
+          <t>42,531</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>39,57798900</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>0,580</t>
+          <t>39,32906600</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>-0,628</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>2,83</t>
+          <t>2,18</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>14,56</t>
+          <t>13,84</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>62,67</t>
+          <t>62,59</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>676,472</t>
+          <t>672,381</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -11896,15 +11896,15 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2,67071100</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>0,798</t>
-        </is>
-      </c>
-      <c r="F102" s="6" t="inlineStr">
+          <t>2,67069400</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>0,000</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
         <is>
           <t>-0,76</t>
         </is>
@@ -11916,12 +11916,12 @@
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>25,22</t>
+          <t>26,30</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>444,617</t>
+          <t>444,288</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -12013,32 +12013,32 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>4,89765200</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>1,272</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr">
-        <is>
-          <t>-4,74</t>
+          <t>4,87185200</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>-0,526</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>-5,24</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>9,13</t>
+          <t>8,55</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>28,10</t>
+          <t>27,14</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>23,674</t>
+          <t>23,550</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -12130,32 +12130,32 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>1.545,88240200</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>2,617</t>
-        </is>
-      </c>
-      <c r="F104" s="6" t="inlineStr">
-        <is>
-          <t>-4,64</t>
+          <t>1.528,22261500</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>-1,142</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>-5,73</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>6,22</t>
+          <t>5,01</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>18,75</t>
+          <t>16,98</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>30,953</t>
+          <t>30,627</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -12247,32 +12247,32 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>1,98537900</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>1,871</t>
-        </is>
-      </c>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>-3,14</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>-2,41</t>
+          <t>1,96731800</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>-0,909</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>-4,02</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>-3,29</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>12,85</t>
+          <t>11,39</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>1,818</t>
+          <t>1,802</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -12364,32 +12364,32 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>5,97893600</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>0,593</t>
-        </is>
-      </c>
-      <c r="F106" s="6" t="inlineStr">
-        <is>
-          <t>-5,44</t>
+          <t>5,97257000</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>-0,106</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>-5,54</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>11,14</t>
+          <t>11,02</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>29,55</t>
+          <t>29,14</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>44,383</t>
+          <t>44,331</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -12481,32 +12481,32 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>2,26121000</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>1,475</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>-3,82</t>
+          <t>2,25158300</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>-0,425</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>-4,23</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>7,77</t>
+          <t>7,31</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>26,29</t>
+          <t>25,48</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>36,314</t>
+          <t>36,139</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -12598,32 +12598,32 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>43,59458200</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>-2,889</t>
-        </is>
-      </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>-10,98</t>
+          <t>43,76941000</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>0,401</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>-10,62</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>49,32</t>
+          <t>49,92</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>55,05</t>
+          <t>55,63</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>874,765</t>
+          <t>875,765</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -12715,32 +12715,32 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>0,88600300</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>1,648</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>-3,58</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>-7,95</t>
-        </is>
-      </c>
-      <c r="H109" s="7" t="inlineStr">
-        <is>
-          <t>-16,49</t>
+          <t>0,88182400</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>-0,471</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>-4,04</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>-8,39</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>-16,98</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>2,989</t>
+          <t>2,985</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -12832,32 +12832,32 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>1,20712400</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>1,056</t>
+          <t>1,20364200</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>-0,288</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>0,81</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>-0,24</t>
+          <t>0,52</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>-0,53</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>16,05</t>
+          <t>14,89</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>3,883</t>
+          <t>3,872</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -12949,15 +12949,15 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>1,31943400</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>0,797</t>
-        </is>
-      </c>
-      <c r="F111" s="7" t="inlineStr">
+          <t>1,31941700</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <t>-0,77</t>
         </is>
@@ -12969,12 +12969,12 @@
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>25,05</t>
+          <t>26,12</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>19,628</t>
+          <t>19,626</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -13066,32 +13066,32 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1,84209900</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>0,753</t>
-        </is>
-      </c>
-      <c r="F112" s="6" t="inlineStr">
-        <is>
-          <t>-12,28</t>
+          <t>1,81287400</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>-1,586</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>-13,67</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>5,45</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>74,27</t>
+          <t>71,39</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>284,948</t>
+          <t>280,269</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -13183,32 +13183,32 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>1.003,28812900</t>
-        </is>
-      </c>
-      <c r="E113" s="7" t="inlineStr">
+          <t>1.013,48075100</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
         <is>
           <t>-0,002</t>
         </is>
       </c>
-      <c r="F113" s="7" t="inlineStr">
-        <is>
-          <t>-6,23</t>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>-5,28</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>3,37</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>17,92</t>
+          <t>18,62</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>7,914</t>
+          <t>7,995</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -13300,32 +13300,32 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1.513,24247100</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>-0,002</t>
-        </is>
-      </c>
-      <c r="F114" s="6" t="inlineStr">
-        <is>
-          <t>-5,93</t>
+          <t>1.532,14438800</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>-0,005</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>-4,75</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>2,43</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>13,50</t>
+          <t>14,20</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>22,057</t>
+          <t>22,304</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -13417,32 +13417,32 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>173,42888064</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>0,891</t>
-        </is>
-      </c>
-      <c r="F115" s="7" t="inlineStr">
-        <is>
-          <t>-4,99</t>
+          <t>172,25114375</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>-0,679</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>-5,63</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>10,05</t>
+          <t>9,31</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>28,42</t>
+          <t>27,26</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>43,358</t>
+          <t>43,064</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -13486,32 +13486,32 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1,88280000</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>0,732</t>
-        </is>
-      </c>
-      <c r="F116" s="6" t="inlineStr">
-        <is>
-          <t>-12,25</t>
+          <t>1,85223500</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>-1,623</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>-13,67</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>7,23</t>
+          <t>5,49</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>74,62</t>
+          <t>71,67</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>5,118</t>
+          <t>5,067</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -13603,32 +13603,32 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1,83649100</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>0,738</t>
-        </is>
-      </c>
-      <c r="F117" s="7" t="inlineStr">
-        <is>
-          <t>-12,30</t>
+          <t>1,80646900</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>-1,634</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>-13,73</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>7,27</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>74,71</t>
+          <t>71,73</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>1.678,798</t>
+          <t>1.650,665</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -13720,32 +13720,32 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>48,49443000</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>-2,889</t>
-        </is>
-      </c>
-      <c r="F118" s="6" t="inlineStr">
-        <is>
-          <t>-10,96</t>
+          <t>48,69024100</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>0,403</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>-10,60</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>49,73</t>
+          <t>50,33</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>55,95</t>
+          <t>56,54</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>702,624</t>
+          <t>704,676</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -13837,32 +13837,32 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>43,84760800</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>0,583</t>
+          <t>43,57238600</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>-0,627</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>2,87</t>
+          <t>2,22</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>14,79</t>
+          <t>14,07</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>63,57</t>
+          <t>63,49</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>794,807</t>
+          <t>789,708</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -13954,32 +13954,32 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>16,93582400</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>1,997</t>
-        </is>
-      </c>
-      <c r="F120" s="6" t="inlineStr">
-        <is>
-          <t>-4,49</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="inlineStr">
-        <is>
-          <t>0,41</t>
+          <t>16,72559700</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>-1,241</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>-5,68</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>18,96</t>
+          <t>16,83</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>117,313</t>
+          <t>115,678</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -14071,32 +14071,32 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>36,76458400</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>0,579</t>
+          <t>36,53390100</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>-0,627</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>2,81</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>14,57</t>
+          <t>13,85</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>62,41</t>
+          <t>62,33</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>12,008</t>
+          <t>11,932</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
@@ -14188,32 +14188,32 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>42,84825100</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>-2,895</t>
-        </is>
-      </c>
-      <c r="F122" s="6" t="inlineStr">
-        <is>
-          <t>-10,98</t>
+          <t>43,02007600</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>0,401</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>-10,62</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>49,45</t>
+          <t>50,05</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>55,22</t>
+          <t>55,81</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>608,346</t>
+          <t>610,366</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -14305,32 +14305,32 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>37,75409600</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>0,580</t>
+          <t>37,51676900</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>-0,628</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>2,83</t>
+          <t>2,18</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>14,57</t>
+          <t>13,85</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>62,69</t>
+          <t>62,61</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>475,790</t>
+          <t>472,667</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -14422,32 +14422,32 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>45,55881400</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>-2,893</t>
-        </is>
-      </c>
-      <c r="F124" s="6" t="inlineStr">
-        <is>
-          <t>-10,96</t>
+          <t>45,74194300</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>0,401</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>-10,60</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>49,60</t>
+          <t>50,21</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>55,58</t>
+          <t>56,16</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>699,500</t>
+          <t>702,242</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -14539,22 +14539,22 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>1,12074800</t>
+          <t>1,12127500</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>4,80</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -14564,7 +14564,7 @@
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>54,589</t>
+          <t>56,895</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>1,35254800</t>
+          <t>1,35318700</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -14666,12 +14666,12 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>4,80</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>196,879</t>
+          <t>211,825</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -14725,22 +14725,22 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>5,86415600</t>
+          <t>5,86711500</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>5,12</t>
+          <t>5,18</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -14750,7 +14750,7 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>41,534</t>
+          <t>41,562</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>5,10345500</t>
+          <t>5,10616800</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -14852,12 +14852,12 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>5,35</t>
+          <t>5,40</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>789,556</t>
+          <t>789,976</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -14959,22 +14959,22 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>3,20625900</t>
+          <t>3,20791900</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>5,20</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>18,683</t>
+          <t>18,773</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -15076,32 +15076,32 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>23,73544000</t>
+          <t>23,74106200</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>0,144</t>
+          <t>0,023</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>6,01</t>
+          <t>6,04</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>11,88</t>
+          <t>11,94</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>94,927</t>
+          <t>94,949</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>3,26071800</t>
+          <t>3,26240600</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -15203,12 +15203,12 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>5,30</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>7.574,843</t>
+          <t>7.637,655</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -15310,22 +15310,22 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>1.878,47946900</t>
+          <t>1.879,50162300</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>0,057</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
@@ -15335,7 +15335,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>15.673,394</t>
+          <t>15.759,437</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -15427,32 +15427,32 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>4,86121500</t>
+          <t>4,86360500</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>0,058</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>5,48</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>14,76</t>
+          <t>14,75</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>3.054,848</t>
+          <t>3.076,217</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -15544,7 +15544,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1,54322678</t>
+          <t>1,54405187</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -15554,22 +15554,22 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>5,42</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>14,76</t>
+          <t>14,75</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>343,973</t>
+          <t>344,157</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>5,10489700</t>
+          <t>5,10764800</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -15671,12 +15671,12 @@
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>5,50</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>284,541</t>
+          <t>284,694</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -15778,22 +15778,22 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>8,67860700</t>
+          <t>8,68284400</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>0,059</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>5,43</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>3.998,992</t>
+          <t>4.000,878</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -15895,32 +15895,32 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>17,85039900</t>
+          <t>17,85930100</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>0,058</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>5,48</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>14,82</t>
+          <t>14,81</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>4.799,062</t>
+          <t>4.782,367</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -16008,7 +16008,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>2,81534100</t>
+          <t>2,81669900</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
@@ -16018,12 +16018,12 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>4,89</t>
+          <t>4,94</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>13.255,768</t>
+          <t>13.329,076</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>4,41177100</t>
+          <t>4,41416800</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -16135,12 +16135,12 @@
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>5,46</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -16150,7 +16150,7 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>12.431,013</t>
+          <t>12.474,465</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>1,36884100</t>
+          <t>1,36958700</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
@@ -16267,7 +16267,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.606,551</t>
+          <t>3.614,012</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -16359,7 +16359,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>1.765,82859000</t>
+          <t>1.766,76082200</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -16369,12 +16369,12 @@
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>5,37</t>
+          <t>5,43</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -16384,7 +16384,7 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>1.436,339</t>
+          <t>1.434,795</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>1,30400800</t>
+          <t>1,30457500</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -16486,12 +16486,12 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>4,39</t>
+          <t>4,43</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>33.526,892</t>
+          <t>33.961,548</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>9,37283700</t>
+          <t>9,37720500</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -16603,12 +16603,12 @@
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>4,71</t>
+          <t>4,76</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
@@ -16618,7 +16618,7 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>2.892,268</t>
+          <t>2.923,563</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>2,46842800</t>
+          <t>2,46957900</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>4,71</t>
+          <t>4,76</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>15.417,030</t>
+          <t>15.479,484</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -16779,22 +16779,22 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>2,59688100</t>
+          <t>2,59823600</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>0,057</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>5,50</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>9.357,276</t>
+          <t>9.358,639</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
@@ -16896,32 +16896,32 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>2,40650900</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="inlineStr">
-        <is>
-          <t>0,284</t>
+          <t>2,40387900</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>-0,109</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>4,49</t>
+          <t>4,37</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>13,00</t>
+          <t>12,84</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>3.786,467</t>
+          <t>3.792,962</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -17013,32 +17013,32 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>2,98599000</t>
+          <t>2,98613300</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>0,169</t>
+          <t>0,004</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>5,88</t>
+          <t>5,89</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>11,99</t>
+          <t>12,01</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>41,811</t>
+          <t>41,813</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
@@ -17130,32 +17130,32 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1.640,09930600</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="inlineStr">
-        <is>
-          <t>0,155</t>
+          <t>1.639,69168900</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>-0,024</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>4,50</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>11,66</t>
+          <t>11,63</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>460,074</t>
+          <t>459,960</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -17247,32 +17247,32 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>4,46243900</t>
+          <t>4,46394000</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>0,076</t>
+          <t>0,033</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>5,20</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>14,27</t>
+          <t>14,23</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>11.182,178</t>
+          <t>11.160,417</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
@@ -17364,32 +17364,32 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>3,81974000</t>
+          <t>3,82122300</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>0,149</t>
+          <t>0,038</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>6,11</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>12,26</t>
+          <t>12,35</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2.982,391</t>
+          <t>2.983,638</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -17433,32 +17433,32 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>3,63777700</t>
-        </is>
-      </c>
-      <c r="E151" s="5" t="inlineStr">
-        <is>
-          <t>0,390</t>
+          <t>3,63189400</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>-0,161</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>4,20</t>
+          <t>4,03</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>13,36</t>
+          <t>13,08</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>1.750,385</t>
+          <t>1.745,899</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
@@ -17550,32 +17550,32 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>5,15048600</t>
+          <t>5,15628600</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>0,142</t>
-        </is>
-      </c>
-      <c r="F152" s="6" t="inlineStr">
-        <is>
-          <t>-0,02</t>
+          <t>0,112</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>4,74</t>
+          <t>4,86</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>10,18</t>
+          <t>10,23</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2.576,322</t>
+          <t>2.583,526</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -17667,32 +17667,32 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>5,17831000</t>
+          <t>5,17971000</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>0,142</t>
+          <t>0,027</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>6,07</t>
+          <t>6,10</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>12,06</t>
+          <t>12,12</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>5.440,008</t>
+          <t>5.441,101</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
@@ -17784,32 +17784,32 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>4,73939400</t>
+          <t>4,74034200</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>0,150</t>
+          <t>0,020</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>5,00</t>
+          <t>5,02</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>13,33</t>
+          <t>13,28</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>515,409</t>
+          <t>514,732</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -17901,32 +17901,32 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>7,91884300</t>
+          <t>7,92259200</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>0,059</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>5,44</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>14,61</t>
+          <t>14,60</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>166,923</t>
+          <t>167,328</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
@@ -17970,32 +17970,32 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>3,45945900</t>
+          <t>3,46600700</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>0,147</t>
-        </is>
-      </c>
-      <c r="F156" s="6" t="inlineStr">
-        <is>
-          <t>-0,71</t>
+          <t>0,189</t>
+        </is>
+      </c>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>-0,52</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>3,69</t>
+          <t>3,88</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>8,75</t>
+          <t>8,81</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>819,463</t>
+          <t>821,013</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -18087,32 +18087,32 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>3,77730800</t>
-        </is>
-      </c>
-      <c r="E157" s="5" t="inlineStr">
-        <is>
-          <t>0,511</t>
+          <t>3,76837100</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>-0,236</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>3,87</t>
+          <t>3,62</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>12,63</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>723,304</t>
+          <t>721,422</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
@@ -18204,32 +18204,32 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>7,14652400</t>
+          <t>7,15013200</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>5,40</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>14,68</t>
+          <t>14,67</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>12.898,853</t>
+          <t>12.892,091</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -18321,7 +18321,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>7,46316300</t>
+          <t>7,46708200</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18331,12 +18331,12 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>5,40</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
@@ -18346,7 +18346,7 @@
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>5.203,714</t>
+          <t>5.207,598</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -18438,32 +18438,32 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>1,44864300</t>
-        </is>
-      </c>
-      <c r="E160" s="3" t="inlineStr">
-        <is>
-          <t>0,324</t>
+          <t>1,44626700</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>-0,164</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>3,89</t>
+          <t>3,72</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>12,66</t>
+          <t>12,36</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>172,950</t>
+          <t>172,666</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
@@ -18555,22 +18555,22 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>3,12782900</t>
+          <t>3,12939800</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>5,06</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
@@ -18580,7 +18580,7 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>1.902,168</t>
+          <t>1.859,155</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
@@ -18672,32 +18672,32 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>6,69259400</t>
+          <t>6,69620200</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>5,51</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>14,86</t>
+          <t>14,85</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>24.463,157</t>
+          <t>24.442,916</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -18741,22 +18741,22 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>5,51998900</t>
+          <t>5,52594700</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>0,151</t>
+          <t>0,107</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>5,02</t>
+          <t>5,13</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
@@ -18766,7 +18766,7 @@
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>598,801</t>
+          <t>597,248</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
@@ -18975,32 +18975,32 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>3,98630400</t>
-        </is>
-      </c>
-      <c r="E165" s="5" t="inlineStr">
-        <is>
-          <t>0,920</t>
-        </is>
-      </c>
-      <c r="F165" s="7" t="inlineStr">
-        <is>
-          <t>-4,97</t>
+          <t>3,95902400</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>-0,684</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>-5,62</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>10,09</t>
+          <t>9,34</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>28,46</t>
+          <t>27,30</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>302,030</t>
+          <t>299,957</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
@@ -19092,32 +19092,32 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>3,66308900</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>0,886</t>
-        </is>
-      </c>
-      <c r="F166" s="6" t="inlineStr">
-        <is>
-          <t>-4,96</t>
+          <t>3,63815900</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>-0,680</t>
+        </is>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>-5,61</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>9,12</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>27,93</t>
+          <t>26,80</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>9,269</t>
+          <t>9,206</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -19209,32 +19209,32 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>11,26971613</t>
+          <t>11,30132976</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>0,516</t>
+          <t>0,280</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>6,78</t>
+          <t>7,08</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>2,12</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
         <is>
-          <t>24,15</t>
+          <t>23,51</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>2.326,280</t>
+          <t>2.332,770</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
@@ -19326,32 +19326,32 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>2,05202900</t>
-        </is>
-      </c>
-      <c r="E168" s="3" t="inlineStr">
-        <is>
-          <t>0,979</t>
-        </is>
-      </c>
-      <c r="F168" s="6" t="inlineStr">
-        <is>
-          <t>-4,64</t>
+          <t>2,03740700</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>-0,712</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>-5,32</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>8,26</t>
+          <t>7,49</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>25,19</t>
+          <t>24,09</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>202,563</t>
+          <t>201,119</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -19443,32 +19443,32 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>2,06042500</t>
-        </is>
-      </c>
-      <c r="E169" s="5" t="inlineStr">
-        <is>
-          <t>2,260</t>
-        </is>
-      </c>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>-4,82</t>
-        </is>
-      </c>
-      <c r="G169" s="7" t="inlineStr">
-        <is>
-          <t>-0,61</t>
+          <t>2,03673200</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>-1,149</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>-5,91</t>
+        </is>
+      </c>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>-1,76</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
         <is>
-          <t>16,85</t>
+          <t>14,81</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>779,987</t>
+          <t>771,017</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
@@ -19560,32 +19560,32 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>3,47809986</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="inlineStr">
-        <is>
-          <t>0,962</t>
-        </is>
-      </c>
-      <c r="F170" s="6" t="inlineStr">
-        <is>
-          <t>-5,65</t>
+          <t>3,45793778</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>-0,579</t>
+        </is>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>-6,19</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>6,90</t>
+          <t>6,29</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>22,43</t>
+          <t>21,40</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>1.333,772</t>
+          <t>1.326,040</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -19673,32 +19673,32 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>2,54729879</t>
-        </is>
-      </c>
-      <c r="E171" s="5" t="inlineStr">
-        <is>
-          <t>1,096</t>
-        </is>
-      </c>
-      <c r="F171" s="7" t="inlineStr">
-        <is>
-          <t>-6,22</t>
+          <t>2,52966840</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>-0,692</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>-6,87</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>7,77</t>
+          <t>7,02</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>24,66</t>
+          <t>23,47</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>788,442</t>
+          <t>782,985</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
@@ -19786,32 +19786,32 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>3,73459200</t>
+          <t>3,73559500</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>0,080</t>
+          <t>0,026</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>5,17</t>
+          <t>5,20</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>14,32</t>
+          <t>14,28</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>4.974,238</t>
+          <t>4.981,567</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -94,10 +94,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -628,7 +628,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,25184400</t>
+          <t>2,25289000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -638,12 +638,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>4,79</t>
+          <t>4,84</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>407,232</t>
+          <t>406,209</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,47319100</t>
+          <t>5,47568800</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>4,70</t>
+          <t>4,75</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.603,336</t>
+          <t>6.618,678</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,76352100</t>
+          <t>2,76478100</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>4,74</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>861,740</t>
+          <t>862,231</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -931,32 +931,32 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>3,31460400</t>
+          <t>3,31629100</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>5,24</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>14,09</t>
+          <t>14,08</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>11,569</t>
+          <t>11,610</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -1000,32 +1000,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,46828400</t>
+          <t>3,46989100</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>5,31</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>14,35</t>
+          <t>14,33</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>120,005</t>
+          <t>120,029</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1117,32 +1117,32 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1.825,48334600</t>
+          <t>1.826,33503800</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>5,39</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>14,66</t>
+          <t>14,64</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>97,079</t>
+          <t>97,117</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1234,32 +1234,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,65656300</t>
+          <t>9,66098400</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>4,97</t>
+          <t>5,02</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>13,38</t>
+          <t>13,36</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>584,983</t>
+          <t>586,371</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1351,32 +1351,32 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3,33852800</t>
+          <t>3,34015900</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>14,26</t>
+          <t>14,25</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>61,284</t>
+          <t>61,213</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1468,22 +1468,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,98041100</t>
+          <t>2,98201400</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>5,46</t>
+          <t>5,51</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1.674,277</t>
+          <t>1.673,521</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1533,32 +1533,32 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>19,85273400</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>-0,183</t>
+          <t>19,85614100</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>0,017</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>3,59</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>12,01</t>
+          <t>11,59</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>123,270</t>
+          <t>123,315</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1650,32 +1650,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,49435700</t>
+          <t>13,50016200</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>0,004</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>4,93</t>
+          <t>4,98</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>10,04</t>
+          <t>9,89</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,433</t>
+          <t>28,441</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>03.218.183/0001-04</t>
+          <t>03.191.874/0001-61</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>100000.0</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1725,27 +1725,27 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0087.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0046.pdf</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0087.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0046.pdf</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0087.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0046.pdf</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_87.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_46.pdf</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_87.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_46.pdf</t>
         </is>
       </c>
     </row>
@@ -1767,32 +1767,32 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>45,92679000</t>
+          <t>45,94775300</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>4,96</t>
+          <t>5,01</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>13,34</t>
+          <t>13,33</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>40,697</t>
+          <t>40,681</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20,11546900</t>
+          <t>20,12501200</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1894,12 +1894,12 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0,80</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>4,87</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,794</t>
+          <t>64,825</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>3,14104800</t>
+          <t>3,14272800</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>0,020</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>5,81</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>11,17</t>
+          <t>11,06</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>79,845</t>
+          <t>79,838</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -2118,27 +2118,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14,87809500</t>
+          <t>14,88493500</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>4,99</t>
+          <t>5,04</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>13,44</t>
+          <t>13,42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2235,27 +2235,27 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2,98509700</t>
+          <t>2,98642600</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>4,85</t>
+          <t>4,90</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>13,11</t>
+          <t>13,10</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -2352,32 +2352,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,31019800</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>-0,163</t>
+          <t>3,31100200</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>0,024</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>3,88</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>12,52</t>
+          <t>12,15</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>139,764</t>
+          <t>139,719</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,02282300</t>
+          <t>3,02443500</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2479,22 +2479,22 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>5,46</t>
+          <t>5,51</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>14,78</t>
+          <t>14,77</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1.761,317</t>
+          <t>1.769,116</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2586,32 +2586,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32,61832600</t>
+          <t>32,63376400</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>5,18</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>13,82</t>
+          <t>13,81</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2.187,597</t>
+          <t>2.183,896</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2703,32 +2703,32 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,28829700</t>
+          <t>3,28985500</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>5,14</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>13,85</t>
+          <t>13,83</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>13,236</t>
+          <t>13,238</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2820,32 +2820,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3,34249700</t>
+          <t>3,34869300</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0,105</t>
+          <t>0,185</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,30</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>4,88</t>
+          <t>5,07</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>9,94</t>
+          <t>9,77</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,983</t>
+          <t>67,034</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2937,32 +2937,32 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>18,93477900</t>
+          <t>18,94345500</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>5,30</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>14,19</t>
+          <t>14,18</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>958,430</t>
+          <t>958,322</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -3002,22 +3002,22 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,11182293</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
+          <t>1,11226478</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>-0,001</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,20</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>212,497</t>
+          <t>212,570</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3119,32 +3119,32 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1,23340200</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
+          <t>1,23415200</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>-0,001</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>5,31</t>
+          <t>5,37</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>14,67</t>
+          <t>14,74</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>70,866</t>
+          <t>70,922</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -3236,32 +3236,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1.821,75907000</t>
+          <t>1.822,70482500</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>5,42</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>14,81</t>
+          <t>14,80</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>175,323</t>
+          <t>175,296</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3305,32 +3305,32 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1,19801900</t>
+          <t>1,19887700</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>0,090</t>
+          <t>0,071</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>6,60</t>
+          <t>6,67</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>12,96</t>
+          <t>12,93</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>40,239</t>
+          <t>40,268</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -3422,22 +3422,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,03359700</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
+          <t>1,03429800</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>-0,001</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>5,41</t>
+          <t>5,48</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,851</t>
+          <t>21,870</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3535,32 +3535,32 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,16170700</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
+          <t>1,16252900</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>-0,001</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>1,25</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>4,61</t>
+          <t>4,69</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>13,85</t>
+          <t>13,93</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>66,562</t>
+          <t>66,619</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,06332986</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
+          <t>1,06417019</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>-0,001</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2,90</t>
+          <t>2,98</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>319,464</t>
+          <t>317,863</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3874,32 +3874,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>5,11230800</t>
+          <t>5,11501700</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>5,50</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>14,84</t>
+          <t>14,83</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>860,938</t>
+          <t>861,211</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3991,22 +3991,22 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>4,91884200</t>
+          <t>4,92146700</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>5,50</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.247,276</t>
+          <t>3.247,360</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>29,10902400</t>
+          <t>29,12307500</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -4118,12 +4118,12 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>4,96</t>
+          <t>5,01</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,251</t>
+          <t>21,261</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4225,32 +4225,32 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>30,45387500</t>
+          <t>30,46813500</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>5,41</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>14,48</t>
+          <t>14,47</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>3.116,203</t>
+          <t>3.114,359</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -4342,32 +4342,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1.766,25761100</t>
+          <t>1.767,21709000</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0,018</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>4,85</t>
+          <t>4,91</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>13,64</t>
+          <t>13,58</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>125,896</t>
+          <t>125,761</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>3,20583400</t>
+          <t>3,20754700</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>5,49</t>
+          <t>5,55</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>581,881</t>
+          <t>585,653</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -4576,32 +4576,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>6,15732400</t>
+          <t>6,16015300</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>5,32</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>14,23</t>
+          <t>14,22</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>122,585</t>
+          <t>122,521</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1,26246000</t>
+          <t>1,26314500</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>5,60</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>337,787</t>
+          <t>336,068</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -4810,32 +4810,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>10,53949200</t>
+          <t>10,54450400</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>5,48</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>14,70</t>
+          <t>14,68</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2.387,796</t>
+          <t>2.388,251</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4927,32 +4927,32 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>5,48875200</t>
+          <t>5,49139000</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>14,88</t>
+          <t>14,87</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>555,566</t>
+          <t>555,822</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3,54911200</t>
+          <t>3,55103400</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15.556,492</t>
+          <t>15.553,300</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5161,32 +5161,32 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>5,27513100</t>
+          <t>5,27797400</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>1,00</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>5,59</t>
+          <t>5,64</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>15,22</t>
+          <t>15,21</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>1.388,284</t>
+          <t>1.388,992</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -5278,22 +5278,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>30,19351400</t>
+          <t>30,20799000</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>4,93</t>
+          <t>4,98</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>165,888</t>
+          <t>165,235</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2,79605200</t>
+          <t>2,79736700</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>0,80</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>4,86</t>
+          <t>4,91</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5.919,794</t>
+          <t>5.924,117</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5625,32 +5625,32 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>3,58689400</t>
+          <t>3,58867700</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>5,31</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>14,33</t>
+          <t>14,32</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>2.188,811</t>
+          <t>2.188,171</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1,28413400</t>
+          <t>1,28481800</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>5,46</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>65,209</t>
+          <t>64,132</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5859,22 +5859,22 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>9,63609500</t>
+          <t>9,64092300</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>5,40</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>838,876</t>
+          <t>838,988</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -5976,22 +5976,22 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>4,43449200</t>
+          <t>4,43682500</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>5,40</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15.784,652</t>
+          <t>15.786,780</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -6093,22 +6093,22 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>4,74973600</t>
+          <t>4,75217300</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>9.431,611</t>
+          <t>9.435,426</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -6210,22 +6210,22 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>5,07543200</t>
+          <t>5,07805100</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>5,49</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>21.035,911</t>
+          <t>21.060,080</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6279,22 +6279,22 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>3,16999900</t>
+          <t>3,17164400</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>5,59</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>13.325,941</t>
+          <t>13.327,624</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1.721,51500400</t>
+          <t>1.722,39705500</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>5,32</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>247,691</t>
+          <t>248,039</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6465,32 +6465,32 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1,40566100</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>-0,080</t>
+          <t>1,40659200</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>-0,070</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>4,99</t>
+          <t>5,05</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>14,20</t>
+          <t>14,28</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>68,272</t>
+          <t>68,048</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1.187,95469000</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
+          <t>1.194,40400600</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
         <is>
           <t>-0,003</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>3,35</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>-5,32</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>-0,39</t>
+          <t>3,91</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>-4,81</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>0,15</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>36,405</t>
+          <t>36,466</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6699,27 +6699,27 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>12,62034000</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>-0,239</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>-0,93</t>
+          <t>12,60968300</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>-0,084</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>-1,02</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>6,31</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>17,63</t>
+          <t>17,17</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -6768,12 +6768,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1.637,55822600</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>-0,163</t>
+          <t>1.637,45665300</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>-0,006</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>115,457</t>
+          <t>115,436</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6885,32 +6885,32 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>2.422,49728200</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>-0,219</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>-0,09</t>
+          <t>2.411,08312700</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>-0,471</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>17,93</t>
+          <t>17,38</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>37,71</t>
+          <t>36,21</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>13,405</t>
+          <t>12,731</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -7115,32 +7115,32 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1,24854500</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>-0,332</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>-0,57</t>
+          <t>1,25212400</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>-0,075</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>2,52</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>10,72</t>
+          <t>11,04</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>6,410</t>
+          <t>6,428</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -7232,32 +7232,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1,14894900</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>-0,787</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>-5,05</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>-0,90</t>
+          <t>1,14863900</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>-0,026</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>-5,07</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>-0,93</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>15,21</t>
+          <t>13,60</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>3,481</t>
+          <t>3,480</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1,41938200</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>-0,729</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>-3,35</t>
+          <t>1,42927100</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>-0,046</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>-2,68</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>4,70</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>18,35</t>
+          <t>19,18</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>11,807</t>
+          <t>11,890</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7692,32 +7692,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1,10437600</t>
+          <t>1,11052300</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>0,174</t>
+          <t>0,556</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>0,61</t>
-        </is>
-      </c>
-      <c r="G66" s="7" t="inlineStr">
-        <is>
-          <t>-8,40</t>
-        </is>
-      </c>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
-          <t>-7,75</t>
+          <t>1,17</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>-7,89</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>-6,37</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>3,738</t>
+          <t>3,754</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7809,17 +7809,17 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>5,33930383</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>-0,121</t>
+          <t>5,33911469</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>33,106</t>
+          <t>33,105</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -7926,32 +7926,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>4,69555700</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>-0,539</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>-2,00</t>
+          <t>4,64191300</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>-1,142</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>-3,12</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>5,67</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>40,77</t>
+          <t>41,82</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>632,603</t>
+          <t>624,426</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8043,32 +8043,32 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>2,84704900</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>-0,401</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>-0,20</t>
+          <t>2,85255900</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>-0,278</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>0,00</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>2,13</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>10,30</t>
+          <t>10,52</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>76,621</t>
+          <t>75,658</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -8160,32 +8160,32 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1.656,65385700</t>
+          <t>1.662,22720900</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>0,316</t>
+          <t>0,336</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2,25</t>
+          <t>2,59</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>5,15</t>
+          <t>5,50</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>11,23</t>
+          <t>11,74</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>29,357</t>
+          <t>29,455</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8277,32 +8277,32 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>3,79340800</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>-0,136</t>
+          <t>3,79685400</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>0,090</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>4,83</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>12,76</t>
+          <t>12,87</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>39,74</t>
+          <t>38,62</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>2.374,711</t>
+          <t>2.377,702</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -8394,32 +8394,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1,90226100</t>
+          <t>1,90309100</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>0,011</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>4,64</t>
+          <t>4,68</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>12,93</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>21,922</t>
+          <t>21,929</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1.658,55978400</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>-0,158</t>
+          <t>1.658,50876800</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>14,836</t>
+          <t>14,865</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -8624,22 +8624,22 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>0,55118618</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>0,000</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>1,60</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr">
-        <is>
-          <t>-23,66</t>
+          <t>0,53812850</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>-0,008</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>-0,80</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>-25,47</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>4,039</t>
+          <t>3,934</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>3,25686300</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>-0,541</t>
+          <t>3,25667400</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>-0,005</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>2,21</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>155,188</t>
+          <t>155,178</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -8858,17 +8858,17 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1,54597100</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>-0,198</t>
+          <t>1,54589900</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>-0,004</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>14,633</t>
+          <t>14,632</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8975,22 +8975,22 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1,38073200</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>-0,220</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
+          <t>1,38067900</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>-1,21</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>1,80</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>70,873</t>
+          <t>70,870</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1,48741900</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>-0,061</t>
+          <t>1,48736200</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>192,950</t>
+          <t>192,942</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9209,32 +9209,32 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1,77271200</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>-0,002</t>
+          <t>1,77711100</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>9,37</t>
+          <t>9,64</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>176,087</t>
+          <t>176,384</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -9326,32 +9326,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>5,60811300</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>-0,081</t>
+          <t>5,61030600</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>0,039</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>14,70</t>
+          <t>14,64</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>902,645</t>
+          <t>902,733</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9443,32 +9443,32 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>3,64492300</t>
+          <t>3,64656700</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>0,013</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>4,79</t>
+          <t>4,84</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>13,42</t>
+          <t>13,34</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>751,725</t>
+          <t>747,368</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -9560,32 +9560,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>6,82039100</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>-0,005</t>
+          <t>6,81637700</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>6,04</t>
+          <t>5,98</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>16,60</t>
+          <t>16,54</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>130,173</t>
+          <t>129,925</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9677,32 +9677,32 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>1,41382700</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
+          <t>1,41991200</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t>-0,003</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>16,18</t>
+          <t>16,68</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>279,703</t>
+          <t>280,907</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -9794,32 +9794,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,32365200</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>-0,001</t>
+          <t>1,32082100</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>-0,002</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>1,10</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>3,12</t>
+          <t>2,90</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>2,53</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>13,386</t>
+          <t>13,358</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9911,32 +9911,32 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>3,74765400</t>
+          <t>3,76861800</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>0,322</t>
+          <t>0,559</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>-6,77</t>
-        </is>
-      </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>-7,14</t>
+          <t>2,28</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>-6,25</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>-6,13</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>96,673</t>
+          <t>97,109</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -10028,32 +10028,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>6,73248300</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>-0,492</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="inlineStr">
-        <is>
-          <t>-5,86</t>
+          <t>6,71695800</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>-0,230</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>-6,08</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>5,90</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>21,39</t>
+          <t>19,96</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>345,724</t>
+          <t>344,965</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10145,32 +10145,32 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>2,62560600</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>-0,682</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>-5,62</t>
+          <t>2,61349600</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>-0,461</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>-6,05</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>9,12</t>
+          <t>8,62</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>26,67</t>
+          <t>24,86</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>13,655</t>
+          <t>13,583</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -10262,32 +10262,32 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1.958,07515100</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>-1,145</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>-5,85</t>
-        </is>
-      </c>
-      <c r="G88" s="7" t="inlineStr">
-        <is>
-          <t>-1,36</t>
+          <t>1.954,16075200</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>-0,199</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>-6,04</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>-1,56</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>15,59</t>
+          <t>13,75</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>10,461</t>
+          <t>10,437</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10375,32 +10375,32 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>10,08273100</t>
+          <t>10,17538000</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>0,277</t>
+          <t>0,918</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>7,01</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>2,76</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>22,50</t>
+          <t>22,42</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>277,347</t>
+          <t>280,963</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -10492,32 +10492,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1,49314600</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>-0,938</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>-2,46</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="inlineStr">
-        <is>
-          <t>-2,05</t>
+          <t>1,48407900</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>-0,607</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>-3,06</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>-2,64</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>4,47</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>453,224</t>
+          <t>450,467</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10609,32 +10609,32 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1,13007300</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>-0,604</t>
-        </is>
-      </c>
-      <c r="F91" s="6" t="inlineStr">
-        <is>
-          <t>-1,55</t>
-        </is>
-      </c>
-      <c r="G91" s="6" t="inlineStr">
-        <is>
-          <t>-2,90</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="inlineStr">
-        <is>
-          <t>0,47</t>
+          <t>1,12496700</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>-0,451</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>-1,99</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>-3,34</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>58,398</t>
+          <t>58,134</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1,73881100</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>-0,912</t>
-        </is>
-      </c>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>-6,36</t>
+          <t>1,72984000</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>-0,515</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>-6,85</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2,00</t>
+          <t>1,48</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>12,52</t>
+          <t>10,25</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>2,156</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10843,32 +10843,32 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>4,71952900</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>0,401</t>
-        </is>
-      </c>
-      <c r="F93" s="6" t="inlineStr">
-        <is>
-          <t>-10,63</t>
+          <t>4,64360100</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>-1,608</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>-12,06</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>49,86</t>
+          <t>47,45</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>55,51</t>
+          <t>51,59</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>80,325</t>
+          <t>78,943</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -10960,32 +10960,32 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>8,79993100</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>-0,687</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>-5,68</t>
+          <t>8,75893800</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>-0,465</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>-6,12</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>8,68</t>
+          <t>8,18</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>25,32</t>
+          <t>23,52</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>91,898</t>
+          <t>91,453</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -11077,32 +11077,32 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1,30250700</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>-0,036</t>
-        </is>
-      </c>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>-4,61</t>
+          <t>1,29144100</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>-0,040</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>-5,42</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>11,11</t>
+          <t>10,22</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>295,008</t>
+          <t>292,507</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -11194,32 +11194,32 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>1,88061600</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>-0,515</t>
-        </is>
-      </c>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>-1,99</t>
-        </is>
-      </c>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>-1,09</t>
+          <t>1,86617000</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>-0,768</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>-2,75</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>-1,85</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>20,59</t>
+          <t>16,91</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>116,098</t>
+          <t>115,190</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11311,32 +11311,32 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>2,95071100</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>-0,809</t>
-        </is>
-      </c>
-      <c r="F97" s="6" t="inlineStr">
-        <is>
-          <t>-8,36</t>
+          <t>2,91876600</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>-1,082</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>-9,35</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>8,26</t>
+          <t>7,09</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>21,13</t>
+          <t>17,76</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>129,845</t>
+          <t>128,390</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -11428,32 +11428,32 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1,90320000</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>-1,148</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
-        <is>
-          <t>-5,91</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr">
-        <is>
-          <t>-1,77</t>
+          <t>1,89931800</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>-0,203</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>-6,10</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>-1,97</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>14,30</t>
+          <t>12,48</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>48,800</t>
+          <t>48,701</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11545,32 +11545,32 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>6,63721700</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>0,089</t>
-        </is>
-      </c>
-      <c r="F99" s="6" t="inlineStr">
-        <is>
-          <t>-11,35</t>
+          <t>6,54339300</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>-1,413</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>-12,61</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>41,50</t>
+          <t>39,50</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>50,35</t>
+          <t>47,16</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>123,858</t>
+          <t>122,002</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -11662,32 +11662,32 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>1.323,79335000</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>-2,488</t>
-        </is>
-      </c>
-      <c r="F100" s="7" t="inlineStr">
-        <is>
-          <t>-5,02</t>
-        </is>
-      </c>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>-3,16</t>
-        </is>
-      </c>
-      <c r="H100" s="7" t="inlineStr">
-        <is>
-          <t>-12,54</t>
+          <t>1.321,22010500</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>-0,194</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>-5,20</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>-3,34</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>-12,35</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>42,531</t>
+          <t>42,429</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>39,32906600</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>-0,628</t>
+          <t>39,50562000</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>0,448</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>2,64</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>13,84</t>
+          <t>14,35</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>62,59</t>
+          <t>63,85</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>672,381</t>
+          <t>674,724</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -11896,32 +11896,32 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2,67069400</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>0,000</t>
-        </is>
-      </c>
-      <c r="F102" s="7" t="inlineStr">
-        <is>
-          <t>-0,76</t>
+          <t>2,64647000</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>-0,907</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>-1,66</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>9,25</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>26,30</t>
+          <t>22,10</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>444,288</t>
+          <t>440,181</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -12013,32 +12013,32 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>4,87185200</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>-0,526</t>
-        </is>
-      </c>
-      <c r="F103" s="6" t="inlineStr">
-        <is>
-          <t>-5,24</t>
+          <t>4,84905700</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>-0,467</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>-5,69</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>8,55</t>
+          <t>8,05</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>27,14</t>
+          <t>25,44</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>23,550</t>
+          <t>23,439</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -12130,32 +12130,32 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>1.528,22261500</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>-1,142</t>
-        </is>
-      </c>
-      <c r="F104" s="7" t="inlineStr">
-        <is>
-          <t>-5,73</t>
+          <t>1.522,21728900</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>-0,392</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>-6,10</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>4,59</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>16,98</t>
+          <t>15,36</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>30,627</t>
+          <t>30,484</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -12247,32 +12247,32 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>1,96731800</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>-0,909</t>
-        </is>
-      </c>
-      <c r="F105" s="6" t="inlineStr">
-        <is>
-          <t>-4,02</t>
-        </is>
-      </c>
-      <c r="G105" s="6" t="inlineStr">
-        <is>
-          <t>-3,29</t>
+          <t>1,96341000</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>-0,198</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>-4,21</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>-3,49</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>11,39</t>
+          <t>9,24</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>1,802</t>
+          <t>1,798</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -12364,32 +12364,32 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>5,97257000</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>-0,106</t>
-        </is>
-      </c>
-      <c r="F106" s="7" t="inlineStr">
-        <is>
-          <t>-5,54</t>
+          <t>5,92982800</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>-0,715</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>-6,21</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>11,02</t>
+          <t>10,23</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>29,14</t>
+          <t>27,01</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>44,331</t>
+          <t>44,013</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -12481,32 +12481,32 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>2,25158300</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>-0,425</t>
-        </is>
-      </c>
-      <c r="F107" s="6" t="inlineStr">
-        <is>
-          <t>-4,23</t>
+          <t>2,24044700</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>-0,494</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>-4,70</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>7,31</t>
+          <t>6,78</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>25,48</t>
+          <t>23,67</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>36,139</t>
+          <t>35,962</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -12598,32 +12598,32 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>43,76941000</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>0,401</t>
-        </is>
-      </c>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>-10,62</t>
+          <t>43,06610400</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>-1,606</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>-12,06</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>49,92</t>
+          <t>47,51</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>55,63</t>
+          <t>51,71</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>875,765</t>
+          <t>860,805</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -12715,32 +12715,32 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>0,88182400</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>-0,471</t>
-        </is>
-      </c>
-      <c r="F109" s="6" t="inlineStr">
-        <is>
-          <t>-4,04</t>
-        </is>
-      </c>
-      <c r="G109" s="6" t="inlineStr">
-        <is>
-          <t>-8,39</t>
-        </is>
-      </c>
-      <c r="H109" s="6" t="inlineStr">
-        <is>
-          <t>-16,98</t>
+          <t>0,87645700</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>-0,608</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>-4,62</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>-8,94</t>
+        </is>
+      </c>
+      <c r="H109" s="7" t="inlineStr">
+        <is>
+          <t>-18,10</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>2,985</t>
+          <t>2,966</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -12832,32 +12832,32 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>1,20364200</t>
-        </is>
-      </c>
-      <c r="E110" s="7" t="inlineStr">
-        <is>
-          <t>-0,288</t>
+          <t>1,20739200</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>0,311</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>0,52</t>
-        </is>
-      </c>
-      <c r="G110" s="7" t="inlineStr">
-        <is>
-          <t>-0,53</t>
+          <t>0,83</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>14,89</t>
+          <t>13,89</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>3,872</t>
+          <t>3,883</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -12949,32 +12949,32 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>1,31941700</t>
-        </is>
-      </c>
-      <c r="E111" s="6" t="inlineStr">
-        <is>
-          <t>-0,001</t>
-        </is>
-      </c>
-      <c r="F111" s="6" t="inlineStr">
-        <is>
-          <t>-0,77</t>
+          <t>1,30745200</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>-0,906</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>-1,67</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>10,18</t>
+          <t>9,18</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>26,12</t>
+          <t>21,93</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>19,626</t>
+          <t>19,439</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -13066,32 +13066,32 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1,81287400</t>
-        </is>
-      </c>
-      <c r="E112" s="7" t="inlineStr">
-        <is>
-          <t>-1,586</t>
-        </is>
-      </c>
-      <c r="F112" s="7" t="inlineStr">
-        <is>
-          <t>-13,67</t>
+          <t>1,78146200</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>-1,732</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>-15,16</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>3,63</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>71,39</t>
+          <t>66,20</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>280,269</t>
+          <t>275,345</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -13183,32 +13183,32 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>1.013,48075100</t>
-        </is>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
-        <is>
-          <t>-0,002</t>
-        </is>
-      </c>
-      <c r="F113" s="6" t="inlineStr">
-        <is>
-          <t>-5,28</t>
+          <t>1.010,25138700</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>-5,58</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>3,04</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>18,62</t>
+          <t>18,25</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>7,995</t>
+          <t>7,969</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -13300,32 +13300,32 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1.532,14438800</t>
-        </is>
-      </c>
-      <c r="E114" s="7" t="inlineStr">
-        <is>
-          <t>-0,005</t>
-        </is>
-      </c>
-      <c r="F114" s="7" t="inlineStr">
-        <is>
-          <t>-4,75</t>
+          <t>1.520,14123300</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>-5,50</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>14,20</t>
+          <t>13,31</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>22,304</t>
+          <t>22,121</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -13417,32 +13417,32 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>172,25114375</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>-0,679</t>
-        </is>
-      </c>
-      <c r="F115" s="6" t="inlineStr">
-        <is>
-          <t>-5,63</t>
+          <t>171,43867441</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>-0,471</t>
+        </is>
+      </c>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>-6,08</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>9,31</t>
+          <t>8,79</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>27,26</t>
+          <t>25,41</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>43,064</t>
+          <t>42,861</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -13486,32 +13486,32 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1,85223500</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="inlineStr">
-        <is>
-          <t>-1,623</t>
-        </is>
-      </c>
-      <c r="F116" s="7" t="inlineStr">
-        <is>
-          <t>-13,67</t>
+          <t>1,82015400</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>-1,732</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>-15,17</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>5,49</t>
+          <t>3,66</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>71,67</t>
+          <t>66,47</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>5,067</t>
+          <t>4,980</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -13603,32 +13603,32 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1,80646900</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>-1,634</t>
-        </is>
-      </c>
-      <c r="F117" s="6" t="inlineStr">
-        <is>
-          <t>-13,73</t>
+          <t>1,77482900</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>-1,751</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>-15,24</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>3,67</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>71,73</t>
+          <t>66,50</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>1.650,665</t>
+          <t>1.621,362</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -13720,32 +13720,32 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>48,69024100</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>0,403</t>
-        </is>
-      </c>
-      <c r="F118" s="7" t="inlineStr">
-        <is>
-          <t>-10,60</t>
+          <t>47,90709400</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>-1,608</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>-12,03</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>50,33</t>
+          <t>47,91</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>56,54</t>
+          <t>52,59</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>704,676</t>
+          <t>693,038</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -13837,32 +13837,32 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>43,57238600</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>-0,627</t>
+          <t>43,76866400</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>0,450</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>2,68</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>14,07</t>
+          <t>14,59</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>63,49</t>
+          <t>64,75</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>789,708</t>
+          <t>792,723</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -13954,32 +13954,32 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>16,72559700</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="inlineStr">
-        <is>
-          <t>-1,241</t>
-        </is>
-      </c>
-      <c r="F120" s="7" t="inlineStr">
-        <is>
-          <t>-5,68</t>
-        </is>
-      </c>
-      <c r="G120" s="7" t="inlineStr">
-        <is>
-          <t>-0,83</t>
+          <t>16,68958100</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>-0,215</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>-5,88</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>16,83</t>
+          <t>14,96</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>115,678</t>
+          <t>115,429</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -14071,32 +14071,32 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>36,53390100</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>-0,627</t>
+          <t>36,69751400</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>0,447</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>2,62</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>13,85</t>
+          <t>14,36</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>62,33</t>
+          <t>63,58</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>11,932</t>
+          <t>11,986</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
@@ -14188,32 +14188,32 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>43,02007600</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>0,401</t>
-        </is>
-      </c>
-      <c r="F122" s="7" t="inlineStr">
-        <is>
-          <t>-10,62</t>
+          <t>42,32924100</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>-1,605</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>-12,06</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>50,05</t>
+          <t>47,64</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>55,81</t>
+          <t>51,88</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>610,366</t>
+          <t>600,094</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -14305,32 +14305,32 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>37,51676900</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
-          <t>-0,628</t>
+          <t>37,68537500</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>0,449</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>2,64</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>13,85</t>
+          <t>14,36</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>62,61</t>
+          <t>63,87</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>472,667</t>
+          <t>474,680</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -14422,32 +14422,32 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>45,74194300</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>0,401</t>
-        </is>
-      </c>
-      <c r="F124" s="7" t="inlineStr">
-        <is>
-          <t>-10,60</t>
+          <t>45,00800600</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>-1,604</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>-12,04</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>50,21</t>
+          <t>47,80</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>56,16</t>
+          <t>52,23</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>702,242</t>
+          <t>690,870</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>1,12127500</t>
+          <t>1,12180200</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -14549,12 +14549,12 @@
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>0,80</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>4,80</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -14564,7 +14564,7 @@
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>56,895</t>
+          <t>55,285</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>1,35318700</t>
+          <t>1,35382500</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -14666,12 +14666,12 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>0,80</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>4,85</t>
+          <t>4,90</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>211,825</t>
+          <t>210,407</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -14725,32 +14725,32 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>5,86711500</t>
+          <t>5,86975800</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>5,22</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>13,98</t>
+          <t>13,96</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>41,562</t>
+          <t>41,527</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -14842,22 +14842,22 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>5,10616800</t>
+          <t>5,10883500</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>5,40</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>789,976</t>
+          <t>790,388</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>3,20791900</t>
+          <t>3,20956300</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>5,26</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>18,773</t>
+          <t>18,758</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -15076,32 +15076,32 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>23,74106200</t>
+          <t>23,75441000</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>0,023</t>
+          <t>0,056</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>6,04</t>
+          <t>6,10</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>11,94</t>
+          <t>11,83</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>94,949</t>
+          <t>95,002</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>3,26240600</t>
+          <t>3,26408300</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -15203,12 +15203,12 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>5,30</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>7.637,655</t>
+          <t>7.656,719</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -15310,7 +15310,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>1.879,50162300</t>
+          <t>1.880,51828300</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
@@ -15320,22 +15320,22 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>5,58</t>
+          <t>5,64</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>15,14</t>
+          <t>15,13</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>15.759,437</t>
+          <t>15.820,144</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -15427,32 +15427,32 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>4,86360500</t>
+          <t>4,86620400</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>14,75</t>
+          <t>14,74</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>3.076,217</t>
+          <t>3.070,220</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -15544,7 +15544,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1,54405187</t>
+          <t>1,54488430</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -15554,12 +15554,12 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
@@ -15569,7 +15569,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>344,157</t>
+          <t>337,752</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>5,10764800</t>
+          <t>5,11036300</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -15671,12 +15671,12 @@
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>5,50</t>
+          <t>5,56</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>284,694</t>
+          <t>284,846</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -15778,32 +15778,32 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>8,68284400</t>
+          <t>8,68749800</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>5,49</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>14,73</t>
+          <t>14,72</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>4.000,878</t>
+          <t>4.013,124</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -15895,32 +15895,32 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>17,85930100</t>
+          <t>17,86895400</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>14,81</t>
+          <t>14,80</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>4.782,367</t>
+          <t>4.782,507</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -16008,22 +16008,22 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>2,81669900</t>
+          <t>2,81804700</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>4,94</t>
+          <t>4,99</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>13.329,076</t>
+          <t>13.409,932</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -16125,22 +16125,22 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>4,41416800</t>
+          <t>4,41653300</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -16150,7 +16150,7 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>12.474,465</t>
+          <t>12.497,549</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -16242,22 +16242,22 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>1,36958700</t>
+          <t>1,37035500</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,056</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>5,57</t>
+          <t>5,63</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
@@ -16267,7 +16267,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.614,012</t>
+          <t>3.607,336</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -16359,7 +16359,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>1.766,76082200</t>
+          <t>1.767,69355600</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -16369,12 +16369,12 @@
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>5,48</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -16384,7 +16384,7 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>1.434,795</t>
+          <t>1.432,367</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -16476,22 +16476,22 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>1,30457500</t>
+          <t>1,30513300</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,042</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>4,43</t>
+          <t>4,48</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>33.961,548</t>
+          <t>33.599,489</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -16593,22 +16593,22 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>9,37720500</t>
+          <t>9,38151500</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>4,76</t>
+          <t>4,81</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
@@ -16618,7 +16618,7 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>2.923,563</t>
+          <t>2.914,312</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>2,46957900</t>
+          <t>2,47071500</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>4,76</t>
+          <t>4,80</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>15.479,484</t>
+          <t>16.583,962</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -16779,32 +16779,32 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>2,59823600</t>
+          <t>2,59958400</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>5,50</t>
+          <t>5,55</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>14,82</t>
+          <t>14,81</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>9.358,639</t>
+          <t>9.345,350</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
@@ -16896,32 +16896,32 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>2,40387900</t>
-        </is>
-      </c>
-      <c r="E146" s="7" t="inlineStr">
-        <is>
-          <t>-0,109</t>
+          <t>2,40447700</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>0,024</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>4,37</t>
+          <t>4,40</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>12,84</t>
+          <t>12,68</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>3.792,962</t>
+          <t>3.694,710</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -17013,32 +17013,32 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>2,98613300</t>
+          <t>2,98721600</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>0,004</t>
+          <t>0,036</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>5,89</t>
+          <t>5,93</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>12,01</t>
+          <t>11,85</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>41,813</t>
+          <t>41,828</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
@@ -17130,32 +17130,32 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1.639,69168900</t>
-        </is>
-      </c>
-      <c r="E148" s="7" t="inlineStr">
-        <is>
-          <t>-0,024</t>
+          <t>1.640,31984700</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>0,038</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>0,80</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>4,47</t>
+          <t>4,51</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>11,63</t>
+          <t>11,47</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>459,960</t>
+          <t>460,136</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -17247,32 +17247,32 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>4,46394000</t>
+          <t>4,46617600</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>0,033</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>5,20</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>14,23</t>
+          <t>14,22</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>11.160,417</t>
+          <t>11.001,217</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
@@ -17364,32 +17364,32 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>3,82122300</t>
+          <t>3,82201900</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>0,038</t>
+          <t>0,020</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>6,17</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>12,35</t>
+          <t>12,24</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2.983,638</t>
+          <t>2.984,945</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -17433,32 +17433,32 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>3,63189400</t>
-        </is>
-      </c>
-      <c r="E151" s="6" t="inlineStr">
-        <is>
-          <t>-0,161</t>
+          <t>3,63284000</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>0,026</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>4,03</t>
+          <t>4,06</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>13,08</t>
+          <t>12,71</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>1.745,899</t>
+          <t>1.749,153</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
@@ -17550,32 +17550,32 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>5,15628600</t>
+          <t>5,16595400</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>0,112</t>
+          <t>0,187</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>4,86</t>
+          <t>5,06</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>10,23</t>
+          <t>10,03</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2.583,526</t>
+          <t>2.588,433</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -17667,32 +17667,32 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>5,17971000</t>
+          <t>5,18235100</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>0,027</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>6,10</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>12,12</t>
+          <t>12,01</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>5.441,101</t>
+          <t>5.439,775</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
@@ -17784,32 +17784,32 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>4,74034200</t>
+          <t>4,74418800</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>0,020</t>
+          <t>0,081</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>5,02</t>
+          <t>5,10</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>13,28</t>
+          <t>13,15</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>514,732</t>
+          <t>512,759</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -17901,32 +17901,32 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>7,92259200</t>
+          <t>7,92674500</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>5,49</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>14,60</t>
+          <t>14,59</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>167,328</t>
+          <t>167,532</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
@@ -17970,32 +17970,32 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>3,46600700</t>
+          <t>3,47603800</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>0,189</t>
-        </is>
-      </c>
-      <c r="F156" s="7" t="inlineStr">
-        <is>
-          <t>-0,52</t>
+          <t>0,289</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
+        <is>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>3,88</t>
+          <t>4,18</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>8,81</t>
+          <t>8,59</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>821,013</t>
+          <t>774,745</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -18087,32 +18087,32 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>3,76837100</t>
-        </is>
-      </c>
-      <c r="E157" s="6" t="inlineStr">
-        <is>
-          <t>-0,236</t>
+          <t>3,76903800</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>0,017</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>3,64</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>12,63</t>
+          <t>12,09</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>721,422</t>
+          <t>720,447</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
@@ -18204,22 +18204,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>7,15013200</t>
+          <t>7,15396100</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>5,46</t>
+          <t>5,51</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>12.892,091</t>
+          <t>12.708,098</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -18321,7 +18321,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>7,46708200</t>
+          <t>7,47100400</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18331,12 +18331,12 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>5,40</t>
+          <t>5,45</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
@@ -18346,7 +18346,7 @@
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>5.207,598</t>
+          <t>5.165,152</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -18438,32 +18438,32 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>1,44626700</t>
-        </is>
-      </c>
-      <c r="E160" s="7" t="inlineStr">
-        <is>
-          <t>-0,164</t>
+          <t>1,44638100</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>0,007</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>3,72</t>
+          <t>3,73</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>12,36</t>
+          <t>12,03</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>172,666</t>
+          <t>172,680</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
@@ -18555,22 +18555,22 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>3,12939800</t>
+          <t>3,13094900</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>5,12</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
@@ -18580,7 +18580,7 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>1.859,155</t>
+          <t>2.188,264</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
@@ -18672,22 +18672,22 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>6,69620200</t>
+          <t>6,69966200</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>5,51</t>
+          <t>5,56</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>24.442,916</t>
+          <t>24.303,742</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -18741,32 +18741,32 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>5,52594700</t>
+          <t>5,53632700</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>0,107</t>
+          <t>0,187</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>5,33</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>10,62</t>
+          <t>10,46</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>597,248</t>
+          <t>598,370</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
@@ -18975,32 +18975,32 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>3,95902400</t>
-        </is>
-      </c>
-      <c r="E165" s="6" t="inlineStr">
-        <is>
-          <t>-0,684</t>
-        </is>
-      </c>
-      <c r="F165" s="6" t="inlineStr">
-        <is>
-          <t>-5,62</t>
+          <t>3,94073600</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t>-0,461</t>
+        </is>
+      </c>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>-6,05</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>9,34</t>
+          <t>8,84</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>27,30</t>
+          <t>25,46</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>299,957</t>
+          <t>298,545</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
@@ -19092,32 +19092,32 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>3,63815900</t>
-        </is>
-      </c>
-      <c r="E166" s="7" t="inlineStr">
-        <is>
-          <t>-0,680</t>
-        </is>
-      </c>
-      <c r="F166" s="7" t="inlineStr">
-        <is>
-          <t>-5,61</t>
+          <t>3,62432500</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>-0,380</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>-5,97</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>9,12</t>
+          <t>8,70</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>26,80</t>
+          <t>25,06</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>9,206</t>
+          <t>9,171</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -19209,32 +19209,32 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>11,30132976</t>
+          <t>11,40560718</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>0,280</t>
+          <t>0,922</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>7,08</t>
+          <t>8,07</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
         <is>
-          <t>23,51</t>
+          <t>23,43</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>2.332,770</t>
+          <t>2.355,362</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
@@ -19326,32 +19326,32 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>2,03740700</t>
-        </is>
-      </c>
-      <c r="E168" s="7" t="inlineStr">
-        <is>
-          <t>-0,712</t>
-        </is>
-      </c>
-      <c r="F168" s="7" t="inlineStr">
-        <is>
-          <t>-5,32</t>
+          <t>2,02607500</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>-0,556</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>-5,85</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>7,49</t>
+          <t>6,89</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>24,09</t>
+          <t>22,29</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>201,119</t>
+          <t>200,001</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -19443,32 +19443,32 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>2,03673200</t>
-        </is>
-      </c>
-      <c r="E169" s="6" t="inlineStr">
-        <is>
-          <t>-1,149</t>
-        </is>
-      </c>
-      <c r="F169" s="6" t="inlineStr">
-        <is>
-          <t>-5,91</t>
-        </is>
-      </c>
-      <c r="G169" s="6" t="inlineStr">
-        <is>
-          <t>-1,76</t>
+          <t>2,03257400</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>-0,204</t>
+        </is>
+      </c>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>-6,10</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>-1,96</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
         <is>
-          <t>14,81</t>
+          <t>12,87</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>771,017</t>
+          <t>767,866</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
@@ -19560,32 +19560,32 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>3,45793778</t>
-        </is>
-      </c>
-      <c r="E170" s="7" t="inlineStr">
-        <is>
-          <t>-0,579</t>
-        </is>
-      </c>
-      <c r="F170" s="7" t="inlineStr">
-        <is>
-          <t>-6,19</t>
+          <t>3,44333233</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>-0,422</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>-6,59</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>6,29</t>
+          <t>5,84</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>21,40</t>
+          <t>19,45</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>1.326,040</t>
+          <t>1.320,439</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -19673,32 +19673,32 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>2,52966840</t>
-        </is>
-      </c>
-      <c r="E171" s="6" t="inlineStr">
-        <is>
-          <t>-0,692</t>
-        </is>
-      </c>
-      <c r="F171" s="6" t="inlineStr">
-        <is>
-          <t>-6,87</t>
+          <t>2,51148698</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>-0,718</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>-7,54</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>7,02</t>
+          <t>6,25</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>23,47</t>
+          <t>21,15</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>782,985</t>
+          <t>777,357</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
@@ -19786,32 +19786,32 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>3,73559500</t>
+          <t>3,73740900</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>0,026</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>5,20</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>14,28</t>
+          <t>14,25</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>4.981,567</t>
+          <t>4.985,423</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,25289000</t>
+          <t>2,25393900</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -638,12 +638,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>4,89</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>406,209</t>
+          <t>406,208</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,47568800</t>
+          <t>5,47818700</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.618,678</t>
+          <t>6.636,438</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,76478100</t>
+          <t>2,76604300</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>4,74</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>862,231</t>
+          <t>875,466</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -931,22 +931,22 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>3,31629100</t>
+          <t>3,31805200</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>5,24</t>
+          <t>5,30</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>11,610</t>
+          <t>11,643</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -1000,32 +1000,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,46989100</t>
+          <t>3,47183100</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>5,42</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>14,33</t>
+          <t>14,34</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>120,029</t>
+          <t>120,016</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1117,32 +1117,32 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1.826,33503800</t>
+          <t>1.827,43144600</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,060</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>5,45</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>14,64</t>
+          <t>14,65</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>97,117</t>
+          <t>97,147</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1234,22 +1234,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,66098400</t>
+          <t>9,66586600</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>5,02</t>
+          <t>5,07</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>586,371</t>
+          <t>586,494</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1351,22 +1351,22 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3,34015900</t>
+          <t>3,34194900</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>5,40</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>61,213</t>
+          <t>61,593</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1468,22 +1468,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,98201400</t>
+          <t>2,98368300</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>5,51</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1.673,521</t>
+          <t>1.672,734</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1533,32 +1533,32 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>19,85614100</t>
+          <t>19,87196000</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>0,017</t>
+          <t>0,079</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,50</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>3,59</t>
+          <t>3,67</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>11,59</t>
+          <t>11,79</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>123,315</t>
+          <t>123,407</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,50016200</t>
+          <t>13,50067400</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,003</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>9,89</t>
+          <t>9,95</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,441</t>
+          <t>28,385</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1767,22 +1767,22 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>45,94775300</t>
+          <t>45,97090600</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>5,06</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>40,681</t>
+          <t>40,697</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1884,22 +1884,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20,12501200</t>
+          <t>20,13475900</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>4,92</t>
+          <t>4,97</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,825</t>
+          <t>64,855</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>3,14272800</t>
+          <t>3,14301500</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,009</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>5,81</t>
+          <t>5,82</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>11,06</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>79,838</t>
+          <t>79,846</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -2118,32 +2118,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14,88493500</t>
+          <t>14,89248500</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>5,09</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>13,42</t>
+          <t>13,43</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,942</t>
+          <t>27,956</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2235,22 +2235,22 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2,98642600</t>
+          <t>2,98789700</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>4,90</t>
+          <t>4,95</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>1,658</t>
+          <t>1,659</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -2352,32 +2352,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,31100200</t>
+          <t>3,31364200</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>0,024</t>
+          <t>0,079</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>3,88</t>
+          <t>3,97</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>12,15</t>
+          <t>12,33</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>139,719</t>
+          <t>139,416</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2469,22 +2469,22 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,02443500</t>
+          <t>3,02610500</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>1,00</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>5,51</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1.769,116</t>
+          <t>1.762,291</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2586,22 +2586,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32,63376400</t>
+          <t>32,65075800</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>5,24</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2.183,896</t>
+          <t>2.183,150</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2703,32 +2703,32 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,28985500</t>
+          <t>3,29157000</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>5,24</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>13,83</t>
+          <t>13,84</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>13,238</t>
+          <t>13,225</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2820,32 +2820,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3,34869300</t>
+          <t>3,35138200</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0,185</t>
+          <t>0,080</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>0,30</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>5,07</t>
+          <t>5,15</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>9,77</t>
+          <t>10,09</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,034</t>
+          <t>66,975</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2937,22 +2937,22 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>18,94345500</t>
+          <t>18,95394700</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>5,30</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>958,322</t>
+          <t>957,954</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,11226478</t>
+          <t>1,11379329</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>0,20</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>3,25</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>212,570</t>
+          <t>212,889</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1,23415200</t>
+          <t>1,23477000</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -3129,22 +3129,22 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>5,37</t>
+          <t>5,42</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>14,74</t>
+          <t>14,65</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>70,922</t>
+          <t>71,036</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -3236,32 +3236,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1.822,70482500</t>
+          <t>1.823,78818500</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,059</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>14,80</t>
+          <t>14,81</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>175,296</t>
+          <t>175,381</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3305,32 +3305,32 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1,19887700</t>
+          <t>1,19950400</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>0,071</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>6,67</t>
+          <t>6,73</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>12,93</t>
+          <t>13,03</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>40,268</t>
+          <t>40,289</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,03429800</t>
+          <t>1,03485900</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>1,00</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,870</t>
+          <t>21,832</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3535,32 +3535,32 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,16252900</t>
+          <t>1,16326800</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>-0,001</t>
+          <t>-0,002</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>4,75</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>13,93</t>
+          <t>13,87</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>66,619</t>
+          <t>66,778</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,06417019</t>
+          <t>1,06553868</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2,98</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>317,863</t>
+          <t>317,610</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3874,22 +3874,22 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>5,11501700</t>
+          <t>5,11789700</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,056</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>5,50</t>
+          <t>5,56</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>861,211</t>
+          <t>860,995</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3991,22 +3991,22 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>4,92146700</t>
+          <t>4,92420100</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>5,50</t>
+          <t>5,56</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.247,360</t>
+          <t>3.247,484</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>29,12307500</t>
+          <t>29,13713400</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -4118,12 +4118,12 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>5,06</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,261</t>
+          <t>21,271</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4225,22 +4225,22 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>30,46813500</t>
+          <t>30,48531800</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,056</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>5,41</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>3.114,359</t>
+          <t>3.113,221</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -4342,32 +4342,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1.767,21709000</t>
+          <t>1.768,23032800</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,057</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>4,91</t>
+          <t>4,97</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>13,58</t>
+          <t>13,63</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>125,761</t>
+          <t>125,729</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4459,22 +4459,22 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>3,20754700</t>
+          <t>3,20929300</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>5,55</t>
+          <t>5,60</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>585,653</t>
+          <t>586,833</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -4576,22 +4576,22 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>6,16015300</t>
+          <t>6,16357300</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>5,32</t>
+          <t>5,37</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>122,521</t>
+          <t>122,581</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1,26314500</t>
+          <t>1,26385900</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,056</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>5,60</t>
+          <t>5,66</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>336,068</t>
+          <t>336,196</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -4810,32 +4810,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>10,54450400</t>
+          <t>10,55052700</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,057</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>14,68</t>
+          <t>14,69</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2.388,251</t>
+          <t>2.387,712</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4927,32 +4927,32 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>5,49139000</t>
+          <t>5,49451900</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,056</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>5,58</t>
+          <t>5,64</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>14,87</t>
+          <t>14,88</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>555,822</t>
+          <t>555,805</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -5044,22 +5044,22 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3,55103400</t>
+          <t>3,55303400</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,056</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>5,58</t>
+          <t>5,64</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15.553,300</t>
+          <t>15.548,132</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5161,22 +5161,22 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>5,27797400</t>
+          <t>5,28106100</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,058</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,11</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>5,64</t>
+          <t>5,70</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>1.388,992</t>
+          <t>1.389,713</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -5278,22 +5278,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>30,20799000</t>
+          <t>30,22306900</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>4,98</t>
+          <t>5,03</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>165,235</t>
+          <t>165,025</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2,79736700</t>
+          <t>2,79869700</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>4,91</t>
+          <t>4,96</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5.924,117</t>
+          <t>5.946,271</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5625,22 +5625,22 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>3,58867700</t>
+          <t>3,59060700</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>5,41</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>2.188,171</t>
+          <t>2.184,635</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -5742,22 +5742,22 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1,28481800</t>
+          <t>1,28552700</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>64,132</t>
+          <t>63,995</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5859,22 +5859,22 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>9,64092300</t>
+          <t>9,64614300</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>5,40</t>
+          <t>5,45</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>838,988</t>
+          <t>838,232</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -5976,22 +5976,22 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>4,43682500</t>
+          <t>4,43924600</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>5,46</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15.786,780</t>
+          <t>15.803,258</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -6093,22 +6093,22 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>4,75217300</t>
+          <t>4,75480300</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>9.435,426</t>
+          <t>9.471,954</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -6210,22 +6210,22 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>5,07805100</t>
+          <t>5,08085900</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>5,60</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>21.060,080</t>
+          <t>21.102,523</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6279,22 +6279,22 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>3,17164400</t>
+          <t>3,17341800</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>1,00</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>5,59</t>
+          <t>5,64</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>13.327,624</t>
+          <t>13.359,359</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1.722,39705500</t>
+          <t>1.723,27960700</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -6406,22 +6406,22 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>5,32</t>
+          <t>5,37</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>14,20</t>
+          <t>14,19</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>248,039</t>
+          <t>248,329</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6465,32 +6465,32 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1,40659200</t>
+          <t>1,40737500</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>-0,070</t>
+          <t>-0,100</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>5,05</t>
+          <t>5,11</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>14,28</t>
+          <t>14,21</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>68,048</t>
+          <t>68,089</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1.194,40400600</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>-0,003</t>
+          <t>1.201,73817000</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>0,000</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>4,55</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>-4,81</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>0,15</t>
+          <t>-4,22</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>-0,44</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>36,466</t>
+          <t>36,689</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6699,27 +6699,27 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>12,60968300</t>
+          <t>12,60560700</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>-0,084</t>
+          <t>-0,032</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>6,22</t>
+          <t>6,19</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>17,17</t>
+          <t>17,22</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1.637,45665300</t>
+          <t>1.637,83796800</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -6778,22 +6778,22 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>4,50</t>
+          <t>4,52</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>13,26</t>
+          <t>13,14</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>115,436</t>
+          <t>115,439</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6885,32 +6885,32 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>2.411,08312700</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>-0,471</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>-0,56</t>
+          <t>2.425,93346700</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>0,615</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>0,04</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>17,38</t>
+          <t>18,10</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>36,21</t>
+          <t>38,09</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>12,731</t>
+          <t>12,811</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -7115,32 +7115,32 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1,25212400</t>
+          <t>1,25246300</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>-0,075</t>
+          <t>-0,056</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,26</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>11,04</t>
+          <t>10,84</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>6,428</t>
+          <t>6,430</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -7232,32 +7232,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1,14863900</t>
+          <t>1,14588800</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>-0,026</t>
+          <t>-0,239</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>-5,07</t>
+          <t>-5,30</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>-0,93</t>
+          <t>-1,17</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>13,60</t>
+          <t>13,33</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>3,480</t>
+          <t>3,471</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7462,27 +7462,27 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1,42927100</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>-0,046</t>
+          <t>1,42936300</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>0,463</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>-2,68</t>
+          <t>-2,67</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>4,70</t>
+          <t>4,71</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>19,18</t>
+          <t>18,21</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -7692,32 +7692,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1,11052300</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>0,556</t>
+          <t>1,10633100</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>-0,377</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>-7,89</t>
+          <t>-8,24</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>-6,37</t>
+          <t>-7,15</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>3,754</t>
+          <t>3,740</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>5,33911469</t>
+          <t>5,34058191</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
@@ -7819,22 +7819,22 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>4,05</t>
+          <t>4,08</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>13,04</t>
+          <t>12,92</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>33,105</t>
+          <t>33,121</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -7926,32 +7926,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>4,64191300</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>-1,142</t>
+          <t>4,69708700</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>1,188</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>-3,12</t>
+          <t>-1,97</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>4,47</t>
+          <t>5,71</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>41,82</t>
+          <t>43,77</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>624,426</t>
+          <t>628,734</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8043,32 +8043,32 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>2,85255900</t>
+          <t>2,85870900</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>-0,278</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>0,00</t>
+          <t>-0,005</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>0,20</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>2,13</t>
+          <t>2,35</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>10,52</t>
+          <t>10,69</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>75,658</t>
+          <t>74,892</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -8160,32 +8160,32 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1.662,22720900</t>
+          <t>1.663,23209600</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>0,336</t>
+          <t>0,060</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>2,65</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>5,50</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>11,74</t>
+          <t>11,64</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>29,455</t>
+          <t>28,982</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8277,32 +8277,32 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>3,79685400</t>
+          <t>3,82068800</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>0,090</t>
+          <t>0,627</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>4,92</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>12,87</t>
+          <t>13,57</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>38,62</t>
+          <t>40,14</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>2.377,702</t>
+          <t>2.396,127</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -8394,32 +8394,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1,90309100</t>
+          <t>1,90423600</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,060</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>4,68</t>
+          <t>4,75</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>12,93</t>
+          <t>12,98</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>21,929</t>
+          <t>21,943</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1.658,50876800</t>
+          <t>1.658,94629200</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
@@ -8521,22 +8521,22 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>4,87</t>
+          <t>4,89</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>14,24</t>
+          <t>14,11</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>14,865</t>
+          <t>14,834</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -8624,22 +8624,22 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>0,53812850</t>
+          <t>0,53709651</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>-0,008</t>
+          <t>-0,006</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>-0,80</t>
+          <t>-0,99</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>-25,47</t>
+          <t>-25,61</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>3,934</t>
+          <t>3,922</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>3,25667400</t>
+          <t>3,25997400</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
@@ -8751,22 +8751,22 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>8,06</t>
+          <t>7,59</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>155,178</t>
+          <t>155,336</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1,54589900</t>
+          <t>1,54644700</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -8868,22 +8868,22 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>0,80</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>3,53</t>
+          <t>3,57</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>20,28</t>
+          <t>19,92</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>14,632</t>
+          <t>14,637</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1,38067900</t>
+          <t>1,38394900</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
@@ -8985,22 +8985,22 @@
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>-1,21</t>
+          <t>-0,98</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>1,80</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>8,00</t>
+          <t>7,99</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>70,870</t>
+          <t>71,012</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1,48736200</t>
+          <t>1,50131600</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -9102,22 +9102,22 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2,55</t>
+          <t>3,51</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2,85</t>
+          <t>3,81</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>15,55</t>
+          <t>16,22</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>192,942</t>
+          <t>194,752</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9209,32 +9209,32 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1,77711100</t>
+          <t>1,77823300</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>-0,001</t>
+          <t>-0,002</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>1,00</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>9,64</t>
+          <t>10,06</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>176,384</t>
+          <t>176,496</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -9326,32 +9326,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>5,61030600</t>
+          <t>5,61529800</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>0,039</t>
+          <t>0,088</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>5,38</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>14,64</t>
+          <t>14,70</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>902,733</t>
+          <t>903,133</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9443,32 +9443,32 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>3,64656700</t>
+          <t>3,64881400</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,061</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>4,90</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>13,34</t>
+          <t>13,39</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>747,368</t>
+          <t>747,374</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -9560,32 +9560,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>6,81637700</t>
+          <t>6,81879100</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>-0,003</t>
+          <t>-0,004</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>5,98</t>
+          <t>6,02</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>16,54</t>
+          <t>16,78</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>129,925</t>
+          <t>129,972</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>1,41991200</t>
+          <t>1,42081800</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -9687,22 +9687,22 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>3,06</t>
+          <t>3,13</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>16,68</t>
+          <t>16,35</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>280,907</t>
+          <t>280,683</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -9794,32 +9794,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,32082100</t>
+          <t>1,32665300</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>-0,002</t>
+          <t>-0,006</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2,90</t>
+          <t>3,36</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>2,64</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>13,358</t>
+          <t>13,416</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9911,32 +9911,32 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>3,76861800</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>0,559</t>
+          <t>3,74929100</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>-0,512</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>2,28</t>
+          <t>1,76</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>-6,25</t>
+          <t>-6,73</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>-6,13</t>
+          <t>-7,40</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>97,109</t>
+          <t>96,505</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -10028,32 +10028,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>6,71695800</t>
+          <t>6,68288400</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>-0,230</t>
+          <t>-0,507</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>-6,08</t>
+          <t>-6,55</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>5,90</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>19,96</t>
+          <t>20,07</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>344,965</t>
+          <t>343,221</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10145,32 +10145,32 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>2,61349600</t>
+          <t>2,60370200</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>-0,461</t>
+          <t>-0,374</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>-6,05</t>
+          <t>-6,40</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>8,62</t>
+          <t>8,21</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>24,86</t>
+          <t>24,97</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>13,583</t>
+          <t>13,531</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -10262,32 +10262,32 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1.954,16075200</t>
+          <t>1.945,69007700</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>-0,199</t>
+          <t>-0,433</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>-6,04</t>
+          <t>-6,44</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>-1,56</t>
+          <t>-1,98</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>13,75</t>
+          <t>13,40</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>10,437</t>
+          <t>10,384</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10375,32 +10375,32 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>10,17538000</t>
+          <t>10,19819600</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>0,918</t>
+          <t>0,224</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>8,00</t>
+          <t>8,24</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>2,76</t>
+          <t>2,99</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>22,42</t>
+          <t>22,09</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>280,963</t>
+          <t>281,573</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -10492,32 +10492,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1,48407900</t>
+          <t>1,48255500</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>-0,607</t>
+          <t>-0,102</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>-3,06</t>
+          <t>-3,16</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>-2,64</t>
+          <t>-2,74</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>1,61</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>450,467</t>
+          <t>450,000</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10609,32 +10609,32 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1,12496700</t>
+          <t>1,11983100</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>-0,451</t>
+          <t>-0,456</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>-1,99</t>
+          <t>-2,44</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>-3,34</t>
+          <t>-3,78</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>-1,49</t>
+          <t>-2,28</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>58,134</t>
+          <t>57,867</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1,72984000</t>
+          <t>1,72179300</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>-0,515</t>
+          <t>-0,465</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>-6,85</t>
+          <t>-7,28</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>9,82</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2,156</t>
+          <t>2,146</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10843,32 +10843,32 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>4,64360100</t>
+          <t>4,58976700</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>-1,608</t>
+          <t>-1,159</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>-12,06</t>
+          <t>-13,08</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>47,45</t>
+          <t>45,74</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>51,59</t>
+          <t>51,70</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>78,943</t>
+          <t>77,906</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -10960,32 +10960,32 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>8,75893800</t>
+          <t>8,72571600</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>-0,465</t>
+          <t>-0,379</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>-6,12</t>
+          <t>-6,48</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>8,18</t>
+          <t>7,77</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>23,52</t>
+          <t>23,63</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>91,453</t>
+          <t>91,020</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -11077,32 +11077,32 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1,29144100</t>
+          <t>1,28567500</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>-0,040</t>
+          <t>-0,042</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>-5,42</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>0,33</t>
+          <t>-5,85</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>10,22</t>
+          <t>8,12</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>292,507</t>
+          <t>291,197</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -11194,32 +11194,32 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>1,86617000</t>
+          <t>1,86378300</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>-0,768</t>
+          <t>-0,127</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>-2,75</t>
+          <t>-2,87</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
-          <t>-1,85</t>
+          <t>-1,97</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>16,91</t>
+          <t>16,94</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>115,190</t>
+          <t>115,014</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11311,32 +11311,32 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>2,91876600</t>
+          <t>2,90661300</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>-1,082</t>
+          <t>-0,416</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>-9,35</t>
+          <t>-9,73</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>7,09</t>
+          <t>6,64</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>17,76</t>
+          <t>17,49</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>128,390</t>
+          <t>127,811</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -11428,32 +11428,32 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1,89931800</t>
+          <t>1,89101400</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>-0,203</t>
+          <t>-0,437</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>-6,10</t>
+          <t>-6,51</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>-1,97</t>
+          <t>-2,40</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>12,48</t>
+          <t>12,14</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>48,701</t>
+          <t>48,488</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11545,32 +11545,32 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>6,54339300</t>
+          <t>6,49637000</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>-1,413</t>
+          <t>-0,718</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>-12,61</t>
+          <t>-13,23</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>39,50</t>
+          <t>38,50</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>47,16</t>
+          <t>46,56</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>122,002</t>
+          <t>120,951</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -11662,32 +11662,32 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>1.321,22010500</t>
+          <t>1.292,41673600</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>-0,194</t>
+          <t>-2,180</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>-5,20</t>
+          <t>-7,27</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>-3,34</t>
+          <t>-5,45</t>
         </is>
       </c>
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>-12,35</t>
+          <t>-12,52</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>42,429</t>
+          <t>41,554</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>39,50562000</t>
+          <t>39,74376400</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>0,448</t>
+          <t>0,602</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>2,64</t>
+          <t>3,26</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>14,35</t>
+          <t>15,04</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>63,85</t>
+          <t>66,17</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>674,724</t>
+          <t>678,069</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -11896,32 +11896,32 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2,64647000</t>
+          <t>2,64343000</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>-0,907</t>
+          <t>-0,114</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>-1,77</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>9,25</t>
+          <t>9,12</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>22,10</t>
+          <t>23,71</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>440,181</t>
+          <t>439,491</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -12013,32 +12013,32 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>4,84905700</t>
+          <t>4,83614700</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>-0,467</t>
+          <t>-0,266</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>-5,69</t>
+          <t>-5,94</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>8,05</t>
+          <t>7,76</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>25,44</t>
+          <t>25,63</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>23,439</t>
+          <t>23,391</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -12130,32 +12130,32 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>1.522,21728900</t>
+          <t>1.510,08429300</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>-0,392</t>
+          <t>-0,797</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>-6,10</t>
+          <t>-6,85</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>4,59</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>15,36</t>
+          <t>14,79</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>30,484</t>
+          <t>30,245</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -12247,32 +12247,32 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>1,96341000</t>
+          <t>1,95601800</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>-0,198</t>
+          <t>-0,376</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>-4,21</t>
+          <t>-4,57</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>-3,49</t>
+          <t>-3,85</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>9,24</t>
+          <t>9,19</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>1,798</t>
+          <t>1,791</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -12364,32 +12364,32 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>5,92982800</t>
+          <t>5,88765100</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>-0,715</t>
+          <t>-0,711</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>-6,21</t>
+          <t>-6,88</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>10,23</t>
+          <t>9,44</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>27,01</t>
+          <t>26,78</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>44,013</t>
+          <t>43,700</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -12481,32 +12481,32 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>2,24044700</t>
+          <t>2,23637400</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>-0,494</t>
+          <t>-0,181</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>-4,70</t>
+          <t>-4,87</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>6,78</t>
+          <t>6,58</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>23,67</t>
+          <t>23,93</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>35,962</t>
+          <t>35,919</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -12598,32 +12598,32 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>43,06610400</t>
+          <t>42,56626500</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>-1,606</t>
+          <t>-1,160</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>-12,06</t>
+          <t>-13,08</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>47,51</t>
+          <t>45,80</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>51,71</t>
+          <t>51,82</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>860,805</t>
+          <t>849,780</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -12715,32 +12715,32 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>0,87645700</t>
+          <t>0,86880900</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>-0,608</t>
+          <t>-0,872</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>-4,62</t>
+          <t>-5,45</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>-8,94</t>
+          <t>-9,74</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>-18,10</t>
+          <t>-18,74</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>2,966</t>
+          <t>2,939</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -12832,32 +12832,32 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>1,20739200</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>0,311</t>
+          <t>1,20192300</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>-0,452</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-0,67</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>13,89</t>
+          <t>13,51</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>3,883</t>
+          <t>3,868</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -12949,32 +12949,32 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>1,30745200</t>
+          <t>1,30594200</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>-0,906</t>
+          <t>-0,115</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>-1,67</t>
+          <t>-1,78</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>9,18</t>
+          <t>9,06</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>21,93</t>
+          <t>23,53</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>19,439</t>
+          <t>19,415</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -13066,32 +13066,32 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1,78146200</t>
-        </is>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>-1,732</t>
+          <t>1,78540400</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>0,221</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>-15,16</t>
+          <t>-14,98</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>3,86</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>66,20</t>
+          <t>69,16</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>275,345</t>
+          <t>275,870</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>1.010,25138700</t>
+          <t>1.004,38746200</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
@@ -13193,22 +13193,22 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>-5,58</t>
+          <t>-6,13</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>2,45</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>18,25</t>
+          <t>16,59</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>7,969</t>
+          <t>7,923</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1.520,14123300</t>
+          <t>1.508,88063300</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -13310,22 +13310,22 @@
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>-5,50</t>
+          <t>-6,20</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>13,31</t>
+          <t>11,15</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>22,121</t>
+          <t>21,944</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -13417,32 +13417,32 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>171,43867441</t>
+          <t>170,78522583</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>-0,471</t>
+          <t>-0,381</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>-6,08</t>
+          <t>-6,44</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>8,79</t>
+          <t>8,38</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>25,41</t>
+          <t>25,51</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>42,861</t>
+          <t>42,698</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -13486,32 +13486,32 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1,82015400</t>
-        </is>
-      </c>
-      <c r="E116" s="6" t="inlineStr">
-        <is>
-          <t>-1,732</t>
+          <t>1,82459800</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>0,244</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>-15,17</t>
+          <t>-14,96</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>3,66</t>
+          <t>3,92</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>66,47</t>
+          <t>69,48</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>4,980</t>
+          <t>4,992</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -13603,32 +13603,32 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1,77482900</t>
-        </is>
-      </c>
-      <c r="E117" s="7" t="inlineStr">
-        <is>
-          <t>-1,751</t>
+          <t>1,77919100</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>0,245</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>-15,24</t>
+          <t>-15,03</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>3,67</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>66,50</t>
+          <t>69,51</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>1.621,362</t>
+          <t>1.624,495</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -13720,32 +13720,32 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>47,90709400</t>
+          <t>47,35253200</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>-1,608</t>
+          <t>-1,157</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>-12,03</t>
+          <t>-13,05</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>47,91</t>
+          <t>46,20</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>52,59</t>
+          <t>52,70</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>693,038</t>
+          <t>684,781</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -13837,32 +13837,32 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>43,76866400</t>
+          <t>44,03307600</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>0,450</t>
+          <t>0,604</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>3,30</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>14,59</t>
+          <t>15,28</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>64,75</t>
+          <t>67,09</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>792,723</t>
+          <t>796,429</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -13954,32 +13954,32 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>16,68958100</t>
+          <t>16,61026700</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>-0,215</t>
+          <t>-0,475</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>-5,88</t>
+          <t>-6,33</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>-1,04</t>
+          <t>-1,51</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>14,96</t>
+          <t>14,41</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>115,429</t>
+          <t>114,692</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -14071,32 +14071,32 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>36,69751400</t>
+          <t>36,91807100</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>0,447</t>
+          <t>0,601</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>3,24</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>14,36</t>
+          <t>15,05</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>63,58</t>
+          <t>65,89</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>11,986</t>
+          <t>12,066</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
@@ -14188,32 +14188,32 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>42,32924100</t>
+          <t>41,83855800</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>-1,605</t>
+          <t>-1,159</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>-12,06</t>
+          <t>-13,08</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>47,64</t>
+          <t>45,93</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>51,88</t>
+          <t>51,99</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>600,094</t>
+          <t>592,734</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -14305,32 +14305,32 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>37,68537500</t>
+          <t>37,91258700</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>0,449</t>
+          <t>0,602</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>2,64</t>
+          <t>3,26</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>14,36</t>
+          <t>15,05</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>63,87</t>
+          <t>66,20</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>474,680</t>
+          <t>477,436</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -14422,32 +14422,32 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>45,00800600</t>
+          <t>44,48709800</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>-1,604</t>
+          <t>-1,157</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>-12,04</t>
+          <t>-13,06</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>47,80</t>
+          <t>46,09</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>52,23</t>
+          <t>52,34</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>690,870</t>
+          <t>682,046</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -14539,22 +14539,22 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>1,12180200</t>
+          <t>1,12232800</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>4,85</t>
+          <t>4,89</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -14564,7 +14564,7 @@
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>55,285</t>
+          <t>54,437</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>1,35382500</t>
+          <t>1,35446400</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -14666,12 +14666,12 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>4,90</t>
+          <t>4,95</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>210,407</t>
+          <t>215,161</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -14725,32 +14725,32 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>5,86975800</t>
+          <t>5,87296400</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>5,22</t>
+          <t>5,28</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>13,96</t>
+          <t>13,97</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>41,527</t>
+          <t>41,523</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>5,10883500</t>
+          <t>5,11151700</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -14852,12 +14852,12 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>5,46</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>790,388</t>
+          <t>790,803</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -14959,32 +14959,32 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>3,20956300</t>
+          <t>3,21124000</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>5,31</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>13,83</t>
+          <t>13,84</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>18,758</t>
+          <t>18,724</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -15076,32 +15076,32 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>23,75441000</t>
+          <t>23,75723300</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,011</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>6,10</t>
+          <t>6,11</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>11,83</t>
+          <t>11,89</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>95,002</t>
+          <t>94,994</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>3,26408300</t>
+          <t>3,26577600</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -15203,12 +15203,12 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>5,41</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>7.656,719</t>
+          <t>7.700,396</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -15310,22 +15310,22 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>1.880,51828300</t>
+          <t>1.881,61004800</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,058</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>1,10</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>5,64</t>
+          <t>5,70</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
@@ -15335,7 +15335,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>15.820,144</t>
+          <t>15.857,627</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -15427,32 +15427,32 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>4,86620400</t>
+          <t>4,86884700</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>5,59</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>14,74</t>
+          <t>14,75</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>3.070,220</t>
+          <t>3.062,202</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -15544,7 +15544,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1,54488430</t>
+          <t>1,54570566</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -15554,12 +15554,12 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>5,59</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
@@ -15569,7 +15569,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>337,752</t>
+          <t>337,932</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>5,11036300</t>
+          <t>5,11309000</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -15671,12 +15671,12 @@
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>5,56</t>
+          <t>5,61</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>284,846</t>
+          <t>284,998</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -15778,22 +15778,22 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>8,68749800</t>
+          <t>8,69221500</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>5,49</t>
+          <t>5,55</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>4.013,124</t>
+          <t>4.011,483</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -15895,7 +15895,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>17,86895400</t>
+          <t>17,87866600</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -15905,22 +15905,22 @@
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>5,60</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>14,80</t>
+          <t>14,81</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>4.782,507</t>
+          <t>4.779,520</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -16008,22 +16008,22 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>2,81804700</t>
+          <t>2,81940900</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>4,99</t>
+          <t>5,04</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>13.409,932</t>
+          <t>13.490,382</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -16125,22 +16125,22 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>4,41653300</t>
+          <t>4,41895400</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>5,57</t>
+          <t>5,63</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -16150,7 +16150,7 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>12.497,549</t>
+          <t>12.537,559</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -16242,22 +16242,22 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>1,37035500</t>
+          <t>1,37109700</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>5,69</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
@@ -16267,7 +16267,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.607,336</t>
+          <t>3.562,893</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -16359,7 +16359,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>1.767,69355600</t>
+          <t>1.768,62679700</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -16369,12 +16369,12 @@
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -16384,7 +16384,7 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>1.432,367</t>
+          <t>1.430,784</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -16476,22 +16476,22 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>1,30513300</t>
+          <t>1,30569900</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>4,48</t>
+          <t>4,52</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>33.599,489</t>
+          <t>33.604,927</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -16593,32 +16593,32 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>9,38151500</t>
+          <t>9,38588300</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>4,81</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>12,51</t>
+          <t>12,52</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>2.914,312</t>
+          <t>3.007,180</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>2,47071500</t>
+          <t>2,47179400</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>4,80</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>16.583,962</t>
+          <t>16.505,497</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -16779,22 +16779,22 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>2,59958400</t>
+          <t>2,60104500</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,056</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>5,55</t>
+          <t>5,61</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>9.345,350</t>
+          <t>9.222,055</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
@@ -16896,32 +16896,32 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>2,40447700</t>
+          <t>2,40623300</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>0,024</t>
+          <t>0,073</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>4,40</t>
+          <t>4,48</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>12,68</t>
+          <t>12,78</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>3.694,710</t>
+          <t>3.696,432</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -17013,12 +17013,12 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>2,98721600</t>
+          <t>2,98741300</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>0,036</t>
+          <t>0,006</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
@@ -17033,12 +17033,12 @@
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>11,85</t>
+          <t>11,90</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>41,828</t>
+          <t>40,361</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
@@ -17130,32 +17130,32 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1.640,31984700</t>
+          <t>1.641,35346900</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>0,038</t>
+          <t>0,063</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>4,51</t>
+          <t>4,58</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>11,47</t>
+          <t>11,59</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>460,136</t>
+          <t>460,426</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -17247,32 +17247,32 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>4,46617600</t>
+          <t>4,46861000</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>14,22</t>
+          <t>14,23</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>11.001,217</t>
+          <t>10.902,457</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
@@ -17364,32 +17364,32 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>3,82201900</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>0,020</t>
+          <t>3,82148700</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>-0,013</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>6,17</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>12,24</t>
+          <t>12,27</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2.984,945</t>
+          <t>2.981,867</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -17433,32 +17433,32 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>3,63284000</t>
+          <t>3,63578600</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>0,026</t>
+          <t>0,081</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>4,06</t>
+          <t>4,14</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>12,71</t>
+          <t>12,88</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>1.749,153</t>
+          <t>1.742,597</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
@@ -17550,32 +17550,32 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>5,16595400</t>
+          <t>5,17026900</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>0,187</t>
+          <t>0,083</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>5,06</t>
+          <t>5,15</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>10,03</t>
+          <t>10,36</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2.588,433</t>
+          <t>2.587,898</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -17667,32 +17667,32 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>5,18235100</t>
+          <t>5,18294500</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,011</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>6,16</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>12,01</t>
+          <t>12,06</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>5.439,775</t>
+          <t>5.434,646</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
@@ -17784,32 +17784,32 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>4,74418800</t>
+          <t>4,74738900</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>0,081</t>
+          <t>0,067</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>5,10</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>13,15</t>
+          <t>13,27</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>512,759</t>
+          <t>512,700</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -17901,32 +17901,32 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>7,92674500</t>
+          <t>7,93104100</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>5,49</t>
+          <t>5,55</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>14,59</t>
+          <t>14,60</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>167,532</t>
+          <t>167,639</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
@@ -17970,32 +17970,32 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>3,47603800</t>
+          <t>3,48105100</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>0,289</t>
+          <t>0,144</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>4,18</t>
+          <t>4,33</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>8,59</t>
+          <t>9,10</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>774,745</t>
+          <t>775,862</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -18087,32 +18087,32 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>3,76903800</t>
+          <t>3,77253800</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>0,017</t>
+          <t>0,092</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>3,64</t>
+          <t>3,74</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>12,09</t>
+          <t>12,34</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>720,447</t>
+          <t>720,361</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
@@ -18204,7 +18204,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>7,15396100</t>
+          <t>7,15779700</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -18214,12 +18214,12 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>5,51</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>12.708,098</t>
+          <t>12.534,771</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -18321,7 +18321,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>7,47100400</t>
+          <t>7,47492700</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18331,12 +18331,12 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>5,51</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
@@ -18346,7 +18346,7 @@
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>5.165,152</t>
+          <t>4.557,645</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -18438,32 +18438,32 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>1,44638100</t>
+          <t>1,44756300</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>0,007</t>
+          <t>0,081</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>3,73</t>
+          <t>3,81</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>12,03</t>
+          <t>12,24</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>172,680</t>
+          <t>172,430</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
@@ -18555,22 +18555,22 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>3,13094900</t>
+          <t>3,13242900</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>5,17</t>
+          <t>5,22</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
@@ -18580,7 +18580,7 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>2.188,264</t>
+          <t>1.748,099</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
@@ -18672,22 +18672,22 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>6,69966200</t>
+          <t>6,70339500</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>5,56</t>
+          <t>5,62</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>24.303,742</t>
+          <t>23.886,065</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -18741,32 +18741,32 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>5,53632700</t>
+          <t>5,54090800</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>0,187</t>
+          <t>0,082</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>5,33</t>
+          <t>5,41</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>10,46</t>
+          <t>10,77</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>598,370</t>
+          <t>596,961</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
@@ -18975,32 +18975,32 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>3,94073600</t>
+          <t>3,92595700</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr">
         <is>
-          <t>-0,461</t>
+          <t>-0,375</t>
         </is>
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>-6,05</t>
+          <t>-6,41</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>8,84</t>
+          <t>8,43</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>25,46</t>
+          <t>25,58</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>298,545</t>
+          <t>297,338</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
@@ -19092,32 +19092,32 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>3,62432500</t>
+          <t>3,60776700</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>-0,380</t>
+          <t>-0,456</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>-5,97</t>
+          <t>-6,40</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>8,70</t>
+          <t>8,20</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>25,06</t>
+          <t>25,03</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>9,171</t>
+          <t>9,129</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -19209,32 +19209,32 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>11,40560718</t>
+          <t>11,43156165</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>0,922</t>
+          <t>0,227</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>8,07</t>
+          <t>8,31</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>3,06</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
         <is>
-          <t>23,43</t>
+          <t>23,10</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>2.355,362</t>
+          <t>2.360,702</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
@@ -19326,32 +19326,32 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>2,02607500</t>
+          <t>2,01895500</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
         <is>
-          <t>-0,556</t>
+          <t>-0,351</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>-5,85</t>
+          <t>-6,18</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>6,89</t>
+          <t>6,51</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>22,29</t>
+          <t>22,39</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>200,001</t>
+          <t>199,298</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -19443,32 +19443,32 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>2,03257400</t>
+          <t>2,02367900</t>
         </is>
       </c>
       <c r="E169" s="7" t="inlineStr">
         <is>
-          <t>-0,204</t>
+          <t>-0,437</t>
         </is>
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>-6,10</t>
+          <t>-6,51</t>
         </is>
       </c>
       <c r="G169" s="7" t="inlineStr">
         <is>
-          <t>-1,96</t>
+          <t>-2,39</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
         <is>
-          <t>12,87</t>
+          <t>12,44</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>767,866</t>
+          <t>764,506</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
@@ -19560,32 +19560,32 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>3,44333233</t>
+          <t>3,43138065</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t>-0,422</t>
+          <t>-0,347</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>-6,59</t>
+          <t>-6,91</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>5,84</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>19,45</t>
+          <t>19,53</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>1.320,439</t>
+          <t>1.315,856</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -19673,32 +19673,32 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>2,51148698</t>
+          <t>2,50520795</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr">
         <is>
-          <t>-0,718</t>
+          <t>-0,250</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>-7,54</t>
+          <t>-7,77</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>21,15</t>
+          <t>21,24</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>777,357</t>
+          <t>775,414</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
@@ -19786,32 +19786,32 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>3,73740900</t>
+          <t>3,73931200</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>14,25</t>
+          <t>14,27</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>4.985,423</t>
+          <t>4.991,112</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W172"/>
+  <dimension ref="A1:X172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -491,6 +491,7 @@
     <col width="15" customWidth="1" min="21" max="21"/>
     <col width="15" customWidth="1" min="22" max="22"/>
     <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -607,6 +608,11 @@
       <c r="W1" s="1" t="inlineStr">
         <is>
           <t>doc_carta</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>doc_boletim</t>
         </is>
       </c>
     </row>
@@ -678,6 +684,7 @@
       <c r="U2" s="2" t="inlineStr"/>
       <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -795,6 +802,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_88.pdf</t>
         </is>
       </c>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_88.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -912,6 +924,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5823.pdf</t>
         </is>
       </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5823.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -969,18 +986,71 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-geracao-jovem-rf-credito-privado-longo-prazo</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
-      <c r="W5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>10.577.485/0001-34</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>5570</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5570.pdf</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5570.pdf</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5570.pdf</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5570.pdf</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5570.pdf</t>
+        </is>
+      </c>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5570.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1098,6 +1168,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5565.pdf</t>
         </is>
       </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5565.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1215,6 +1290,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6532.pdf</t>
         </is>
       </c>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6532.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1332,6 +1412,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_59.pdf</t>
         </is>
       </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_59.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1449,6 +1534,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5834.pdf</t>
         </is>
       </c>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5834.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1502,18 +1592,71 @@
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr"/>
-      <c r="U10" s="2" t="inlineStr"/>
-      <c r="V10" s="2" t="inlineStr"/>
-      <c r="W10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>15.154.319/0001-49</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5972</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5972.pdf</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5972.pdf</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5972.pdf</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5972.pdf</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5972.pdf</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5972.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1631,6 +1774,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_86.pdf</t>
         </is>
       </c>
+      <c r="X11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_86.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1748,6 +1896,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_87.pdf</t>
         </is>
       </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_87.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1865,6 +2018,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_54.pdf</t>
         </is>
       </c>
+      <c r="X13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_54.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1982,6 +2140,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_57.pdf</t>
         </is>
       </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_57.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -2099,6 +2262,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5414.pdf</t>
         </is>
       </c>
+      <c r="X15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5414.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2216,6 +2384,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_85.pdf</t>
         </is>
       </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_85.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2333,6 +2506,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5892.pdf</t>
         </is>
       </c>
+      <c r="X17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5892.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2450,6 +2628,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5576.pdf</t>
         </is>
       </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5576.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -2567,6 +2750,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5970.pdf</t>
         </is>
       </c>
+      <c r="X19" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5970.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2684,6 +2872,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_58.pdf</t>
         </is>
       </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_58.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2801,6 +2994,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5566.pdf</t>
         </is>
       </c>
+      <c r="X21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5566.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2918,6 +3116,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5571.pdf</t>
         </is>
       </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5571.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -2970,19 +3173,76 @@
           <t>PF | PJ | TODOS</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="4" t="inlineStr"/>
-      <c r="M23" s="4" t="inlineStr"/>
-      <c r="N23" s="4" t="inlineStr"/>
-      <c r="O23" s="4" t="inlineStr"/>
-      <c r="P23" s="4" t="inlineStr"/>
-      <c r="Q23" s="4" t="inlineStr"/>
-      <c r="R23" s="4" t="inlineStr"/>
-      <c r="S23" s="4" t="inlineStr"/>
-      <c r="T23" s="4" t="inlineStr"/>
-      <c r="U23" s="4" t="inlineStr"/>
-      <c r="V23" s="4" t="inlineStr"/>
-      <c r="W23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-investidor-rf-longo-prazo</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>03.164.294/0001-85</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0089.pdf</t>
+        </is>
+      </c>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0089.pdf</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0089.pdf</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_0089.pdf</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_89.pdf</t>
+        </is>
+      </c>
+      <c r="X23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_89.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3100,6 +3360,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7938.pdf</t>
         </is>
       </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7938.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -3217,6 +3482,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7931.pdf</t>
         </is>
       </c>
+      <c r="X25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7931.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -3274,18 +3544,71 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-plus-qualificado-rf-credito-privado-longo-prazo/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="2" t="inlineStr"/>
-      <c r="Q26" s="2" t="inlineStr"/>
-      <c r="R26" s="2" t="inlineStr"/>
-      <c r="S26" s="2" t="inlineStr"/>
-      <c r="T26" s="2" t="inlineStr"/>
-      <c r="U26" s="2" t="inlineStr"/>
-      <c r="V26" s="2" t="inlineStr"/>
-      <c r="W26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>40.194.314/0001-97</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>6533</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>D+14 (du)</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>D+15 (du)</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6533.pdf</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6533.pdf</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6533.pdf</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6533.pdf</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6533.pdf</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6533.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -3403,6 +3726,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7887.pdf</t>
         </is>
       </c>
+      <c r="X27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7887.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3516,6 +3844,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7987.pdf</t>
         </is>
       </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7987.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -3629,6 +3962,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7940.pdf</t>
         </is>
       </c>
+      <c r="X29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7940.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3746,6 +4084,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7978.pdf</t>
         </is>
       </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7978.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -3855,6 +4198,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7999.pdf</t>
         </is>
       </c>
+      <c r="X31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7999.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3972,6 +4320,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5154.pdf</t>
         </is>
       </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5154.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -4089,6 +4442,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5156.pdf</t>
         </is>
       </c>
+      <c r="X33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5156.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -4206,6 +4564,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5401.pdf</t>
         </is>
       </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5401.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -4323,6 +4686,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_83.pdf</t>
         </is>
       </c>
+      <c r="X35" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_83.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -4440,6 +4808,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6482.pdf</t>
         </is>
       </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6482.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -4557,6 +4930,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5940.pdf</t>
         </is>
       </c>
+      <c r="X37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5940.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -4674,6 +5052,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5406.pdf</t>
         </is>
       </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5406.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -4791,6 +5174,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7916.pdf</t>
         </is>
       </c>
+      <c r="X39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7916.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -4908,6 +5296,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_84.pdf</t>
         </is>
       </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_84.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -5025,6 +5418,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5408.pdf</t>
         </is>
       </c>
+      <c r="X41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5408.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -5142,6 +5540,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5908.pdf</t>
         </is>
       </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5908.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -5259,6 +5662,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5410.pdf</t>
         </is>
       </c>
+      <c r="X43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5410.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -5376,6 +5784,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_56.pdf</t>
         </is>
       </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_56.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -5489,6 +5902,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_8500.pdf</t>
         </is>
       </c>
+      <c r="X45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_8500.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -5606,6 +6024,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5930.pdf</t>
         </is>
       </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5930.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -5723,6 +6146,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5498.pdf</t>
         </is>
       </c>
+      <c r="X47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5498.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -5840,6 +6268,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7914.pdf</t>
         </is>
       </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7914.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -5957,6 +6390,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5402.pdf</t>
         </is>
       </c>
+      <c r="X49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5402.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -6074,6 +6512,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5171.pdf</t>
         </is>
       </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5171.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -6191,6 +6634,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5157.pdf</t>
         </is>
       </c>
+      <c r="X51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5157.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -6248,18 +6696,71 @@
           <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-mega-ref-di-longo-prazo/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr"/>
-      <c r="O52" s="2" t="inlineStr"/>
-      <c r="P52" s="2" t="inlineStr"/>
-      <c r="Q52" s="2" t="inlineStr"/>
-      <c r="R52" s="2" t="inlineStr"/>
-      <c r="S52" s="2" t="inlineStr"/>
-      <c r="T52" s="2" t="inlineStr"/>
-      <c r="U52" s="2" t="inlineStr"/>
-      <c r="V52" s="2" t="inlineStr"/>
-      <c r="W52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>10.322.633/0001-70</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5411</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>50000.0</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5411.pdf</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5411.pdf</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5411.pdf</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5411.pdf</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5411.pdf</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5411.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -6377,6 +6878,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5969.pdf</t>
         </is>
       </c>
+      <c r="X53" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5969.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -6494,6 +7000,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6520.pdf</t>
         </is>
       </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6520.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -6611,6 +7122,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7880.pdf</t>
         </is>
       </c>
+      <c r="X55" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7880.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -6726,6 +7242,11 @@
       <c r="W56" s="2" t="inlineStr">
         <is>
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6518.pdf</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6518.pdf</t>
         </is>
       </c>
     </row>
@@ -6797,6 +7318,7 @@
       <c r="U57" s="4" t="inlineStr"/>
       <c r="V57" s="4" t="inlineStr"/>
       <c r="W57" s="4" t="inlineStr"/>
+      <c r="X57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -6914,6 +7436,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6439.pdf</t>
         </is>
       </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6439.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -7031,6 +7558,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6446.pdf</t>
         </is>
       </c>
+      <c r="X59" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6446.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -7144,6 +7676,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7990.pdf</t>
         </is>
       </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7990.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -7261,6 +7798,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7877.pdf</t>
         </is>
       </c>
+      <c r="X61" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7877.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -7378,6 +7920,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6950.pdf</t>
         </is>
       </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6950.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -7491,6 +8038,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7991.pdf</t>
         </is>
       </c>
+      <c r="X63" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7991.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -7608,6 +8160,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7876.pdf</t>
         </is>
       </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7876.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -7721,6 +8278,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7992.pdf</t>
         </is>
       </c>
+      <c r="X65" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7992.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -7838,6 +8400,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7910.pdf</t>
         </is>
       </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7910.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -7955,6 +8522,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5490.pdf</t>
         </is>
       </c>
+      <c r="X67" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5490.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -8072,6 +8644,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5902.pdf</t>
         </is>
       </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5902.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -8189,6 +8766,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5954.pdf</t>
         </is>
       </c>
+      <c r="X69" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5954.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -8306,6 +8888,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6399.pdf</t>
         </is>
       </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6399.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -8423,6 +9010,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6999.pdf</t>
         </is>
       </c>
+      <c r="X71" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6999.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -8540,6 +9132,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6353.pdf</t>
         </is>
       </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6353.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -8653,6 +9250,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6479.pdf</t>
         </is>
       </c>
+      <c r="X73" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6479.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -8770,6 +9372,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7980.pdf</t>
         </is>
       </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7980.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -8887,6 +9494,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5475.pdf</t>
         </is>
       </c>
+      <c r="X75" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5475.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -9004,6 +9616,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6608.pdf</t>
         </is>
       </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6608.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -9121,6 +9738,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6621.pdf</t>
         </is>
       </c>
+      <c r="X77" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6621.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -9238,6 +9860,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6623.pdf</t>
         </is>
       </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6623.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -9355,6 +9982,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6475.pdf</t>
         </is>
       </c>
+      <c r="X79" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6475.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -9472,6 +10104,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5492.pdf</t>
         </is>
       </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5492.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -9589,6 +10226,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5582.pdf</t>
         </is>
       </c>
+      <c r="X81" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5582.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -9706,6 +10348,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5911.pdf</t>
         </is>
       </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5911.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -9823,6 +10470,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7875.pdf</t>
         </is>
       </c>
+      <c r="X83" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7875.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -9940,6 +10592,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6535.pdf</t>
         </is>
       </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6535.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -10057,6 +10714,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5403.pdf</t>
         </is>
       </c>
+      <c r="X85" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5403.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -10174,6 +10836,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5390.pdf</t>
         </is>
       </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5390.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -10291,6 +10958,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_53.pdf</t>
         </is>
       </c>
+      <c r="X87" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_53.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -10404,6 +11076,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6478.pdf</t>
         </is>
       </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6478.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -10521,6 +11198,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5928.pdf</t>
         </is>
       </c>
+      <c r="X89" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5928.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -10638,6 +11320,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5841.pdf</t>
         </is>
       </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5841.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -10755,6 +11442,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5567.pdf</t>
         </is>
       </c>
+      <c r="X91" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5567.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -10872,6 +11564,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5395.pdf</t>
         </is>
       </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5395.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -10989,6 +11686,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6420.pdf</t>
         </is>
       </c>
+      <c r="X93" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6420.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -11106,6 +11808,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_53.pdf</t>
         </is>
       </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_53.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -11223,6 +11930,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6421.pdf</t>
         </is>
       </c>
+      <c r="X95" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6421.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -11340,6 +12052,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5397.pdf</t>
         </is>
       </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5397.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -11457,6 +12174,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5398.pdf</t>
         </is>
       </c>
+      <c r="X97" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5398.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -11574,6 +12296,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5978.pdf</t>
         </is>
       </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5978.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -11691,6 +12418,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5420.pdf</t>
         </is>
       </c>
+      <c r="X99" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5420.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -11808,6 +12540,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6447.pdf</t>
         </is>
       </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6447.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -11925,6 +12662,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5301.pdf</t>
         </is>
       </c>
+      <c r="X101" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5301.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -12042,6 +12784,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6499.pdf</t>
         </is>
       </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6499.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -12159,6 +12906,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5392.pdf</t>
         </is>
       </c>
+      <c r="X103" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5392.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -12276,6 +13028,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6530.pdf</t>
         </is>
       </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6530.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -12393,6 +13150,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6591.pdf</t>
         </is>
       </c>
+      <c r="X105" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6591.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -12510,6 +13272,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5393.pdf</t>
         </is>
       </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5393.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -12627,6 +13394,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5394.pdf</t>
         </is>
       </c>
+      <c r="X107" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5394.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -12744,6 +13516,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_48.pdf</t>
         </is>
       </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_48.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -12861,6 +13638,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6620.pdf</t>
         </is>
       </c>
+      <c r="X109" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6620.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -12978,6 +13760,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6593.pdf</t>
         </is>
       </c>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6593.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -13095,6 +13882,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7971.pdf</t>
         </is>
       </c>
+      <c r="X111" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7971.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -13212,6 +14004,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6602.pdf</t>
         </is>
       </c>
+      <c r="X112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6602.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -13329,6 +14126,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6994.pdf</t>
         </is>
       </c>
+      <c r="X113" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6994.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -13446,6 +14248,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6397.pdf</t>
         </is>
       </c>
+      <c r="X114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6397.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -13503,18 +14310,71 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-indices/etf-ibovespa-fundo-de-indice/</t>
         </is>
       </c>
-      <c r="L115" s="4" t="inlineStr"/>
-      <c r="M115" s="4" t="inlineStr"/>
-      <c r="N115" s="4" t="inlineStr"/>
-      <c r="O115" s="4" t="inlineStr"/>
-      <c r="P115" s="4" t="inlineStr"/>
-      <c r="Q115" s="4" t="inlineStr"/>
-      <c r="R115" s="4" t="inlineStr"/>
-      <c r="S115" s="4" t="inlineStr"/>
-      <c r="T115" s="4" t="inlineStr"/>
-      <c r="U115" s="4" t="inlineStr"/>
-      <c r="V115" s="4" t="inlineStr"/>
-      <c r="W115" s="4" t="inlineStr"/>
+      <c r="L115" s="4" t="inlineStr">
+        <is>
+          <t>15.154.236/0001-50</t>
+        </is>
+      </c>
+      <c r="M115" s="4" t="inlineStr">
+        <is>
+          <t>5842</t>
+        </is>
+      </c>
+      <c r="N115" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="O115" s="4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P115" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Q115" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="R115" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
+      <c r="S115" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5842.pdf</t>
+        </is>
+      </c>
+      <c r="T115" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5842.pdf</t>
+        </is>
+      </c>
+      <c r="U115" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5842.pdf</t>
+        </is>
+      </c>
+      <c r="V115" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5842.pdf</t>
+        </is>
+      </c>
+      <c r="W115" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5842.pdf</t>
+        </is>
+      </c>
+      <c r="X115" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5842.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -13632,6 +14492,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6601.pdf</t>
         </is>
       </c>
+      <c r="X116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6601.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -13749,6 +14614,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6600.pdf</t>
         </is>
       </c>
+      <c r="X117" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6600.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -13866,6 +14736,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5204.pdf</t>
         </is>
       </c>
+      <c r="X118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5204.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -13983,6 +14858,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5205.pdf</t>
         </is>
       </c>
+      <c r="X119" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5205.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -14100,6 +14980,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5251.pdf</t>
         </is>
       </c>
+      <c r="X120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5251.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -14217,6 +15102,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5253.pdf</t>
         </is>
       </c>
+      <c r="X121" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5253.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -14334,6 +15224,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5202.pdf</t>
         </is>
       </c>
+      <c r="X122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5202.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -14451,6 +15346,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5205.pdf</t>
         </is>
       </c>
+      <c r="X123" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5205.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -14568,6 +15468,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5203.pdf</t>
         </is>
       </c>
+      <c r="X124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5203.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -14685,6 +15590,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7972.pdf</t>
         </is>
       </c>
+      <c r="X125" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7972.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -14742,18 +15652,71 @@
           <t>https://www.caixa.gov.br/fundos-investimento/fundo-simples/fic-ametista-corporativo-rf-simples/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L126" s="2" t="inlineStr"/>
-      <c r="M126" s="2" t="inlineStr"/>
-      <c r="N126" s="2" t="inlineStr"/>
-      <c r="O126" s="2" t="inlineStr"/>
-      <c r="P126" s="2" t="inlineStr"/>
-      <c r="Q126" s="2" t="inlineStr"/>
-      <c r="R126" s="2" t="inlineStr"/>
-      <c r="S126" s="2" t="inlineStr"/>
-      <c r="T126" s="2" t="inlineStr"/>
-      <c r="U126" s="2" t="inlineStr"/>
-      <c r="V126" s="2" t="inlineStr"/>
-      <c r="W126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>51.255.391/0001-26</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>7861</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_7861.pdf</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_7861.pdf</t>
+        </is>
+      </c>
+      <c r="U126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_7861.pdf</t>
+        </is>
+      </c>
+      <c r="V126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_7861.pdf</t>
+        </is>
+      </c>
+      <c r="W126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7861.pdf</t>
+        </is>
+      </c>
+      <c r="X126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7861.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -14871,6 +15834,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5405.pdf</t>
         </is>
       </c>
+      <c r="X127" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5405.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -14988,6 +15956,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5080.pdf</t>
         </is>
       </c>
+      <c r="X128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5080.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -15105,6 +16078,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5833.pdf</t>
         </is>
       </c>
+      <c r="X129" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5833.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -15222,6 +16200,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_46.pdf</t>
         </is>
       </c>
+      <c r="X130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_46.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -15339,6 +16322,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5901.pdf</t>
         </is>
       </c>
+      <c r="X131" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5901.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -15456,6 +16444,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6445.pdf</t>
         </is>
       </c>
+      <c r="X132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6445.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -15573,6 +16566,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5148.pdf</t>
         </is>
       </c>
+      <c r="X133" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5148.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -15690,6 +16688,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6606.pdf</t>
         </is>
       </c>
+      <c r="X134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6606.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -15807,6 +16810,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5132.pdf</t>
         </is>
       </c>
+      <c r="X135" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5132.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -15924,6 +16932,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5066.pdf</t>
         </is>
       </c>
+      <c r="X136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5066.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -16037,6 +17050,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5053.pdf</t>
         </is>
       </c>
+      <c r="X137" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5053.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -16154,6 +17172,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5948.pdf</t>
         </is>
       </c>
+      <c r="X138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5948.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -16271,6 +17294,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5189.pdf</t>
         </is>
       </c>
+      <c r="X139" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5189.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -16388,6 +17416,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6996.pdf</t>
         </is>
       </c>
+      <c r="X140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6996.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -16505,6 +17538,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5946.pdf</t>
         </is>
       </c>
+      <c r="X141" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5946.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -16622,6 +17660,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7869.pdf</t>
         </is>
       </c>
+      <c r="X142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7869.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -16739,6 +17782,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_55.pdf</t>
         </is>
       </c>
+      <c r="X143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_55.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -16796,18 +17844,71 @@
           <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-transferencias-voluntarias-curto-prazo</t>
         </is>
       </c>
-      <c r="L144" s="2" t="inlineStr"/>
-      <c r="M144" s="2" t="inlineStr"/>
-      <c r="N144" s="2" t="inlineStr"/>
-      <c r="O144" s="2" t="inlineStr"/>
-      <c r="P144" s="2" t="inlineStr"/>
-      <c r="Q144" s="2" t="inlineStr"/>
-      <c r="R144" s="2" t="inlineStr"/>
-      <c r="S144" s="2" t="inlineStr"/>
-      <c r="T144" s="2" t="inlineStr"/>
-      <c r="U144" s="2" t="inlineStr"/>
-      <c r="V144" s="2" t="inlineStr"/>
-      <c r="W144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>10.740.552/0001-90</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="P144" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5413.pdf</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5413.pdf</t>
+        </is>
+      </c>
+      <c r="U144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5413.pdf</t>
+        </is>
+      </c>
+      <c r="V144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5413.pdf</t>
+        </is>
+      </c>
+      <c r="W144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5413.pdf</t>
+        </is>
+      </c>
+      <c r="X144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5413.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -16925,6 +18026,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5982.pdf</t>
         </is>
       </c>
+      <c r="X145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5982.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -17042,6 +18148,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5993.pdf</t>
         </is>
       </c>
+      <c r="X146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5993.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -17159,6 +18270,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5975.pdf</t>
         </is>
       </c>
+      <c r="X147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5975.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -17276,6 +18392,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6481.pdf</t>
         </is>
       </c>
+      <c r="X148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6481.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -17393,6 +18514,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5824.pdf</t>
         </is>
       </c>
+      <c r="X149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5824.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -17450,18 +18576,71 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-idka-ipca-2a-rf-longo-prazo</t>
         </is>
       </c>
-      <c r="L150" s="2" t="inlineStr"/>
-      <c r="M150" s="2" t="inlineStr"/>
-      <c r="N150" s="2" t="inlineStr"/>
-      <c r="O150" s="2" t="inlineStr"/>
-      <c r="P150" s="2" t="inlineStr"/>
-      <c r="Q150" s="2" t="inlineStr"/>
-      <c r="R150" s="2" t="inlineStr"/>
-      <c r="S150" s="2" t="inlineStr"/>
-      <c r="T150" s="2" t="inlineStr"/>
-      <c r="U150" s="2" t="inlineStr"/>
-      <c r="V150" s="2" t="inlineStr"/>
-      <c r="W150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>14.386.926/0001-71</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>5825</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5825.pdf</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5825.pdf</t>
+        </is>
+      </c>
+      <c r="U150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5825.pdf</t>
+        </is>
+      </c>
+      <c r="V150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5825.pdf</t>
+        </is>
+      </c>
+      <c r="W150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5825.pdf</t>
+        </is>
+      </c>
+      <c r="X150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5825.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -17579,6 +18758,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5824.pdf</t>
         </is>
       </c>
+      <c r="X151" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5824.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -17696,6 +18880,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5184.pdf</t>
         </is>
       </c>
+      <c r="X152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5184.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -17813,6 +19002,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5184.pdf</t>
         </is>
       </c>
+      <c r="X153" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5184.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -17928,6 +19122,11 @@
       <c r="W154" s="2" t="inlineStr">
         <is>
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5188.pdf</t>
+        </is>
+      </c>
+      <c r="X154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5188.pdf</t>
         </is>
       </c>
     </row>
@@ -17999,6 +19198,7 @@
       <c r="U155" s="4" t="inlineStr"/>
       <c r="V155" s="4" t="inlineStr"/>
       <c r="W155" s="4" t="inlineStr"/>
+      <c r="X155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -18116,6 +19316,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5184.pdf</t>
         </is>
       </c>
+      <c r="X156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5184.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -18233,6 +19438,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5824.pdf</t>
         </is>
       </c>
+      <c r="X157" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5824.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -18350,6 +19560,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5404.pdf</t>
         </is>
       </c>
+      <c r="X158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5404.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -18467,6 +19682,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5461.pdf</t>
         </is>
       </c>
+      <c r="X159" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5461.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -18584,6 +19804,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6634.pdf</t>
         </is>
       </c>
+      <c r="X160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6634.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -18699,6 +19924,11 @@
       <c r="W161" s="4" t="inlineStr">
         <is>
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5826.pdf</t>
+        </is>
+      </c>
+      <c r="X161" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5826.pdf</t>
         </is>
       </c>
     </row>
@@ -18770,6 +20000,7 @@
       <c r="U162" s="2" t="inlineStr"/>
       <c r="V162" s="2" t="inlineStr"/>
       <c r="W162" s="2" t="inlineStr"/>
+      <c r="X162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -18887,6 +20118,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5168.pdf</t>
         </is>
       </c>
+      <c r="X163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5168.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -19004,6 +20240,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6439.pdf</t>
         </is>
       </c>
+      <c r="X164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6439.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -19121,6 +20362,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5445.pdf</t>
         </is>
       </c>
+      <c r="X165" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5445.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -19238,6 +20484,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5842.pdf</t>
         </is>
       </c>
+      <c r="X166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5842.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -19355,6 +20606,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5929.pdf</t>
         </is>
       </c>
+      <c r="X167" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5929.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -19472,6 +20728,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5396.pdf</t>
         </is>
       </c>
+      <c r="X168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5396.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -19589,6 +20850,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6425.pdf</t>
         </is>
       </c>
+      <c r="X169" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6425.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -19702,6 +20968,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6160.pdf</t>
         </is>
       </c>
+      <c r="X170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6160.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -19815,6 +21086,11 @@
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5563.pdf</t>
         </is>
       </c>
+      <c r="X171" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5563.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -19930,6 +21206,11 @@
       <c r="W172" s="2" t="inlineStr">
         <is>
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5487.pdf</t>
+        </is>
+      </c>
+      <c r="X172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5487.pdf</t>
         </is>
       </c>
     </row>

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -5676,62 +5676,58 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF BETA RF REF DI LP RESP LTDA</t>
+          <t>CAIXA SIGMA FUNCIONARIOS FIC FIF RF REF DI LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>02/10/1995</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>30,23758400</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>0,048</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>0,96</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>5,08</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>13,21</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>165,211</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>PF | TODOS</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-beta-ref-di-lp</t>
-        </is>
-      </c>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>00.834.072/0001-34</t>
+          <t>66.034.762/0001-17</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5741,7 +5737,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5761,32 +5757,32 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0056.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_8500.pdf</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0056.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_8500.pdf</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0056.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_8500.pdf</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_0056.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_8500.pdf</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_56.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_8500.pdf</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_56.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_8500.pdf</t>
         </is>
       </c>
     </row>
@@ -5798,58 +5794,62 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>CAIXA SIGMA FUNCIONARIOS FIC FIF RF REF DI LP - RESP LTDA</t>
+          <t>CAIXA FIC FIF BETA RF REF DI LP RESP LTDA</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>02/10/1995</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>30,23758400</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>0,048</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>0,96</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>5,08</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>13,21</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>165,211</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>PF</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr"/>
+          <t>PF | TODOS</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-beta-ref-di-lp</t>
+        </is>
+      </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>66.034.762/0001-17</t>
+          <t>00.834.072/0001-34</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
@@ -5879,32 +5879,32 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_8500.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0056.pdf</t>
         </is>
       </c>
       <c r="T45" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_8500.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0056.pdf</t>
         </is>
       </c>
       <c r="U45" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_8500.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0056.pdf</t>
         </is>
       </c>
       <c r="V45" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_8500.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_0056.pdf</t>
         </is>
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_8500.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_56.pdf</t>
         </is>
       </c>
       <c r="X45" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_8500.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_56.pdf</t>
         </is>
       </c>
     </row>

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -659,7 +659,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>407,706</t>
+          <t>402,851</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.783,321</t>
+          <t>6.646,794</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>876,296</t>
+          <t>886,956</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>11,649</t>
+          <t>11,550</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>120,046</t>
+          <t>119,002</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>97,403</t>
+          <t>96,504</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>586,164</t>
+          <t>581,391</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>61,836</t>
+          <t>61,339</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1.674,712</t>
+          <t>1.661,172</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>123,417</t>
+          <t>122,783</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,382</t>
+          <t>28,033</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>03.218.183/0001-04</t>
+          <t>03.191.874/0001-61</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>100000.0</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1873,32 +1873,32 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0087.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0046.pdf</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0087.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0046.pdf</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0087.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0046.pdf</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_87.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_46.pdf</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_87.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_46.pdf</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_87.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_46.pdf</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>40,715</t>
+          <t>40,384</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,881</t>
+          <t>64,363</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>79,838</t>
+          <t>79,084</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,956</t>
+          <t>27,719</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>1,659</t>
+          <t>1,646</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>139,380</t>
+          <t>138,691</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1.801,377</t>
+          <t>1.771,652</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="Q19" s="4" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2.192,556</t>
+          <t>2.175,893</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>13,227</t>
+          <t>13,106</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,747</t>
+          <t>66,269</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>957,410</t>
+          <t>948,894</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,11446441</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>-0,039</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>0,39</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>3,31</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>212,664</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3384,32 +3384,32 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,23544100</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>1,22</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>5,48</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>14,65</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>71,169</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>175,484</t>
+          <t>173,953</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>40,304</t>
+          <t>39,867</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -3750,32 +3750,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,03539400</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>5,59</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21,752</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3868,32 +3868,32 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,16411800</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>1,39</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>4,83</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>13,88</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>66,448</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -3986,32 +3986,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,06921896</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>0,149</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>1,40</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>3,47</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>311,054</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       <c r="O31" s="4" t="inlineStr"/>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="Q31" s="4" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>861,613</t>
+          <t>851,672</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.249,946</t>
+          <t>3.222,999</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,281</t>
+          <t>21,029</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>3.114,091</t>
+          <t>3.090,447</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>125,785</t>
+          <t>124,407</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>592,393</t>
+          <t>588,678</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>122,631</t>
+          <t>121,489</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>347,289</t>
+          <t>344,859</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2.387,379</t>
+          <t>2.369,834</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>556,112</t>
+          <t>551,459</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15.558,982</t>
+          <t>15.431,671</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>50000.0</t>
+          <t>200000.0</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>1.390,430</t>
+          <t>1.384,208</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>165,211</t>
+          <t>163,886</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6.060,253</t>
+          <t>5.941,253</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>2.185,880</t>
+          <t>2.168,505</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>63,837</t>
+          <t>63,321</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>838,049</t>
+          <t>830,131</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15.819,078</t>
+          <t>15.719,475</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>5000.0</t>
+          <t>50000.0</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>9.472,413</t>
+          <t>9.412,983</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>100000.0</t>
+          <t>200000.0</t>
         </is>
       </c>
       <c r="Q51" s="4" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>21.145,854</t>
+          <t>20.988,542</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>50000.0</t>
+          <t>300000.0</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>13.384,828</t>
+          <t>13.310,330</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>100000.0</t>
+          <t>1000000.0</t>
         </is>
       </c>
       <c r="Q53" s="4" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>247,206</t>
+          <t>245,506</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6940,71 +6940,19 @@
           <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-automatico-polis-rf-cp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>39.594.941/0001-36</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>6520</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>Conservador</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>D+0 (du)</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>D+00 (du)</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6520.pdf</t>
-        </is>
-      </c>
-      <c r="T54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6520.pdf</t>
-        </is>
-      </c>
-      <c r="U54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6520.pdf</t>
-        </is>
-      </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6520.pdf</t>
-        </is>
-      </c>
-      <c r="W54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6520.pdf</t>
-        </is>
-      </c>
-      <c r="X54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6520.pdf</t>
-        </is>
-      </c>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -7024,32 +6972,32 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,40949900</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0,000</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>1,33</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>5,27</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>14,31</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>67,622</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -7146,32 +7094,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.193,19101100</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>-0,002</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>3,81</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>-4,90</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>-0,75</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36,431</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -7293,7 +7241,7 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>327,947</t>
+          <t>540,035</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -7338,32 +7286,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.637,20394000</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>-0,114</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>4,48</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>13,07</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>114,507</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -7485,7 +7433,7 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>12,847</t>
+          <t>12,674</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -7700,32 +7648,32 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,25386200</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>-0,005</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>-0,15</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>2,66</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>10,74</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6,430</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -8062,32 +8010,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,42327300</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>-0,004</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>-3,09</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>4,26</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>17,44</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11,840</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -8327,7 +8275,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>3,754</t>
+          <t>3,753</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -8424,32 +8372,32 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>5,33686931</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>-0,114</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>4,01</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>12,82</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32,833</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -8571,7 +8519,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>639,783</t>
+          <t>628,367</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8668,32 +8616,32 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>2,86271200</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>-0,004</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>0,34</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>2,49</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>10,66</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>74,533</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -8815,7 +8763,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>29,006</t>
+          <t>28,806</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8937,7 +8885,7 @@
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>2.402,829</t>
+          <t>2.388,736</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -9059,7 +9007,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>21,994</t>
+          <t>21,850</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -9156,32 +9104,32 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.658,37370000</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>-0,110</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>0,16</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>4,86</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>14,05</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14,674</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -9274,32 +9222,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0,52057047</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>-0,007</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>-4,04</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>-27,90</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,876</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -9396,32 +9344,32 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>3,27988400</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>0,532</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>1,93</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>2,94</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>8,54</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>156,216</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -9518,32 +9466,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,54915500</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>0,003</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>1,01</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>3,75</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>20,28</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14,594</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -9640,32 +9588,32 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,37383500</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>-0,660</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>-1,70</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>7,37</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70,402</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -9762,32 +9710,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,50209900</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>0,180</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>3,57</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>3,86</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>16,32</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>194,763</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9797,7 +9745,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fic-capital-protegido-ciclico-ii-multimercado-lp/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fim-cap-protegido-ciclico-ii</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -9884,32 +9832,32 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,77828200</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>-0,002</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>1,07</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>0,66</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>10,09</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>176,122</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -10031,7 +9979,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>902,819</t>
+          <t>898,155</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -10153,7 +10101,7 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>747,266</t>
+          <t>745,586</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -10250,32 +10198,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>6,82921600</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>-0,004</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>0,75</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>6,18</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>16,85</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>128,939</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -10372,32 +10320,32 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,42390900</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>1,09</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>3,35</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>16,21</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>281,056</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -10494,32 +10442,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,32775300</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>-0,002</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>1,41</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>3,44</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>3,06</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13,382</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -10641,7 +10589,7 @@
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>96,762</t>
+          <t>96,616</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -10763,7 +10711,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>340,588</t>
+          <t>340,536</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -11007,7 +10955,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>10,300</t>
+          <t>10,297</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -11125,7 +11073,7 @@
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>283,484</t>
+          <t>283,357</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -11247,7 +11195,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>446,677</t>
+          <t>446,580</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -11491,7 +11439,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2,130</t>
+          <t>2,126</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -11613,7 +11561,7 @@
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>76,584</t>
+          <t>76,536</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -11735,7 +11683,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>90,397</t>
+          <t>90,378</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -11832,32 +11780,32 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,27967300</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>-0,045</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>-6,28</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>-0,57</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>7,69</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>289,458</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -11979,7 +11927,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>114,891</t>
+          <t>114,886</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -12101,7 +12049,7 @@
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>127,209</t>
+          <t>127,196</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -12223,7 +12171,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>48,093</t>
+          <t>48,074</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -12345,7 +12293,7 @@
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>119,528</t>
+          <t>119,373</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -12467,7 +12415,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>40,929</t>
+          <t>40,893</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -12589,7 +12537,7 @@
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>668,903</t>
+          <t>668,752</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -12711,7 +12659,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>446,282</t>
+          <t>446,175</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -13321,7 +13269,7 @@
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>35,566</t>
+          <t>35,541</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -13443,7 +13391,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>835,509</t>
+          <t>834,938</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -13565,7 +13513,7 @@
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>2,908</t>
+          <t>2,906</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -13809,7 +13757,7 @@
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>19,715</t>
+          <t>19,698</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -13931,7 +13879,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>274,449</t>
+          <t>274,269</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -14028,32 +13976,32 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.003,15033500</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>-6,24</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>2,32</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>16,31</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7,913</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -14150,32 +14098,32 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.505,83720300</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>-0,002</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>-6,39</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>0,67</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>10,99</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -14272,7 +14220,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>169,55922300</t>
+          <t>169,55922343</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
@@ -14541,7 +14489,7 @@
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>1.616,184</t>
+          <t>1.615,388</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -14785,7 +14733,7 @@
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>785,583</t>
+          <t>785,107</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -14795,17 +14743,17 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-1</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-2</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>04.885.818/0001-90</t>
+          <t>04.885.824/0001-47</t>
         </is>
       </c>
       <c r="M119" s="4" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="N119" s="4" t="inlineStr">
@@ -14815,12 +14763,12 @@
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="Q119" s="4" t="inlineStr">
@@ -14835,32 +14783,32 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5206.pdf</t>
         </is>
       </c>
       <c r="T119" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5205.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5206.pdf</t>
         </is>
       </c>
       <c r="U119" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5206.pdf</t>
         </is>
       </c>
       <c r="V119" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5206.pdf</t>
         </is>
       </c>
       <c r="W119" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5206.pdf</t>
         </is>
       </c>
       <c r="X119" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5206.pdf</t>
         </is>
       </c>
     </row>
@@ -14907,7 +14855,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>113,591</t>
+          <t>113,569</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -15151,7 +15099,7 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>582,688</t>
+          <t>581,978</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -15273,7 +15221,7 @@
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>470,938</t>
+          <t>470,848</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -15283,17 +15231,17 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-1</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-2</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>04.885.818/0001-90</t>
+          <t>04.885.824/0001-47</t>
         </is>
       </c>
       <c r="M123" s="4" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="N123" s="4" t="inlineStr">
@@ -15303,12 +15251,12 @@
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="Q123" s="4" t="inlineStr">
@@ -15323,32 +15271,32 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5206.pdf</t>
         </is>
       </c>
       <c r="T123" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5205.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5206.pdf</t>
         </is>
       </c>
       <c r="U123" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5206.pdf</t>
         </is>
       </c>
       <c r="V123" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5206.pdf</t>
         </is>
       </c>
       <c r="W123" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5206.pdf</t>
         </is>
       </c>
       <c r="X123" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5206.pdf</t>
         </is>
       </c>
     </row>
@@ -15395,7 +15343,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>670,495</t>
+          <t>669,850</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -15639,7 +15587,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>215,263</t>
+          <t>196,696</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -15761,7 +15709,7 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>41,338</t>
+          <t>41,030</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -15883,7 +15831,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>791,217</t>
+          <t>784,325</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -16005,7 +15953,7 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>18,924</t>
+          <t>18,812</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -16127,7 +16075,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>94,973</t>
+          <t>94,369</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -16249,7 +16197,7 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>7.939,338</t>
+          <t>7.710,838</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -16371,7 +16319,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>15.867,048</t>
+          <t>15.793,725</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -16406,7 +16354,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>1000000.0</t>
+          <t>3000000.0</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16493,7 +16441,7 @@
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>3.045,452</t>
+          <t>3.031,660</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -16528,7 +16476,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>1000000.0</t>
+          <t>3000000.0</t>
         </is>
       </c>
       <c r="Q133" s="4" t="inlineStr">
@@ -16590,7 +16538,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1,54654300</t>
+          <t>1,54654296</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -16737,7 +16685,7 @@
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>285,149</t>
+          <t>284,379</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -16859,7 +16807,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>4.013,008</t>
+          <t>4.011,477</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -16981,7 +16929,7 @@
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>4.781,473</t>
+          <t>4.780,987</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -17099,7 +17047,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>13.989,956</t>
+          <t>13.597,824</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -17221,7 +17169,7 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>12.515,793</t>
+          <t>12.463,903</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -17256,7 +17204,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>1000000.0</t>
+          <t>3000000.0</t>
         </is>
       </c>
       <c r="Q139" s="4" t="inlineStr">
@@ -17343,7 +17291,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.596,587</t>
+          <t>3.582,717</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -17378,7 +17326,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>1000000.0</t>
+          <t>3000000.0</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17465,7 +17413,7 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>1.468,990</t>
+          <t>1.461,203</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -17587,7 +17535,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>33.690,972</t>
+          <t>31.773,754</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -17709,7 +17657,7 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>3.007,512</t>
+          <t>2.804,769</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
@@ -17831,7 +17779,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>16.519,133</t>
+          <t>16.634,401</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -18456,12 +18404,12 @@
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t>14.508.605/0001-00</t>
+          <t>10.740.670/0001-06</t>
         </is>
       </c>
       <c r="M149" s="4" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="N149" s="4" t="inlineStr">
@@ -18491,32 +18439,32 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5824.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5464.pdf</t>
         </is>
       </c>
       <c r="T149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5824.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5464.pdf</t>
         </is>
       </c>
       <c r="U149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5464.pdf</t>
         </is>
       </c>
       <c r="V149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5464.pdf</t>
         </is>
       </c>
       <c r="W149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5464.pdf</t>
         </is>
       </c>
       <c r="X149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5464.pdf</t>
         </is>
       </c>
     </row>
@@ -18700,12 +18648,12 @@
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t>14.508.605/0001-00</t>
+          <t>10.740.670/0001-06</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="N151" s="4" t="inlineStr">
@@ -18735,32 +18683,32 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5824.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5464.pdf</t>
         </is>
       </c>
       <c r="T151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5824.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5464.pdf</t>
         </is>
       </c>
       <c r="U151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5464.pdf</t>
         </is>
       </c>
       <c r="V151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5464.pdf</t>
         </is>
       </c>
       <c r="W151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5464.pdf</t>
         </is>
       </c>
       <c r="X151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5464.pdf</t>
         </is>
       </c>
     </row>
@@ -19365,7 +19313,7 @@
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>720,376</t>
+          <t>720,375</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
@@ -19380,12 +19328,12 @@
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>14.508.605/0001-00</t>
+          <t>10.740.670/0001-06</t>
         </is>
       </c>
       <c r="M157" s="4" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="N157" s="4" t="inlineStr">
@@ -19415,32 +19363,32 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5824.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5464.pdf</t>
         </is>
       </c>
       <c r="T157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5824.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5464.pdf</t>
         </is>
       </c>
       <c r="U157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5464.pdf</t>
         </is>
       </c>
       <c r="V157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5464.pdf</t>
         </is>
       </c>
       <c r="W157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5464.pdf</t>
         </is>
       </c>
       <c r="X157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5464.pdf</t>
         </is>
       </c>
     </row>
@@ -19487,7 +19435,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>12.901,464</t>
+          <t>12.901,293</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -19502,12 +19450,12 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>03.737.206/0001-97</t>
+          <t>05.164.356/0001-84</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -19537,32 +19485,32 @@
       </c>
       <c r="S158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5404.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5462.pdf</t>
         </is>
       </c>
       <c r="T158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5404.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5462.pdf</t>
         </is>
       </c>
       <c r="U158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5404.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5462.pdf</t>
         </is>
       </c>
       <c r="V158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5404.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5462.pdf</t>
         </is>
       </c>
       <c r="W158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5404.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5462.pdf</t>
         </is>
       </c>
       <c r="X158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5404.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5462.pdf</t>
         </is>
       </c>
     </row>
@@ -19609,7 +19557,7 @@
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>4.621,489</t>
+          <t>4.621,477</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -19853,7 +19801,7 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>1.750,478</t>
+          <t>1.543,199</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
@@ -19975,7 +19923,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>23.815,568</t>
+          <t>23.815,493</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -20289,7 +20237,7 @@
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>295,252</t>
+          <t>295,234</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
@@ -20508,7 +20456,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>11,49497800</t>
+          <t>11,49497823</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -20874,7 +20822,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>3,41371100</t>
+          <t>3,41371062</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -20992,7 +20940,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>2,48907700</t>
+          <t>2,48907659</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr">
@@ -21135,7 +21083,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>4.929,702</t>
+          <t>4.880,670</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X171"/>
+  <dimension ref="A1:X172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,25604400</t>
+          <t>2,25710100</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>4,99</t>
+          <t>5,04</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>406,021</t>
+          <t>407,369</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,48322100</t>
+          <t>5,48574300</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>4,89</t>
+          <t>4,94</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.592,347</t>
+          <t>6.577,348</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,76857800</t>
+          <t>2,76984500</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -836,12 +836,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>4,88</t>
+          <t>4,93</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1.059,901</t>
+          <t>912,964</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -948,22 +948,22 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>3,32149900</t>
+          <t>3,32316600</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>5,41</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>11,594</t>
+          <t>11,604</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -1070,22 +1070,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,47543300</t>
+          <t>3,47709100</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>119,152</t>
+          <t>119,357</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1192,32 +1192,32 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1.829,38402700</t>
+          <t>1.830,37413000</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>5,57</t>
+          <t>5,62</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>14,63</t>
+          <t>14,64</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>96,533</t>
+          <t>96,626</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,67522600</t>
+          <t>9,67975000</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1324,22 +1324,22 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>5,23</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>13,36</t>
+          <t>13,37</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>581,231</t>
+          <t>581,312</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3,34539100</t>
+          <t>3,34705800</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>5,51</t>
+          <t>5,56</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>61,491</t>
+          <t>61,637</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,98686500</t>
+          <t>2,98841300</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1568,12 +1568,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>5,69</t>
+          <t>5,74</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1.661,686</t>
+          <t>1.663,270</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1676,32 +1676,32 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>19,84480900</t>
+          <t>19,81939200</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>-0,161</t>
+          <t>-0,128</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>3,53</t>
+          <t>3,40</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>11,78</t>
+          <t>11,76</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>122,538</t>
+          <t>121,705</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1798,32 +1798,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,48526900</t>
+          <t>13,47617500</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>-0,073</t>
+          <t>-0,067</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>4,86</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>9,95</t>
+          <t>9,98</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,012</t>
+          <t>27,996</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>46,01529600</t>
+          <t>46,03674800</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>5,21</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>40,401</t>
+          <t>40,420</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>PF | PJ | TODOS</t>
+          <t>GOV | PF | PJ | TODOS</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20,15395900</t>
+          <t>20,16358100</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>5,07</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,390</t>
+          <t>64,419</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2164,32 +2164,32 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>3,14084100</t>
+          <t>3,13935900</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>-0,045</t>
+          <t>-0,047</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>5,74</t>
+          <t>5,69</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>11,14</t>
+          <t>11,17</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>78,926</t>
+          <t>78,804</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14,90696700</t>
+          <t>14,91396900</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>5,20</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,715</t>
+          <t>27,727</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2,99071500</t>
+          <t>2,99207500</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>5,05</t>
+          <t>5,09</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>1,647</t>
+          <t>1,648</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -2530,32 +2530,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,31011000</t>
+          <t>3,30601200</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>-0,141</t>
+          <t>-0,123</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>-0,26</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>3,85</t>
+          <t>3,73</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>12,31</t>
+          <t>12,27</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>138,307</t>
+          <t>137,645</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2652,22 +2652,22 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,02938300</t>
+          <t>3,03098000</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>5,69</t>
+          <t>5,74</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1.762,949</t>
+          <t>1.756,237</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2774,22 +2774,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32,68337700</t>
+          <t>32,69915500</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>5,39</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2.181,124</t>
+          <t>2.219,414</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2896,22 +2896,22 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,29486500</t>
+          <t>3,29646000</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>5,35</t>
+          <t>5,40</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>13,112</t>
+          <t>13,113</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -3018,32 +3018,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3,33955100</t>
+          <t>3,33248500</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>-0,271</t>
+          <t>-0,211</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>4,56</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>9,95</t>
+          <t>9,89</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,271</t>
+          <t>66,098</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3140,22 +3140,22 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>18,97341300</t>
+          <t>18,98237200</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>948,231</t>
+          <t>949,330</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,11444930</t>
+          <t>1,11325852</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -3270,24 +3270,24 @@
           <t>-0,001</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>-0,10</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>3,20</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>0,00</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>3,31</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>212,636</t>
+          <t>212,384</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1,23616000</t>
+          <t>1,23677100</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -3392,24 +3392,24 @@
           <t>0,000</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>0,00</t>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>0,04</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>5,59</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>14,66</t>
+          <t>14,64</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>71,252</t>
+          <t>71,297</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1.825,77453700</t>
+          <t>1.826,86888200</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,059</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>5,65</t>
+          <t>5,71</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>14,80</t>
+          <t>14,82</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>174,170</t>
+          <t>174,465</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3628,32 +3628,32 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1,20062700</t>
+          <t>1,20120100</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>6,83</t>
+          <t>6,88</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>13,26</t>
+          <t>13,36</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>39,889</t>
+          <t>39,909</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,03603000</t>
+          <t>1,03655000</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3758,24 +3758,24 @@
           <t>0,000</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>0,04</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>5,71</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>0,00</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>5,65</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,768</t>
+          <t>21,779</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,16518300</t>
+          <t>1,16642800</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -3876,24 +3876,24 @@
           <t>0,000</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>0,00</t>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>4,92</t>
+          <t>5,04</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>13,93</t>
+          <t>14,01</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>66,402</t>
+          <t>66,292</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,06920445</t>
+          <t>1,06847084</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -3994,24 +3994,24 @@
           <t>-0,001</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>-0,06</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>3,40</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>0,00</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>3,47</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>322,922</t>
+          <t>320,774</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>5,12325100</t>
+          <t>5,12574500</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>5,67</t>
+          <t>5,72</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>852,342</t>
+          <t>848,456</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -4344,22 +4344,22 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>4,92955700</t>
+          <t>4,93215100</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>5,67</t>
+          <t>5,73</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.226,484</t>
+          <t>3.234,610</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>29,16546100</t>
+          <t>29,17973000</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>5,17</t>
+          <t>5,22</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,038</t>
+          <t>21,048</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4588,22 +4588,22 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>30,51722200</t>
+          <t>30,53191800</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>5,58</t>
+          <t>5,63</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>3.091,593</t>
+          <t>3.092,632</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>PF | PJ | TODOS</t>
+          <t>GOV | PF | PJ | TODOS</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -4710,32 +4710,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1.768,89412600</t>
+          <t>1.769,32684700</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0,005</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
+          <t>0,024</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>0,02</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>5,04</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>13,64</t>
+          <t>13,63</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>124,246</t>
+          <t>124,370</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>3,21273500</t>
+          <t>3,21445900</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>5,72</t>
+          <t>5,77</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>587,637</t>
+          <t>588,232</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -4954,22 +4954,22 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>6,16992000</t>
+          <t>6,17284300</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>121,545</t>
+          <t>121,601</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -5076,22 +5076,22 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1,26525600</t>
+          <t>1,26593300</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>5,83</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>346,554</t>
+          <t>352,697</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -5198,22 +5198,22 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>10,56172100</t>
+          <t>10,56688300</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>5,66</t>
+          <t>5,71</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2.369,813</t>
+          <t>2.368,700</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>5,50048100</t>
+          <t>5,50332500</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>5,76</t>
+          <t>5,81</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>551,659</t>
+          <t>551,725</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -5442,32 +5442,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3,55695500</t>
+          <t>3,55885400</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>5,76</t>
+          <t>5,81</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>14,99</t>
+          <t>15,00</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15.415,218</t>
+          <t>15.439,583</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5564,22 +5564,22 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>5,28647200</t>
+          <t>5,28908600</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>5,81</t>
+          <t>5,87</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>1.384,821</t>
+          <t>1.384,933</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>30,25214000</t>
+          <t>30,26667100</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>5,18</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>163,963</t>
+          <t>164,115</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2,80134200</t>
+          <t>2,80266800</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>5,06</t>
+          <t>5,11</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5.930,346</t>
+          <t>5.931,048</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -6048,22 +6048,22 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>3,59438100</t>
+          <t>3,59620500</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>2.171,170</t>
+          <t>2.177,093</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1,28689900</t>
+          <t>1,28758500</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>5,69</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>63,584</t>
+          <t>63,603</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -6292,32 +6292,32 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>9,65635900</t>
+          <t>9,66130400</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>5,57</t>
+          <t>5,62</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>14,42</t>
+          <t>14,43</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>829,903</t>
+          <t>829,554</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>4,44392600</t>
+          <t>4,44626300</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -6424,12 +6424,12 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>5,68</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15.695,756</t>
+          <t>15.719,208</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>PF | PJ | TODOS</t>
+          <t>GOV | PF | PJ | TODOS</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -6536,22 +6536,22 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>4,75994500</t>
+          <t>4,76243200</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>5,70</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>9.407,605</t>
+          <t>9.407,817</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>PF | PJ | TODOS</t>
+          <t>GOV | PF | PJ | TODOS</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -6658,22 +6658,22 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>5,08637900</t>
+          <t>5,08904100</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>5,72</t>
+          <t>5,77</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>20.971,074</t>
+          <t>20.995,057</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6780,22 +6780,22 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>3,17688700</t>
+          <t>3,17856400</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>5,76</t>
+          <t>5,82</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>13.361,548</t>
+          <t>13.360,586</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1.725,05257100</t>
+          <t>1.725,94238600</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>251,101</t>
+          <t>249,675</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6972,32 +6972,32 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1,41059700</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>0,001</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>0,00</t>
+          <t>1,41149900</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>0,000</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>0,06</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>5,35</t>
+          <t>5,42</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>14,35</t>
+          <t>14,37</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>67,673</t>
+          <t>67,716</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1.195,86346600</t>
+          <t>1.196,25317100</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
@@ -7102,24 +7102,24 @@
           <t>-0,002</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>0,02</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>-4,69</t>
+          <t>-4,66</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>-1,15</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>36,502</t>
+          <t>36,514</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -7216,27 +7216,27 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>12,54525800</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>-0,339</t>
+          <t>12,58599900</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>0,324</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>-0,01</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>5,68</t>
+          <t>6,02</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>16,96</t>
+          <t>17,44</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -7286,32 +7286,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1.633,60636400</t>
+          <t>1.633,50512400</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>-0,219</t>
+          <t>-0,006</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>4,25</t>
+          <t>4,24</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>12,84</t>
+          <t>12,72</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>114,273</t>
+          <t>114,271</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -7408,37 +7408,37 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>2.437,05192500</t>
+          <t>2.440,85621200</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>0,593</t>
+          <t>0,156</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>18,64</t>
+          <t>18,83</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>39,13</t>
+          <t>38,51</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>12,773</t>
+          <t>12,996</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>PF | PJ | RPPS</t>
+          <t>GOV | PF | PJ | RPPS</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1,25144100</t>
+          <t>1,25086900</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -7656,24 +7656,24 @@
           <t>-0,004</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>0,00</t>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>2,41</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>10,34</t>
+          <t>10,10</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>6,413</t>
+          <t>6,310</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -7770,32 +7770,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1,13241700</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>-0,503</t>
+          <t>1,13638900</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>0,350</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>-0,50</t>
+          <t>-0,15</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>-2,33</t>
+          <t>-1,99</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>13,15</t>
+          <t>14,31</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>3,431</t>
+          <t>3,442</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1,42030300</t>
+          <t>1,41814900</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
@@ -8018,24 +8018,24 @@
           <t>-0,004</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>-0,15</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>4,04</t>
+          <t>3,88</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>17,67</t>
+          <t>17,33</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>11,753</t>
+          <t>11,783</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -8250,37 +8250,37 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1,10187800</t>
+          <t>1,10109800</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>-0,776</t>
+          <t>-0,070</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>-0,84</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>-8,61</t>
+          <t>-8,67</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>-8,42</t>
+          <t>-8,68</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>3,727</t>
+          <t>3,656</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>PF | PJ | RPPS</t>
+          <t>GOV | PF | PJ | RPPS</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -8372,12 +8372,12 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>5,32662426</t>
+          <t>5,32643598</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>-0,191</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -8387,17 +8387,17 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>3,81</t>
+          <t>3,80</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>12,58</t>
+          <t>12,49</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>32,781</t>
+          <t>32,804</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -8494,32 +8494,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>4,67558400</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>-1,813</t>
+          <t>4,69197800</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>0,350</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>-1,81</t>
+          <t>-1,46</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>5,23</t>
+          <t>5,59</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>43,32</t>
+          <t>40,23</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>618,043</t>
+          <t>618,007</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>2,86309500</t>
+          <t>2,85980600</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -8624,24 +8624,24 @@
           <t>-0,002</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>0,00</t>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>2,50</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>10,80</t>
+          <t>10,47</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>74,523</t>
+          <t>74,437</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -8738,37 +8738,37 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1.667,58772100</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>0,230</t>
+          <t>1.665,12304600</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>-0,147</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>5,84</t>
+          <t>5,69</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>11,95</t>
+          <t>11,74</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>28,979</t>
+          <t>28,931</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>PF | PJ | RPPS | TODOS</t>
+          <t>GOV | PF | PJ | RPPS | TODOS</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -8860,37 +8860,37 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>3,83930000</t>
+          <t>3,84654700</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>0,278</t>
+          <t>0,188</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>14,13</t>
+          <t>14,34</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>40,32</t>
+          <t>39,85</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>2.395,805</t>
+          <t>2.401,931</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>PF | PJ | RPPS | TODOS</t>
+          <t>GOV | PF | PJ | RPPS | TODOS</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
@@ -8982,22 +8982,22 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1,90502600</t>
+          <t>1,90552100</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>0,014</t>
+          <t>0,025</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>4,79</t>
+          <t>4,82</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>22,019</t>
+          <t>22,028</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -9104,12 +9104,12 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1.654,78966100</t>
+          <t>1.654,73884500</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>-0,216</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
@@ -9124,12 +9124,12 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>13,81</t>
+          <t>13,69</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>14,558</t>
+          <t>14,560</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>0,52687173</t>
+          <t>0,50984150</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
@@ -9230,24 +9230,24 @@
           <t>-0,004</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>-3,23</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>-29,39</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>0,00</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr">
-        <is>
-          <t>-27,03</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>4,142</t>
+          <t>4,020</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -9344,32 +9344,32 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>3,27860600</t>
+          <t>3,27841500</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>-0,038</t>
+          <t>-0,005</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>2,90</t>
+          <t>2,89</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>9,69</t>
+          <t>9,92</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>156,155</t>
+          <t>156,146</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -9466,32 +9466,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1,54528700</t>
+          <t>1,54521700</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>-0,249</t>
+          <t>-0,004</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>3,49</t>
+          <t>3,48</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>20,69</t>
+          <t>20,78</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>14,558</t>
+          <t>14,557</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -9588,12 +9588,12 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1,37307800</t>
+          <t>1,37302500</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>-0,055</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>7,61</t>
+          <t>7,66</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>70,363</t>
+          <t>70,360</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>PF | PJ | RPPS</t>
+          <t>GOV | PF | PJ | RPPS</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
@@ -9710,17 +9710,17 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1,48785900</t>
+          <t>1,48780300</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>-0,948</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>-0,94</t>
+          <t>-0,95</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -9730,17 +9730,17 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>15,10</t>
+          <t>15,03</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>192,916</t>
+          <t>192,909</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>PF | PJ | RPPS</t>
+          <t>GOV | PF | PJ | RPPS</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1,78051400</t>
+          <t>1,78163400</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -9840,24 +9840,24 @@
           <t>-0,001</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>0,00</t>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>0,06</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>10,59</t>
+          <t>10,33</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>175,720</t>
+          <t>175,744</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -9954,32 +9954,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>5,60766600</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>-0,100</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>-0,10</t>
+          <t>5,61720700</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>0,170</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>0,06</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>5,24</t>
+          <t>5,42</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>14,47</t>
+          <t>14,58</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>897,298</t>
+          <t>898,704</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -10076,32 +10076,32 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>3,65043300</t>
+          <t>3,65143000</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>0,016</t>
+          <t>0,027</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>4,95</t>
+          <t>4,98</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>13,40</t>
+          <t>13,39</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>745,549</t>
+          <t>744,987</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>6,83811500</t>
+          <t>6,83389900</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
@@ -10206,24 +10206,24 @@
           <t>-0,002</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>6,32</t>
+          <t>6,25</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>16,98</t>
+          <t>16,79</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>129,079</t>
+          <t>128,964</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>1,42667400</t>
+          <t>1,42545000</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -10328,24 +10328,24 @@
           <t>-0,003</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>0,00</t>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>3,55</t>
+          <t>3,46</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>16,19</t>
+          <t>16,03</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>281,599</t>
+          <t>281,360</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,32302500</t>
+          <t>1,32904600</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -10450,24 +10450,24 @@
           <t>-0,001</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>2,65</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>13,212</t>
+          <t>13,225</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -10564,32 +10564,32 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>3,73957000</t>
+          <t>3,73746600</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>-0,490</t>
+          <t>-0,056</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>-6,97</t>
+          <t>-7,02</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>-8,06</t>
+          <t>-7,64</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>96,202</t>
+          <t>96,220</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -10686,32 +10686,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>6,58239900</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>-0,741</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="inlineStr">
-        <is>
-          <t>-0,74</t>
+          <t>6,64489300</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>0,949</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>0,20</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>3,78</t>
+          <t>4,77</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>19,61</t>
+          <t>21,02</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>338,038</t>
+          <t>341,242</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10808,37 +10808,37 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>2,56153500</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>-0,912</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>-0,91</t>
+          <t>2,59187100</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>1,184</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>0,26</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>6,46</t>
+          <t>7,72</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>24,60</t>
+          <t>26,29</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>13,320</t>
+          <t>13,409</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>PF | PJ</t>
+          <t>GOV | PF | PJ</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
@@ -10930,32 +10930,32 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1.907,26505300</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>-1,174</t>
+          <t>1.919,36570900</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>0,634</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>-3,92</t>
+          <t>-3,31</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>12,35</t>
+          <t>13,63</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>10,148</t>
+          <t>10,212</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -11048,12 +11048,12 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>10,25860800</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>0,040</t>
+          <t>10,25862300</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>0,000</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
@@ -11068,12 +11068,12 @@
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>21,97</t>
+          <t>22,13</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>283,507</t>
+          <t>284,555</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -11170,32 +11170,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1,46009300</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>-0,782</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>-0,78</t>
+          <t>1,47442800</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>0,981</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>0,19</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>-4,22</t>
+          <t>-3,28</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>0,80</t>
+          <t>1,90</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>443,001</t>
+          <t>447,321</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -11292,32 +11292,32 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1,09768800</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>-0,955</t>
+          <t>1,10748000</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>0,892</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>-5,69</t>
+          <t>-4,85</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>-3,86</t>
+          <t>-2,76</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>56,459</t>
+          <t>56,962</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -11414,32 +11414,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1,69046000</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>-1,062</t>
-        </is>
-      </c>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr">
-        <is>
-          <t>-0,82</t>
+          <t>1,71064800</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>1,194</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>0,11</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>0,35</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>8,20</t>
+          <t>9,85</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2,102</t>
+          <t>2,127</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -11536,32 +11536,32 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>4,56994800</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>1,286</t>
+          <t>4,55350900</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>-0,359</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>45,11</t>
+          <t>44,59</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>53,24</t>
+          <t>52,24</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>77,487</t>
+          <t>77,152</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -11658,32 +11658,32 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>8,58357800</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>-0,917</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>-0,91</t>
+          <t>8,68489900</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>1,180</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>0,25</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>6,01</t>
+          <t>7,26</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>23,27</t>
+          <t>24,95</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>89,560</t>
+          <t>90,627</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -11780,32 +11780,32 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1,26957400</t>
+          <t>1,25943900</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>-0,090</t>
+          <t>-0,006</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>-0,88</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>-1,36</t>
+          <t>-2,14</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>7,74</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>287,144</t>
+          <t>284,852</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -11902,32 +11902,32 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>1,85353700</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>-0,434</t>
-        </is>
-      </c>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>-0,43</t>
+          <t>1,86586600</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>0,665</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>0,22</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>-2,51</t>
+          <t>-1,86</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>16,49</t>
+          <t>17,16</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>114,309</t>
+          <t>114,427</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -12024,32 +12024,32 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>2,88392500</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>-0,310</t>
-        </is>
-      </c>
-      <c r="F97" s="6" t="inlineStr">
-        <is>
-          <t>-0,31</t>
+          <t>2,90836800</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>0,847</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>5,81</t>
+          <t>6,70</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>17,53</t>
+          <t>18,54</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>126,354</t>
+          <t>127,392</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -12146,32 +12146,32 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1,85354300</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>-1,177</t>
+          <t>1,86521700</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>0,629</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-0,55</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>-4,33</t>
+          <t>-3,73</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>11,10</t>
+          <t>12,37</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>47,757</t>
+          <t>49,068</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -12268,32 +12268,32 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>6,47502500</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>0,869</t>
+          <t>6,45994100</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>-0,232</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>38,05</t>
+          <t>37,72</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>48,55</t>
+          <t>47,37</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>120,046</t>
+          <t>119,782</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -12390,32 +12390,32 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>1.259,15771200</t>
+          <t>1.256,03835100</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>-1,086</t>
+          <t>-0,247</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>-7,88</t>
+          <t>-8,11</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>-12,36</t>
+          <t>-12,05</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>40,445</t>
+          <t>40,388</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -12512,32 +12512,32 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>38,67028500</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>-1,357</t>
-        </is>
-      </c>
-      <c r="F101" s="6" t="inlineStr">
-        <is>
-          <t>-1,35</t>
+          <t>40,22550200</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>4,021</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>2,60</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>11,93</t>
+          <t>16,43</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>65,77</t>
+          <t>70,94</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>661,623</t>
+          <t>687,520</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -12634,37 +12634,37 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2,64489600</t>
-        </is>
-      </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t>-1,464</t>
-        </is>
-      </c>
-      <c r="F102" s="7" t="inlineStr">
-        <is>
-          <t>-1,46</t>
+          <t>2,69175500</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>1,771</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>0,28</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>9,18</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>25,50</t>
+          <t>30,49</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>439,454</t>
+          <t>447,176</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>PF | PJ</t>
+          <t>GOV | PF | PJ</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -12756,32 +12756,32 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>4,75193400</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>-1,206</t>
+          <t>4,79261700</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>0,856</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>-1,20</t>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>5,88</t>
+          <t>6,79</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>24,99</t>
+          <t>26,25</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>22,991</t>
+          <t>23,178</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -12878,37 +12878,37 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>1.483,75953300</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>-1,337</t>
+          <t>1.492,99282500</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>0,622</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>-1,33</t>
+          <t>-0,72</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>2,59</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>14,54</t>
+          <t>15,85</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>29,490</t>
+          <t>29,620</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>PF | PJ | RPPS | TODOS</t>
+          <t>GOV | PF | PJ | RPPS | TODOS</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -13000,32 +13000,32 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>1,91831700</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>-0,946</t>
-        </is>
-      </c>
-      <c r="F105" s="6" t="inlineStr">
-        <is>
-          <t>-0,94</t>
+          <t>1,94557900</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>1,421</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>-5,70</t>
+          <t>-4,36</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>7,58</t>
+          <t>9,05</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>1,742</t>
+          <t>1,769</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -13122,32 +13122,32 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>5,80270200</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>-1,068</t>
+          <t>5,86053900</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>0,996</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>-1,06</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>7,87</t>
+          <t>8,94</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>26,73</t>
+          <t>28,23</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>42,745</t>
+          <t>43,147</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>2,18610300</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>-1,190</t>
+          <t>2,21009600</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>1,097</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>-1,19</t>
+          <t>-0,10</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>5,33</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>22,67</t>
+          <t>24,15</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>35,130</t>
+          <t>35,485</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -13366,32 +13366,32 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>42,38437600</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>1,287</t>
+          <t>42,23178900</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>-0,360</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>45,17</t>
+          <t>44,65</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>53,36</t>
+          <t>52,36</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>844,655</t>
+          <t>840,878</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -13488,32 +13488,32 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>0,85211000</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>-0,866</t>
+          <t>0,85762000</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>0,646</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>-0,86</t>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>-11,47</t>
+          <t>-10,90</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>-19,27</t>
+          <t>-18,54</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>2,884</t>
+          <t>2,904</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -13610,32 +13610,32 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>1,18142000</t>
-        </is>
-      </c>
-      <c r="E110" s="7" t="inlineStr">
-        <is>
-          <t>-1,131</t>
+          <t>1,18776400</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>0,536</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>-1,13</t>
+          <t>-0,60</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>-2,37</t>
+          <t>-1,84</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>11,86</t>
+          <t>13,01</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>3,802</t>
+          <t>3,820</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -13732,32 +13732,32 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>1,30663800</t>
-        </is>
-      </c>
-      <c r="E111" s="6" t="inlineStr">
-        <is>
-          <t>-1,465</t>
-        </is>
-      </c>
-      <c r="F111" s="6" t="inlineStr">
-        <is>
-          <t>-1,46</t>
+          <t>1,32977400</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>1,770</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>9,12</t>
+          <t>11,05</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>25,32</t>
+          <t>30,30</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>19,409</t>
+          <t>19,753</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -13854,32 +13854,32 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1,73310400</t>
-        </is>
-      </c>
-      <c r="E112" s="7" t="inlineStr">
-        <is>
-          <t>-2,408</t>
+          <t>1,77396600</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>2,357</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>-2,40</t>
+          <t>-0,10</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>3,19</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>62,96</t>
+          <t>68,41</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>267,610</t>
+          <t>270,719</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>999,47563700</t>
+          <t>990,42623200</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -13984,24 +13984,24 @@
           <t>-0,002</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>0,00</t>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>-0,90</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>16,87</t>
+          <t>15,93</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>8,134</t>
+          <t>8,063</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -14098,7 +14098,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1.495,22939500</t>
+          <t>1.484,18511100</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
@@ -14106,29 +14106,29 @@
           <t>-0,002</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>-0,74</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>11,11</t>
+          <t>10,45</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>21,731</t>
+          <t>21,570</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>PF | PJ | RPPS | TODOS</t>
+          <t>GOV | PF | PJ | RPPS | TODOS</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -14220,32 +14220,32 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>168,05168757</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>-0,889</t>
-        </is>
-      </c>
-      <c r="F115" s="6" t="inlineStr">
-        <is>
-          <t>-0,88</t>
+          <t>170,02273889</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>1,172</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>6,64</t>
+          <t>7,89</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>25,16</t>
+          <t>26,83</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>42,014</t>
+          <t>42,507</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -14342,32 +14342,32 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1,77137100</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="inlineStr">
-        <is>
-          <t>-2,420</t>
+          <t>1,81286500</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>2,342</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>-2,42</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>3,25</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>63,28</t>
+          <t>68,71</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>4,846</t>
+          <t>4,960</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -14464,32 +14464,32 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1,72695600</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>-2,436</t>
+          <t>1,76771500</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>2,360</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>-2,43</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>3,26</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>63,29</t>
+          <t>68,75</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>1.575,789</t>
+          <t>1.611,857</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -14586,32 +14586,32 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>47,15159600</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>1,290</t>
+          <t>46,98292600</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>-0,357</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>1,29</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>45,58</t>
+          <t>45,06</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>54,25</t>
+          <t>53,25</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>681,766</t>
+          <t>679,192</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -14708,32 +14708,32 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>42,84379600</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>-1,357</t>
-        </is>
-      </c>
-      <c r="F119" s="6" t="inlineStr">
-        <is>
-          <t>-1,35</t>
+          <t>44,56564800</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>4,018</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>2,60</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>12,17</t>
+          <t>16,67</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>66,67</t>
+          <t>71,86</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>774,355</t>
+          <t>804,744</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -14830,32 +14830,32 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>16,27511000</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="inlineStr">
-        <is>
-          <t>-1,068</t>
+          <t>16,41460000</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>0,857</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>-1,06</t>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>-3,50</t>
+          <t>-2,67</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>13,27</t>
+          <t>15,03</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>112,312</t>
+          <t>113,257</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -14952,32 +14952,32 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>35,92285100</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>-1,354</t>
-        </is>
-      </c>
-      <c r="F121" s="6" t="inlineStr">
-        <is>
-          <t>-1,35</t>
+          <t>37,36477700</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>4,013</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>2,60</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>11,95</t>
+          <t>16,44</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>65,48</t>
+          <t>70,64</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>11,741</t>
+          <t>12,212</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
@@ -15074,32 +15074,32 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>41,66011600</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>1,290</t>
+          <t>41,51048100</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>-0,359</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>1,29</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>45,30</t>
+          <t>44,78</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>53,54</t>
+          <t>52,54</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>589,396</t>
+          <t>586,678</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -15196,32 +15196,32 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>36,88953900</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
-          <t>-1,355</t>
-        </is>
-      </c>
-      <c r="F123" s="6" t="inlineStr">
-        <is>
-          <t>-1,35</t>
+          <t>38,37295500</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>4,021</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>2,61</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>11,95</t>
+          <t>16,45</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>65,79</t>
+          <t>70,97</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>464,330</t>
+          <t>482,819</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -15318,32 +15318,32 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>44,29801700</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>1,290</t>
+          <t>44,13882900</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>-0,359</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>1,29</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>45,46</t>
+          <t>44,94</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>53,89</t>
+          <t>52,89</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>677,984</t>
+          <t>675,374</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>1,12338600</t>
+          <t>1,12391400</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -15450,12 +15450,12 @@
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>4,99</t>
+          <t>5,04</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>54,902</t>
+          <t>57,072</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
@@ -15562,7 +15562,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>1,35574400</t>
+          <t>1,35638400</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -15572,22 +15572,22 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>5,05</t>
+          <t>5,09</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>13,04</t>
+          <t>13,03</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>184,204</t>
+          <t>213,639</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -15684,32 +15684,32 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>5,87890100</t>
+          <t>5,88162700</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>5,44</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>13,97</t>
+          <t>13,96</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>40,990</t>
+          <t>40,998</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>5,11688500</t>
+          <t>5,11957800</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -15816,12 +15816,12 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>5,68</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>785,189</t>
+          <t>785,564</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -15928,7 +15928,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>3,21454300</t>
+          <t>3,21619600</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -15938,22 +15938,22 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>13,84</t>
+          <t>13,85</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>18,790</t>
+          <t>18,402</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -16050,32 +16050,32 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>23,74214400</t>
+          <t>23,73163100</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>-0,042</t>
+          <t>-0,044</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>6,04</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>11,91</t>
+          <t>11,94</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>94,329</t>
+          <t>94,268</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -16172,7 +16172,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>3,26914300</t>
+          <t>3,27082900</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -16182,12 +16182,12 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -16197,7 +16197,7 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>7.654,579</t>
+          <t>7.675,903</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -16294,22 +16294,22 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>1.883,70725500</t>
+          <t>1.884,69121900</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>5,82</t>
+          <t>5,87</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
@@ -16319,7 +16319,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>15.866,765</t>
+          <t>15.960,962</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -16416,22 +16416,22 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>4,87368500</t>
+          <t>4,87614100</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>5,70</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -16441,7 +16441,7 @@
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>3.023,793</t>
+          <t>3.025,731</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -16538,22 +16538,22 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1,54736516</t>
+          <t>1,54818489</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>5,70</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
@@ -16563,7 +16563,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>339,195</t>
+          <t>359,475</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -16660,7 +16660,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>5,11854000</t>
+          <t>5,12126900</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -16670,12 +16670,12 @@
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>5,73</t>
+          <t>5,78</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -16685,7 +16685,7 @@
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>284,531</t>
+          <t>284,682</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -16782,22 +16782,22 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>8,70072700</t>
+          <t>8,70507200</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>5,65</t>
+          <t>5,70</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>4.013,427</t>
+          <t>4.012,398</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -16904,32 +16904,32 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>17,89651400</t>
+          <t>17,90550600</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>5,70</t>
+          <t>5,76</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>14,81</t>
+          <t>14,80</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>4.775,256</t>
+          <t>4.766,065</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -17022,22 +17022,22 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>2,82211600</t>
+          <t>2,82347200</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>5,14</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
@@ -17047,7 +17047,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>13.431,808</t>
+          <t>13.427,885</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -17144,7 +17144,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>4,42369100</t>
+          <t>4,42605900</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17154,12 +17154,12 @@
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>5,74</t>
+          <t>5,80</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -17169,12 +17169,12 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>12.553,939</t>
+          <t>12.579,543</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>PJ | RPPS</t>
+          <t>GOV | PJ | RPPS</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>1,37258400</t>
+          <t>1,37332700</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -17276,12 +17276,12 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>5,80</t>
+          <t>5,86</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.483,727</t>
+          <t>3.493,160</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>1.770,49996000</t>
+          <t>1.771,43946400</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17398,12 +17398,12 @@
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>5,65</t>
+          <t>5,71</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>1.434,317</t>
+          <t>1.441,985</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -17495,67 +17495,67 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>RENDA FIXA</t>
+          <t>RENDA FIXA CURTO PRAZO</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF BRASIL MATRIZ RF RESP LTDA</t>
+          <t>CAIXA FIC FIF AUTOMATICO POLIS RF CURTO PRAZO RESP LTDA</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>17/12/2015</t>
+          <t>13/06/2023</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>2,60375900</t>
+          <t>1,30740000</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>5,72</t>
+          <t>4,66</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>14,81</t>
+          <t>11,63</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>9.177,106</t>
+          <t>31.541,267</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>RPPS</t>
+          <t>GOV</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-matriz-rf/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-automatico-polis-rf-cp/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>23.215.008/0001-70</t>
+          <t>50.803.936/0001-29</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -17565,7 +17565,7 @@
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="P142" s="2" t="inlineStr">
@@ -17585,109 +17585,109 @@
       </c>
       <c r="S142" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5982.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_7869.pdf</t>
         </is>
       </c>
       <c r="T142" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5982.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_7869.pdf</t>
         </is>
       </c>
       <c r="U142" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5982.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_7869.pdf</t>
         </is>
       </c>
       <c r="V142" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5982.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_7869.pdf</t>
         </is>
       </c>
       <c r="W142" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5982.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7869.pdf</t>
         </is>
       </c>
       <c r="X142" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5982.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7869.pdf</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>RENDA FIXA</t>
+          <t>RENDA FIXA CURTO PRAZO</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF BRASIL GESTÃO ESTRATÉGICA RF RESP LTDA</t>
+          <t>CAIXA FIC FIF PRÁTICO RF CURTO PRAZO RESP LTDA</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>04/11/2016</t>
+          <t>02/10/1995</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>2,40351800</t>
-        </is>
-      </c>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>-0,122</t>
-        </is>
-      </c>
-      <c r="F143" s="6" t="inlineStr">
-        <is>
-          <t>-0,12</t>
+          <t>9,39899600</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>0,046</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>5,00</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>12,66</t>
+          <t>12,52</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>3.691,303</t>
+          <t>2.798,376</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>RPPS | TODOS</t>
+          <t>GOV | TODOS</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-brasil-gestao-estrategica-rf</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-pratico-curto-prazo</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
-          <t>23.215.097/0001-55</t>
+          <t>00.834.074/0001-23</t>
         </is>
       </c>
       <c r="M143" s="4" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>55</t>
         </is>
       </c>
       <c r="N143" s="4" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Conservador</t>
         </is>
       </c>
       <c r="O143" s="4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="P143" s="4" t="inlineStr">
@@ -17707,109 +17707,109 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5993.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0055.pdf</t>
         </is>
       </c>
       <c r="T143" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5993.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0055.pdf</t>
         </is>
       </c>
       <c r="U143" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5993.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0055.pdf</t>
         </is>
       </c>
       <c r="V143" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5993.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_0055.pdf</t>
         </is>
       </c>
       <c r="W143" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5993.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_55.pdf</t>
         </is>
       </c>
       <c r="X143" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5993.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_55.pdf</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>RENDA FIXA</t>
+          <t>RENDA FIXA CURTO PRAZO</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL INFLAÇÃO ATIVA FIF RF CRED PRIV RESP LTDA</t>
+          <t>CAIXA FIC FIF TRANSFERÊNCIA VOLUNTÁRIA RF CP RESP LTDA</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>17/04/2015</t>
+          <t>16/10/2012</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>2,98403400</t>
-        </is>
-      </c>
-      <c r="E144" s="7" t="inlineStr">
-        <is>
-          <t>-0,070</t>
-        </is>
-      </c>
-      <c r="F144" s="7" t="inlineStr">
-        <is>
-          <t>-0,07</t>
+          <t>2,47525000</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>0,046</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>5,81</t>
+          <t>5,00</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>11,86</t>
+          <t>12,52</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>40,316</t>
+          <t>16.582,682</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>RPPS | TODOS</t>
+          <t>GOV | TODOS</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/brasil-IPCA</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-transferencias-voluntarias-curto-prazo</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>21.918.896/0001-62</t>
+          <t>10.740.552/0001-90</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>5413</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Conservador</t>
         </is>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
@@ -17829,32 +17829,32 @@
       </c>
       <c r="S144" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5975.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5413.pdf</t>
         </is>
       </c>
       <c r="T144" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5975.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5413.pdf</t>
         </is>
       </c>
       <c r="U144" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5975.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5413.pdf</t>
         </is>
       </c>
       <c r="V144" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5975.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5413.pdf</t>
         </is>
       </c>
       <c r="W144" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5975.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5413.pdf</t>
         </is>
       </c>
       <c r="X144" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5975.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5413.pdf</t>
         </is>
       </c>
     </row>
@@ -17866,42 +17866,42 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF BRASIL RENDA FIXA ATIVA LP RESP LTDA</t>
+          <t>CAIXA FIF BRASIL MATRIZ RF RESP LTDA</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>15/04/2020</t>
+          <t>17/12/2015</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>1.641,12109600</t>
-        </is>
-      </c>
-      <c r="E145" s="6" t="inlineStr">
-        <is>
-          <t>-0,037</t>
-        </is>
-      </c>
-      <c r="F145" s="6" t="inlineStr">
-        <is>
-          <t>-0,03</t>
+          <t>2,60506900</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>0,050</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>4,57</t>
+          <t>5,77</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>11,69</t>
+          <t>14,81</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>460,361</t>
+          <t>9.199,948</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
@@ -17911,27 +17911,27 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/brasil-IPCA/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-matriz-rf/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
-          <t>35.536.532/0001-22</t>
+          <t>23.215.008/0001-70</t>
         </is>
       </c>
       <c r="M145" s="4" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="N145" s="4" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Conservador</t>
         </is>
       </c>
       <c r="O145" s="4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="P145" s="4" t="inlineStr">
@@ -17946,37 +17946,37 @@
       </c>
       <c r="R145" s="4" t="inlineStr">
         <is>
-          <t>D+01 (du)</t>
+          <t>D+00 (du)</t>
         </is>
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6481.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5982.pdf</t>
         </is>
       </c>
       <c r="T145" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6481.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5982.pdf</t>
         </is>
       </c>
       <c r="U145" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6481.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5982.pdf</t>
         </is>
       </c>
       <c r="V145" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6481.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5982.pdf</t>
         </is>
       </c>
       <c r="W145" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6481.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5982.pdf</t>
         </is>
       </c>
       <c r="X145" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6481.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5982.pdf</t>
         </is>
       </c>
     </row>
@@ -17988,42 +17988,42 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FI BRASIL IRF-M 1 TP RF</t>
+          <t>CAIXA FIC FIF BRASIL GESTÃO ESTRATÉGICA RF RESP LTDA</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>28/05/2010</t>
+          <t>04/11/2016</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>4,47142400</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="inlineStr">
-        <is>
-          <t>0,022</t>
-        </is>
-      </c>
-      <c r="F146" s="3" t="inlineStr">
-        <is>
-          <t>0,02</t>
+          <t>2,40223700</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>-0,053</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>-0,17</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>4,30</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>14,22</t>
+          <t>12,63</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>10.725,861</t>
+          <t>3.628,550</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -18033,27 +18033,27 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-irfm-1-titulos-publicos-rf</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-brasil-gestao-estrategica-rf</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>10.740.670/0001-06</t>
+          <t>23.215.097/0001-55</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
         <is>
-          <t>Conservador</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
@@ -18073,32 +18073,32 @@
       </c>
       <c r="S146" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5464.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5993.pdf</t>
         </is>
       </c>
       <c r="T146" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5464.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5993.pdf</t>
         </is>
       </c>
       <c r="U146" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5464.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5993.pdf</t>
         </is>
       </c>
       <c r="V146" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5464.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5993.pdf</t>
         </is>
       </c>
       <c r="W146" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5464.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5993.pdf</t>
         </is>
       </c>
       <c r="X146" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5464.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5993.pdf</t>
         </is>
       </c>
     </row>
@@ -18110,42 +18110,42 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF BRASIL IDKA IPCA 2A TIT PUB RF LP RESP LTDA</t>
+          <t>CAIXA BRASIL INFLAÇÃO ATIVA FIF RF CRED PRIV RESP LTDA</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>16/08/2012</t>
+          <t>17/04/2015</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>3,81943600</t>
-        </is>
-      </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>0,000</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>0,00</t>
+          <t>2,98223000</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>-0,060</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>6,10</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>12,32</t>
+          <t>11,87</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>2.990,353</t>
+          <t>40,291</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
@@ -18155,17 +18155,17 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-idka-ipca-2a-rf-longo-prazo</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/brasil-IPCA</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
-          <t>14.386.926/0001-71</t>
+          <t>21.918.896/0001-62</t>
         </is>
       </c>
       <c r="M147" s="4" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="N147" s="4" t="inlineStr">
@@ -18195,32 +18195,32 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5825.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5975.pdf</t>
         </is>
       </c>
       <c r="T147" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5825.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5975.pdf</t>
         </is>
       </c>
       <c r="U147" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5825.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5975.pdf</t>
         </is>
       </c>
       <c r="V147" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5825.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5975.pdf</t>
         </is>
       </c>
       <c r="W147" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5825.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5975.pdf</t>
         </is>
       </c>
       <c r="X147" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5825.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5975.pdf</t>
         </is>
       </c>
     </row>
@@ -18232,72 +18232,72 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF BRASIL IRF-M TP RF LP - RESP LTDA</t>
+          <t>CAIXA FIC FIF BRASIL RENDA FIXA ATIVA LP RESP LTDA</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>16/08/2012</t>
+          <t>15/04/2020</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>3,63207700</t>
-        </is>
-      </c>
-      <c r="E148" s="7" t="inlineStr">
-        <is>
-          <t>-0,139</t>
+          <t>1.641,35750000</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>0,014</t>
         </is>
       </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>4,04</t>
+          <t>4,58</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>12,86</t>
+          <t>11,77</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>1.742,514</t>
+          <t>460,427</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>RPPS | TODOS</t>
+          <t>RPPS</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/brasil-irf-m-titulos-publicos-renda-fixa-longo-prazo</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/brasil-IPCA/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>10.740.670/0001-06</t>
+          <t>35.536.532/0001-22</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>Conservador</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr">
@@ -18312,37 +18312,37 @@
       </c>
       <c r="R148" s="2" t="inlineStr">
         <is>
-          <t>D+00 (du)</t>
+          <t>D+01 (du)</t>
         </is>
       </c>
       <c r="S148" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5464.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6481.pdf</t>
         </is>
       </c>
       <c r="T148" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5464.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6481.pdf</t>
         </is>
       </c>
       <c r="U148" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5464.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6481.pdf</t>
         </is>
       </c>
       <c r="V148" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5464.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6481.pdf</t>
         </is>
       </c>
       <c r="W148" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5464.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6481.pdf</t>
         </is>
       </c>
       <c r="X148" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5464.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6481.pdf</t>
         </is>
       </c>
     </row>
@@ -18354,42 +18354,42 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FI BRASIL IMA-B TP RF LP</t>
+          <t>CAIXA FI BRASIL IRF-M 1 TP RF</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>08/03/2010</t>
+          <t>28/05/2010</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>5,15395000</t>
-        </is>
-      </c>
-      <c r="E149" s="6" t="inlineStr">
-        <is>
-          <t>-0,245</t>
-        </is>
-      </c>
-      <c r="F149" s="6" t="inlineStr">
-        <is>
-          <t>-0,24</t>
+          <t>4,47381700</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>0,053</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>0,07</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>4,81</t>
+          <t>5,43</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>10,31</t>
+          <t>14,22</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>2.584,049</t>
+          <t>10.749,539</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
@@ -18399,22 +18399,22 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-ima-b-titulos-rf-longo-prazo</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-irfm-1-titulos-publicos-rf</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t>10.740.658/0001-93</t>
+          <t>10.740.670/0001-06</t>
         </is>
       </c>
       <c r="M149" s="4" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="N149" s="4" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Conservador</t>
         </is>
       </c>
       <c r="O149" s="4" t="inlineStr">
@@ -18439,32 +18439,32 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5184.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5464.pdf</t>
         </is>
       </c>
       <c r="T149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5184.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5464.pdf</t>
         </is>
       </c>
       <c r="U149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5184.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5464.pdf</t>
         </is>
       </c>
       <c r="V149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5184.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5464.pdf</t>
         </is>
       </c>
       <c r="W149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5184.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5464.pdf</t>
         </is>
       </c>
       <c r="X149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5184.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5464.pdf</t>
         </is>
       </c>
     </row>
@@ -18476,42 +18476,42 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF BRASIL IMA-B 5 TP RF LP - RESP LTDA</t>
+          <t>CAIXA FIF BRASIL IDKA IPCA 2A TIT PUB RF LP RESP LTDA</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>09/07/2010</t>
+          <t>16/08/2012</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>5,17975600</t>
+          <t>3,81875800</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr">
         <is>
-          <t>-0,040</t>
+          <t>-0,017</t>
         </is>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>-0,01</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>6,10</t>
+          <t>6,08</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>12,08</t>
+          <t>12,35</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>5.557,344</t>
+          <t>2.992,804</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -18521,17 +18521,17 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-ima-b-5-titulos-publicos-rf-longo-prazo</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-idka-ipca-2a-rf-longo-prazo</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>10.740.658/0001-93</t>
+          <t>14.386.926/0001-71</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5825</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -18561,32 +18561,32 @@
       </c>
       <c r="S150" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5184.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5825.pdf</t>
         </is>
       </c>
       <c r="T150" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5184.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5825.pdf</t>
         </is>
       </c>
       <c r="U150" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5184.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5825.pdf</t>
         </is>
       </c>
       <c r="V150" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5184.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5825.pdf</t>
         </is>
       </c>
       <c r="W150" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5184.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5825.pdf</t>
         </is>
       </c>
       <c r="X150" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5184.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5825.pdf</t>
         </is>
       </c>
     </row>
@@ -18598,42 +18598,42 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF BRASIL IMA GERAL TP RF LP - RESP LTDA</t>
+          <t>CAIXA FIF BRASIL IRF-M TP RF LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>08/07/2010</t>
+          <t>16/08/2012</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>4,74521200</t>
+          <t>3,62768300</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>-0,064</t>
+          <t>-0,120</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>3,91</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>13,26</t>
+          <t>12,82</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>512,831</t>
+          <t>1.740,406</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
@@ -18643,22 +18643,22 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-ima-geral-tp-rf-longo-prazo</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/brasil-irf-m-titulos-publicos-renda-fixa-longo-prazo</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t>11.061.217/0001-28</t>
+          <t>10.740.670/0001-06</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="N151" s="4" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Conservador</t>
         </is>
       </c>
       <c r="O151" s="4" t="inlineStr">
@@ -18683,32 +18683,32 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5188.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5464.pdf</t>
         </is>
       </c>
       <c r="T151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5188.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5464.pdf</t>
         </is>
       </c>
       <c r="U151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5188.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5464.pdf</t>
         </is>
       </c>
       <c r="V151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5188.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5464.pdf</t>
         </is>
       </c>
       <c r="W151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5188.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5464.pdf</t>
         </is>
       </c>
       <c r="X151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5188.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5464.pdf</t>
         </is>
       </c>
     </row>
@@ -18720,42 +18720,42 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF RS TITULOS PUBLICOS RF LP - RESP LTDA</t>
+          <t>CAIXA FI BRASIL IMA-B TP RF LP</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>18/07/2005</t>
+          <t>08/03/2010</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>7,93860700</t>
-        </is>
-      </c>
-      <c r="E152" s="3" t="inlineStr">
-        <is>
-          <t>0,044</t>
-        </is>
-      </c>
-      <c r="F152" s="3" t="inlineStr">
-        <is>
-          <t>0,04</t>
+          <t>5,14357700</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>-0,201</t>
+        </is>
+      </c>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>-0,44</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>5,65</t>
+          <t>4,60</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>14,60</t>
+          <t>10,28</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>172,214</t>
+          <t>2.576,120</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -18765,22 +18765,74 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-rs-titulos-publicos-rf-longo-prazo</t>
-        </is>
-      </c>
-      <c r="L152" s="2" t="inlineStr"/>
-      <c r="M152" s="2" t="inlineStr"/>
-      <c r="N152" s="2" t="inlineStr"/>
-      <c r="O152" s="2" t="inlineStr"/>
-      <c r="P152" s="2" t="inlineStr"/>
-      <c r="Q152" s="2" t="inlineStr"/>
-      <c r="R152" s="2" t="inlineStr"/>
-      <c r="S152" s="2" t="inlineStr"/>
-      <c r="T152" s="2" t="inlineStr"/>
-      <c r="U152" s="2" t="inlineStr"/>
-      <c r="V152" s="2" t="inlineStr"/>
-      <c r="W152" s="2" t="inlineStr"/>
-      <c r="X152" s="2" t="inlineStr"/>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-ima-b-titulos-rf-longo-prazo</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>10.740.658/0001-93</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5184.pdf</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5184.pdf</t>
+        </is>
+      </c>
+      <c r="U152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5184.pdf</t>
+        </is>
+      </c>
+      <c r="V152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5184.pdf</t>
+        </is>
+      </c>
+      <c r="W152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5184.pdf</t>
+        </is>
+      </c>
+      <c r="X152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5184.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -18790,42 +18842,42 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF BRASIL IMA-B 5+ TP RF LP - RESP LTDA</t>
+          <t>CAIXA FIF BRASIL IMA-B 5 TP RF LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>18/04/2012</t>
+          <t>09/07/2010</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>3,46303400</t>
+          <t>5,17742400</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>-0,401</t>
+          <t>-0,045</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>-0,40</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>6,05</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>8,96</t>
+          <t>12,11</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>773,584</t>
+          <t>5.558,662</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
@@ -18835,7 +18887,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-ima-b-5_mais-titulos-publicos-rf-lp/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-ima-b-5-titulos-publicos-rf-longo-prazo</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
@@ -18912,42 +18964,42 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FI BRASIL IRF-M 1+ TP RF LP</t>
+          <t>CAIXA FIF BRASIL IMA GERAL TP RF LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>11/05/2012</t>
+          <t>08/07/2010</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>3,76624600</t>
+          <t>4,74288700</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
         <is>
-          <t>-0,202</t>
+          <t>-0,048</t>
         </is>
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>-0,20</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>3,56</t>
+          <t>5,07</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>12,33</t>
+          <t>13,24</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>770,969</t>
+          <t>512,580</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -18957,22 +19009,22 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-irfm-1-titulos-publicos-rf-longo-prazo/</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-ima-geral-tp-rf-longo-prazo</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>10.740.670/0001-06</t>
+          <t>11.061.217/0001-28</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5188</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>Conservador</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="O154" s="2" t="inlineStr">
@@ -18997,32 +19049,32 @@
       </c>
       <c r="S154" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5464.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5188.pdf</t>
         </is>
       </c>
       <c r="T154" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5464.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5188.pdf</t>
         </is>
       </c>
       <c r="U154" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5464.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5188.pdf</t>
         </is>
       </c>
       <c r="V154" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5464.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5188.pdf</t>
         </is>
       </c>
       <c r="W154" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5464.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5188.pdf</t>
         </is>
       </c>
       <c r="X154" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5464.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5188.pdf</t>
         </is>
       </c>
     </row>
@@ -19034,42 +19086,42 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF BRASIL TITULOS PUBLICOS RF LP - RESP LTDA</t>
+          <t>CAIXA FIF RS TITULOS PUBLICOS RF LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>10/02/2006</t>
+          <t>18/07/2005</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>7,16498700</t>
+          <t>7,94254100</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>5,68</t>
+          <t>5,70</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>14,67</t>
+          <t>14,60</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>12.754,808</t>
+          <t>172,551</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
@@ -19079,74 +19131,22 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-titulos-publicos-rf-longo-prazo</t>
-        </is>
-      </c>
-      <c r="L155" s="4" t="inlineStr">
-        <is>
-          <t>05.164.356/0001-84</t>
-        </is>
-      </c>
-      <c r="M155" s="4" t="inlineStr">
-        <is>
-          <t>5462</t>
-        </is>
-      </c>
-      <c r="N155" s="4" t="inlineStr">
-        <is>
-          <t>Conservador</t>
-        </is>
-      </c>
-      <c r="O155" s="4" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="P155" s="4" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="Q155" s="4" t="inlineStr">
-        <is>
-          <t>D+0 (du)</t>
-        </is>
-      </c>
-      <c r="R155" s="4" t="inlineStr">
-        <is>
-          <t>D+00 (du)</t>
-        </is>
-      </c>
-      <c r="S155" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5462.pdf</t>
-        </is>
-      </c>
-      <c r="T155" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5462.pdf</t>
-        </is>
-      </c>
-      <c r="U155" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5462.pdf</t>
-        </is>
-      </c>
-      <c r="V155" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5462.pdf</t>
-        </is>
-      </c>
-      <c r="W155" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5462.pdf</t>
-        </is>
-      </c>
-      <c r="X155" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5462.pdf</t>
-        </is>
-      </c>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-rs-titulos-publicos-rf-longo-prazo</t>
+        </is>
+      </c>
+      <c r="L155" s="4" t="inlineStr"/>
+      <c r="M155" s="4" t="inlineStr"/>
+      <c r="N155" s="4" t="inlineStr"/>
+      <c r="O155" s="4" t="inlineStr"/>
+      <c r="P155" s="4" t="inlineStr"/>
+      <c r="Q155" s="4" t="inlineStr"/>
+      <c r="R155" s="4" t="inlineStr"/>
+      <c r="S155" s="4" t="inlineStr"/>
+      <c r="T155" s="4" t="inlineStr"/>
+      <c r="U155" s="4" t="inlineStr"/>
+      <c r="V155" s="4" t="inlineStr"/>
+      <c r="W155" s="4" t="inlineStr"/>
+      <c r="X155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -19156,42 +19156,42 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF ALIANÇA TP RF CURTO PRAZO - RESP LTDA</t>
+          <t>CAIXA FIF BRASIL IMA-B 5+ TP RF LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>01/11/2005</t>
+          <t>18/04/2012</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>7,48276500</t>
-        </is>
-      </c>
-      <c r="E156" s="3" t="inlineStr">
-        <is>
-          <t>0,052</t>
-        </is>
-      </c>
-      <c r="F156" s="3" t="inlineStr">
-        <is>
-          <t>0,05</t>
+          <t>3,45170400</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>-0,327</t>
+        </is>
+      </c>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>-0,72</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>5,62</t>
+          <t>3,45</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>14,55</t>
+          <t>8,86</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>4.560,977</t>
+          <t>771,110</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -19201,22 +19201,22 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-alianca-rf</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-ima-b-5_mais-titulos-publicos-rf-lp/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>05.164.358/0001-73</t>
+          <t>10.740.658/0001-93</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>Conservador</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="O156" s="2" t="inlineStr">
@@ -19241,32 +19241,32 @@
       </c>
       <c r="S156" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5461.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5184.pdf</t>
         </is>
       </c>
       <c r="T156" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5461.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5184.pdf</t>
         </is>
       </c>
       <c r="U156" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5461.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5184.pdf</t>
         </is>
       </c>
       <c r="V156" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5461.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5184.pdf</t>
         </is>
       </c>
       <c r="W156" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5461.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5184.pdf</t>
         </is>
       </c>
       <c r="X156" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5461.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5184.pdf</t>
         </is>
       </c>
     </row>
@@ -19278,67 +19278,67 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF BRASIL IDKA PRE 2A RF LP RESP LTDA</t>
+          <t>CAIXA FI BRASIL IRF-M 1+ TP RF LP</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>21/09/2022</t>
+          <t>11/05/2012</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>1,44406900</t>
+          <t>3,75904800</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>-0,206</t>
+          <t>-0,191</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>-0,20</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>3,56</t>
+          <t>3,37</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>12,26</t>
+          <t>12,29</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>172,013</t>
+          <t>717,863</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>RPPS</t>
+          <t>RPPS | TODOS</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-caixa-brasil-idka-pre2a-rf-lp/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-irfm-1-titulos-publicos-rf-longo-prazo/</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>45.163.710/0001-70</t>
+          <t>10.740.670/0001-06</t>
         </is>
       </c>
       <c r="M157" s="4" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="N157" s="4" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Conservador</t>
         </is>
       </c>
       <c r="O157" s="4" t="inlineStr">
@@ -19363,32 +19363,32 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6634.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5464.pdf</t>
         </is>
       </c>
       <c r="T157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6634.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5464.pdf</t>
         </is>
       </c>
       <c r="U157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6634.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5464.pdf</t>
         </is>
       </c>
       <c r="V157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6634.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5464.pdf</t>
         </is>
       </c>
       <c r="W157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6634.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5464.pdf</t>
         </is>
       </c>
       <c r="X157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6634.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5464.pdf</t>
         </is>
       </c>
     </row>
@@ -19400,17 +19400,17 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF BRASIL DISPONIBILIDADES SIMPLES RF RESP LTDA</t>
+          <t>CAIXA FIF BRASIL TITULOS PUBLICOS RF LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>30/08/2012</t>
+          <t>10/02/2006</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>3,13557000</t>
+          <t>7,16858700</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -19420,22 +19420,22 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>5,32</t>
+          <t>5,73</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>13,67</t>
+          <t>14,67</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>1.520,329</t>
+          <t>12.733,156</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -19445,17 +19445,17 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/brasil-disponibilidades</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-titulos-publicos-rf-longo-prazo</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>14.508.643/0001-55</t>
+          <t>05.164.356/0001-84</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -19465,12 +19465,12 @@
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -19485,79 +19485,79 @@
       </c>
       <c r="S158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5826.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5462.pdf</t>
         </is>
       </c>
       <c r="T158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5826.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5462.pdf</t>
         </is>
       </c>
       <c r="U158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5826.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5462.pdf</t>
         </is>
       </c>
       <c r="V158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5826.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5462.pdf</t>
         </is>
       </c>
       <c r="W158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5826.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5462.pdf</t>
         </is>
       </c>
       <c r="X158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5826.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5462.pdf</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>RENDA FIXA REFERENCIADO</t>
+          <t>RENDA FIXA</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF BRASIL RF REFER DI LONGO PRAZO RESP LTDA</t>
+          <t>CAIXA FIF ALIANÇA TP RF CURTO PRAZO - RESP LTDA</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>05/07/2006</t>
+          <t>01/11/2005</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>6,71067300</t>
+          <t>7,48669100</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>5,74</t>
+          <t>5,67</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>14,85</t>
+          <t>14,55</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>23.857,075</t>
+          <t>4.476,403</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -19567,87 +19567,139 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fi-brasil-ref-di-longo-prazo</t>
-        </is>
-      </c>
-      <c r="L159" s="4" t="inlineStr"/>
-      <c r="M159" s="4" t="inlineStr"/>
-      <c r="N159" s="4" t="inlineStr"/>
-      <c r="O159" s="4" t="inlineStr"/>
-      <c r="P159" s="4" t="inlineStr"/>
-      <c r="Q159" s="4" t="inlineStr"/>
-      <c r="R159" s="4" t="inlineStr"/>
-      <c r="S159" s="4" t="inlineStr"/>
-      <c r="T159" s="4" t="inlineStr"/>
-      <c r="U159" s="4" t="inlineStr"/>
-      <c r="V159" s="4" t="inlineStr"/>
-      <c r="W159" s="4" t="inlineStr"/>
-      <c r="X159" s="4" t="inlineStr"/>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-alianca-rf</t>
+        </is>
+      </c>
+      <c r="L159" s="4" t="inlineStr">
+        <is>
+          <t>05.164.358/0001-73</t>
+        </is>
+      </c>
+      <c r="M159" s="4" t="inlineStr">
+        <is>
+          <t>5461</t>
+        </is>
+      </c>
+      <c r="N159" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="O159" s="4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="P159" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Q159" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="R159" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="S159" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5461.pdf</t>
+        </is>
+      </c>
+      <c r="T159" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5461.pdf</t>
+        </is>
+      </c>
+      <c r="U159" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5461.pdf</t>
+        </is>
+      </c>
+      <c r="V159" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5461.pdf</t>
+        </is>
+      </c>
+      <c r="W159" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5461.pdf</t>
+        </is>
+      </c>
+      <c r="X159" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5461.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>RENDA FIXA REFERENCIADO</t>
+          <t>RENDA FIXA</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF NOVO BRASIL RF IMA-B LP RESP LTDA</t>
+          <t>CAIXA FIC FIF BRASIL IDKA PRE 2A RF LP RESP LTDA</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>27/10/2009</t>
+          <t>21/09/2022</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>5,52173000</t>
+          <t>1,44353600</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr">
         <is>
-          <t>-0,267</t>
+          <t>-0,036</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>5,05</t>
+          <t>3,52</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>10,64</t>
+          <t>12,25</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>594,895</t>
+          <t>171,950</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>RPPS | TODOS</t>
+          <t>RPPS</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-novo-brasil-ima-b-rf-longo-prazo</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-caixa-brasil-idka-pre2a-rf-lp/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>10.646.895/0001-90</t>
+          <t>45.163.710/0001-70</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -19677,201 +19729,201 @@
       </c>
       <c r="S160" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5168.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6634.pdf</t>
         </is>
       </c>
       <c r="T160" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5168.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6634.pdf</t>
         </is>
       </c>
       <c r="U160" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5168.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6634.pdf</t>
         </is>
       </c>
       <c r="V160" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5168.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6634.pdf</t>
         </is>
       </c>
       <c r="W160" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5168.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6634.pdf</t>
         </is>
       </c>
       <c r="X160" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5168.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6634.pdf</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>MULTIMERCADO</t>
+          <t>RENDA FIXA</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF BRASIL ESTRATÉGIA LIVRE MM LP RESP LTDA</t>
+          <t>CAIXA FIC FIF BRASIL DISPONIBILIDADES SIMPLES RF RESP LTDA</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>21/10/2019</t>
+          <t>30/08/2012</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E161" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F161" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G161" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H161" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>3,13714100</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>0,050</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>0,10</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>5,38</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>13,67</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.428,025</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>RPPS</t>
+          <t>RPPS | TODOS</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/estrategia-livre-mm-lp/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/brasil-disponibilidades</t>
         </is>
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
-          <t>34.660.276/0001-18</t>
+          <t>14.508.643/0001-55</t>
         </is>
       </c>
       <c r="M161" s="4" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="N161" s="4" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Conservador</t>
         </is>
       </c>
       <c r="O161" s="4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="Q161" s="4" t="inlineStr">
         <is>
-          <t>D+13 (du)</t>
+          <t>D+0 (du)</t>
         </is>
       </c>
       <c r="R161" s="4" t="inlineStr">
         <is>
-          <t>D+15 (du)</t>
+          <t>D+00 (du)</t>
         </is>
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6439.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5826.pdf</t>
         </is>
       </c>
       <c r="T161" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6439.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5826.pdf</t>
         </is>
       </c>
       <c r="U161" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6439.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5826.pdf</t>
         </is>
       </c>
       <c r="V161" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6439.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5826.pdf</t>
         </is>
       </c>
       <c r="W161" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6439.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5826.pdf</t>
         </is>
       </c>
       <c r="X161" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6439.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5826.pdf</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>ACOES</t>
+          <t>RENDA FIXA REFERENCIADO</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF AÇOES BRASIL IBOVESPA RESP LTDA</t>
+          <t>CAIXA FIC FIF BRASIL RF REFER DI LONGO PRAZO RESP LTDA</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>29/07/2011</t>
+          <t>05/07/2006</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>3,86220100</t>
-        </is>
-      </c>
-      <c r="E162" s="7" t="inlineStr">
-        <is>
-          <t>-0,915</t>
-        </is>
-      </c>
-      <c r="F162" s="7" t="inlineStr">
-        <is>
-          <t>-0,91</t>
+          <t>6,71418300</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>0,052</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>6,67</t>
+          <t>5,79</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>25,20</t>
+          <t>14,85</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>291,541</t>
+          <t>23.574,588</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -19881,119 +19933,67 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-brasil-ibovespa/Paginas/default.aspx</t>
-        </is>
-      </c>
-      <c r="L162" s="2" t="inlineStr">
-        <is>
-          <t>13.058.816/0001-18</t>
-        </is>
-      </c>
-      <c r="M162" s="2" t="inlineStr">
-        <is>
-          <t>5445</t>
-        </is>
-      </c>
-      <c r="N162" s="2" t="inlineStr">
-        <is>
-          <t>Arrojado</t>
-        </is>
-      </c>
-      <c r="O162" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="P162" s="2" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="Q162" s="2" t="inlineStr">
-        <is>
-          <t>D+1 (du)</t>
-        </is>
-      </c>
-      <c r="R162" s="2" t="inlineStr">
-        <is>
-          <t>D+03 (du)</t>
-        </is>
-      </c>
-      <c r="S162" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5445.pdf</t>
-        </is>
-      </c>
-      <c r="T162" s="2" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5445.pdf</t>
-        </is>
-      </c>
-      <c r="U162" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5445.pdf</t>
-        </is>
-      </c>
-      <c r="V162" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5445.pdf</t>
-        </is>
-      </c>
-      <c r="W162" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5445.pdf</t>
-        </is>
-      </c>
-      <c r="X162" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5445.pdf</t>
-        </is>
-      </c>
+          <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fi-brasil-ref-di-longo-prazo</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr"/>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr"/>
+      <c r="O162" s="2" t="inlineStr"/>
+      <c r="P162" s="2" t="inlineStr"/>
+      <c r="Q162" s="2" t="inlineStr"/>
+      <c r="R162" s="2" t="inlineStr"/>
+      <c r="S162" s="2" t="inlineStr"/>
+      <c r="T162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr"/>
+      <c r="W162" s="2" t="inlineStr"/>
+      <c r="X162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>ACOES</t>
+          <t>RENDA FIXA REFERENCIADO</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF AÇÕES BRASIL ETF IBOVESPA RESP LTDA</t>
+          <t>CAIXA FIC FIF NOVO BRASIL RF IMA-B LP RESP LTDA</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>27/11/2012</t>
+          <t>27/10/2009</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>3,55014900</t>
+          <t>5,51026900</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>-0,906</t>
+          <t>-0,207</t>
         </is>
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>-0,90</t>
+          <t>-0,47</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>6,48</t>
+          <t>4,83</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>24,62</t>
+          <t>10,57</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>8,983</t>
+          <t>593,660</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
@@ -20003,27 +20003,27 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-brasil-etf-bovespa</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-novo-brasil-ima-b-rf-longo-prazo</t>
         </is>
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
-          <t>15.154.236/0001-50</t>
+          <t>10.646.895/0001-90</t>
         </is>
       </c>
       <c r="M163" s="4" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N163" s="4" t="inlineStr">
         <is>
-          <t>Arrojado</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="O163" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="P163" s="4" t="inlineStr">
@@ -20033,119 +20033,119 @@
       </c>
       <c r="Q163" s="4" t="inlineStr">
         <is>
-          <t>D+1 (du)</t>
+          <t>D+0 (du)</t>
         </is>
       </c>
       <c r="R163" s="4" t="inlineStr">
         <is>
-          <t>D+03 (du)</t>
+          <t>D+00 (du)</t>
         </is>
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5842.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5168.pdf</t>
         </is>
       </c>
       <c r="T163" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5842.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5168.pdf</t>
         </is>
       </c>
       <c r="U163" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5842.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5168.pdf</t>
         </is>
       </c>
       <c r="V163" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5842.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5168.pdf</t>
         </is>
       </c>
       <c r="W163" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5842.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5168.pdf</t>
         </is>
       </c>
       <c r="X163" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5842.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5168.pdf</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>ACOES</t>
+          <t>MULTIMERCADO</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF AÇÕES INSTITUCIONAL BDR NIVEL I RESP LTDA</t>
+          <t>CAIXA FIC FIF BRASIL ESTRATÉGIA LIVRE MM LP RESP LTDA</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>24/06/2013</t>
+          <t>21/10/2019</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>11,50005216</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>0,044</t>
-        </is>
-      </c>
-      <c r="F164" s="3" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
-      <c r="G164" s="3" t="inlineStr">
-        <is>
-          <t>3,91</t>
-        </is>
-      </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>22,97</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>2.374,521</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>RPPS | TODOS</t>
+          <t>RPPS</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/FIA-Institucional-BDR-nivel-I/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/estrategia-livre-mm-lp/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>17.502.937/0001-68</t>
+          <t>34.660.276/0001-18</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>5929</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>Arrojado</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="P164" s="2" t="inlineStr">
@@ -20155,42 +20155,42 @@
       </c>
       <c r="Q164" s="2" t="inlineStr">
         <is>
-          <t>D+1 (du)</t>
+          <t>D+13 (du)</t>
         </is>
       </c>
       <c r="R164" s="2" t="inlineStr">
         <is>
-          <t>D+03 (du)</t>
+          <t>D+15 (du)</t>
         </is>
       </c>
       <c r="S164" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5929.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6439.pdf</t>
         </is>
       </c>
       <c r="T164" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5929.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6439.pdf</t>
         </is>
       </c>
       <c r="U164" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5929.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6439.pdf</t>
         </is>
       </c>
       <c r="V164" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5929.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6439.pdf</t>
         </is>
       </c>
       <c r="W164" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5929.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6439.pdf</t>
         </is>
       </c>
       <c r="X164" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5929.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6439.pdf</t>
         </is>
       </c>
     </row>
@@ -20202,42 +20202,42 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF ACOES BRASIL IBX-50 RESP LTDA</t>
+          <t>CAIXA FIF AÇOES BRASIL IBOVESPA RESP LTDA</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>18/02/2008</t>
+          <t>29/07/2011</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>1,98439700</t>
-        </is>
-      </c>
-      <c r="E165" s="6" t="inlineStr">
-        <is>
-          <t>-0,968</t>
-        </is>
-      </c>
-      <c r="F165" s="6" t="inlineStr">
-        <is>
-          <t>-0,96</t>
+          <t>3,90820000</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>1,191</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>0,26</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>7,94</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>21,92</t>
+          <t>26,91</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>195,886</t>
+          <t>294,955</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
@@ -20247,17 +20247,17 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-brasil-ibx-50</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-brasil-ibovespa/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
-          <t>03.737.217/0001-77</t>
+          <t>13.058.816/0001-18</t>
         </is>
       </c>
       <c r="M165" s="4" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="N165" s="4" t="inlineStr">
@@ -20267,7 +20267,7 @@
       </c>
       <c r="O165" s="4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="P165" s="4" t="inlineStr">
@@ -20287,32 +20287,32 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5396.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5445.pdf</t>
         </is>
       </c>
       <c r="T165" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5396.pdf</t>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5445.pdf</t>
         </is>
       </c>
       <c r="U165" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5396.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5445.pdf</t>
         </is>
       </c>
       <c r="V165" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5396.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5445.pdf</t>
         </is>
       </c>
       <c r="W165" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5396.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5445.pdf</t>
         </is>
       </c>
       <c r="X165" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5396.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5445.pdf</t>
         </is>
       </c>
     </row>
@@ -20324,62 +20324,62 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>CAIXA ATENA FIC FIF AÇÕES BRASIL LIVRE QUANT RESP LTDA</t>
+          <t>CAIXA FIF AÇÕES BRASIL ETF IBOVESPA RESP LTDA</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>31/07/2019</t>
+          <t>27/11/2012</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>1,98353800</t>
-        </is>
-      </c>
-      <c r="E166" s="7" t="inlineStr">
-        <is>
-          <t>-1,178</t>
-        </is>
-      </c>
-      <c r="F166" s="7" t="inlineStr">
-        <is>
-          <t>-1,17</t>
-        </is>
-      </c>
-      <c r="G166" s="7" t="inlineStr">
-        <is>
-          <t>-4,32</t>
+          <t>3,59305400</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>1,208</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>0,29</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>7,76</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>11,33</t>
+          <t>26,44</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>749,341</t>
+          <t>9,092</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>RPPS</t>
+          <t>RPPS | TODOS</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/FIC-FIA-Brasil-Acoes-Livres/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-brasil-etf-bovespa</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>30.068.169/0001-44</t>
+          <t>15.154.236/0001-50</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -20389,7 +20389,7 @@
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="P166" s="2" t="inlineStr">
@@ -20399,42 +20399,42 @@
       </c>
       <c r="Q166" s="2" t="inlineStr">
         <is>
-          <t>D+13 (du)</t>
+          <t>D+1 (du)</t>
         </is>
       </c>
       <c r="R166" s="2" t="inlineStr">
         <is>
-          <t>D+15 (du)</t>
+          <t>D+03 (du)</t>
         </is>
       </c>
       <c r="S166" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6425.pdf</t>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5842.pdf</t>
         </is>
       </c>
       <c r="T166" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6425.pdf</t>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5842.pdf</t>
         </is>
       </c>
       <c r="U166" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6425.pdf</t>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5842.pdf</t>
         </is>
       </c>
       <c r="V166" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_6425.pdf</t>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5842.pdf</t>
         </is>
       </c>
       <c r="W166" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6425.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5842.pdf</t>
         </is>
       </c>
       <c r="X166" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6425.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5842.pdf</t>
         </is>
       </c>
     </row>
@@ -20446,42 +20446,42 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC ACOES EXPERT VINCI VALOR DIVIDENDOS RPPS RESP LTDA</t>
+          <t>CAIXA FIF AÇÕES INSTITUCIONAL BDR NIVEL I RESP LTDA</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>23/08/2012</t>
+          <t>24/06/2013</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>3,38407517</t>
-        </is>
-      </c>
-      <c r="E167" s="6" t="inlineStr">
-        <is>
-          <t>-0,868</t>
-        </is>
-      </c>
-      <c r="F167" s="6" t="inlineStr">
-        <is>
-          <t>-0,86</t>
+          <t>11,50043671</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>0,003</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>0,04</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>3,91</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
         <is>
-          <t>18,78</t>
+          <t>23,14</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>1.297,715</t>
+          <t>2.375,666</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
@@ -20491,17 +20491,17 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/rpps/caixa-fic-acoes-vinci-valor-dividendos-rpps</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/FIA-Institucional-BDR-nivel-I/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
-          <t>15.154.441/0001-15</t>
+          <t>17.502.937/0001-68</t>
         </is>
       </c>
       <c r="M167" s="4" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="N167" s="4" t="inlineStr">
@@ -20509,50 +20509,54 @@
           <t>Arrojado</t>
         </is>
       </c>
-      <c r="O167" s="4" t="inlineStr"/>
+      <c r="O167" s="4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>10000.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="Q167" s="4" t="inlineStr">
         <is>
-          <t>D+30 (du)</t>
+          <t>D+1 (du)</t>
         </is>
       </c>
       <c r="R167" s="4" t="inlineStr">
         <is>
-          <t>D+32 (du)</t>
+          <t>D+03 (du)</t>
         </is>
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6160.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5929.pdf</t>
         </is>
       </c>
       <c r="T167" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6160.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5929.pdf</t>
         </is>
       </c>
       <c r="U167" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6160.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5929.pdf</t>
         </is>
       </c>
       <c r="V167" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_6160.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5929.pdf</t>
         </is>
       </c>
       <c r="W167" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6160.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5929.pdf</t>
         </is>
       </c>
       <c r="X167" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6160.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5929.pdf</t>
         </is>
       </c>
     </row>
@@ -20564,42 +20568,42 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC ACOES EXPERT VINCI VALOR RPPS RESP LTDA</t>
+          <t>CAIXA FIF ACOES BRASIL IBX-50 RESP LTDA</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>12/12/2011</t>
+          <t>18/02/2008</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>2,46337156</t>
-        </is>
-      </c>
-      <c r="E168" s="7" t="inlineStr">
-        <is>
-          <t>-1,032</t>
-        </is>
-      </c>
-      <c r="F168" s="7" t="inlineStr">
-        <is>
-          <t>-1,03</t>
+          <t>2,00676300</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>1,127</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>5,87</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>20,42</t>
+          <t>23,41</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>762,464</t>
+          <t>198,094</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -20609,17 +20613,17 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/rpps/caixa-fic-acoes-vinci-valor-rpps</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-brasil-ibx-50</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>14.507.699/0001-95</t>
+          <t>03.737.217/0001-77</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -20627,127 +20631,131 @@
           <t>Arrojado</t>
         </is>
       </c>
-      <c r="O168" s="2" t="inlineStr"/>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>10000.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
         <is>
-          <t>D+21 (du)</t>
+          <t>D+1 (du)</t>
         </is>
       </c>
       <c r="R168" s="2" t="inlineStr">
         <is>
-          <t>D+23 (du)</t>
+          <t>D+03 (du)</t>
         </is>
       </c>
       <c r="S168" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5563.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5396.pdf</t>
         </is>
       </c>
       <c r="T168" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5563.pdf</t>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5396.pdf</t>
         </is>
       </c>
       <c r="U168" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5563.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5396.pdf</t>
         </is>
       </c>
       <c r="V168" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5563.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5396.pdf</t>
         </is>
       </c>
       <c r="W168" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5563.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5396.pdf</t>
         </is>
       </c>
       <c r="X168" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5563.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5396.pdf</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>RENDA FIXA</t>
+          <t>ACOES</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF EXTRAMERCADO COMUM IRFM-1 RF RESP LTDA</t>
+          <t>CAIXA ATENA FIC FIF AÇÕES BRASIL LIVRE QUANT RESP LTDA</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>13/02/2012</t>
+          <t>31/07/2019</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>3,74127000</t>
+          <t>1,99604400</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>0,013</t>
-        </is>
-      </c>
-      <c r="F169" s="5" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="G169" s="5" t="inlineStr">
-        <is>
-          <t>5,36</t>
+          <t>0,630</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>-0,55</t>
+        </is>
+      </c>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>-3,72</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
         <is>
-          <t>14,26</t>
+          <t>12,69</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>4.858,096</t>
+          <t>754,066</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>TODOS</t>
+          <t>RPPS</t>
         </is>
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-extramercado-comum-irfm-1-rf/Paginas/default.aspx</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/FIC-FIA-Brasil-Acoes-Livres/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
-          <t>14.507.897/0001-59</t>
+          <t>30.068.169/0001-44</t>
         </is>
       </c>
       <c r="M169" s="4" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="N169" s="4" t="inlineStr">
         <is>
-          <t>Conservador</t>
+          <t>Arrojado</t>
         </is>
       </c>
       <c r="O169" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="P169" s="4" t="inlineStr">
@@ -20757,286 +20765,400 @@
       </c>
       <c r="Q169" s="4" t="inlineStr">
         <is>
-          <t>D+0 (du)</t>
+          <t>D+13 (du)</t>
         </is>
       </c>
       <c r="R169" s="4" t="inlineStr">
         <is>
-          <t>D+00 (du)</t>
+          <t>D+15 (du)</t>
         </is>
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5487.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6425.pdf</t>
         </is>
       </c>
       <c r="T169" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5487.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6425.pdf</t>
         </is>
       </c>
       <c r="U169" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5487.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6425.pdf</t>
         </is>
       </c>
       <c r="V169" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5487.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_6425.pdf</t>
         </is>
       </c>
       <c r="W169" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5487.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6425.pdf</t>
         </is>
       </c>
       <c r="X169" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5487.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6425.pdf</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>RENDA FIXA CURTO PRAZO</t>
+          <t>ACOES</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF PRÁTICO RF CURTO PRAZO RESP LTDA</t>
+          <t>CAIXA FIC ACOES EXPERT VINCI VALOR DIVIDENDOS RPPS RESP LTDA</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>02/10/1995</t>
+          <t>23/08/2012</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>9,39462200</t>
+          <t>3,41555950</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,930</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>4,95</t>
+          <t>4,98</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>12,52</t>
+          <t>20,12</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>2.761,976</t>
+          <t>1.309,789</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>TODOS</t>
+          <t>RPPS | TODOS</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-pratico-curto-prazo</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/rpps/caixa-fic-acoes-vinci-valor-dividendos-rpps</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>00.834.074/0001-23</t>
+          <t>15.154.441/0001-15</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>6160</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>Conservador</t>
-        </is>
-      </c>
-      <c r="O170" s="2" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr"/>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
         <is>
-          <t>D+0 (du)</t>
+          <t>D+30 (du)</t>
         </is>
       </c>
       <c r="R170" s="2" t="inlineStr">
         <is>
-          <t>D+00 (du)</t>
+          <t>D+32 (du)</t>
         </is>
       </c>
       <c r="S170" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0055.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6160.pdf</t>
         </is>
       </c>
       <c r="T170" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0055.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6160.pdf</t>
         </is>
       </c>
       <c r="U170" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0055.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6160.pdf</t>
         </is>
       </c>
       <c r="V170" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_0055.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_6160.pdf</t>
         </is>
       </c>
       <c r="W170" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_55.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6160.pdf</t>
         </is>
       </c>
       <c r="X170" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_55.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6160.pdf</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>RENDA FIXA CURTO PRAZO</t>
+          <t>ACOES</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF TRANSFERÊNCIA VOLUNTÁRIA RF CP RESP LTDA</t>
+          <t>CAIXA FIC ACOES EXPERT VINCI VALOR RPPS RESP LTDA</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>16/10/2012</t>
+          <t>12/12/2011</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>2,47409800</t>
+          <t>2,48918181</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
-        </is>
-      </c>
-      <c r="F171" s="5" t="inlineStr">
-        <is>
-          <t>0,04</t>
+          <t>1,047</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>0,00</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>4,95</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>12,51</t>
+          <t>21,89</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>16.587,316</t>
+          <t>770,453</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
+          <t>RPPS | TODOS</t>
+        </is>
+      </c>
+      <c r="K171" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/rpps/caixa-fic-acoes-vinci-valor-rpps</t>
+        </is>
+      </c>
+      <c r="L171" s="4" t="inlineStr">
+        <is>
+          <t>14.507.699/0001-95</t>
+        </is>
+      </c>
+      <c r="M171" s="4" t="inlineStr">
+        <is>
+          <t>5563</t>
+        </is>
+      </c>
+      <c r="N171" s="4" t="inlineStr">
+        <is>
+          <t>Arrojado</t>
+        </is>
+      </c>
+      <c r="O171" s="4" t="inlineStr"/>
+      <c r="P171" s="4" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="Q171" s="4" t="inlineStr">
+        <is>
+          <t>D+21 (du)</t>
+        </is>
+      </c>
+      <c r="R171" s="4" t="inlineStr">
+        <is>
+          <t>D+23 (du)</t>
+        </is>
+      </c>
+      <c r="S171" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5563.pdf</t>
+        </is>
+      </c>
+      <c r="T171" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5563.pdf</t>
+        </is>
+      </c>
+      <c r="U171" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5563.pdf</t>
+        </is>
+      </c>
+      <c r="V171" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5563.pdf</t>
+        </is>
+      </c>
+      <c r="W171" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5563.pdf</t>
+        </is>
+      </c>
+      <c r="X171" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5563.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>RENDA FIXA</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>CAIXA FIF EXTRAMERCADO COMUM IRFM-1 RF RESP LTDA</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>13/02/2012</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>3,74332300</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>0,054</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>5,42</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>14,26</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>5.020,242</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
           <t>TODOS</t>
         </is>
       </c>
-      <c r="K171" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-transferencias-voluntarias-curto-prazo</t>
-        </is>
-      </c>
-      <c r="L171" s="4" t="inlineStr">
-        <is>
-          <t>10.740.552/0001-90</t>
-        </is>
-      </c>
-      <c r="M171" s="4" t="inlineStr">
-        <is>
-          <t>5413</t>
-        </is>
-      </c>
-      <c r="N171" s="4" t="inlineStr">
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-extramercado-comum-irfm-1-rf/Paginas/default.aspx</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>14.507.897/0001-59</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>5487</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
         <is>
           <t>Conservador</t>
         </is>
       </c>
-      <c r="O171" s="4" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="P171" s="4" t="inlineStr">
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="Q171" s="4" t="inlineStr">
+      <c r="Q172" s="2" t="inlineStr">
         <is>
           <t>D+0 (du)</t>
         </is>
       </c>
-      <c r="R171" s="4" t="inlineStr">
+      <c r="R172" s="2" t="inlineStr">
         <is>
           <t>D+00 (du)</t>
         </is>
       </c>
-      <c r="S171" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5413.pdf</t>
-        </is>
-      </c>
-      <c r="T171" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5413.pdf</t>
-        </is>
-      </c>
-      <c r="U171" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5413.pdf</t>
-        </is>
-      </c>
-      <c r="V171" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5413.pdf</t>
-        </is>
-      </c>
-      <c r="W171" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5413.pdf</t>
-        </is>
-      </c>
-      <c r="X171" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5413.pdf</t>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5487.pdf</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5487.pdf</t>
+        </is>
+      </c>
+      <c r="U172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5487.pdf</t>
+        </is>
+      </c>
+      <c r="V172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5487.pdf</t>
+        </is>
+      </c>
+      <c r="W172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5487.pdf</t>
+        </is>
+      </c>
+      <c r="X172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5487.pdf</t>
         </is>
       </c>
     </row>

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,25710100</t>
+          <t>2,25814600</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -644,22 +644,22 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>5,08</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>12,86</t>
+          <t>12,85</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>407,369</t>
+          <t>408,094</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,48574300</t>
+          <t>5,48825000</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>4,94</t>
+          <t>4,99</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.577,348</t>
+          <t>6.647,958</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,76984500</t>
+          <t>2,77111000</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -836,12 +836,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>4,93</t>
+          <t>4,98</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>912,964</t>
+          <t>914,911</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -948,22 +948,22 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>3,32316600</t>
+          <t>3,32503500</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,056</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>5,46</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>11,604</t>
+          <t>11,619</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -1070,22 +1070,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,47709100</t>
+          <t>3,47879200</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>5,58</t>
+          <t>5,63</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>119,357</t>
+          <t>119,676</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1192,32 +1192,32 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1.830,37413000</t>
+          <t>1.831,40541700</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,056</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>5,62</t>
+          <t>5,68</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>14,64</t>
+          <t>14,63</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>96,626</t>
+          <t>96,725</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1314,32 +1314,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,67975000</t>
+          <t>9,68389600</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,042</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>5,23</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>13,37</t>
+          <t>13,36</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>581,312</t>
+          <t>581,053</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1436,22 +1436,22 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3,34705800</t>
+          <t>3,34859400</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>5,56</t>
+          <t>5,61</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>61,637</t>
+          <t>61,840</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1558,22 +1558,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,98841300</t>
+          <t>2,98999900</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>5,74</t>
+          <t>5,80</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1.663,270</t>
+          <t>1.661,853</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1676,32 +1676,32 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>19,81939200</t>
+          <t>19,68707100</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>-0,128</t>
+          <t>-0,667</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,95</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>3,40</t>
+          <t>2,71</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>11,76</t>
+          <t>10,90</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>121,705</t>
+          <t>120,771</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1798,32 +1798,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,47617500</t>
+          <t>13,42584800</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>-0,067</t>
+          <t>-0,373</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>-0,51</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>4,79</t>
+          <t>4,40</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>9,98</t>
+          <t>9,57</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,996</t>
+          <t>27,893</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>46,03674800</t>
+          <t>46,05640300</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,042</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>5,21</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>40,420</t>
+          <t>40,437</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20,16358100</t>
+          <t>20,17313400</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>5,12</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,419</t>
+          <t>64,449</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2164,32 +2164,32 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>3,13935900</t>
+          <t>3,12963200</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>-0,047</t>
+          <t>-0,309</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>-0,40</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>5,69</t>
+          <t>5,37</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>11,17</t>
+          <t>10,83</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>78,804</t>
+          <t>78,563</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -2286,32 +2286,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14,91396900</t>
+          <t>14,92038500</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>13,43</t>
+          <t>13,42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,727</t>
+          <t>27,739</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2408,32 +2408,32 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2,99207500</t>
+          <t>2,99331800</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,041</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>5,09</t>
+          <t>5,14</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>13,10</t>
+          <t>13,09</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>1,648</t>
+          <t>1,624</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -2530,32 +2530,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,30601200</t>
+          <t>3,28528800</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>-0,123</t>
+          <t>-0,626</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>-0,89</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>3,73</t>
+          <t>3,08</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>12,27</t>
+          <t>11,45</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>137,645</t>
+          <t>136,697</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2652,22 +2652,22 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,03098000</t>
+          <t>3,03273000</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,057</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>5,74</t>
+          <t>5,80</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1.756,237</t>
+          <t>1.786,191</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2774,22 +2774,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32,69915500</t>
+          <t>32,71366800</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>5,44</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2.219,414</t>
+          <t>2.208,200</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,29646000</t>
+          <t>3,29792400</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>5,40</t>
+          <t>5,45</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>13,84</t>
+          <t>13,83</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>13,113</t>
+          <t>13,119</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -3018,32 +3018,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3,33248500</t>
+          <t>3,30881100</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>-0,211</t>
+          <t>-0,710</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>-0,48</t>
+          <t>-1,18</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>4,56</t>
+          <t>3,82</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>9,89</t>
+          <t>9,09</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,098</t>
+          <t>65,634</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3140,22 +3140,22 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>18,98237200</t>
+          <t>18,99155600</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>949,330</t>
+          <t>950,253</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,11325852</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>-0,001</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>-0,10</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>3,20</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>212,384</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3384,32 +3384,32 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1,23677100</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>0,000</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>5,59</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>14,64</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>71,297</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/debentures-incentivadas/caixa-expert-vinlanddebenture-</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/debentures-incentivadas/caixa-expert-vinland-debenture-incentivado/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1.826,86888200</t>
+          <t>1.827,95187800</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>5,71</t>
+          <t>5,78</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>174,465</t>
+          <t>174,588</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3628,32 +3628,32 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1,20120100</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>0,047</t>
+          <t>1,20054500</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>-0,054</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>6,88</t>
+          <t>6,82</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>13,36</t>
+          <t>13,33</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>39,909</t>
+          <t>39,887</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -3750,32 +3750,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,03655000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,000</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>5,71</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,779</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3868,32 +3868,32 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,16642800</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>0,000</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>0,10</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>5,04</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>14,01</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>66,292</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -3986,32 +3986,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,06847084</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>-0,001</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>3,40</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>320,774</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -4222,22 +4222,22 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>5,12574500</t>
+          <t>5,12861200</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>5,72</t>
+          <t>5,78</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>848,456</t>
+          <t>849,219</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -4344,22 +4344,22 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>4,93215100</t>
+          <t>4,93504500</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,058</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>5,73</t>
+          <t>5,79</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.234,610</t>
+          <t>3.239,603</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>29,17973000</t>
+          <t>29,19381600</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>5,22</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,048</t>
+          <t>21,059</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4588,22 +4588,22 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>30,53191800</t>
+          <t>30,54699800</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>5,68</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>3.092,632</t>
+          <t>3.094,999</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -4710,32 +4710,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1.769,32684700</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>0,024</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>0,02</t>
+          <t>1.767,74423400</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>-0,089</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>4,94</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>13,63</t>
+          <t>13,48</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>124,370</t>
+          <t>124,365</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>3,21445900</t>
+          <t>3,21617500</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>5,83</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>588,232</t>
+          <t>588,128</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -4954,22 +4954,22 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>6,17284300</t>
+          <t>6,17583700</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>121,601</t>
+          <t>121,657</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -5076,32 +5076,32 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1,26593300</t>
+          <t>1,26668800</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,059</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>5,83</t>
+          <t>5,89</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>15,01</t>
+          <t>15,02</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>352,697</t>
+          <t>355,362</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -5198,22 +5198,22 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>10,56688300</t>
+          <t>10,57217900</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>5,71</t>
+          <t>5,76</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2.368,700</t>
+          <t>2.363,010</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -5320,22 +5320,22 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>5,50332500</t>
+          <t>5,50610100</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>5,81</t>
+          <t>5,86</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>551,725</t>
+          <t>552,007</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -5442,22 +5442,22 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3,55885400</t>
+          <t>3,56097100</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,059</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>5,81</t>
+          <t>5,88</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15.439,583</t>
+          <t>15.455,845</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5564,32 +5564,32 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>5,28908600</t>
+          <t>5,29163600</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>5,92</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>15,21</t>
+          <t>15,20</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>1.384,933</t>
+          <t>1.384,029</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -5804,22 +5804,22 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>30,26667100</t>
+          <t>30,28108400</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>5,23</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>164,115</t>
+          <t>164,182</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2,80266800</t>
+          <t>2,80398700</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>5,11</t>
+          <t>5,15</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5.931,048</t>
+          <t>5.995,222</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -6048,22 +6048,22 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>3,59620500</t>
+          <t>3,59813100</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>5,58</t>
+          <t>5,64</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>2.177,093</t>
+          <t>2.176,319</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -6170,22 +6170,22 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1,28758500</t>
+          <t>1,28826500</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>5,80</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>63,603</t>
+          <t>63,615</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -6292,22 +6292,22 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>9,66130400</t>
+          <t>9,66651500</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>5,62</t>
+          <t>5,68</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>829,554</t>
+          <t>829,603</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>4,44626300</t>
+          <t>4,44858800</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -6424,22 +6424,22 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>5,68</t>
+          <t>5,74</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>14,54</t>
+          <t>14,53</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15.719,208</t>
+          <t>15.788,429</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -6536,32 +6536,32 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>4,76243200</t>
+          <t>4,76505800</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>5,81</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>14,77</t>
+          <t>14,78</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>9.407,817</t>
+          <t>9.377,531</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -6658,22 +6658,22 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>5,08904100</t>
+          <t>5,09190100</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,056</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>5,83</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>20.995,057</t>
+          <t>21.000,259</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6780,22 +6780,22 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>3,17856400</t>
+          <t>3,18033600</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>5,82</t>
+          <t>5,87</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>13.360,586</t>
+          <t>13.405,911</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1.725,94238600</t>
+          <t>1.726,82669700</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>5,59</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>249,675</t>
+          <t>246,935</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6940,19 +6940,71 @@
           <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-automatico-polis-rf-cp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr"/>
-      <c r="O54" s="2" t="inlineStr"/>
-      <c r="P54" s="2" t="inlineStr"/>
-      <c r="Q54" s="2" t="inlineStr"/>
-      <c r="R54" s="2" t="inlineStr"/>
-      <c r="S54" s="2" t="inlineStr"/>
-      <c r="T54" s="2" t="inlineStr"/>
-      <c r="U54" s="2" t="inlineStr"/>
-      <c r="V54" s="2" t="inlineStr"/>
-      <c r="W54" s="2" t="inlineStr"/>
-      <c r="X54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>39.594.941/0001-36</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>6520</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6520.pdf</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6520.pdf</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6520.pdf</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6520.pdf</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6520.pdf</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6520.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -6972,32 +7024,32 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1,41149900</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>0,000</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>5,42</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>14,37</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>67,716</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -7094,32 +7146,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1.196,25317100</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>-0,002</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>-4,66</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>-0,69</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>36,514</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -7216,32 +7268,32 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>12,58599900</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>0,324</t>
+          <t>12,48257200</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>-0,821</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>6,02</t>
+          <t>5,15</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>17,44</t>
+          <t>16,30</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>540,035</t>
+          <t>323,807</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -7286,32 +7338,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1.633,50512400</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>-0,006</t>
-        </is>
-      </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>-0,22</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>4,24</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>12,72</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>114,271</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -7408,32 +7460,32 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>2.440,85621200</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>0,156</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>0,75</t>
+          <t>2.411,20749100</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>-1,214</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>-0,47</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>18,83</t>
+          <t>17,38</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>38,51</t>
+          <t>35,65</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>12,996</t>
+          <t>12,948</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -7648,32 +7700,32 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1,25086900</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>-0,004</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>2,41</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>10,10</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>6,310</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -7770,32 +7822,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1,13638900</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>0,350</t>
+          <t>1,11854700</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>-1,570</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>-1,72</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>-1,99</t>
+          <t>-3,52</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>14,31</t>
+          <t>10,84</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>3,442</t>
+          <t>3,388</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -8010,32 +8062,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1,41814900</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>-0,004</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>3,88</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>17,33</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>11,783</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -8250,32 +8302,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1,10109800</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>-0,070</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>-0,84</t>
+          <t>1,11229200</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>1,016</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>-8,67</t>
+          <t>-7,74</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>-8,68</t>
+          <t>-6,48</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>3,656</t>
+          <t>3,694</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -8372,32 +8424,32 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>5,32643598</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>-0,003</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>3,80</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>12,49</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>32,804</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -8494,32 +8546,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>4,69197800</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>0,350</t>
+          <t>4,63986700</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>-1,110</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-2,56</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>5,59</t>
+          <t>4,42</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>40,23</t>
+          <t>39,43</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>618,007</t>
+          <t>611,398</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8616,32 +8668,32 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>2,85980600</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>-0,002</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>2,38</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>10,47</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>74,437</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -8738,32 +8790,32 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1.665,12304600</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>-0,147</t>
+          <t>1.675,38826300</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>0,616</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>5,69</t>
+          <t>6,34</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>11,74</t>
+          <t>12,59</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>28,931</t>
+          <t>29,119</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8860,32 +8912,32 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>3,84654700</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>0,188</t>
-        </is>
-      </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>0,46</t>
+          <t>3,82142400</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>-0,653</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>14,34</t>
+          <t>13,60</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>39,85</t>
+          <t>38,00</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>2.401,931</t>
+          <t>2.387,381</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -8982,32 +9034,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1,90552100</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>0,025</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>0,04</t>
+          <t>1,90367300</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>-0,096</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>4,82</t>
+          <t>4,72</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>12,98</t>
+          <t>12,82</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>22,028</t>
+          <t>22,026</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -9104,32 +9156,32 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1.654,73884500</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>-0,003</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>4,63</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>13,69</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>14,560</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -9222,32 +9274,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>0,50984150</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>-0,004</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>-3,23</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr">
-        <is>
-          <t>-29,39</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>4,020</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -9344,32 +9396,32 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>3,27841500</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>-0,005</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>2,89</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>9,92</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>156,146</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -9466,32 +9518,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1,54521700</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>-0,004</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>-0,25</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t>3,48</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>20,78</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>14,557</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -9588,32 +9640,32 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1,37302500</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>-0,003</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>7,66</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>70,360</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -9710,32 +9762,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1,48780300</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>-0,003</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t>2,88</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>15,03</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>192,909</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9745,7 +9797,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fim-cap-protegido-ciclico-ii</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fic-capital-protegido-ciclico-ii-multimercado-lp/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -9832,32 +9884,32 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1,78163400</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>-0,001</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>0,85</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>10,33</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>175,744</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -9954,32 +10006,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>5,61720700</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>0,170</t>
-        </is>
-      </c>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>0,06</t>
+          <t>5,59416800</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>-0,410</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>-0,34</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>5,42</t>
+          <t>4,99</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>14,58</t>
+          <t>14,03</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>898,704</t>
+          <t>895,059</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -10076,32 +10128,32 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>3,65143000</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>0,027</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>0,04</t>
+          <t>3,64794000</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>-0,095</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>4,98</t>
+          <t>4,88</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>13,39</t>
+          <t>13,23</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>744,987</t>
+          <t>744,192</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -10198,32 +10250,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>6,83389900</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>-0,002</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="inlineStr">
-        <is>
-          <t>6,25</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>16,79</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>128,964</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -10320,32 +10372,32 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>1,42545000</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>-0,003</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>3,46</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>16,03</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>281,360</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -10442,32 +10494,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,32904600</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>-0,001</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>0,45</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>3,54</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>3,06</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>13,225</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -10564,32 +10616,32 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>3,73746600</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>-0,056</t>
-        </is>
-      </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>-0,54</t>
+          <t>3,78644400</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>1,310</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>0,75</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>-7,02</t>
+          <t>-5,80</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>-7,64</t>
+          <t>-5,70</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>96,220</t>
+          <t>97,502</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -10686,32 +10738,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>6,64489300</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>0,949</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="inlineStr">
-        <is>
-          <t>0,20</t>
+          <t>6,55035400</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>-1,422</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>-1,22</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>4,77</t>
+          <t>3,27</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>21,02</t>
+          <t>18,63</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>341,242</t>
+          <t>336,419</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10808,32 +10860,32 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>2,59187100</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>1,184</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>0,26</t>
+          <t>2,53501200</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>-2,193</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>-1,93</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>7,72</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>26,29</t>
+          <t>22,81</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>13,409</t>
+          <t>13,158</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -10930,32 +10982,32 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1.919,36570900</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>0,634</t>
+          <t>1.864,02397700</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>-2,883</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-3,41</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>-3,31</t>
+          <t>-6,10</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>13,63</t>
+          <t>8,94</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>10,212</t>
+          <t>9,919</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -11048,32 +11100,32 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>10,25862300</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>0,000</t>
+          <t>10,28348100</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>0,242</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>3,60</t>
+          <t>3,85</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>22,13</t>
+          <t>22,96</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>284,555</t>
+          <t>285,322</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -11170,32 +11222,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1,47442800</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>0,981</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t>0,19</t>
+          <t>1,42497300</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>-3,354</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>-3,16</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>-3,28</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>1,90</t>
+          <t>-6,52</t>
+        </is>
+      </c>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>-3,43</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>447,321</t>
+          <t>432,318</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -11292,32 +11344,32 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1,10748000</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>0,892</t>
+          <t>1,07150400</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>-3,248</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>-3,31</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>-4,85</t>
+          <t>-7,94</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>-2,76</t>
+          <t>-6,27</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>56,962</t>
+          <t>55,112</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -11414,32 +11466,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1,71064800</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>1,194</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
-        <is>
-          <t>0,35</t>
+          <t>1,67818900</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>-1,897</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>-1,78</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>-1,54</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>9,85</t>
+          <t>6,27</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2,127</t>
+          <t>2,087</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -11536,32 +11588,32 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>4,55350900</t>
+          <t>4,50346300</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>-0,359</t>
-        </is>
-      </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>0,92</t>
+          <t>-1,099</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>44,59</t>
+          <t>43,00</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>52,24</t>
+          <t>49,64</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>77,152</t>
+          <t>76,304</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -11658,32 +11710,32 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>8,68489900</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>1,180</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="inlineStr">
-        <is>
-          <t>0,25</t>
+          <t>8,49389300</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>-2,199</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>-1,95</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>7,26</t>
+          <t>4,90</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>24,95</t>
+          <t>21,50</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>90,627</t>
+          <t>88,678</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -11780,32 +11832,32 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1,25943900</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>-0,006</t>
-        </is>
-      </c>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>-0,88</t>
-        </is>
-      </c>
-      <c r="G95" s="6" t="inlineStr">
-        <is>
-          <t>-2,14</t>
-        </is>
-      </c>
-      <c r="H95" s="5" t="inlineStr">
-        <is>
-          <t>7,04</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>284,852</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -11902,32 +11954,32 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>1,86586600</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>0,665</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>0,22</t>
+          <t>1,77104400</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>-5,081</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>-4,86</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>-1,86</t>
+          <t>-6,85</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>17,16</t>
+          <t>9,56</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>114,427</t>
+          <t>108,615</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -12024,32 +12076,32 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>2,90836800</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>0,847</t>
-        </is>
-      </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>0,53</t>
+          <t>2,87409900</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>-1,178</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>-0,65</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>6,70</t>
+          <t>5,45</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>18,54</t>
+          <t>16,04</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>127,392</t>
+          <t>125,891</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -12146,32 +12198,32 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1,86521700</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>0,629</t>
+          <t>1,81137600</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>-2,886</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-3,42</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>-3,73</t>
+          <t>-6,51</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>12,37</t>
+          <t>7,72</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>49,068</t>
+          <t>47,652</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -12268,32 +12320,32 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>6,45994100</t>
+          <t>6,41147000</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>-0,232</t>
-        </is>
-      </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>0,63</t>
+          <t>-0,750</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>-0,12</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>37,72</t>
+          <t>36,69</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>47,37</t>
+          <t>46,22</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>119,782</t>
+          <t>119,009</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -12390,32 +12442,32 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>1.256,03835100</t>
+          <t>1.233,48628600</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>-0,247</t>
+          <t>-1,795</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>-1,33</t>
+          <t>-3,10</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>-8,11</t>
+          <t>-9,76</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>-12,05</t>
+          <t>-14,08</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>40,388</t>
+          <t>39,772</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -12512,32 +12564,32 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>40,22550200</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>4,021</t>
-        </is>
-      </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>2,60</t>
+          <t>38,70513600</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>-3,779</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>-1,26</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>16,43</t>
+          <t>12,03</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>70,94</t>
+          <t>64,59</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>687,520</t>
+          <t>661,852</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -12634,32 +12686,32 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2,69175500</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>1,771</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>0,28</t>
+          <t>2,64485300</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>-1,742</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>-1,46</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>9,18</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>30,49</t>
+          <t>29,53</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>447,176</t>
+          <t>439,560</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -12756,32 +12808,32 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>4,79261700</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>0,856</t>
+          <t>4,66828400</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>-2,594</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-2,94</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>6,79</t>
+          <t>4,02</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>26,25</t>
+          <t>22,28</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>23,178</t>
+          <t>22,577</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -12878,32 +12930,32 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>1.492,99282500</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>0,622</t>
+          <t>1.451,78743500</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>-2,759</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>-0,72</t>
-        </is>
-      </c>
-      <c r="G104" s="3" t="inlineStr">
-        <is>
-          <t>2,59</t>
+          <t>-3,46</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>15,85</t>
+          <t>11,39</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>29,620</t>
+          <t>28,805</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -13000,32 +13052,32 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>1,94557900</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>1,421</t>
-        </is>
-      </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>0,46</t>
+          <t>1,90090600</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>-2,296</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>-1,84</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>-4,36</t>
+          <t>-6,56</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>9,05</t>
+          <t>5,37</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>1,769</t>
+          <t>1,729</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -13122,32 +13174,32 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>5,86053900</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>0,996</t>
+          <t>5,73246700</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>-2,185</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>-2,26</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>8,94</t>
+          <t>6,56</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>28,23</t>
+          <t>24,85</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>43,147</t>
+          <t>42,205</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -13244,32 +13296,32 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>2,21009600</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>1,097</t>
+          <t>2,16646300</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>-1,974</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>-0,10</t>
+          <t>-2,07</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>5,33</t>
+          <t>3,25</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>24,15</t>
+          <t>21,02</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>35,485</t>
+          <t>34,785</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -13366,32 +13418,32 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>42,23178900</t>
+          <t>41,76826900</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>-0,360</t>
-        </is>
-      </c>
-      <c r="F108" s="3" t="inlineStr">
-        <is>
-          <t>0,92</t>
+          <t>-1,097</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>44,65</t>
+          <t>43,06</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>52,36</t>
+          <t>49,76</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>840,878</t>
+          <t>831,680</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -13488,32 +13540,32 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>0,85762000</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>0,646</t>
+          <t>0,84186100</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>-1,837</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-2,05</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>-10,90</t>
+          <t>-12,54</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>-18,54</t>
+          <t>-21,50</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>2,904</t>
+          <t>2,858</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -13610,32 +13662,32 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>1,18776400</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>0,536</t>
+          <t>1,17753300</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>-0,861</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>-0,60</t>
+          <t>-1,45</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>-1,84</t>
+          <t>-2,69</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>11,54</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>3,820</t>
+          <t>3,787</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -13732,32 +13784,32 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>1,32977400</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>1,770</t>
-        </is>
-      </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>0,27</t>
+          <t>1,30660100</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>-1,742</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>-1,46</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>11,05</t>
+          <t>9,11</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>30,30</t>
+          <t>29,34</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>19,753</t>
+          <t>19,409</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -13854,32 +13906,32 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1,77396600</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>2,357</t>
+          <t>1,71993600</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>-3,045</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>-0,10</t>
+          <t>-3,15</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>3,19</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>68,41</t>
+          <t>62,70</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>270,719</t>
+          <t>262,525</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -13976,32 +14028,32 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>990,42623200</t>
-        </is>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
-        <is>
-          <t>-0,002</t>
-        </is>
-      </c>
-      <c r="F113" s="6" t="inlineStr">
-        <is>
-          <t>-0,90</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
-      <c r="H113" s="5" t="inlineStr">
-        <is>
-          <t>15,93</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>8,063</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -14098,32 +14150,32 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1.484,18511100</t>
-        </is>
-      </c>
-      <c r="E114" s="7" t="inlineStr">
-        <is>
-          <t>-0,002</t>
-        </is>
-      </c>
-      <c r="F114" s="7" t="inlineStr">
-        <is>
-          <t>-0,74</t>
-        </is>
-      </c>
-      <c r="G114" s="7" t="inlineStr">
-        <is>
-          <t>-0,77</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>10,45</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>21,570</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -14220,32 +14272,32 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>170,02273889</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>1,172</t>
-        </is>
-      </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>0,27</t>
+          <t>166,32637200</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>-2,174</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>-1,90</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>7,89</t>
+          <t>5,55</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>26,83</t>
+          <t>23,36</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>42,507</t>
+          <t>41,583</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -14342,32 +14394,32 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1,81286500</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>2,342</t>
+          <t>1,75759700</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>-3,048</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-3,17</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>3,25</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>68,71</t>
+          <t>62,98</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>4,960</t>
+          <t>4,808</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -14464,32 +14516,32 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1,76771500</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>2,360</t>
+          <t>1,71341400</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>-3,071</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-3,20</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>3,26</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>68,75</t>
+          <t>62,98</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>1.611,857</t>
+          <t>1.562,344</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -14586,32 +14638,32 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>46,98292600</t>
+          <t>46,46741400</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>-0,357</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>0,92</t>
+          <t>-1,097</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>-0,17</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>45,06</t>
+          <t>43,47</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>53,25</t>
+          <t>50,63</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>679,192</t>
+          <t>671,740</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -14708,32 +14760,32 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>44,56564800</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>4,018</t>
-        </is>
-      </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>2,60</t>
+          <t>42,88446700</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>-3,772</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>-1,26</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>16,67</t>
+          <t>12,27</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>71,86</t>
+          <t>65,48</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>804,744</t>
+          <t>774,386</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -14830,32 +14882,32 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>16,41460000</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>0,857</t>
+          <t>15,96297600</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>-2,751</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-2,96</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>-2,67</t>
+          <t>-5,35</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>15,03</t>
+          <t>10,17</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>113,257</t>
+          <t>110,141</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -14952,32 +15004,32 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>37,36477700</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>4,013</t>
-        </is>
-      </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>2,60</t>
+          <t>35,95643500</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>-3,769</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>-1,26</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>16,44</t>
+          <t>12,05</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>70,64</t>
+          <t>64,32</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>12,212</t>
+          <t>11,752</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
@@ -15074,32 +15126,32 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>41,51048100</t>
+          <t>41,05430400</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>-0,359</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="inlineStr">
-        <is>
-          <t>0,92</t>
+          <t>-1,098</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>44,78</t>
+          <t>43,19</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>52,54</t>
+          <t>49,93</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>586,678</t>
+          <t>580,231</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -15196,32 +15248,32 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>38,37295500</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>4,021</t>
-        </is>
-      </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>2,61</t>
+          <t>36,92389700</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>-3,776</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>-1,26</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>16,45</t>
+          <t>12,05</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>70,97</t>
+          <t>64,62</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>482,819</t>
+          <t>464,587</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -15318,32 +15370,32 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>44,13882900</t>
+          <t>43,65459200</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>-0,359</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr">
-        <is>
-          <t>0,92</t>
+          <t>-1,097</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>44,94</t>
+          <t>43,35</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>52,89</t>
+          <t>50,28</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>675,374</t>
+          <t>667,964</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -15440,7 +15492,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>1,12391400</t>
+          <t>1,12444300</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -15450,12 +15502,12 @@
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>5,09</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -15465,7 +15517,7 @@
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>57,072</t>
+          <t>57,576</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
@@ -15562,7 +15614,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>1,35638400</t>
+          <t>1,35702400</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -15572,12 +15624,12 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>5,09</t>
+          <t>5,14</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
@@ -15587,7 +15639,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>213,639</t>
+          <t>213,740</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -15684,22 +15736,22 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>5,88162700</t>
+          <t>5,88442700</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>5,49</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -15709,7 +15761,7 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>40,998</t>
+          <t>41,073</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -15806,7 +15858,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>5,11957800</t>
+          <t>5,12224100</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -15816,12 +15868,12 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>5,68</t>
+          <t>5,74</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
@@ -15831,7 +15883,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>785,564</t>
+          <t>785,972</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -15928,7 +15980,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>3,21619600</t>
+          <t>3,21784200</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -15938,12 +15990,12 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -15953,7 +16005,7 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>18,402</t>
+          <t>18,315</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -16050,32 +16102,32 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>23,73163100</t>
+          <t>23,65876400</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>-0,044</t>
+          <t>-0,307</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>5,99</t>
+          <t>5,67</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>11,94</t>
+          <t>11,60</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>94,268</t>
+          <t>93,979</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -16172,7 +16224,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>3,27082900</t>
+          <t>3,27251000</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -16182,12 +16234,12 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>5,57</t>
+          <t>5,63</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -16197,7 +16249,7 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>7.675,903</t>
+          <t>7.923,929</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -16294,22 +16346,22 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>1.884,69121900</t>
+          <t>1.885,73937300</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>5,93</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
@@ -16319,7 +16371,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>15.960,962</t>
+          <t>15.974,883</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -16416,32 +16468,32 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>4,87614100</t>
+          <t>4,87788700</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,035</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>5,79</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>14,75</t>
+          <t>14,73</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>3.025,731</t>
+          <t>3.048,420</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -16538,7 +16590,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1,54818489</t>
+          <t>1,54900400</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -16548,22 +16600,22 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>5,81</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>14,76</t>
+          <t>14,75</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>359,475</t>
+          <t>353,765</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -16660,22 +16712,22 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>5,12126900</t>
+          <t>5,12397800</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>5,78</t>
+          <t>5,84</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -16685,7 +16737,7 @@
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>284,682</t>
+          <t>284,833</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -16782,32 +16834,32 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>8,70507200</t>
+          <t>8,70799000</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,033</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>5,70</t>
+          <t>5,74</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>14,72</t>
+          <t>14,69</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>4.012,398</t>
+          <t>4.012,747</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -16904,32 +16956,32 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>17,90550600</t>
+          <t>17,91205200</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,036</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>5,76</t>
+          <t>5,80</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>14,80</t>
+          <t>14,78</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>4.766,065</t>
+          <t>4.765,462</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -17022,22 +17074,22 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>2,82347200</t>
+          <t>2,82482300</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>5,24</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
@@ -17047,7 +17099,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>13.427,885</t>
+          <t>13.707,443</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -17144,7 +17196,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>4,42605900</t>
+          <t>4,42841400</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17154,12 +17206,12 @@
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>5,80</t>
+          <t>5,86</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -17169,7 +17221,7 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>12.579,543</t>
+          <t>12.815,048</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -17266,22 +17318,22 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>1,37332700</t>
+          <t>1,37406400</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>5,86</t>
+          <t>5,92</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
@@ -17291,7 +17343,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.493,160</t>
+          <t>3.499,499</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -17388,22 +17440,22 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>1.771,43946400</t>
+          <t>1.772,37476800</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>5,71</t>
+          <t>5,76</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -17413,7 +17465,7 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>1.441,985</t>
+          <t>1.438,501</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -17510,7 +17562,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>1,30740000</t>
+          <t>1,30796400</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -17520,12 +17572,12 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>4,66</t>
+          <t>4,71</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
@@ -17535,7 +17587,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>31.541,267</t>
+          <t>31.577,913</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -17632,7 +17684,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>9,39899600</t>
+          <t>9,40334800</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17642,12 +17694,12 @@
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>5,00</t>
+          <t>5,05</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
@@ -17657,7 +17709,7 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>2.798,376</t>
+          <t>2.799,657</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
@@ -17754,7 +17806,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>2,47525000</t>
+          <t>2,47640300</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -17764,12 +17816,12 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>5,00</t>
+          <t>5,05</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
@@ -17779,7 +17831,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>16.582,682</t>
+          <t>16.589,724</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -17876,32 +17928,32 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>2,60506900</t>
+          <t>2,60624400</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>5,82</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>14,81</t>
+          <t>14,80</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>9.199,948</t>
+          <t>9.194,046</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
@@ -17998,32 +18050,32 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>2,40223700</t>
+          <t>2,39143500</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr">
         <is>
-          <t>-0,053</t>
+          <t>-0,449</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,62</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>4,30</t>
+          <t>3,83</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>12,63</t>
+          <t>12,08</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>3.628,550</t>
+          <t>3.612,831</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -18120,32 +18172,32 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>2,98223000</t>
+          <t>2,97118900</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>-0,060</t>
+          <t>-0,370</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-0,50</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>11,87</t>
+          <t>11,44</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>40,291</t>
+          <t>40,142</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
@@ -18242,32 +18294,32 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1.641,35750000</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="inlineStr">
-        <is>
-          <t>0,014</t>
+          <t>1.638,49077200</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>-0,174</t>
         </is>
       </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>-0,19</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>4,58</t>
+          <t>4,40</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>11,77</t>
+          <t>11,56</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>460,427</t>
+          <t>459,623</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -18364,32 +18416,32 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>4,47381700</t>
+          <t>4,47413400</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,007</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>5,44</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>14,22</t>
+          <t>14,17</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>10.749,539</t>
+          <t>10.780,280</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
@@ -18486,32 +18538,32 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>3,81875800</t>
+          <t>3,80724100</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr">
         <is>
-          <t>-0,017</t>
+          <t>-0,301</t>
         </is>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>-0,31</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>6,08</t>
+          <t>5,76</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>12,35</t>
+          <t>12,05</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2.992,804</t>
+          <t>2.983,699</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -18608,32 +18660,32 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>3,62768300</t>
+          <t>3,60511000</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>-0,120</t>
+          <t>-0,622</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-0,88</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>3,27</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>12,82</t>
+          <t>12,00</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>1.740,406</t>
+          <t>1.729,322</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
@@ -18730,32 +18782,32 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>5,14357700</t>
+          <t>5,10998100</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr">
         <is>
-          <t>-0,201</t>
+          <t>-0,653</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-1,09</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>4,60</t>
+          <t>3,92</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>10,28</t>
+          <t>9,55</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2.576,120</t>
+          <t>2.559,434</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -18852,32 +18904,32 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>5,17742400</t>
+          <t>5,16184100</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>-0,045</t>
+          <t>-0,300</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>-0,38</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>6,05</t>
+          <t>5,73</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>12,11</t>
+          <t>11,77</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>5.558,662</t>
+          <t>5.542,757</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
@@ -18974,32 +19026,32 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>4,74288700</t>
+          <t>4,73005800</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
         <is>
-          <t>-0,048</t>
+          <t>-0,270</t>
         </is>
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>-0,38</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>5,07</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>13,24</t>
+          <t>12,87</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>512,580</t>
+          <t>511,793</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -19096,32 +19148,32 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>7,94254100</t>
+          <t>7,94513400</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,032</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>5,70</t>
+          <t>5,74</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>14,60</t>
+          <t>14,57</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>172,551</t>
+          <t>172,170</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
@@ -19166,32 +19218,32 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>3,45170400</t>
+          <t>3,41896700</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr">
         <is>
-          <t>-0,327</t>
+          <t>-0,948</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>-0,72</t>
+          <t>-1,66</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>3,45</t>
+          <t>2,47</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>8,86</t>
+          <t>7,80</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>771,110</t>
+          <t>763,797</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -19288,32 +19340,32 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>3,75904800</t>
+          <t>3,72634800</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>-0,191</t>
+          <t>-0,869</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-1,25</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>2,47</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>12,29</t>
+          <t>11,16</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>717,863</t>
+          <t>711,974</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
@@ -19410,32 +19462,32 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>7,16858700</t>
+          <t>7,17137200</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,038</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>5,73</t>
+          <t>5,77</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>14,67</t>
+          <t>14,66</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>12.733,156</t>
+          <t>12.622,037</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -19532,7 +19584,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>7,48669100</t>
+          <t>7,49062000</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -19542,22 +19594,22 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>5,67</t>
+          <t>5,73</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>14,55</t>
+          <t>14,54</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>4.476,403</t>
+          <t>4.064,727</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -19654,32 +19706,32 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>1,44353600</t>
+          <t>1,43565300</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr">
         <is>
-          <t>-0,036</t>
+          <t>-0,546</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,78</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>2,96</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>12,25</t>
+          <t>11,59</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>171,950</t>
+          <t>171,627</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
@@ -19776,7 +19828,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>3,13714100</t>
+          <t>3,13871400</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -19786,12 +19838,12 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>5,43</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
@@ -19801,7 +19853,7 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>1.428,025</t>
+          <t>1.430,215</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
@@ -19898,22 +19950,22 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>6,71418300</t>
+          <t>6,71791200</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>5,79</t>
+          <t>5,85</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
@@ -19923,7 +19975,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>23.574,588</t>
+          <t>23.629,247</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -19968,32 +20020,32 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>5,51026900</t>
+          <t>5,47126100</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>-0,207</t>
+          <t>-0,707</t>
         </is>
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>-0,47</t>
+          <t>-1,17</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>4,83</t>
+          <t>4,09</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>10,57</t>
+          <t>9,77</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>593,660</t>
+          <t>589,457</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
@@ -20212,32 +20264,32 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>3,90820000</t>
-        </is>
-      </c>
-      <c r="E165" s="5" t="inlineStr">
-        <is>
-          <t>1,191</t>
-        </is>
-      </c>
-      <c r="F165" s="5" t="inlineStr">
-        <is>
-          <t>0,26</t>
+          <t>3,82213800</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>-2,202</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>-1,94</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>7,94</t>
+          <t>5,56</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>26,91</t>
+          <t>23,40</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>294,955</t>
+          <t>288,548</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
@@ -20334,32 +20386,32 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>3,59305400</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>1,208</t>
-        </is>
-      </c>
-      <c r="F166" s="3" t="inlineStr">
-        <is>
-          <t>0,29</t>
+          <t>3,51574500</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>-2,151</t>
+        </is>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>-1,86</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>7,76</t>
+          <t>5,44</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>26,44</t>
+          <t>22,98</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>9,092</t>
+          <t>8,896</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -20456,32 +20508,32 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>11,50043671</t>
+          <t>11,52868200</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>0,003</t>
+          <t>0,245</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>4,17</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
         <is>
-          <t>23,14</t>
+          <t>23,98</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>2.375,666</t>
+          <t>2.380,064</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
@@ -20578,32 +20630,32 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>2,00676300</t>
-        </is>
-      </c>
-      <c r="E168" s="3" t="inlineStr">
-        <is>
-          <t>1,127</t>
-        </is>
-      </c>
-      <c r="F168" s="3" t="inlineStr">
-        <is>
-          <t>0,14</t>
+          <t>1,96188500</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>-2,236</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>-2,09</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>3,50</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>23,41</t>
+          <t>20,03</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>198,094</t>
+          <t>193,664</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -20700,32 +20752,32 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>1,99604400</t>
-        </is>
-      </c>
-      <c r="E169" s="5" t="inlineStr">
-        <is>
-          <t>0,630</t>
+          <t>1,93838100</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>-2,888</t>
         </is>
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-3,42</t>
         </is>
       </c>
       <c r="G169" s="6" t="inlineStr">
         <is>
-          <t>-3,72</t>
+          <t>-6,50</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
         <is>
-          <t>12,69</t>
+          <t>7,83</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>754,066</t>
+          <t>732,282</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
@@ -20822,32 +20874,32 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>3,41555950</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="inlineStr">
-        <is>
-          <t>0,930</t>
-        </is>
-      </c>
-      <c r="F170" s="3" t="inlineStr">
-        <is>
-          <t>0,05</t>
+          <t>3,35139200</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>-1,878</t>
+        </is>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>-1,82</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>4,98</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>20,12</t>
+          <t>17,26</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>1.309,789</t>
+          <t>1.285,182</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -20940,32 +20992,32 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>2,48918181</t>
-        </is>
-      </c>
-      <c r="E171" s="5" t="inlineStr">
-        <is>
-          <t>1,047</t>
-        </is>
-      </c>
-      <c r="F171" s="4" t="inlineStr">
-        <is>
-          <t>0,00</t>
+          <t>2,43292500</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>-2,260</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>-2,25</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>5,31</t>
+          <t>2,93</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>21,89</t>
+          <t>18,51</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>770,453</t>
+          <t>744,714</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
@@ -21058,12 +21110,12 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>3,74332300</t>
-        </is>
-      </c>
-      <c r="E172" s="3" t="inlineStr">
-        <is>
-          <t>0,054</t>
+          <t>3,74314200</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>-0,004</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -21073,17 +21125,17 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>5,42</t>
+          <t>5,41</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>14,26</t>
+          <t>14,21</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>5.020,242</t>
+          <t>5.018,208</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,26023700</t>
+          <t>2,26128600</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>5,23</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>406,359</t>
+          <t>406,683</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,49326900</t>
+          <t>5,49578100</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>5,13</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.550,554</t>
+          <t>6.567,089</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,77364400</t>
+          <t>2,77491200</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -836,12 +836,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>861,483</t>
+          <t>899,726</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -948,22 +948,22 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>3,32873200</t>
+          <t>3,33047700</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0,062</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>5,64</t>
+          <t>5,69</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>11,590</t>
+          <t>11,622</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -1070,22 +1070,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,48280400</t>
+          <t>3,48461200</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,067</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>5,80</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>119,682</t>
+          <t>119,608</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1192,22 +1192,22 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1.834,08173800</t>
+          <t>1.835,13540300</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,094</t>
+          <t>0,057</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,30</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>5,84</t>
+          <t>5,90</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>96,512</t>
+          <t>96,551</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1314,32 +1314,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,69299300</t>
+          <t>9,69755500</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>5,37</t>
+          <t>5,42</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>13,30</t>
+          <t>13,29</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>582,397</t>
+          <t>582,313</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1436,32 +1436,32 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3,35194600</t>
+          <t>3,35362700</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>5,71</t>
+          <t>5,77</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>14,18</t>
+          <t>14,17</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>61,997</t>
+          <t>62,542</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1558,22 +1558,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,99321700</t>
+          <t>2,99484700</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0,061</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>5,91</t>
+          <t>5,97</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1.659,071</t>
+          <t>1.660,295</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1676,32 +1676,32 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>19,54575700</t>
+          <t>19,53911900</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>-0,238</t>
+          <t>-0,033</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>-1,69</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>1,94</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>9,89</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>119,589</t>
+          <t>119,107</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1798,17 +1798,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,36299500</t>
+          <t>13,36241400</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>-0,161</t>
+          <t>-0,004</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>-0,97</t>
+          <t>-0,98</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>9,08</t>
+          <t>9,01</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,764</t>
+          <t>27,565</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1920,32 +1920,32 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>46,09954600</t>
+          <t>46,12118000</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>5,35</t>
+          <t>5,40</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>13,27</t>
+          <t>13,26</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>40,471</t>
+          <t>40,490</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -2042,22 +2042,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20,19215800</t>
+          <t>20,20171900</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>5,32</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,508</t>
+          <t>64,524</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>3,11779300</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>-0,130</t>
+          <t>3,11790900</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>0,003</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>10,45</t>
+          <t>10,37</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>78,197</t>
+          <t>78,010</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -2286,32 +2286,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14,93446000</t>
+          <t>14,94151800</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>5,44</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>13,36</t>
+          <t>13,35</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,730</t>
+          <t>27,743</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2408,32 +2408,32 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2,99605300</t>
+          <t>2,99742500</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>5,23</t>
+          <t>5,28</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>13,03</t>
+          <t>13,02</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>1,624</t>
+          <t>1,625</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -2530,32 +2530,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,26399700</t>
+          <t>3,26318500</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>-0,207</t>
+          <t>-0,024</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-1,55</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>10,76</t>
+          <t>10,53</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>134,952</t>
+          <t>134,585</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2652,32 +2652,32 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,03619900</t>
+          <t>3,03785700</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0,062</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>5,92</t>
+          <t>5,98</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>14,71</t>
+          <t>14,72</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1.759,840</t>
+          <t>1.756,024</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2774,22 +2774,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32,74540900</t>
+          <t>32,76132700</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>5,59</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2.193,650</t>
+          <t>2.194,059</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,30112800</t>
+          <t>3,30273500</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>5,55</t>
+          <t>5,60</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>13,77</t>
+          <t>13,76</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>13,095</t>
+          <t>13,051</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -3018,32 +3018,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3,26800400</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>-0,333</t>
+          <t>3,27073700</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>0,083</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>-2,40</t>
+          <t>-2,32</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2,54</t>
+          <t>2,62</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>7,59</t>
+          <t>7,73</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,639</t>
+          <t>64,669</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3140,32 +3140,32 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>19,01326400</t>
+          <t>19,02303300</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0,066</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>5,69</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>14,13</t>
+          <t>14,12</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>950,700</t>
+          <t>950,769</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,10141452</t>
+          <t>1,10139950</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>-0,208</t>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>203,581</t>
+          <t>203,526</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1,23872300</t>
+          <t>1,23944100</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -3394,22 +3394,22 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>0,20</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>5,76</t>
+          <t>5,82</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>14,54</t>
+          <t>14,55</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>72,425</t>
+          <t>72,418</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -3506,22 +3506,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1.830,31522500</t>
+          <t>1.831,37006100</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0,082</t>
+          <t>0,057</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>5,91</t>
+          <t>5,97</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>174,907</t>
+          <t>174,982</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3628,32 +3628,32 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1,19982800</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>-0,005</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>-0,01</t>
+          <t>1,20026200</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>0,036</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>0,02</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>6,76</t>
+          <t>6,79</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>13,34</t>
+          <t>13,28</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>39,863</t>
+          <t>39,877</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,03814800</t>
+          <t>1,03873800</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>0,20</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>5,93</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,925</t>
+          <t>21,933</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,16896300</t>
+          <t>1,16973100</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>5,26</t>
+          <t>5,33</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>66,431</t>
+          <t>66,473</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -3986,17 +3986,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,07233008</t>
+          <t>1,07231554</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>-0,009</t>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>315,552</t>
+          <t>305,018</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -4222,22 +4222,22 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>5,13463600</t>
+          <t>5,13750900</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,068</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>5,90</t>
+          <t>5,96</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>850,243</t>
+          <t>849,947</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -4344,22 +4344,22 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>4,94077400</t>
+          <t>4,94348400</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>0,064</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>5,91</t>
+          <t>5,97</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.244,447</t>
+          <t>3.249,257</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>29,22201300</t>
+          <t>29,23612200</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>5,37</t>
+          <t>5,42</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,078</t>
+          <t>21,087</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4588,32 +4588,32 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>30,58253000</t>
+          <t>30,59855100</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>0,067</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>5,80</t>
+          <t>5,86</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>14,42</t>
+          <t>14,41</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>3.098,764</t>
+          <t>3.100,623</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -4710,32 +4710,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1.765,80400500</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>-0,025</t>
+          <t>1.766,43092300</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>0,035</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>4,83</t>
+          <t>4,86</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>13,23</t>
+          <t>13,16</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>123,281</t>
+          <t>122,541</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4832,22 +4832,22 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>3,21959300</t>
+          <t>3,22131100</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>5,94</t>
+          <t>6,00</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>587,452</t>
+          <t>587,097</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -4954,32 +4954,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>6,18291200</t>
+          <t>6,18609600</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0,066</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>5,71</t>
+          <t>5,76</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>14,17</t>
+          <t>14,16</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>121,381</t>
+          <t>121,440</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -5076,22 +5076,22 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1,26818200</t>
+          <t>1,26889000</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>0,065</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>6,02</t>
+          <t>6,08</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>367,529</t>
+          <t>370,925</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -5198,32 +5198,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>10,58462900</t>
+          <t>10,59025100</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>0,068</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>5,89</t>
+          <t>5,94</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>14,63</t>
+          <t>14,62</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2.361,646</t>
+          <t>2.362,864</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -5320,32 +5320,32 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>5,51252700</t>
+          <t>5,51540900</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>0,066</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>5,99</t>
+          <t>6,04</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>14,82</t>
+          <t>14,81</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>550,982</t>
+          <t>549,973</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -5442,22 +5442,22 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3,56516000</t>
+          <t>3,56714500</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0,065</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>6,00</t>
+          <t>6,06</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15.472,329</t>
+          <t>15.491,843</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5564,22 +5564,22 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>5,29747900</t>
+          <t>5,30052400</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>0,063</t>
+          <t>0,057</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>6,03</t>
+          <t>6,09</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>1.387,842</t>
+          <t>1.388,517</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>30,30983100</t>
+          <t>30,32418600</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>5,33</t>
+          <t>5,38</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>164,388</t>
+          <t>164,294</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -5926,22 +5926,22 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2,80662300</t>
+          <t>2,80794300</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>5,30</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5.944,893</t>
+          <t>5.950,782</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -6048,22 +6048,22 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>3,60224300</t>
+          <t>3,60415000</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>0,062</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>5,76</t>
+          <t>5,81</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>2.183,147</t>
+          <t>2.188,709</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1,28962400</t>
+          <t>1,29030200</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -6180,22 +6180,22 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>5,92</t>
+          <t>5,97</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>14,63</t>
+          <t>14,62</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>64,166</t>
+          <t>64,450</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -6292,22 +6292,22 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>9,67763500</t>
+          <t>9,68279500</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>0,063</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>5,80</t>
+          <t>5,86</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>829,569</t>
+          <t>829,717</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>4,45322600</t>
+          <t>4,45554200</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -6424,12 +6424,12 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>5,85</t>
+          <t>5,90</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15.866,230</t>
+          <t>15.870,899</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -6536,22 +6536,22 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>4,77065400</t>
+          <t>4,77325500</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>0,064</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>5,93</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>9.524,361</t>
+          <t>9.514,813</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -6658,22 +6658,22 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>5,09778300</t>
+          <t>5,10052400</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>0,064</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>5,95</t>
+          <t>6,01</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>21.015,256</t>
+          <t>21.051,125</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6780,22 +6780,22 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>3,18410900</t>
+          <t>3,18586400</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>0,065</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>6,00</t>
+          <t>6,06</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>13.499,273</t>
+          <t>13.512,916</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1.728,59662900</t>
+          <t>1.729,48233200</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,30</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>5,70</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>247,834</t>
+          <t>247,118</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1,41453900</t>
+          <t>1,41542300</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -6982,22 +6982,22 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>5,65</t>
+          <t>5,71</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>14,38</t>
+          <t>14,37</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>67,727</t>
+          <t>67,770</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1.215,24680900</t>
+          <t>1.212,37869700</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
@@ -7104,22 +7104,22 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>-3,15</t>
+          <t>-3,37</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>1,42</t>
+          <t>1,37</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>37,050</t>
+          <t>36,964</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -7216,27 +7216,27 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>12,40492600</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>-0,174</t>
+          <t>12,42903800</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>0,194</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-1,26</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>4,50</t>
+          <t>4,70</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>15,78</t>
+          <t>16,04</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -7286,17 +7286,17 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1.615,34054700</t>
+          <t>1.615,24039600</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>-0,163</t>
+          <t>-0,006</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>-1,33</t>
+          <t>-1,34</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -7306,12 +7306,12 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>11,29</t>
+          <t>11,19</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>113,027</t>
+          <t>113,020</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -7408,32 +7408,32 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>2.366,39748300</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>-0,527</t>
+          <t>2.374,30019500</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>0,333</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>-2,32</t>
+          <t>-1,99</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>15,20</t>
+          <t>15,59</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>31,12</t>
+          <t>31,31</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>12,761</t>
+          <t>12,862</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1,24492100</t>
+          <t>1,24375100</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -7658,22 +7658,22 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,61</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>9,43</t>
+          <t>9,39</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>6,270</t>
+          <t>6,264</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -7770,32 +7770,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1,11457300</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>-0,648</t>
+          <t>1,12849200</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>1,248</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>-2,07</t>
+          <t>-0,84</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>-3,87</t>
+          <t>-2,67</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>12,91</t>
+          <t>14,55</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>3,578</t>
+          <t>3,618</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1,38783600</t>
+          <t>1,38415800</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
@@ -8020,22 +8020,22 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>-2,29</t>
+          <t>-2,54</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>14,62</t>
+          <t>14,54</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>11,506</t>
+          <t>11,477</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -8250,32 +8250,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1,12834700</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>0,685</t>
+          <t>1,12730500</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>-0,092</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>1,60</t>
+          <t>1,51</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>-6,41</t>
+          <t>-6,50</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>-4,13</t>
+          <t>-4,33</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>3,781</t>
+          <t>3,777</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -8372,12 +8372,12 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>5,27056264</t>
+          <t>5,27037612</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>-0,162</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>11,11</t>
+          <t>11,02</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>32,450</t>
+          <t>32,446</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -8494,32 +8494,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>4,53314400</t>
+          <t>4,45598700</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>-0,028</t>
+          <t>-1,702</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>-4,80</t>
+          <t>-6,42</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2,02</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>37,28</t>
+          <t>34,55</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>593,747</t>
+          <t>577,988</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>2,83506500</t>
+          <t>2,83109800</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -8626,22 +8626,22 @@
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>-0,98</t>
+          <t>-1,11</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>1,50</t>
+          <t>1,36</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>9,35</t>
+          <t>9,03</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>73,588</t>
+          <t>73,482</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -8738,32 +8738,32 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1.689,92261300</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>-0,009</t>
+          <t>1.691,88332700</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>0,116</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>1,69</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>7,26</t>
+          <t>7,39</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>13,61</t>
+          <t>13,66</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>29,604</t>
+          <t>29,649</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8860,32 +8860,32 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>3,74561000</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>0,227</t>
+          <t>3,73527700</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>-0,275</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>-2,16</t>
+          <t>-2,43</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>11,34</t>
+          <t>11,03</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>34,50</t>
+          <t>34,01</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>2.342,253</t>
+          <t>2.325,471</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -8982,32 +8982,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1,90110700</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>-0,033</t>
+          <t>1,90177400</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>0,035</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>-0,15</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>4,58</t>
+          <t>4,61</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>12,54</t>
+          <t>12,49</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>21,825</t>
+          <t>21,881</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -9104,12 +9104,12 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1.636,70062800</t>
+          <t>1.636,65023300</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>-0,159</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
@@ -9119,17 +9119,17 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>3,49</t>
+          <t>3,48</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>12,26</t>
+          <t>12,16</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>14,383</t>
+          <t>14,379</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>0,44223846</t>
+          <t>0,46633549</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>-16,06</t>
+          <t>-11,49</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>-38,75</t>
+          <t>-35,41</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>3,588</t>
+          <t>3,782</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -9344,17 +9344,17 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>3,28322800</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>1,004</t>
+          <t>3,28303700</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>-0,005</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>10,76</t>
+          <t>10,70</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>156,375</t>
+          <t>156,366</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1,52233700</t>
+          <t>1,52226700</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>-0,325</t>
+          <t>-0,004</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>19,26</t>
+          <t>19,18</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -9588,12 +9588,12 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1,37519600</t>
+          <t>1,37514300</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>-0,289</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -9603,17 +9603,17 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>1,40</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>7,48</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>70,472</t>
+          <t>70,469</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -9710,17 +9710,17 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1,48845900</t>
+          <t>1,48840200</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>-0,075</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>-0,90</t>
+          <t>-0,91</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -9730,12 +9730,12 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>14,78</t>
+          <t>14,65</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>192,994</t>
+          <t>192,987</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1,79039100</t>
+          <t>1,79239800</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -9842,22 +9842,22 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>10,83</t>
+          <t>10,67</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>176,111</t>
+          <t>176,126</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -9954,32 +9954,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>5,56905300</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>-0,071</t>
+          <t>5,57376900</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>0,084</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-0,70</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>4,52</t>
+          <t>4,60</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>13,34</t>
+          <t>13,37</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>890,798</t>
+          <t>891,302</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -10076,32 +10076,32 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>3,64312700</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>-0,031</t>
+          <t>3,64445700</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>0,036</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>4,74</t>
+          <t>4,78</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>12,95</t>
+          <t>12,90</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>745,740</t>
+          <t>745,840</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>6,77039000</t>
+          <t>6,73839100</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
@@ -10208,22 +10208,22 @@
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>-0,99</t>
+          <t>-1,46</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>4,77</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>15,77</t>
+          <t>15,01</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>127,873</t>
+          <t>127,269</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>1,42002400</t>
+          <t>1,41878100</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -10330,22 +10330,22 @@
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>-0,55</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>2,98</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>15,55</t>
+          <t>15,18</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>281,260</t>
+          <t>281,021</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,34550700</t>
+          <t>1,34492200</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -10452,22 +10452,22 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>1,69</t>
+          <t>1,65</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>4,83</t>
+          <t>4,78</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>4,14</t>
+          <t>4,36</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>13,130</t>
+          <t>13,124</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -10564,32 +10564,32 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>3,86482000</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>0,628</t>
+          <t>3,85575800</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>-0,234</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>2,84</t>
+          <t>2,60</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>-3,85</t>
+          <t>-4,08</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>-2,57</t>
+          <t>-2,71</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>98,321</t>
+          <t>98,017</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -10686,32 +10686,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>6,48872900</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>-0,281</t>
+          <t>6,55629500</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>1,041</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>-2,15</t>
+          <t>-1,13</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2,30</t>
+          <t>3,37</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>18,77</t>
+          <t>20,19</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>331,935</t>
+          <t>334,612</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10808,32 +10808,32 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>2,51041500</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>-0,208</t>
+          <t>2,52696400</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>0,659</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>-2,89</t>
+          <t>-2,25</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>4,33</t>
+          <t>5,02</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>22,88</t>
+          <t>24,05</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>12,951</t>
+          <t>13,019</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -10930,32 +10930,32 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1.848,30809400</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>-0,760</t>
+          <t>1.879,71006300</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>1,698</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>-4,22</t>
+          <t>-2,60</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>-6,89</t>
+          <t>-5,31</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>10,06</t>
+          <t>12,32</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>9,789</t>
+          <t>9,648</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -11048,32 +11048,32 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>10,21572900</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>1,069</t>
+          <t>10,12777100</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>-0,861</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>3,17</t>
+          <t>2,28</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>22,24</t>
+          <t>20,86</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>281,973</t>
+          <t>279,481</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -11170,32 +11170,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1,40564800</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>-0,627</t>
+          <t>1,42683000</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>1,506</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>-4,48</t>
+          <t>-3,04</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>-7,79</t>
+          <t>-6,40</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>-2,72</t>
+          <t>-1,13</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>426,379</t>
+          <t>432,510</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -11292,32 +11292,32 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1,06371600</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>-0,516</t>
+          <t>1,07870600</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>1,409</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>-4,02</t>
+          <t>-2,66</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>-8,61</t>
+          <t>-7,32</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>-6,01</t>
+          <t>-4,49</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>54,673</t>
+          <t>55,395</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -11414,32 +11414,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1,65996000</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>-0,480</t>
+          <t>1,67370600</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>0,828</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>-2,84</t>
+          <t>-2,04</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>-2,61</t>
+          <t>-1,81</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>7,10</t>
+          <t>8,36</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2,053</t>
+          <t>2,070</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -11536,32 +11536,32 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>4,51150900</t>
+          <t>4,51888500</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>0,696</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>0,00</t>
+          <t>0,163</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>43,26</t>
+          <t>43,49</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>53,31</t>
+          <t>55,12</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>76,026</t>
+          <t>76,144</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -11658,32 +11658,32 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>8,41064000</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>-0,213</t>
+          <t>8,46585100</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>0,656</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>-2,91</t>
+          <t>-2,27</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>3,87</t>
+          <t>4,56</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>21,58</t>
+          <t>22,74</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>83,977</t>
+          <t>84,518</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -11780,32 +11780,32 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1,23421200</t>
+          <t>1,22677900</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>-0,014</t>
+          <t>-0,016</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>-2,87</t>
+          <t>-3,45</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>-4,10</t>
+          <t>-4,68</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>5,03</t>
+          <t>4,64</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>279,084</t>
+          <t>277,405</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -11902,32 +11902,32 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>1,74287100</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>-0,459</t>
+          <t>1,79234400</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>2,838</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>-6,37</t>
+          <t>-3,72</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>-8,33</t>
+          <t>-5,73</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>7,93</t>
+          <t>11,35</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>106,819</t>
+          <t>109,593</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -12024,32 +12024,32 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>2,84435400</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>-0,249</t>
+          <t>2,85006800</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>0,200</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>-1,67</t>
+          <t>-1,48</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>4,57</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>15,93</t>
+          <t>16,99</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>124,401</t>
+          <t>124,642</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -12146,32 +12146,32 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1,79597100</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>-0,763</t>
+          <t>1,82636600</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>1,692</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>-4,24</t>
+          <t>-2,62</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>-7,30</t>
+          <t>-5,73</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>8,83</t>
+          <t>11,07</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>47,372</t>
+          <t>48,174</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -12268,32 +12268,32 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>6,40656500</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>0,782</t>
+          <t>6,39888000</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>-0,119</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>-0,31</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>36,59</t>
+          <t>36,42</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>48,70</t>
+          <t>50,76</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>117,873</t>
+          <t>117,472</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -12390,32 +12390,32 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>1.206,54152000</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>-0,366</t>
+          <t>1.207,09736900</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>-5,21</t>
+          <t>-5,17</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>-11,73</t>
+          <t>-11,69</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>-11,14</t>
+          <t>-11,17</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>38,623</t>
+          <t>38,654</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -12512,32 +12512,32 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>36,94620100</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>-0,803</t>
+          <t>37,14567200</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>0,539</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>-5,75</t>
+          <t>-5,24</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>6,94</t>
+          <t>7,52</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>55,81</t>
+          <t>55,76</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>632,194</t>
+          <t>631,747</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -12634,32 +12634,32 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2,68107200</t>
+          <t>2,72181700</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>0,679</t>
-        </is>
-      </c>
-      <c r="F102" s="7" t="inlineStr">
-        <is>
-          <t>-0,11</t>
+          <t>1,519</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>1,40</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>10,68</t>
+          <t>12,36</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>29,89</t>
+          <t>32,31</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>445,201</t>
+          <t>451,569</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -12756,32 +12756,32 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>4,60741300</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>-0,406</t>
+          <t>4,64954900</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>0,914</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>-4,21</t>
+          <t>-3,33</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>3,60</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>22,06</t>
+          <t>23,50</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>22,264</t>
+          <t>22,498</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -12878,32 +12878,32 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>1.439,85776000</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>-0,674</t>
+          <t>1.456,04335700</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>1,124</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>-4,25</t>
-        </is>
-      </c>
-      <c r="G104" s="7" t="inlineStr">
-        <is>
-          <t>-1,06</t>
+          <t>-3,18</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>0,05</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>13,62</t>
+          <t>15,91</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>28,624</t>
+          <t>28,908</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -13000,32 +13000,32 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>1,87347300</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>-0,616</t>
+          <t>1,89974100</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>1,402</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>-3,26</t>
+          <t>-1,90</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>-7,91</t>
+          <t>-6,62</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>5,65</t>
+          <t>7,01</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>1,688</t>
+          <t>1,714</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -13122,32 +13122,32 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>5,67690500</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>-0,315</t>
+          <t>5,71082500</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>0,597</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>-3,21</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>6,16</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>24,89</t>
+          <t>25,92</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>41,784</t>
+          <t>42,005</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>2,14394600</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>-0,410</t>
+          <t>2,16217500</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>0,850</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>-3,09</t>
+          <t>-2,27</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>3,05</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>21,05</t>
+          <t>22,42</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>34,421</t>
+          <t>34,726</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -13366,32 +13366,32 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>41,84315800</t>
+          <t>41,91153600</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>0,698</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
+          <t>0,163</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>43,32</t>
+          <t>43,55</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>53,43</t>
+          <t>55,25</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>832,352</t>
+          <t>833,419</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -13488,32 +13488,32 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>0,83184600</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>-0,787</t>
+          <t>0,83619300</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>0,522</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>-3,22</t>
+          <t>-2,71</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>-13,58</t>
+          <t>-13,13</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>-21,34</t>
+          <t>-20,83</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>2,827</t>
+          <t>2,864</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -13610,32 +13610,32 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>1,18944600</t>
+          <t>1,19582800</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>0,043</t>
-        </is>
-      </c>
-      <c r="F110" s="7" t="inlineStr">
-        <is>
-          <t>-0,45</t>
+          <t>0,536</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>0,07</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>-1,71</t>
+          <t>-1,18</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>13,49</t>
+          <t>13,82</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>3,837</t>
+          <t>3,858</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -13732,32 +13732,32 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>1,32445800</t>
+          <t>1,34457400</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>0,678</t>
-        </is>
-      </c>
-      <c r="F111" s="6" t="inlineStr">
-        <is>
-          <t>-0,12</t>
+          <t>1,518</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>1,39</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>10,60</t>
+          <t>12,28</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>29,70</t>
+          <t>32,12</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>19,645</t>
+          <t>19,937</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -13854,32 +13854,32 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1,71183100</t>
+          <t>1,70974200</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>-0,471</t>
+          <t>-0,122</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>-3,60</t>
+          <t>-3,72</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>-0,53</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>63,50</t>
+          <t>64,46</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>261,028</t>
+          <t>260,575</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>971,29800200</t>
+          <t>968,46125800</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -13986,22 +13986,22 @@
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>-2,82</t>
+          <t>-3,10</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-1,21</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>14,17</t>
+          <t>14,49</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>7,880</t>
+          <t>7,867</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -14098,7 +14098,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1.451,09834000</t>
+          <t>1.446,11053600</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
@@ -14108,22 +14108,22 @@
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>-2,95</t>
+          <t>-3,28</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>-2,98</t>
+          <t>-3,32</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>8,72</t>
+          <t>8,71</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>20,919</t>
+          <t>20,831</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -14220,32 +14220,32 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>164,73259674</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>-0,204</t>
+          <t>165,82352522</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>0,662</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>-2,84</t>
+          <t>-2,20</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>4,54</t>
+          <t>5,23</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>23,45</t>
+          <t>24,63</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>41,184</t>
+          <t>41,457</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -14342,32 +14342,32 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1,74965700</t>
+          <t>1,74757400</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>-0,469</t>
+          <t>-0,119</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>-3,61</t>
+          <t>-3,73</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,46</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>63,83</t>
+          <t>64,79</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>4,787</t>
+          <t>4,781</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -14464,32 +14464,32 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1,70565000</t>
+          <t>1,70362000</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>-0,472</t>
+          <t>-0,119</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>-3,64</t>
+          <t>-3,75</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>63,82</t>
+          <t>64,78</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>1.553,638</t>
+          <t>1.550,125</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -14586,32 +14586,32 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>46,55262700</t>
+          <t>46,62977700</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>0,699</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
+          <t>0,165</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>43,73</t>
+          <t>43,97</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>54,31</t>
+          <t>56,14</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>672,581</t>
+          <t>673,663</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -14708,32 +14708,32 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>40,93322500</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>-0,804</t>
+          <t>41,15621300</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>0,544</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>-5,75</t>
+          <t>-5,24</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>7,16</t>
+          <t>7,75</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>56,64</t>
+          <t>56,59</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>737,744</t>
+          <t>741,020</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -14830,32 +14830,32 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>15,83528100</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="inlineStr">
-        <is>
-          <t>-0,773</t>
+          <t>16,09770700</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>1,657</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>-3,74</t>
+          <t>-2,14</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>-6,11</t>
+          <t>-4,55</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>11,67</t>
+          <t>13,76</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>109,206</t>
+          <t>111,016</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -14952,32 +14952,32 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>34,32216200</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>-0,805</t>
+          <t>34,49886000</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>0,514</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>-5,74</t>
+          <t>-5,26</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>6,96</t>
+          <t>7,51</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>55,57</t>
+          <t>55,48</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>11,713</t>
+          <t>11,773</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
@@ -15074,32 +15074,32 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>41,12836100</t>
+          <t>41,19589400</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>0,698</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
+          <t>0,164</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>43,45</t>
+          <t>43,68</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>53,61</t>
+          <t>55,43</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>580,165</t>
+          <t>580,924</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -15196,32 +15196,32 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>35,24183700</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
-          <t>-0,806</t>
+          <t>35,43311700</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>0,542</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>-5,76</t>
+          <t>-5,25</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>6,95</t>
+          <t>7,53</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>55,82</t>
+          <t>55,77</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>442,843</t>
+          <t>445,139</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -15318,32 +15318,32 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>43,73471600</t>
+          <t>43,80675900</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>0,701</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
+          <t>0,164</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>43,61</t>
+          <t>43,85</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>53,97</t>
+          <t>55,79</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>667,092</t>
+          <t>668,191</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>1,12550100</t>
+          <t>1,12603000</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -15450,12 +15450,12 @@
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>5,24</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>54,817</t>
+          <t>57,598</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
@@ -15562,7 +15562,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>1,35830600</t>
+          <t>1,35894700</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -15572,12 +15572,12 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>5,24</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>219,584</t>
+          <t>219,238</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -15684,22 +15684,22 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>5,89106300</t>
+          <t>5,89404400</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>0,065</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,30</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>5,61</t>
+          <t>5,66</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -15709,7 +15709,7 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>40,915</t>
+          <t>40,941</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>5,12756300</t>
+          <t>5,13023800</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -15816,12 +15816,12 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>5,85</t>
+          <t>5,90</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>786,789</t>
+          <t>787,200</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -15928,22 +15928,22 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>3,22112100</t>
+          <t>3,22276900</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,30</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>5,69</t>
+          <t>5,74</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -15953,7 +15953,7 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>18,384</t>
+          <t>18,365</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -16050,32 +16050,32 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>23,57057700</t>
-        </is>
-      </c>
-      <c r="E130" s="7" t="inlineStr">
-        <is>
-          <t>-0,127</t>
+          <t>23,57210300</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>0,006</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>-0,75</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>5,28</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>11,21</t>
+          <t>11,14</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>93,629</t>
+          <t>93,605</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -16172,7 +16172,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>3,27587100</t>
+          <t>3,27755400</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -16182,12 +16182,12 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,30</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>5,74</t>
+          <t>5,79</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -16197,7 +16197,7 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>7.557,653</t>
+          <t>7.659,426</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -16294,22 +16294,22 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>1.888,05462800</t>
+          <t>1.889,11592100</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>0,071</t>
+          <t>0,056</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>6,06</t>
+          <t>6,12</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
@@ -16319,7 +16319,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>15.947,424</t>
+          <t>16.036,524</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -16416,32 +16416,32 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>4,88194400</t>
+          <t>4,88444200</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>5,88</t>
+          <t>5,93</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>14,64</t>
+          <t>14,63</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>3.055,353</t>
+          <t>3.061,214</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -16538,7 +16538,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1,55064626</t>
+          <t>1,55146645</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -16548,22 +16548,22 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>5,92</t>
+          <t>5,98</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>14,69</t>
+          <t>14,68</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>361,247</t>
+          <t>361,438</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -16660,7 +16660,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>5,12940600</t>
+          <t>5,13213000</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -16670,12 +16670,12 @@
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>5,95</t>
+          <t>6,01</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -16685,7 +16685,7 @@
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>285,134</t>
+          <t>285,286</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -16782,22 +16782,22 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>8,71493000</t>
+          <t>8,71940900</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>0,20</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>5,82</t>
+          <t>5,88</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>4.008,931</t>
+          <t>3.971,551</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -16904,32 +16904,32 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>17,92723000</t>
+          <t>17,93653600</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>5,89</t>
+          <t>5,94</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>14,70</t>
+          <t>14,69</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>4.768,690</t>
+          <t>4.766,105</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -17022,7 +17022,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>2,82752400</t>
+          <t>2,82887700</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
@@ -17032,12 +17032,12 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>5,39</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
@@ -17047,7 +17047,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>13.235,972</t>
+          <t>13.306,738</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -17144,7 +17144,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>4,43311700</t>
+          <t>4,43547100</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17154,12 +17154,12 @@
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>5,97</t>
+          <t>6,02</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -17169,7 +17169,7 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>13.334,614</t>
+          <t>13.397,224</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>1,37554300</t>
+          <t>1,37628200</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -17276,12 +17276,12 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>6,03</t>
+          <t>6,09</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.499,251</t>
+          <t>3.527,274</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>1.774,24679200</t>
+          <t>1.775,18355800</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17398,12 +17398,12 @@
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>5,93</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>1.436,120</t>
+          <t>1.438,314</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -17510,22 +17510,22 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>1,30907100</t>
+          <t>1,30964000</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>0,041</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>4,79</t>
+          <t>4,84</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
@@ -17535,7 +17535,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>32.239,973</t>
+          <t>32.378,969</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -17632,22 +17632,22 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>9,41190500</t>
+          <t>9,41628900</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>5,15</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
@@ -17657,7 +17657,7 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>2.814,812</t>
+          <t>2.833,352</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>2,47869600</t>
+          <t>2,47984400</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -17764,22 +17764,22 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>5,14</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>12,47</t>
+          <t>12,48</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>16.618,220</t>
+          <t>16.540,431</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -17876,32 +17876,32 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>2,60895300</t>
+          <t>2,61031800</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>0,057</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,30</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>5,93</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>14,74</t>
+          <t>14,73</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>9.187,056</t>
+          <t>9.181,922</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
@@ -17998,12 +17998,12 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>2,37849700</t>
-        </is>
-      </c>
-      <c r="E146" s="7" t="inlineStr">
-        <is>
-          <t>-0,178</t>
+          <t>2,37847400</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>0,000</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
@@ -18018,12 +18018,12 @@
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>11,39</t>
+          <t>11,29</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>3.594,829</t>
+          <t>3.594,792</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -18120,12 +18120,12 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>2,95698000</t>
-        </is>
-      </c>
-      <c r="E147" s="6" t="inlineStr">
-        <is>
-          <t>-0,165</t>
+          <t>2,95716000</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>0,006</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr">
@@ -18135,17 +18135,17 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>4,85</t>
+          <t>4,86</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>10,87</t>
+          <t>10,80</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>39,950</t>
+          <t>39,953</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
@@ -18242,32 +18242,32 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1.635,42235500</t>
-        </is>
-      </c>
-      <c r="E148" s="7" t="inlineStr">
-        <is>
-          <t>-0,054</t>
+          <t>1.635,87857200</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>0,027</t>
         </is>
       </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>4,20</t>
+          <t>4,23</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>11,36</t>
+          <t>11,31</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>458,762</t>
+          <t>458,890</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -18364,32 +18364,32 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>4,47579200</t>
+          <t>4,47754900</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>0,021</t>
+          <t>0,039</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>14,08</t>
+          <t>14,04</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>10.916,702</t>
+          <t>10.934,005</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
@@ -18486,32 +18486,32 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>3,78954800</t>
+          <t>3,78907400</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr">
         <is>
-          <t>-0,186</t>
+          <t>-0,012</t>
         </is>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-0,79</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>11,60</t>
+          <t>11,48</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2.974,228</t>
+          <t>2.974,706</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -18608,32 +18608,32 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>3,58186800</t>
+          <t>3,58105600</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>-0,205</t>
+          <t>-0,022</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>-1,51</t>
+          <t>-1,54</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>2,60</t>
+          <t>2,58</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>11,30</t>
+          <t>11,07</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>1.717,618</t>
+          <t>1.719,272</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
@@ -18730,32 +18730,32 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>5,04779300</t>
-        </is>
-      </c>
-      <c r="E152" s="7" t="inlineStr">
-        <is>
-          <t>-0,324</t>
+          <t>5,05094700</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>0,062</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>-2,30</t>
+          <t>-2,23</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2,65</t>
+          <t>2,72</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>8,05</t>
+          <t>8,22</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2.529,200</t>
+          <t>2.529,801</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -18852,32 +18852,32 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>5,14225000</t>
-        </is>
-      </c>
-      <c r="E153" s="6" t="inlineStr">
-        <is>
-          <t>-0,126</t>
+          <t>5,14260000</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>0,006</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>-0,75</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>5,33</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>11,38</t>
+          <t>11,30</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>5.522,560</t>
+          <t>5.523,050</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
@@ -18974,32 +18974,32 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>4,71200500</t>
-        </is>
-      </c>
-      <c r="E154" s="7" t="inlineStr">
-        <is>
-          <t>-0,095</t>
+          <t>4,71381500</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>0,038</t>
         </is>
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>-0,72</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>4,39</t>
+          <t>4,43</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>12,31</t>
+          <t>12,30</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>510,267</t>
+          <t>510,509</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -19096,22 +19096,22 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>7,95139000</t>
+          <t>7,95545800</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>0,20</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>5,82</t>
+          <t>5,87</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
@@ -19121,7 +19121,7 @@
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>176,628</t>
+          <t>176,719</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
@@ -19166,32 +19166,32 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>3,35441900</t>
-        </is>
-      </c>
-      <c r="E156" s="7" t="inlineStr">
-        <is>
-          <t>-0,485</t>
+          <t>3,35806200</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>0,108</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>-3,52</t>
+          <t>-3,42</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>5,50</t>
+          <t>5,82</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>749,377</t>
+          <t>749,202</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -19288,32 +19288,32 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>3,69226500</t>
+          <t>3,69051000</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>-0,296</t>
+          <t>-0,047</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>-2,16</t>
+          <t>-2,20</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>1,53</t>
+          <t>1,48</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>10,23</t>
+          <t>9,92</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>707,190</t>
+          <t>706,745</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
@@ -19410,32 +19410,32 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>7,17756500</t>
+          <t>7,18121800</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>5,86</t>
+          <t>5,92</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>14,57</t>
+          <t>14,56</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>12.667,737</t>
+          <t>12.587,978</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>7,49848100</t>
+          <t>7,50241800</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -19542,12 +19542,12 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>5,84</t>
+          <t>5,89</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>4.066,657</t>
+          <t>3.947,870</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -19654,32 +19654,32 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>1,42487900</t>
+          <t>1,42439100</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr">
         <is>
-          <t>-0,296</t>
+          <t>-0,034</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-1,56</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>10,83</t>
+          <t>10,52</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>170,339</t>
+          <t>167,281</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>3,14184400</t>
+          <t>3,14341000</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -19786,12 +19786,12 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,30</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>5,59</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
@@ -19801,7 +19801,7 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>1.493,730</t>
+          <t>1.495,211</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
@@ -19898,22 +19898,22 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>6,72589000</t>
+          <t>6,72958400</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>0,065</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>5,98</t>
+          <t>6,03</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
@@ -19923,7 +19923,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>23.567,077</t>
+          <t>23.793,004</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -19968,32 +19968,32 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>5,40405800</t>
-        </is>
-      </c>
-      <c r="E163" s="6" t="inlineStr">
-        <is>
-          <t>-0,330</t>
+          <t>5,40871100</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>0,086</t>
         </is>
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>-2,39</t>
+          <t>-2,30</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>2,81</t>
+          <t>2,90</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>8,25</t>
+          <t>8,40</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>582,154</t>
+          <t>581,030</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
@@ -20212,32 +20212,32 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>3,78498900</t>
-        </is>
-      </c>
-      <c r="E165" s="6" t="inlineStr">
-        <is>
-          <t>-0,207</t>
+          <t>3,81010000</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>0,663</t>
         </is>
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>-2,89</t>
+          <t>-2,25</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>4,53</t>
+          <t>5,23</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>23,47</t>
+          <t>24,65</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>282,032</t>
+          <t>283,576</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
@@ -20334,32 +20334,32 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>3,48196900</t>
-        </is>
-      </c>
-      <c r="E166" s="7" t="inlineStr">
-        <is>
-          <t>-0,156</t>
+          <t>3,50353000</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>0,619</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>-2,80</t>
+          <t>-2,20</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>4,43</t>
+          <t>5,08</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>22,96</t>
+          <t>24,21</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>8,811</t>
+          <t>8,865</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -20456,32 +20456,32 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>11,45303187</t>
-        </is>
-      </c>
-      <c r="E167" s="5" t="inlineStr">
-        <is>
-          <t>1,079</t>
+          <t>11,35421000</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>-0,862</t>
         </is>
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-1,22</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>3,49</t>
+          <t>2,59</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
         <is>
-          <t>23,25</t>
+          <t>21,84</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>2.357,875</t>
+          <t>2.337,469</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
@@ -20578,32 +20578,32 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>1,94444400</t>
-        </is>
-      </c>
-      <c r="E168" s="7" t="inlineStr">
-        <is>
-          <t>-0,247</t>
+          <t>1,96012900</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>0,806</t>
         </is>
       </c>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>-2,96</t>
+          <t>-2,17</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2,58</t>
+          <t>3,41</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>20,15</t>
+          <t>21,47</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>191,943</t>
+          <t>193,491</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -20700,32 +20700,32 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>1,92188400</t>
-        </is>
-      </c>
-      <c r="E169" s="6" t="inlineStr">
-        <is>
-          <t>-0,763</t>
+          <t>1,95450100</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>1,697</t>
         </is>
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>-4,25</t>
+          <t>-2,62</t>
         </is>
       </c>
       <c r="G169" s="6" t="inlineStr">
         <is>
-          <t>-7,30</t>
+          <t>-5,72</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
         <is>
-          <t>9,18</t>
+          <t>11,44</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>726,050</t>
+          <t>738,372</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
@@ -20822,32 +20822,32 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>3,32133597</t>
-        </is>
-      </c>
-      <c r="E170" s="7" t="inlineStr">
-        <is>
-          <t>-0,257</t>
+          <t>3,35737052</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>1,084</t>
         </is>
       </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>-2,70</t>
+          <t>-1,65</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>3,19</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>17,58</t>
+          <t>19,23</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>1.273,656</t>
+          <t>1.287,475</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -20940,32 +20940,32 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>2,40654903</t>
-        </is>
-      </c>
-      <c r="E171" s="6" t="inlineStr">
-        <is>
-          <t>-0,236</t>
+          <t>2,43020628</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>0,983</t>
         </is>
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>-3,31</t>
+          <t>-2,36</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>18,51</t>
+          <t>20,22</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>736,641</t>
+          <t>743,882</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
@@ -21058,32 +21058,32 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>3,74364100</t>
+          <t>3,74480500</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>0,007</t>
+          <t>0,031</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>14,11</t>
+          <t>14,05</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>4.840,742</t>
+          <t>5.370,241</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -3262,22 +3262,22 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,10173366</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>-0,001</t>
+          <t>1,10380800</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>0,186</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-0,95</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2,13</t>
+          <t>2,32</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>203,565</t>
+          <t>203,949</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3384,32 +3384,32 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1,24015200</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>-0,001</t>
+          <t>1,24082700</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>5,88</t>
+          <t>5,94</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>14,54</t>
+          <t>14,61</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>71,144</t>
+          <t>71,182</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -3750,22 +3750,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,03873100</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>-0,001</t>
+          <t>1,03996200</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>0,056</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>5,93</t>
+          <t>6,05</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,933</t>
+          <t>21,959</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3868,32 +3868,32 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,17052700</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>-0,001</t>
+          <t>1,17114000</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>5,41</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>13,99</t>
+          <t>14,05</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>66,479</t>
+          <t>66,514</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -3986,22 +3986,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,07281439</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>-0,001</t>
+          <t>1,07439400</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>0,145</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>3,97</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>305,940</t>
+          <t>306,390</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -6972,32 +6972,32 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1,41608300</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>0,000</t>
+          <t>1,41627200</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>0,013</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>5,76</t>
+          <t>5,78</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>14,35</t>
+          <t>14,36</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>67,801</t>
+          <t>67,810</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -7094,32 +7094,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1.218,68940700</t>
+          <t>1.207,29403300</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>-0,002</t>
+          <t>-0,937</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>0,30</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>-2,87</t>
+          <t>-3,78</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>37,155</t>
+          <t>36,808</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -7286,32 +7286,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1.617,46323900</t>
+          <t>1.614,86272800</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>-0,006</t>
+          <t>-0,166</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>-1,20</t>
+          <t>-1,36</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>3,22</t>
+          <t>3,05</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>11,18</t>
+          <t>11,00</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>113,173</t>
+          <t>112,991</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -7648,32 +7648,32 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1,24518700</t>
+          <t>1,24466400</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>-0,005</t>
+          <t>-0,047</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>-0,50</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>1,91</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>9,44</t>
+          <t>9,39</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>6,272</t>
+          <t>6,269</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -8010,32 +8010,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1,38982100</t>
+          <t>1,37630800</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>-0,004</t>
+          <t>-0,977</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>-2,15</t>
+          <t>-3,10</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>14,52</t>
+          <t>13,41</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>11,523</t>
+          <t>11,411</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -8372,32 +8372,32 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>5,27698843</t>
+          <t>5,26976600</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>-0,003</t>
+          <t>-0,140</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>-1,25</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>2,84</t>
+          <t>2,70</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>11,02</t>
+          <t>10,87</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>32,492</t>
+          <t>32,447</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -8616,32 +8616,32 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>2,83240800</t>
+          <t>2,82738400</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>-0,004</t>
+          <t>-0,181</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>-1,07</t>
+          <t>-1,24</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>1,40</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>9,05</t>
+          <t>8,85</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>73,514</t>
+          <t>73,384</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -9104,32 +9104,32 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1.638,96341700</t>
+          <t>1.636,33252700</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>-0,003</t>
+          <t>-0,163</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-1,32</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>3,46</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>12,15</t>
+          <t>11,97</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>14,384</t>
+          <t>14,361</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -9222,22 +9222,22 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>0,45575376</t>
+          <t>0,45277400</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>-0,005</t>
+          <t>-0,659</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>-13,50</t>
+          <t>-14,06</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>-36,88</t>
+          <t>-37,29</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>3,609</t>
+          <t>3,585</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -9344,32 +9344,32 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>3,27918200</t>
+          <t>3,24636900</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>-0,005</t>
+          <t>-1,006</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>-1,02</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>1,89</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>10,40</t>
+          <t>9,30</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>156,182</t>
+          <t>154,619</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1,52179200</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>-0,004</t>
+          <t>1,52188600</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>0,001</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -9481,17 +9481,17 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>1,91</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>18,98</t>
+          <t>18,99</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>14,336</t>
+          <t>14,337</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -9588,32 +9588,32 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1,37835200</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>-0,003</t>
+          <t>1,37872300</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>0,023</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>1,63</t>
+          <t>1,66</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>6,77</t>
+          <t>6,80</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>70,633</t>
+          <t>70,652</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -9710,32 +9710,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1,47839000</t>
+          <t>1,47241800</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>-0,003</t>
+          <t>-0,407</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>-1,57</t>
+          <t>-1,97</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>1,81</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>13,58</t>
+          <t>13,12</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>191,689</t>
+          <t>190,914</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9832,32 +9832,32 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1,79303600</t>
+          <t>1,78949700</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>-0,002</t>
+          <t>-0,199</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>0,70</t>
+          <t>0,50</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>1,50</t>
+          <t>1,30</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>10,87</t>
+          <t>10,65</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>176,188</t>
+          <t>175,840</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -10198,32 +10198,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>6,73078500</t>
+          <t>6,72459500</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>-0,004</t>
+          <t>-0,096</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>-1,57</t>
+          <t>-1,66</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>4,65</t>
+          <t>4,56</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>14,66</t>
+          <t>14,55</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>127,299</t>
+          <t>127,182</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -10442,32 +10442,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,34407000</t>
+          <t>1,33970400</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>-0,002</t>
+          <t>-0,326</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>1,25</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>4,71</t>
+          <t>4,37</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>4,48</t>
+          <t>4,14</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>13,116</t>
+          <t>13,074</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -11780,32 +11780,32 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1,23980500</t>
+          <t>1,22546800</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>-0,017</t>
+          <t>-1,174</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>-2,43</t>
+          <t>-3,56</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>-3,67</t>
+          <t>-4,78</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>5,15</t>
+          <t>3,94</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>280,349</t>
+          <t>277,107</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -13976,32 +13976,32 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>977,98991400</t>
+          <t>969,32849400</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>-0,003</t>
+          <t>-0,888</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>-2,15</t>
+          <t>-3,01</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-1,12</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>14,75</t>
+          <t>13,73</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>7,944</t>
+          <t>7,874</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -14098,32 +14098,32 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1.464,51393600</t>
+          <t>1.450,47136800</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>-0,002</t>
+          <t>-0,961</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>-2,05</t>
+          <t>-2,99</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>-2,09</t>
+          <t>-3,03</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>9,29</t>
+          <t>8,24</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>21,110</t>
+          <t>20,907</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -19450,12 +19450,12 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>05.164.356/0001-84</t>
+          <t>03.737.206/0001-97</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -19485,32 +19485,32 @@
       </c>
       <c r="S158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5462.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5404.pdf</t>
         </is>
       </c>
       <c r="T158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5462.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5404.pdf</t>
         </is>
       </c>
       <c r="U158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5462.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5404.pdf</t>
         </is>
       </c>
       <c r="V158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5462.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5404.pdf</t>
         </is>
       </c>
       <c r="W158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5462.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5404.pdf</t>
         </is>
       </c>
       <c r="X158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5462.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5404.pdf</t>
         </is>
       </c>
     </row>
@@ -20090,32 +20090,32 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.530,12954000</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="inlineStr">
+        <is>
+          <t>-0,167</t>
+        </is>
+      </c>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>-1,35</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>3,08</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>11,03</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>128,581</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,26338000</t>
+          <t>2,26442300</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>5,33</t>
+          <t>5,38</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>407,242</t>
+          <t>408,242</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,50080300</t>
+          <t>5,50331500</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>5,23</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.581,452</t>
+          <t>6.675,758</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,77744800</t>
+          <t>2,77871600</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>5,22</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>978,870</t>
+          <t>982,612</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1354,22 +1354,22 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>3,33387500</t>
+          <t>3,33555600</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>5,80</t>
+          <t>5,86</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>11,635</t>
+          <t>11,671</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -1593,22 +1593,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,48841400</t>
+          <t>3,49026300</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>5,92</t>
+          <t>5,98</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>119,692</t>
+          <t>119,869</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1835,22 +1835,22 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1.837,19064200</t>
+          <t>1.838,17745300</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>6,02</t>
+          <t>6,07</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>96,703</t>
+          <t>96,756</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -2070,22 +2070,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,70767200</t>
+          <t>9,71248000</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>582,731</t>
+          <t>582,977</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2309,22 +2309,22 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3,35733200</t>
+          <t>3,35909700</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>0,058</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>5,88</t>
+          <t>5,94</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>62,629</t>
+          <t>62,638</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -2544,22 +2544,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,99820900</t>
+          <t>2,99984900</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0,059</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>6,09</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1.663,337</t>
+          <t>1.665,658</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2779,32 +2779,32 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>19,70992200</t>
+          <t>19,76386800</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>0,839</t>
+          <t>0,273</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>-0,84</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>2,83</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>10,56</t>
+          <t>10,85</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>118,998</t>
+          <t>119,263</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -3022,32 +3022,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,44751900</t>
+          <t>13,47058700</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>0,532</t>
+          <t>0,171</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>4,57</t>
+          <t>4,75</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>9,91</t>
+          <t>9,94</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,588</t>
+          <t>27,636</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>03.218.183/0001-04</t>
+          <t>03.191.874/0001-61</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3077,27 +3077,27 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>100000.0</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="AG12" s="2" t="inlineStr">
         <is>
-          <t>["Pessoa Física"]</t>
+          <t>["Institucional", "PJ Atacado"]</t>
         </is>
       </c>
       <c r="AH12" s="2" t="inlineStr">
         <is>
-          <t>["Pessoa Física"]</t>
+          <t>["Institucional", "PJ Atacado"]</t>
         </is>
       </c>
       <c r="AI12" s="2" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="AM12" s="2" t="inlineStr">
         <is>
-          <t>CAIXA CAPITAL ÍNDICE DE PREÇOS FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESP LIMITADA</t>
+          <t>CAIXA PATRIMÔNIO ÍNDICE DE PREÇOS FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESP LIMITADA</t>
         </is>
       </c>
       <c r="AN12" s="2" t="inlineStr">
@@ -3203,47 +3203,47 @@
       </c>
       <c r="AO12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0087.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0046.pdf</t>
         </is>
       </c>
       <c r="AP12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0087.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0046.pdf</t>
         </is>
       </c>
       <c r="AQ12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0087.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0046.pdf</t>
         </is>
       </c>
       <c r="AR12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_87.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_46.pdf</t>
         </is>
       </c>
       <c r="AS12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_87.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_46.pdf</t>
         </is>
       </c>
       <c r="AT12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_87.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_46.pdf</t>
         </is>
       </c>
       <c r="AU12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_0087.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_0046.pdf</t>
         </is>
       </c>
       <c r="AV12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/0087-SUMARIO.pdf</t>
+          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/0046-SUMARIO.pdf</t>
         </is>
       </c>
       <c r="AW12" s="2" t="inlineStr">
         <is>
-          <t>https://web.microsoftstream.com/video/32d65536-1de1-4f2f-a9b8-0fbb0d9347fc?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
+          <t>https://web.microsoftstream.com/video/140b7682-00df-491d-b451-73ae70a040fa?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
     </row>
@@ -3265,22 +3265,22 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>46,16917100</t>
+          <t>46,19197300</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>5,51</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>40,511</t>
+          <t>40,531</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20,22075100</t>
+          <t>20,23025600</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>5,42</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,570</t>
+          <t>64,594</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3744,32 +3744,32 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>3,13515000</t>
+          <t>3,14012900</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>0,462</t>
+          <t>0,158</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>5,55</t>
+          <t>5,72</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>11,18</t>
+          <t>11,19</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>78,325</t>
+          <t>78,480</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14,95716400</t>
+          <t>14,96460000</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>5,55</t>
+          <t>5,60</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,751</t>
+          <t>27,763</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4226,22 +4226,22 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>3,00047500</t>
+          <t>3,00192300</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>5,44</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -4461,32 +4461,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,28993500</t>
+          <t>3,29859200</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>0,787</t>
+          <t>0,263</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>3,22</t>
+          <t>3,49</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>11,15</t>
+          <t>11,43</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>134,925</t>
+          <t>135,107</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4704,22 +4704,22 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,04110300</t>
+          <t>3,04271100</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>6,10</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1.758,123</t>
+          <t>1.778,480</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -4935,22 +4935,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32,79652200</t>
+          <t>32,81327100</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>5,71</t>
+          <t>5,76</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2.189,738</t>
+          <t>2.192,110</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5174,22 +5174,22 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,30628600</t>
+          <t>3,30797600</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>5,72</t>
+          <t>5,77</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -5418,32 +5418,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3,33299200</t>
+          <t>3,34396800</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>1,455</t>
+          <t>0,329</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>4,58</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>9,84</t>
+          <t>10,18</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,606</t>
+          <t>65,618</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5657,22 +5657,22 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>19,04358800</t>
+          <t>19,05358700</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>5,86</t>
+          <t>5,92</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>950,274</t>
+          <t>950,542</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -5896,32 +5896,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,11215364</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>0,756</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>-0,20</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>3,10</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>205,465</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6131,32 +6131,32 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1,24080900</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>-0,001</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>0,37</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>5,94</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>14,53</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>71,182</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -6362,32 +6362,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1.833,41147500</t>
+          <t>1.834,37329900</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>6,09</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>14,78</t>
+          <t>14,77</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>175,205</t>
+          <t>175,519</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1,20241000</t>
+          <t>1,20397200</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>0,130</t>
+          <t>0,129</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>0,20</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>6,99</t>
+          <t>7,13</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>13,71</t>
+          <t>13,75</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>39,949</t>
+          <t>40,001</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -6840,32 +6840,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,04045000</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>0,046</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>0,42</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>6,10</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,960</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7063,32 +7063,32 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,17112400</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>-0,001</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>0,50</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>5,46</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>13,97</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>66,514</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -7294,32 +7294,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,07568162</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>0,119</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>0,60</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>4,10</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>306,099</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7748,22 +7748,22 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>5,14322800</t>
+          <t>5,14588400</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,058</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>6,08</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>851,088</t>
+          <t>851,906</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7987,22 +7987,22 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>4,94877000</t>
+          <t>4,95138600</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>6,09</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.263,546</t>
+          <t>3.270,411</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>29,26435900</t>
+          <t>29,27848900</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -8236,12 +8236,12 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,102</t>
+          <t>21,112</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8453,22 +8453,22 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>30,63223200</t>
+          <t>30,64862400</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>5,98</t>
+          <t>6,03</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>3.109,524</t>
+          <t>3.109,343</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -8688,32 +8688,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1.770,34894500</t>
+          <t>1.771,92412100</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0,177</t>
+          <t>0,088</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>5,10</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>13,28</t>
+          <t>13,31</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>121,410</t>
+          <t>123,284</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8923,22 +8923,22 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>3,22473200</t>
+          <t>3,22644100</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>6,11</t>
+          <t>6,17</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>586,364</t>
+          <t>586,365</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -9162,22 +9162,22 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>6,19279600</t>
+          <t>6,19605500</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>5,93</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>121,536</t>
+          <t>121,534</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9402,22 +9402,22 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1,27027100</t>
+          <t>1,27095400</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,50</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>6,19</t>
+          <t>6,25</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>387,938</t>
+          <t>391,367</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -9641,22 +9641,22 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>10,60206300</t>
+          <t>10,60781400</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>6,06</t>
+          <t>6,12</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2.367,781</t>
+          <t>2.369,327</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9880,22 +9880,22 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>5,52157200</t>
+          <t>5,52453600</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>6,16</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>545,551</t>
+          <t>545,808</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -10120,32 +10120,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3,57101500</t>
+          <t>3,57293100</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,50</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>6,18</t>
+          <t>6,23</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>14,94</t>
+          <t>14,93</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15.555,921</t>
+          <t>15.579,370</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10363,22 +10363,22 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>5,30681100</t>
+          <t>5,30971400</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>0,064</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>6,22</t>
+          <t>6,28</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>1.389,731</t>
+          <t>1.391,015</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>30,35284500</t>
+          <t>30,36715200</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -10840,12 +10840,12 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>164,638</t>
+          <t>163,978</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2,81058300</t>
+          <t>2,81189300</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -11083,12 +11083,12 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>5,40</t>
+          <t>5,45</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -11098,7 +11098,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5.943,159</t>
+          <t>6.013,350</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>3,60791100</t>
+          <t>3,60974700</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>5,92</t>
+          <t>5,98</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>2.208,959</t>
+          <t>2.212,006</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1,29165700</t>
+          <t>1,29233400</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -11563,12 +11563,12 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>6,08</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -11578,7 +11578,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>64,502</t>
+          <t>64,526</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>9,69297000</t>
+          <t>9,69794000</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>5,97</t>
+          <t>6,02</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>829,739</t>
+          <t>830,053</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>4,46016900</t>
+          <t>4,46247900</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -12046,12 +12046,12 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>6,01</t>
+          <t>6,07</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15.950,193</t>
+          <t>15.996,953</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>4,77838500</t>
+          <t>4,78089300</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -12285,12 +12285,12 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>6,10</t>
+          <t>6,16</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>9.513,299</t>
+          <t>9.484,560</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -12518,22 +12518,22 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>5,10598500</t>
+          <t>5,10871600</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>6,13</t>
+          <t>6,18</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>21.123,983</t>
+          <t>21.165,250</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12757,7 +12757,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>3,18932700</t>
+          <t>3,19102000</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>6,17</t>
+          <t>6,23</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>13.514,438</t>
+          <t>13.583,436</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1.731,25501200</t>
+          <t>1.732,14210600</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -13006,12 +13006,12 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>5,86</t>
+          <t>5,92</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>250,085</t>
+          <t>253,822</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -13034,43 +13034,187 @@
           <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-automatico-polis-rf-cp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr"/>
-      <c r="O54" s="2" t="inlineStr"/>
-      <c r="P54" s="2" t="inlineStr"/>
-      <c r="Q54" s="2" t="inlineStr"/>
-      <c r="R54" s="2" t="inlineStr"/>
-      <c r="S54" s="2" t="inlineStr"/>
-      <c r="T54" s="2" t="inlineStr"/>
-      <c r="U54" s="2" t="inlineStr"/>
-      <c r="V54" s="2" t="inlineStr"/>
-      <c r="W54" s="2" t="inlineStr"/>
-      <c r="X54" s="2" t="inlineStr"/>
-      <c r="Y54" s="2" t="inlineStr"/>
-      <c r="Z54" s="2" t="inlineStr"/>
-      <c r="AA54" s="2" t="inlineStr"/>
-      <c r="AB54" s="2" t="inlineStr"/>
-      <c r="AC54" s="2" t="inlineStr"/>
-      <c r="AD54" s="2" t="inlineStr"/>
-      <c r="AE54" s="2" t="inlineStr"/>
-      <c r="AF54" s="2" t="inlineStr"/>
-      <c r="AG54" s="2" t="inlineStr"/>
-      <c r="AH54" s="2" t="inlineStr"/>
-      <c r="AI54" s="2" t="inlineStr"/>
-      <c r="AJ54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>39.594.941/0001-36</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>6520</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>RF 100% TPF - Curto Prazo</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>Aberto para captação</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>CURTO PRAZO</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>GERAL</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>17h00</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>Sim · Automatico · 100%</t>
+        </is>
+      </c>
+      <c r="AE54" s="2" t="inlineStr">
+        <is>
+          <t>AUTOMATICO</t>
+        </is>
+      </c>
+      <c r="AF54" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG54" s="2" t="inlineStr">
+        <is>
+          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AH54" s="2" t="inlineStr">
+        <is>
+          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AI54" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AJ54" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="AK54" s="2" t="inlineStr"/>
-      <c r="AL54" s="2" t="inlineStr"/>
-      <c r="AM54" s="2" t="inlineStr"/>
-      <c r="AN54" s="2" t="inlineStr"/>
-      <c r="AO54" s="2" t="inlineStr"/>
-      <c r="AP54" s="2" t="inlineStr"/>
-      <c r="AQ54" s="2" t="inlineStr"/>
-      <c r="AR54" s="2" t="inlineStr"/>
-      <c r="AS54" s="2" t="inlineStr"/>
-      <c r="AT54" s="2" t="inlineStr"/>
-      <c r="AU54" s="2" t="inlineStr"/>
-      <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AL54" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AM54" s="2" t="inlineStr">
+        <is>
+          <t>CAIXA FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA CURTO PRAZO - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AN54" s="2" t="inlineStr">
+        <is>
+          <t>*Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).</t>
+        </is>
+      </c>
+      <c r="AO54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AP54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AQ54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AR54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AS54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AT54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AU54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AV54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/6520-SUMARIO.pdf</t>
+        </is>
+      </c>
       <c r="AW54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
@@ -13091,32 +13235,32 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1,41616700</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>-0,007</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>0,39</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>5,77</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>14,27</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>67,810</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -13322,32 +13466,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1.207,25972200</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>-0,002</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>0,30</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>-3,78</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>0,89</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>36,806</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13571,32 +13715,32 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>12,52022900</t>
+          <t>12,52326200</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>0,856</t>
+          <t>0,024</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>-0,51</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,49</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>16,50</t>
+          <t>16,33</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>540,035</t>
+          <t>323,482</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -13666,32 +13810,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1.628,14220100</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>0,822</t>
-        </is>
-      </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>3,90</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>11,91</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>113,900</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -13897,32 +14041,32 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>2.402,29547900</t>
+          <t>2.429,39254100</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>1,029</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>-0,84</t>
+          <t>1,127</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>16,95</t>
+          <t>18,27</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>32,18</t>
+          <t>33,63</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>13,045</t>
+          <t>13,427</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -14359,32 +14503,32 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1,24439000</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>-0,022</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>9,23</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>6,267</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -14594,32 +14738,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1,13379900</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>1,252</t>
+          <t>1,13180900</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>-0,175</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-0,55</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>-2,21</t>
+          <t>-2,38</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>13,22</t>
+          <t>12,71</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>3,634</t>
+          <t>3,628</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -15056,32 +15200,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1,37605900</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>-0,018</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>-3,11</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>0,80</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>13,21</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>11,409</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -15518,32 +15662,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1,11757300</t>
+          <t>1,10700000</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>-0,796</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>0,63</t>
+          <t>-0,946</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>-0,31</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>-7,30</t>
+          <t>-8,18</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>-5,34</t>
+          <t>-7,02</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>3,765</t>
+          <t>3,729</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -15753,32 +15897,32 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>5,31265953</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>0,813</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>3,53</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>11,75</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>32,727</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -15992,32 +16136,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>4,28426100</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>-0,348</t>
+          <t>4,41990600</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>3,166</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>-10,03</t>
+          <t>-7,18</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>-3,57</t>
+          <t>-0,52</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>29,66</t>
+          <t>31,47</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>543,201</t>
+          <t>561,157</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -16231,32 +16375,32 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>2,82704500</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>-0,011</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>-1,26</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>1,21</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>8,72</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>73,165</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -16466,32 +16610,32 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1.691,03715400</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>-0,704</t>
+          <t>1.691,47682200</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>0,025</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>1,63</t>
+          <t>1,66</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>7,33</t>
+          <t>7,36</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>13,60</t>
+          <t>13,56</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>29,690</t>
+          <t>29,701</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -16705,32 +16849,32 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>3,74171300</t>
+          <t>3,76181100</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>1,624</t>
+          <t>0,537</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>-2,27</t>
+          <t>-1,74</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>11,23</t>
+          <t>11,82</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>33,71</t>
+          <t>33,93</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>2.329,193</t>
+          <t>2.342,414</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -16944,32 +17088,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1,90592500</t>
+          <t>1,90788000</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>0,177</t>
+          <t>0,102</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>4,95</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>12,59</t>
+          <t>12,65</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>21,956</t>
+          <t>21,645</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -17183,32 +17327,32 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1.649,84258900</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>0,825</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>4,32</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>12,89</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>14,466</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -17410,32 +17554,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>0,45274716</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>-0,005</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>-14,07</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr">
-        <is>
-          <t>-37,30</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>3,578</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -17652,32 +17796,32 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>3,25681500</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>0,321</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>-0,70</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>2,21</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>9,09</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>155,117</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -17692,12 +17836,12 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>14.239.659/0001-00</t>
+          <t>45.443.651/0001-94</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -17707,7 +17851,7 @@
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="P75" s="4" t="inlineStr">
@@ -17737,17 +17881,17 @@
       </c>
       <c r="U75" s="4" t="inlineStr">
         <is>
-          <t>D+1 (du)</t>
+          <t>D+0 (du)</t>
         </is>
       </c>
       <c r="V75" s="4" t="inlineStr">
         <is>
-          <t>D+03 (du)</t>
+          <t>D+02 (du)</t>
         </is>
       </c>
       <c r="W75" s="4" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>NÃO SE APLICA</t>
         </is>
       </c>
       <c r="X75" s="4" t="inlineStr">
@@ -17772,12 +17916,12 @@
       </c>
       <c r="AB75" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC75" s="4" t="inlineStr">
         <is>
-          <t>17h00</t>
+          <t>16h00</t>
         </is>
       </c>
       <c r="AD75" s="4" t="inlineStr">
@@ -17797,12 +17941,12 @@
       </c>
       <c r="AG75" s="4" t="inlineStr">
         <is>
-          <t>["GOV"]</t>
+          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
         </is>
       </c>
       <c r="AH75" s="4" t="inlineStr">
         <is>
-          <t>["GOV"]</t>
+          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
         </is>
       </c>
       <c r="AI75" s="4" t="inlineStr">
@@ -17817,7 +17961,7 @@
       </c>
       <c r="AK75" s="4" t="inlineStr">
         <is>
-          <t>2027-10-01T00:00:00Z</t>
+          <t>2026-07-01T00:00:00Z</t>
         </is>
       </c>
       <c r="AL75" s="4" t="inlineStr">
@@ -17827,54 +17971,56 @@
       </c>
       <c r="AM75" s="4" t="inlineStr">
         <is>
-          <t>CAIXA CAPITAL PROTEGIDO IBOVESPA CÍCLICO I FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO - RESPOSANBILIDAD</t>
+          <t>CAIXA CAPITAL PROTEGIDO CICLICO II FIC DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AN75" s="4" t="inlineStr">
         <is>
           <t>Fundo com prazo de carência para aplicação e resgate, conforme Regulamento. Durante a carência, não é permitida a realização de aplicações ou resgates.
-Nova operação estruturada com inicio em 02/SET/2025 e termino em 01/OUT/2027. 
-Fundo Fechado a para aplicações a partir de 02/09/2025 (inclusive)</t>
+Fechado para Aplicações e Resgates a partir de 26/08/2024 
+-------
+Início da Operação Estruturada - 27/08/2024
+Fim da Operação Estruturada - 01/07/2026</t>
         </is>
       </c>
       <c r="AO75" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5475.pdf</t>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6623.pdf</t>
         </is>
       </c>
       <c r="AP75" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5475.pdf</t>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6623.pdf</t>
         </is>
       </c>
       <c r="AQ75" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5475.pdf</t>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6623.pdf</t>
         </is>
       </c>
       <c r="AR75" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5475.pdf</t>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_6623.pdf</t>
         </is>
       </c>
       <c r="AS75" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5475.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6623.pdf</t>
         </is>
       </c>
       <c r="AT75" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5475.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6623.pdf</t>
         </is>
       </c>
       <c r="AU75" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5475.pdf</t>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6623.pdf</t>
         </is>
       </c>
       <c r="AV75" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5475-SUMARIO.pdf</t>
+          <t>http://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/6623-SUMARIO.pdf</t>
         </is>
       </c>
       <c r="AW75" s="4" t="inlineStr"/>
@@ -17897,32 +18043,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1,53089000</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>0,591</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>-1,17</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t>2,52</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>19,33</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>14,422</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -18142,32 +18288,32 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1,38042400</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>0,123</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>0,47</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>6,79</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>70,739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -18389,32 +18535,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1,47080400</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>-0,109</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>-2,08</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t>1,70</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>13,39</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>190,705</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -18424,7 +18570,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fim-cap-protegido-ciclico-ii</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fic-capital-protegido-ciclico-ii-multimercado-lp/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -18636,32 +18782,32 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1,78946000</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>-0,002</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>0,50</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>10,68</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>175,837</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -18871,32 +19017,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>5,59967200</t>
+          <t>5,60631700</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>0,602</t>
+          <t>0,118</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,12</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>5,09</t>
+          <t>5,22</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>13,73</t>
+          <t>13,80</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>894,946</t>
+          <t>896,026</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -19110,32 +19256,32 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>3,65251900</t>
+          <t>3,65631800</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>0,179</t>
+          <t>0,104</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>13,00</t>
+          <t>13,06</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>745,849</t>
+          <t>746,101</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -19345,32 +19491,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>6,72431700</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>-0,004</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="inlineStr">
-        <is>
-          <t>-1,66</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="inlineStr">
-        <is>
-          <t>4,55</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>14,47</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>127,058</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -19580,32 +19726,32 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>1,42335000</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>-0,003</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>-0,23</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>3,31</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>14,83</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>281,861</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -19820,32 +19966,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,33967700</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>-0,002</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>1,25</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>4,37</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>3,83</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>13,073</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -20059,32 +20205,32 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>3,81773100</t>
+          <t>3,77803600</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>-0,937</t>
+          <t>-1,039</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>-5,02</t>
+          <t>-6,01</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>-3,38</t>
+          <t>-4,45</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>96,790</t>
+          <t>95,784</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -20298,32 +20444,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>6,67137300</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>1,773</t>
+          <t>6,65128300</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>-0,301</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>4,87</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>21,35</t>
+          <t>20,26</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>327,910</t>
+          <t>326,943</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -20537,32 +20683,32 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>2,55141600</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>1,664</t>
+          <t>2,54603900</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>-0,210</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>-1,30</t>
+          <t>-1,51</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>6,04</t>
+          <t>5,81</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>23,97</t>
+          <t>23,13</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>13,085</t>
+          <t>13,069</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -20577,12 +20723,12 @@
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>01.525.057/0001-77</t>
+          <t>15.154.410/0001-64</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -20592,7 +20738,7 @@
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
@@ -20655,11 +20801,7 @@
           <t>GERAL</t>
         </is>
       </c>
-      <c r="AB87" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
+      <c r="AB87" s="4" t="inlineStr"/>
       <c r="AC87" s="4" t="inlineStr">
         <is>
           <t>17h00</t>
@@ -20708,52 +20850,52 @@
       </c>
       <c r="AM87" s="4" t="inlineStr">
         <is>
-          <t>CAIXA IBOVESPA FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO EM AÇÕES - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA E-FUNDO IBOVESPA FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO EM AÇÕES - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AN87" s="4" t="inlineStr">
         <is>
-          <t>A contagem para conversão de cotas e pagamento do resgate é feita em dias úteis, conforme estabelecido no Regulamento do Fundo.</t>
+          <t>As movimentações neste Fundo são realizadas exclusivamente pelo Internet Banking. A contagem para conversão de cotas e pagamento do resgate é feita em dias úteis, conforme estabelecido no Regulamento do Fundo. Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).</t>
         </is>
       </c>
       <c r="AO87" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0053.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5832.pdf</t>
         </is>
       </c>
       <c r="AP87" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0053.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5832.pdf</t>
         </is>
       </c>
       <c r="AQ87" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0053.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5832.pdf</t>
         </is>
       </c>
       <c r="AR87" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_0053.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5832.pdf</t>
         </is>
       </c>
       <c r="AS87" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_53.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5832.pdf</t>
         </is>
       </c>
       <c r="AT87" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_53.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5832.pdf</t>
         </is>
       </c>
       <c r="AU87" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_0053.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5832.pdf</t>
         </is>
       </c>
       <c r="AV87" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/0053-SUMARIO.pdf</t>
+          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5832-SUMARIO.pdf</t>
         </is>
       </c>
       <c r="AW87" s="4" t="inlineStr"/>
@@ -20776,32 +20918,32 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1.893,57702000</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>2,182</t>
+          <t>1.888,82756500</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>-0,250</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>-1,88</t>
+          <t>-2,12</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>-4,61</t>
+          <t>-4,85</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>11,60</t>
+          <t>10,92</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>9,685</t>
+          <t>9,661</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -21004,32 +21146,32 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>9,95630400</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>0,265</t>
+          <t>9,91461300</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>-0,418</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>-2,90</t>
+          <t>-3,31</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>18,76</t>
+          <t>17,82</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>274,271</t>
+          <t>273,136</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -21243,32 +21385,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1,44388800</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>2,322</t>
+          <t>1,44007700</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>-0,263</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>-1,88</t>
+          <t>-2,14</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>-5,28</t>
+          <t>-5,53</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>-1,03</t>
+          <t>-1,26</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>437,625</t>
+          <t>436,541</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -21482,32 +21624,32 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1,09014700</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>2,462</t>
+          <t>1,08634900</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>-0,348</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>-1,63</t>
+          <t>-1,97</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>-6,34</t>
+          <t>-6,66</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>-3,69</t>
+          <t>-3,89</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>55,973</t>
+          <t>55,778</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -21721,32 +21863,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1,68345000</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>1,639</t>
+          <t>1,67760000</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>-0,347</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>-1,47</t>
+          <t>-1,81</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>-1,23</t>
+          <t>-1,58</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>8,07</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2,082</t>
+          <t>2,075</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -21960,32 +22102,32 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>4,58330500</t>
+          <t>4,52473500</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>-0,026</t>
+          <t>-1,277</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>45,54</t>
+          <t>43,68</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>47,87</t>
+          <t>42,22</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>77,191</t>
+          <t>76,204</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -22199,32 +22341,32 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>8,54688500</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>1,658</t>
+          <t>8,52851900</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>-0,214</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>-1,55</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>5,56</t>
+          <t>5,33</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>22,66</t>
+          <t>21,82</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>85,287</t>
+          <t>85,103</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -22438,32 +22580,32 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1,22522100</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>-0,020</t>
-        </is>
-      </c>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>-3,58</t>
-        </is>
-      </c>
-      <c r="G95" s="6" t="inlineStr">
-        <is>
-          <t>-4,80</t>
-        </is>
-      </c>
-      <c r="H95" s="5" t="inlineStr">
-        <is>
-          <t>3,62</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>277,051</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -22677,32 +22819,32 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>1,82815500</t>
+          <t>1,83119700</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>3,224</t>
+          <t>0,166</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>-1,79</t>
+          <t>-1,63</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>-3,85</t>
+          <t>-3,69</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>14,03</t>
+          <t>15,51</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>111,507</t>
+          <t>111,700</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -22916,32 +23058,32 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>2,87443300</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>1,852</t>
+          <t>2,85358500</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>-0,725</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>-0,63</t>
+          <t>-1,35</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>5,46</t>
+          <t>4,69</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>15,44</t>
+          <t>14,02</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>125,626</t>
+          <t>124,715</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -23155,32 +23297,32 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1,83966400</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>2,173</t>
+          <t>1,83498300</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>-0,254</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>-2,16</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>-5,05</t>
+          <t>-5,29</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>10,36</t>
+          <t>9,68</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>48,525</t>
+          <t>48,402</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -23398,32 +23540,32 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>6,48771000</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>0,254</t>
-        </is>
-      </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>1,06</t>
+          <t>6,40002500</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>-1,351</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>38,32</t>
+          <t>36,45</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>43,99</t>
+          <t>39,05</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>118,683</t>
+          <t>117,088</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -23637,32 +23779,32 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>1.225,80027500</t>
+          <t>1.228,87659800</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>2,139</t>
+          <t>0,250</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>-3,70</t>
+          <t>-3,46</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>-10,32</t>
+          <t>-10,10</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>-8,41</t>
+          <t>-8,26</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>39,689</t>
+          <t>39,901</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -23876,32 +24018,32 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>37,28119700</t>
+          <t>37,45275900</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>1,402</t>
+          <t>0,460</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>-4,90</t>
+          <t>-4,46</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>7,91</t>
+          <t>8,41</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>56,67</t>
+          <t>58,45</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>626,679</t>
+          <t>629,705</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -24115,32 +24257,32 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2,82455500</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>1,575</t>
+          <t>2,81849700</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>-0,214</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>5,22</t>
+          <t>5,00</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>16,60</t>
+          <t>16,35</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>39,18</t>
+          <t>38,32</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>467,882</t>
+          <t>466,941</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -24358,32 +24500,32 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>4,70164000</t>
+          <t>4,71554300</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>2,022</t>
+          <t>0,295</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>-2,25</t>
+          <t>-1,96</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>4,76</t>
+          <t>5,07</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>23,60</t>
+          <t>23,34</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>22,726</t>
+          <t>22,794</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -24597,32 +24739,32 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>1.477,79911600</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>2,357</t>
+          <t>1.477,28512000</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>-0,034</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>-1,73</t>
+          <t>-1,76</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>1,54</t>
+          <t>1,51</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>16,74</t>
+          <t>16,17</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>29,336</t>
+          <t>29,338</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -24836,32 +24978,32 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>1,91439900</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>1,735</t>
+          <t>1,90973200</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>-0,243</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-1,38</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>-5,89</t>
+          <t>-6,12</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>7,23</t>
+          <t>6,55</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>1,727</t>
+          <t>1,723</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -25067,32 +25209,32 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>5,76539900</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>1,605</t>
+          <t>5,75153900</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>-0,240</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>-1,70</t>
+          <t>-1,94</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>7,17</t>
+          <t>6,91</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>25,76</t>
+          <t>24,79</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>42,405</t>
+          <t>42,303</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -25298,32 +25440,32 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>2,18908600</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>2,018</t>
+          <t>2,18682200</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>-0,103</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>-1,05</t>
+          <t>-1,15</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>4,33</t>
+          <t>4,22</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>22,66</t>
+          <t>21,99</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>35,038</t>
+          <t>35,003</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -25537,32 +25679,32 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>42,50886600</t>
+          <t>41,96579100</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>-0,026</t>
+          <t>-1,277</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>45,60</t>
+          <t>43,74</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>47,99</t>
+          <t>42,34</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>844,830</t>
+          <t>834,076</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -25776,32 +25918,32 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>0,83673800</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>0,837</t>
+          <t>0,83409100</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>-0,316</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>-2,65</t>
+          <t>-2,96</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>-13,07</t>
+          <t>-13,35</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>-21,46</t>
+          <t>-21,40</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>2,871</t>
+          <t>2,864</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -26011,32 +26153,32 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>1,18780400</t>
+          <t>1,18843000</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>0,752</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>-0,59</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>-1,84</t>
+          <t>-1,79</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>12,05</t>
+          <t>11,70</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>3,675</t>
+          <t>3,677</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -26246,32 +26388,32 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>1,39526000</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>1,573</t>
+          <t>1,39225800</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>-0,215</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>5,21</t>
+          <t>4,99</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>16,52</t>
+          <t>16,27</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>38,98</t>
+          <t>38,12</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>20,682</t>
+          <t>20,638</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -26485,32 +26627,32 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1,77127400</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>3,453</t>
+          <t>1,76181600</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>-0,533</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-0,79</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>3,03</t>
+          <t>2,48</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>69,68</t>
+          <t>67,85</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>269,601</t>
+          <t>268,165</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -26728,32 +26870,32 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>969,29612000</t>
-        </is>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
-        <is>
-          <t>-0,003</t>
-        </is>
-      </c>
-      <c r="F113" s="6" t="inlineStr">
-        <is>
-          <t>-3,02</t>
-        </is>
-      </c>
-      <c r="G113" s="6" t="inlineStr">
-        <is>
-          <t>-1,12</t>
-        </is>
-      </c>
-      <c r="H113" s="5" t="inlineStr">
-        <is>
-          <t>13,60</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>7,865</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -26967,32 +27109,32 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1.450,43212700</t>
-        </is>
-      </c>
-      <c r="E114" s="7" t="inlineStr">
-        <is>
-          <t>-0,002</t>
-        </is>
-      </c>
-      <c r="F114" s="7" t="inlineStr">
-        <is>
-          <t>-2,99</t>
-        </is>
-      </c>
-      <c r="G114" s="7" t="inlineStr">
-        <is>
-          <t>-3,03</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>7,87</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>20,906</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -27202,32 +27344,32 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>167,42752586</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>1,668</t>
+          <t>167,07500900</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>-0,210</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>-1,25</t>
+          <t>-1,46</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>6,02</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>24,55</t>
+          <t>23,70</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>41,858</t>
+          <t>41,770</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -27441,32 +27583,32 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1,80963100</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>3,410</t>
+          <t>1,80034200</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>-0,513</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-0,82</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>3,06</t>
+          <t>2,53</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>69,94</t>
+          <t>68,14</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>4,951</t>
+          <t>4,925</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -27677,32 +27819,32 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1,76460400</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>3,437</t>
+          <t>1,75550800</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>-0,515</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>-0,30</t>
+          <t>-0,82</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>69,98</t>
+          <t>68,17</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>1.604,862</t>
+          <t>1.596,589</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -27909,32 +28051,32 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>47,29656600</t>
+          <t>46,69341000</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>-0,024</t>
+          <t>-1,275</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>1,60</t>
+          <t>0,30</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>46,03</t>
+          <t>44,17</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>48,83</t>
+          <t>43,14</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>683,079</t>
+          <t>674,368</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -28132,32 +28274,32 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>41,30885400</t>
+          <t>41,50027300</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>1,407</t>
+          <t>0,463</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>-4,89</t>
+          <t>-4,45</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>8,15</t>
+          <t>8,65</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>57,51</t>
+          <t>59,30</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>743,123</t>
+          <t>746,566</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -28355,32 +28497,32 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>16,25501100</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>2,170</t>
+          <t>16,19869400</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>-0,346</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>-1,19</t>
+          <t>-1,53</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>-3,62</t>
+          <t>-3,95</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>12,29</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>112,049</t>
+          <t>111,660</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -28587,32 +28729,32 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>34,62577100</t>
+          <t>34,78451100</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>1,398</t>
+          <t>0,458</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>-4,91</t>
+          <t>-4,48</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>7,90</t>
+          <t>8,40</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>56,40</t>
+          <t>58,17</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>11,811</t>
+          <t>11,865</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
@@ -28815,32 +28957,32 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>41,78456600</t>
+          <t>41,25122500</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>-0,026</t>
+          <t>-1,276</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>45,74</t>
+          <t>43,88</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>48,16</t>
+          <t>42,49</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>589,141</t>
+          <t>581,621</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -29043,32 +29185,32 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>35,56313600</t>
+          <t>35,72717400</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>1,405</t>
+          <t>0,461</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>-4,90</t>
+          <t>-4,46</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>7,92</t>
+          <t>8,42</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>56,69</t>
+          <t>58,47</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>446,499</t>
+          <t>448,559</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -29266,32 +29408,32 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>44,43171300</t>
+          <t>43,86371800</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>-0,025</t>
+          <t>-1,278</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>45,90</t>
+          <t>44,04</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>48,51</t>
+          <t>42,83</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>675,946</t>
+          <t>667,305</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -29493,7 +29635,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>1,12708900</t>
+          <t>1,12761900</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -29503,12 +29645,12 @@
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>5,39</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -29518,7 +29660,7 @@
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>57,976</t>
+          <t>57,693</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
@@ -29731,7 +29873,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>1,36023100</t>
+          <t>1,36087300</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -29741,12 +29883,12 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>5,44</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
@@ -29756,7 +29898,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>272,044</t>
+          <t>273,172</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -29973,22 +30115,22 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>5,90032300</t>
+          <t>5,90337500</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>5,83</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -29998,7 +30140,7 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>40,821</t>
+          <t>40,895</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -30213,7 +30355,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>5,13555200</t>
+          <t>5,13819300</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -30223,12 +30365,12 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>6,01</t>
+          <t>6,07</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
@@ -30238,7 +30380,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>788,015</t>
+          <t>788,420</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -30449,7 +30591,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>3,22605000</t>
+          <t>3,22768900</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -30459,12 +30601,12 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>5,85</t>
+          <t>5,90</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -30474,7 +30616,7 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>18,435</t>
+          <t>19,404</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -30690,32 +30832,32 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>23,70373500</t>
+          <t>23,74203200</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>0,464</t>
+          <t>0,161</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>-0,20</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>6,04</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>11,95</t>
+          <t>11,96</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>94,127</t>
+          <t>94,279</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -30933,22 +31075,22 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>3,28092000</t>
+          <t>3,28259200</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>5,90</t>
+          <t>5,95</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -30958,7 +31100,7 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>7.867,230</t>
+          <t>8.116,732</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -31171,22 +31313,22 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>1.891,23419400</t>
+          <t>1.892,27004800</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>0,057</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,50</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>6,24</t>
+          <t>6,30</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
@@ -31196,7 +31338,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>16.080,285</t>
+          <t>16.099,200</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -31410,22 +31552,22 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>4,89026200</t>
+          <t>4,89295300</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>0,065</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>6,06</t>
+          <t>6,12</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -31435,7 +31577,7 @@
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>3.063,513</t>
+          <t>3.007,320</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -31649,7 +31791,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1,55310341</t>
+          <t>1,55391800</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -31659,22 +31801,22 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>6,09</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>14,68</t>
+          <t>14,67</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>372,075</t>
+          <t>369,850</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -31872,7 +32014,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>5,13755500</t>
+          <t>5,14024000</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -31882,12 +32024,12 @@
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>6,12</t>
+          <t>6,17</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -31897,7 +32039,7 @@
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>285,588</t>
+          <t>285,737</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -32108,22 +32250,22 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>8,73005900</t>
+          <t>8,73496700</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>0,068</t>
+          <t>0,056</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>6,01</t>
+          <t>6,07</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
@@ -32133,7 +32275,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>3.960,420</t>
+          <t>3.962,335</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -32335,22 +32477,22 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>17,95790600</t>
+          <t>17,96785000</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>0,065</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>6,07</t>
+          <t>6,13</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -32360,7 +32502,7 @@
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>4.765,563</t>
+          <t>4.768,060</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -32558,7 +32700,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>2,83158200</t>
+          <t>2,83292400</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
@@ -32568,12 +32710,12 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>5,49</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
@@ -32583,7 +32725,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>13.461,277</t>
+          <t>13.781,689</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -32796,7 +32938,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>4,44016300</t>
+          <t>4,44250500</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -32806,12 +32948,12 @@
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>6,14</t>
+          <t>6,19</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -32821,7 +32963,7 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>13.477,285</t>
+          <t>13.293,626</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -33035,7 +33177,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>1,37775600</t>
+          <t>1,37849600</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -33045,12 +33187,12 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>6,20</t>
+          <t>6,26</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
@@ -33060,7 +33202,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.504,575</t>
+          <t>3.515,620</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -33270,7 +33412,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>1.777,05855400</t>
+          <t>1.777,99684200</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -33280,12 +33422,12 @@
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>6,04</t>
+          <t>6,10</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -33295,7 +33437,7 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>1.436,041</t>
+          <t>1.439,288</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -33509,32 +33651,32 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>1,31077100</t>
+          <t>1,31134000</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>4,93</t>
+          <t>4,98</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>11,59</t>
+          <t>11,60</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>32.754,545</t>
+          <t>32.821,865</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -33745,7 +33887,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>9,42502100</t>
+          <t>9,42941000</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -33755,22 +33897,22 @@
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>12,48</t>
+          <t>12,49</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>2.830,268</t>
+          <t>2.831,498</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
@@ -33983,7 +34125,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>2,48215400</t>
+          <t>2,48330600</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -33993,12 +34135,12 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
@@ -34008,7 +34150,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>16.473,181</t>
+          <t>16.487,897</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -34223,22 +34365,22 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>2,61336000</t>
+          <t>2,61477700</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>0,061</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>6,11</t>
+          <t>6,17</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -34248,7 +34390,7 @@
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>9.191,806</t>
+          <t>9.199,850</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
@@ -34466,32 +34608,32 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>2,39309500</t>
+          <t>2,39782000</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>0,564</t>
+          <t>0,197</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>4,11</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>11,94</t>
+          <t>12,07</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>3.613,292</t>
+          <t>3.618,444</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -34710,32 +34852,32 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>2,97564600</t>
+          <t>2,98068700</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>0,511</t>
+          <t>0,169</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>5,51</t>
+          <t>5,69</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>11,64</t>
+          <t>11,67</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>40,203</t>
+          <t>40,121</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
@@ -34945,32 +35087,32 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1.640,52151300</t>
+          <t>1.642,09004800</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>0,231</t>
-        </is>
-      </c>
-      <c r="F148" s="7" t="inlineStr">
-        <is>
-          <t>-0,07</t>
+          <t>0,095</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>0,02</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>4,53</t>
+          <t>4,63</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>11,75</t>
+          <t>11,72</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>460,193</t>
+          <t>460,633</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -35184,32 +35326,32 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>4,48485200</t>
+          <t>4,48700900</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>0,103</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>5,69</t>
+          <t>5,74</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>14,11</t>
+          <t>14,09</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>10.979,787</t>
+          <t>10.995,933</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
@@ -35430,32 +35572,32 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>3,80612900</t>
+          <t>3,81374400</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>0,429</t>
+          <t>0,200</t>
         </is>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>5,73</t>
+          <t>5,94</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>12,22</t>
+          <t>12,32</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2.995,250</t>
+          <t>3.003,772</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -35672,32 +35814,32 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>3,61057700</t>
+          <t>3,62017000</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>0,789</t>
+          <t>0,265</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-0,46</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>3,42</t>
+          <t>3,70</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>11,69</t>
+          <t>11,97</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>1.734,214</t>
+          <t>1.730,392</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
@@ -35918,32 +36060,32 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>5,14326700</t>
+          <t>5,16020000</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>1,402</t>
+          <t>0,329</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>-0,45</t>
+          <t>-0,12</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>4,60</t>
+          <t>4,94</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>10,33</t>
+          <t>10,66</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2.578,964</t>
+          <t>2.588,227</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -36159,32 +36301,32 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>5,17129400</t>
+          <t>5,17958500</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>0,463</t>
+          <t>0,160</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>-0,20</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>5,93</t>
+          <t>6,10</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>12,11</t>
+          <t>12,12</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>5.553,196</t>
+          <t>5.569,991</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
@@ -36400,32 +36542,32 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>4,74581100</t>
+          <t>4,75373800</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>0,541</t>
-        </is>
-      </c>
-      <c r="F154" s="7" t="inlineStr">
-        <is>
-          <t>-0,05</t>
+          <t>0,167</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>0,11</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>5,14</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>12,96</t>
+          <t>13,11</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>513,974</t>
+          <t>517,562</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -36641,22 +36783,22 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>7,96492200</t>
+          <t>7,96922500</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>0,065</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>6,00</t>
+          <t>6,06</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
@@ -36666,7 +36808,7 @@
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>176,752</t>
+          <t>174,798</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
@@ -36736,32 +36878,32 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>3,45444000</t>
+          <t>3,47036200</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>2,168</t>
+          <t>0,460</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>-0,19</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>4,01</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>8,95</t>
+          <t>9,50</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>770,704</t>
+          <t>774,257</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -36977,32 +37119,32 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>3,73073700</t>
+          <t>3,74390100</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>1,065</t>
+          <t>0,352</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-0,79</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>2,95</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>10,75</t>
+          <t>11,15</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>715,768</t>
+          <t>718,385</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
@@ -37223,22 +37365,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>7,18956900</t>
+          <t>7,19347900</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>0,063</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>6,04</t>
+          <t>6,10</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
@@ -37248,7 +37390,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>13.200,017</t>
+          <t>13.113,026</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -37263,12 +37405,12 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>03.737.206/0001-97</t>
+          <t>05.164.356/0001-84</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -37323,7 +37465,7 @@
       </c>
       <c r="X158" s="2" t="inlineStr">
         <is>
-          <t>RF DI até 49% Crédito Privado</t>
+          <t>RF 100% TPF - Longo Prazo</t>
         </is>
       </c>
       <c r="Y158" s="2" t="inlineStr">
@@ -37394,58 +37536,57 @@
       </c>
       <c r="AM158" s="2" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA REFERENCIADO DI LONGO PRAZO - RESP LIMITADA</t>
+          <t>CAIXA BRASIL TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AN158" s="2" t="inlineStr">
         <is>
-          <t>1. Para aplicação por meio de conta operação 003, é necessário o cadastramento prévio de cotistas, conforme descrito no item Adesão, do FI612.
-2. O procedimento de inclusão da conta deverá ser realizado sempre que houver qualquer aplicação por meio de conta operação 003, mesmo para os clientes que já realizaram o cadastramento anteriormente.</t>
+          <t>Para aplicação no fundo é necessário o cadastramento prévio de cotistas, conforme descrito no FI657. O procedimento de inclusão da conta deverá ser realizado sempre que houver qualquer aplicação, mesmo para os clientes que já realizaram o cadsatramento anteriormente.</t>
         </is>
       </c>
       <c r="AO158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5404.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5462.pdf</t>
         </is>
       </c>
       <c r="AP158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5404.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5462.pdf</t>
         </is>
       </c>
       <c r="AQ158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5404.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5462.pdf</t>
         </is>
       </c>
       <c r="AR158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5404.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5462.pdf</t>
         </is>
       </c>
       <c r="AS158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5404.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5462.pdf</t>
         </is>
       </c>
       <c r="AT158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5404.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5462.pdf</t>
         </is>
       </c>
       <c r="AU158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5404.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5462.pdf</t>
         </is>
       </c>
       <c r="AV158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5404-SUMARIO.pdf</t>
+          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5462-SUMARIO.pdf</t>
         </is>
       </c>
       <c r="AW158" s="2" t="inlineStr">
         <is>
-          <t>https://web.microsoftstream.com/video/f88f1fc7-aac3-44df-a2a5-ce3ac05edfb3?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
+          <t>https://web.microsoftstream.com/video/91aaf70b-85c2-4cf1-b537-e42b3bd894ec?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
     </row>
@@ -37467,7 +37608,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>7,51029700</t>
+          <t>7,51424000</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -37477,12 +37618,12 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>6,01</t>
+          <t>6,06</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
@@ -37492,7 +37633,7 @@
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>4.043,170</t>
+          <t>4.005,079</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -37706,32 +37847,32 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>1,43573000</t>
+          <t>1,43854400</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>0,721</t>
+          <t>0,195</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-0,58</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>3,17</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>11,22</t>
+          <t>11,40</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>168,613</t>
+          <t>168,943</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
@@ -37941,22 +38082,22 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>3,14656100</t>
+          <t>3,14813300</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>5,69</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
@@ -37966,7 +38107,7 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>1.567,761</t>
+          <t>1.568,519</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
@@ -38178,7 +38319,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>6,73687100</t>
+          <t>6,74043300</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
@@ -38188,12 +38329,12 @@
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>6,20</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
@@ -38203,7 +38344,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>24.107,753</t>
+          <t>24.067,652</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -38273,32 +38414,32 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>5,51192300</t>
+          <t>5,53020900</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>1,457</t>
+          <t>0,331</t>
         </is>
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>4,86</t>
+          <t>5,21</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>10,52</t>
+          <t>10,87</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>592,118</t>
+          <t>594,082</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
@@ -38744,32 +38885,32 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>3,84720300</t>
-        </is>
-      </c>
-      <c r="E165" s="5" t="inlineStr">
-        <is>
-          <t>1,672</t>
+          <t>3,83912000</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>-0,210</t>
         </is>
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>-1,30</t>
+          <t>-1,50</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>6,03</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>24,57</t>
+          <t>23,71</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>282,888</t>
+          <t>282,305</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
@@ -38784,12 +38925,12 @@
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
-          <t>13.058.816/0001-18</t>
+          <t>15.154.236/0001-50</t>
         </is>
       </c>
       <c r="M165" s="4" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="N165" s="4" t="inlineStr">
@@ -38849,7 +38990,7 @@
       </c>
       <c r="Y165" s="4" t="inlineStr">
         <is>
-          <t>Aberto para captação</t>
+          <t>Fechado para captação</t>
         </is>
       </c>
       <c r="Z165" s="4" t="inlineStr">
@@ -38915,48 +39056,52 @@
       </c>
       <c r="AM165" s="4" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL INDEXA IBOVESPA FUNDO DE INVESTIMENTO FINANCEIRO EM AÇÕES - RESPONSABILIDADE LIMITADA</t>
-        </is>
-      </c>
-      <c r="AN165" s="4" t="inlineStr"/>
+          <t>CAIXA BRASIL ETF IBOVESPA FUNDO DE INVESTIMENTO FINANCEIRO EM AÇÕES - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AN165" s="4" t="inlineStr">
+        <is>
+          <t>Fundo fechado para novas aplicações, a novos investidores e cotistas atuais a partir de 03/04/2023 (inclusive)</t>
+        </is>
+      </c>
       <c r="AO165" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5445.pdf</t>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5842.pdf</t>
         </is>
       </c>
       <c r="AP165" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5445.pdf</t>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5842.pdf</t>
         </is>
       </c>
       <c r="AQ165" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5445.pdf</t>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5842.pdf</t>
         </is>
       </c>
       <c r="AR165" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5445.pdf</t>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5842.pdf</t>
         </is>
       </c>
       <c r="AS165" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5445.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5842.pdf</t>
         </is>
       </c>
       <c r="AT165" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5445.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5842.pdf</t>
         </is>
       </c>
       <c r="AU165" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5445.pdf</t>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5842.pdf</t>
         </is>
       </c>
       <c r="AV165" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5445-SUMARIO.pdf</t>
+          <t>http://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5842-SUMARIO.pdf</t>
         </is>
       </c>
       <c r="AW165" s="4" t="inlineStr"/>
@@ -38979,32 +39124,32 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>3,53721500</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>1,680</t>
+          <t>3,52943300</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>-0,220</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>-1,26</t>
+          <t>-1,48</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>6,09</t>
+          <t>5,86</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>24,11</t>
+          <t>23,26</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>8,950</t>
+          <t>8,931</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -39218,32 +39363,32 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>11,16157100</t>
-        </is>
-      </c>
-      <c r="E167" s="5" t="inlineStr">
-        <is>
-          <t>0,269</t>
+          <t>11,11490200</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>-0,418</t>
         </is>
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>-2,90</t>
+          <t>-3,30</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
         <is>
-          <t>19,72</t>
+          <t>18,77</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>2.297,334</t>
+          <t>2.287,569</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
@@ -39457,32 +39602,32 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>1,97970400</t>
-        </is>
-      </c>
-      <c r="E168" s="3" t="inlineStr">
-        <is>
-          <t>1,784</t>
+          <t>1,97704700</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>-0,134</t>
         </is>
       </c>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>-1,20</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>4,44</t>
+          <t>4,30</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>21,29</t>
+          <t>20,55</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>195,423</t>
+          <t>195,161</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -39692,32 +39837,32 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>1,96877000</t>
-        </is>
-      </c>
-      <c r="E169" s="5" t="inlineStr">
-        <is>
-          <t>2,180</t>
+          <t>1,96374600</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>-0,255</t>
         </is>
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>-2,16</t>
         </is>
       </c>
       <c r="G169" s="6" t="inlineStr">
         <is>
-          <t>-5,03</t>
+          <t>-5,28</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
         <is>
-          <t>10,63</t>
+          <t>9,99</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>742,739</t>
+          <t>740,843</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
@@ -39931,32 +40076,32 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>3,40468304</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="inlineStr">
-        <is>
-          <t>1,886</t>
+          <t>3,39992000</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>-0,139</t>
         </is>
       </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>-0,40</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>4,65</t>
+          <t>4,50</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>19,96</t>
+          <t>19,14</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>1.305,618</t>
+          <t>1.303,791</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -40162,32 +40307,32 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>2,45761211</t>
-        </is>
-      </c>
-      <c r="E171" s="5" t="inlineStr">
-        <is>
-          <t>1,856</t>
+          <t>2,45068700</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>-0,281</t>
         </is>
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>-1,26</t>
+          <t>-1,54</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>3,68</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>20,32</t>
+          <t>19,42</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>752,271</t>
+          <t>750,152</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
@@ -40393,32 +40538,32 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>3,75137600</t>
+          <t>3,75335000</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>0,116</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>5,65</t>
+          <t>5,70</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>14,13</t>
+          <t>14,12</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>5.374,111</t>
+          <t>5.377,605</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -809,7 +809,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>408,242</t>
+          <t>405,891</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.675,758</t>
+          <t>6.599,761</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>982,612</t>
+          <t>971,966</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>119,869</t>
+          <t>119,868</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>96,756</t>
+          <t>96,673</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>40.194.309/0001-84</t>
+          <t>40.194.314/0001-97</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1890,27 +1890,27 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="T7" s="4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AA7" s="4" t="inlineStr">
         <is>
-          <t>GERAL</t>
+          <t>QUALIFICADO</t>
         </is>
       </c>
       <c r="AB7" s="4" t="inlineStr">
@@ -2006,48 +2006,52 @@
       </c>
       <c r="AM7" s="4" t="inlineStr">
         <is>
-          <t>CAIXA PLUS FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA CRÉDITO PRIVADO LONGO PRAZO - RESP LIMITADA</t>
-        </is>
-      </c>
-      <c r="AN7" s="4" t="inlineStr"/>
+          <t>CAIXA PLUS QUALIFICADO FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA CRÉDITO PRIVADO LP - RESP LIMITADA</t>
+        </is>
+      </c>
+      <c r="AN7" s="4" t="inlineStr">
+        <is>
+          <t>OBS: Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).</t>
+        </is>
+      </c>
       <c r="AO7" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6532.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6533.pdf</t>
         </is>
       </c>
       <c r="AP7" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6532.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6533.pdf</t>
         </is>
       </c>
       <c r="AQ7" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6532.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6533.pdf</t>
         </is>
       </c>
       <c r="AR7" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6532.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6533.pdf</t>
         </is>
       </c>
       <c r="AS7" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6532.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6533.pdf</t>
         </is>
       </c>
       <c r="AT7" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6532.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6533.pdf</t>
         </is>
       </c>
       <c r="AU7" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6532.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6533.pdf</t>
         </is>
       </c>
       <c r="AV7" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/6532-SUMARIO.pdf</t>
+          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/6533-SUMARIO.pdf</t>
         </is>
       </c>
       <c r="AW7" s="4" t="inlineStr"/>
@@ -2095,7 +2099,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>582,977</t>
+          <t>582,976</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2569,7 +2573,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1.665,658</t>
+          <t>1.665,645</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3047,7 +3051,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,636</t>
+          <t>27,602</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3062,12 +3066,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>03.191.874/0001-61</t>
+          <t>09.548.729/0001-71</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3077,27 +3081,27 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100000.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10000.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -3117,7 +3121,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>IPCA+6%</t>
+          <t>NÃO SE APLICA</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
@@ -3167,12 +3171,12 @@
       </c>
       <c r="AG12" s="2" t="inlineStr">
         <is>
-          <t>["Institucional", "PJ Atacado"]</t>
+          <t>["Pessoa Física"]</t>
         </is>
       </c>
       <c r="AH12" s="2" t="inlineStr">
         <is>
-          <t>["Institucional", "PJ Atacado"]</t>
+          <t>["Pessoa Física"]</t>
         </is>
       </c>
       <c r="AI12" s="2" t="inlineStr">
@@ -3193,7 +3197,7 @@
       </c>
       <c r="AM12" s="2" t="inlineStr">
         <is>
-          <t>CAIXA PATRIMÔNIO ÍNDICE DE PREÇOS FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESP LIMITADA</t>
+          <t>CAIXA FOCO ÍNDICE DE PREÇOS FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESP LIMITADA</t>
         </is>
       </c>
       <c r="AN12" s="2" t="inlineStr">
@@ -3203,47 +3207,47 @@
       </c>
       <c r="AO12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0046.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5414.pdf</t>
         </is>
       </c>
       <c r="AP12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0046.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5414.pdf</t>
         </is>
       </c>
       <c r="AQ12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0046.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5414.pdf</t>
         </is>
       </c>
       <c r="AR12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_46.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5414.pdf</t>
         </is>
       </c>
       <c r="AS12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_46.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5414.pdf</t>
         </is>
       </c>
       <c r="AT12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_46.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5414.pdf</t>
         </is>
       </c>
       <c r="AU12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_0046.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5414.pdf</t>
         </is>
       </c>
       <c r="AV12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/0046-SUMARIO.pdf</t>
+          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5414-SUMARIO.pdf</t>
         </is>
       </c>
       <c r="AW12" s="2" t="inlineStr">
         <is>
-          <t>https://web.microsoftstream.com/video/140b7682-00df-491d-b451-73ae70a040fa?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
+          <t>https://web.microsoftstream.com/video/a5ab94de-1f04-4f00-87d2-ffa0c6babbaf?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3773,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>78,480</t>
+          <t>78,270</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -4486,7 +4490,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>135,107</t>
+          <t>135,106</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4729,7 +4733,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1.778,480</t>
+          <t>1.763,912</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -4960,7 +4964,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2.192,110</t>
+          <t>2.192,107</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5682,7 +5686,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>950,542</t>
+          <t>950,541</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -5896,32 +5900,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,11213849</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>-0,20</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>3,10</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>205,303</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6131,32 +6135,32 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,24146100</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>0,42</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>5,99</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>14,53</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>71,379</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -6387,7 +6391,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>175,519</t>
+          <t>175,488</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6840,32 +6844,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,04048600</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>0,42</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>6,11</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21,972</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7063,32 +7067,32 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,17181800</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>0,56</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>5,52</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>13,98</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>66,553</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -7294,32 +7298,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,07566699</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>0,60</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>4,09</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>305,785</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7773,7 +7777,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>851,906</t>
+          <t>851,782</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8012,7 +8016,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.270,411</t>
+          <t>3.270,389</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -8478,7 +8482,7 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>3.109,343</t>
+          <t>3.109,338</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -8713,7 +8717,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>123,284</t>
+          <t>123,161</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8948,7 +8952,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>586,365</t>
+          <t>586,364</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -9427,7 +9431,7 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>391,367</t>
+          <t>391,366</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -9666,7 +9670,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2.369,327</t>
+          <t>2.369,324</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9905,7 +9909,7 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>545,808</t>
+          <t>545,807</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -10145,7 +10149,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15.579,370</t>
+          <t>15.579,204</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10388,7 +10392,7 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>1.391,015</t>
+          <t>1.391,014</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -10855,7 +10859,7 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>163,978</t>
+          <t>163,975</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -11098,7 +11102,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6.013,350</t>
+          <t>5.953,859</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11335,7 +11339,7 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>2.212,006</t>
+          <t>2.211,981</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -12061,7 +12065,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15.996,953</t>
+          <t>15.996,852</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12300,7 +12304,7 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>9.484,560</t>
+          <t>9.484,514</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -12543,7 +12547,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>21.165,250</t>
+          <t>21.165,088</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12782,7 +12786,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>13.583,436</t>
+          <t>13.583,393</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -13034,187 +13038,43 @@
           <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-automatico-polis-rf-cp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>39.594.941/0001-36</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>6520</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>Conservador</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="T54" s="2" t="inlineStr">
-        <is>
-          <t>D+0 (du)</t>
-        </is>
-      </c>
-      <c r="U54" s="2" t="inlineStr">
-        <is>
-          <t>D+0 (du)</t>
-        </is>
-      </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>D+00 (du)</t>
-        </is>
-      </c>
-      <c r="W54" s="2" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="X54" s="2" t="inlineStr">
-        <is>
-          <t>RF 100% TPF - Curto Prazo</t>
-        </is>
-      </c>
-      <c r="Y54" s="2" t="inlineStr">
-        <is>
-          <t>Aberto para captação</t>
-        </is>
-      </c>
-      <c r="Z54" s="2" t="inlineStr">
-        <is>
-          <t>CURTO PRAZO</t>
-        </is>
-      </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>GERAL</t>
-        </is>
-      </c>
-      <c r="AB54" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>17h00</t>
-        </is>
-      </c>
-      <c r="AD54" s="2" t="inlineStr">
-        <is>
-          <t>Sim · Automatico · 100%</t>
-        </is>
-      </c>
-      <c r="AE54" s="2" t="inlineStr">
-        <is>
-          <t>AUTOMATICO</t>
-        </is>
-      </c>
-      <c r="AF54" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG54" s="2" t="inlineStr">
-        <is>
-          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
-        </is>
-      </c>
-      <c r="AH54" s="2" t="inlineStr">
-        <is>
-          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
-        </is>
-      </c>
-      <c r="AI54" s="2" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AJ54" s="2" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr"/>
+      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr"/>
+      <c r="AE54" s="2" t="inlineStr"/>
+      <c r="AF54" s="2" t="inlineStr"/>
+      <c r="AG54" s="2" t="inlineStr"/>
+      <c r="AH54" s="2" t="inlineStr"/>
+      <c r="AI54" s="2" t="inlineStr"/>
+      <c r="AJ54" s="2" t="inlineStr"/>
       <c r="AK54" s="2" t="inlineStr"/>
-      <c r="AL54" s="2" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AM54" s="2" t="inlineStr">
-        <is>
-          <t>CAIXA FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA CURTO PRAZO - RESPONSABILIDADE LIMITADA</t>
-        </is>
-      </c>
-      <c r="AN54" s="2" t="inlineStr">
-        <is>
-          <t>*Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).</t>
-        </is>
-      </c>
-      <c r="AO54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6520.pdf</t>
-        </is>
-      </c>
-      <c r="AP54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6520.pdf</t>
-        </is>
-      </c>
-      <c r="AQ54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6520.pdf</t>
-        </is>
-      </c>
-      <c r="AR54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6520.pdf</t>
-        </is>
-      </c>
-      <c r="AS54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6520.pdf</t>
-        </is>
-      </c>
-      <c r="AT54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6520.pdf</t>
-        </is>
-      </c>
-      <c r="AU54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6520.pdf</t>
-        </is>
-      </c>
-      <c r="AV54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/6520-SUMARIO.pdf</t>
-        </is>
-      </c>
+      <c r="AL54" s="2" t="inlineStr"/>
+      <c r="AM54" s="2" t="inlineStr"/>
+      <c r="AN54" s="2" t="inlineStr"/>
+      <c r="AO54" s="2" t="inlineStr"/>
+      <c r="AP54" s="2" t="inlineStr"/>
+      <c r="AQ54" s="2" t="inlineStr"/>
+      <c r="AR54" s="2" t="inlineStr"/>
+      <c r="AS54" s="2" t="inlineStr"/>
+      <c r="AT54" s="2" t="inlineStr"/>
+      <c r="AU54" s="2" t="inlineStr"/>
+      <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
@@ -13235,32 +13095,32 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,41687500</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>0,049</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>0,44</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>5,82</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>14,26</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>67,794</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -13466,32 +13326,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.196,86800100</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>-0,002</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>-0,56</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>-4,61</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>0,02</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36,489</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13740,7 +13600,7 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>323,482</t>
+          <t>540,035</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -13810,32 +13670,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.628,04128700</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>-0,006</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>-0,55</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>3,89</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>11,83</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>113,885</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -13850,12 +13710,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>34.660.276/0001-18</t>
+          <t>34.660.333/0001-69</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -13940,23 +13800,27 @@
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Sim · Automatico · 100%</t>
         </is>
       </c>
       <c r="AE58" s="2" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
-        </is>
-      </c>
-      <c r="AF58" s="2" t="inlineStr"/>
+          <t>AUTOMATICO</t>
+        </is>
+      </c>
+      <c r="AF58" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AG58" s="2" t="inlineStr">
         <is>
-          <t>["GOV", "RPPS"]</t>
+          <t>["Pessoa Física", "Private"]</t>
         </is>
       </c>
       <c r="AH58" s="2" t="inlineStr">
         <is>
-          <t>["GOV", "RPPS"]</t>
+          <t>["Pessoa Física", "Private"]</t>
         </is>
       </c>
       <c r="AI58" s="2" t="inlineStr">
@@ -13977,48 +13841,48 @@
       </c>
       <c r="AM58" s="2" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL ESTRATÉGIA LIVRE FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESPONSABILIDADE</t>
+          <t>CAIXA ESTRATÉGIA LIVRE FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESPONSABILIDADE LIMITA</t>
         </is>
       </c>
       <c r="AN58" s="2" t="inlineStr"/>
       <c r="AO58" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6439.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6440.pdf</t>
         </is>
       </c>
       <c r="AP58" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6439.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6440.pdf</t>
         </is>
       </c>
       <c r="AQ58" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6439.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6440.pdf</t>
         </is>
       </c>
       <c r="AR58" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6439.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6440.pdf</t>
         </is>
       </c>
       <c r="AS58" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6439.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6440.pdf</t>
         </is>
       </c>
       <c r="AT58" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6439.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6440.pdf</t>
         </is>
       </c>
       <c r="AU58" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6439.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6440.pdf</t>
         </is>
       </c>
       <c r="AV58" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/6439-SUMARIO.pdf</t>
+          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/6440-SUMARIO.pdf</t>
         </is>
       </c>
       <c r="AW58" s="2" t="inlineStr"/>
@@ -14503,32 +14367,32 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,24946500</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>-0,005</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>-0,16</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>2,30</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>9,79</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6,293</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -15200,32 +15064,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,39551400</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>-0,004</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>-1,74</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>2,23</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>14,69</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11,570</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -15687,7 +15551,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>3,729</t>
+          <t>3,705</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -15897,32 +15761,32 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>5,31247165</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>-0,45</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>3,53</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>11,68</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32,632</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -16161,7 +16025,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>561,157</t>
+          <t>554,596</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -16375,32 +16239,32 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>2,84200700</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>-0,013</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>-0,73</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>1,75</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>9,10</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>73,553</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -16874,7 +16738,7 @@
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>2.342,414</t>
+          <t>2.341,499</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -17113,7 +16977,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>21,645</t>
+          <t>21,644</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -17327,32 +17191,32 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.649,79185500</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>-0,51</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>4,31</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>12,80</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14,434</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -17554,32 +17418,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0,45956255</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>-0,005</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>-12,77</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>-36,35</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,631</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -17796,32 +17660,32 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>3,25662600</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>-0,005</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>-0,70</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>2,21</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>8,55</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>155,108</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -17836,145 +17700,882 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
+          <t>14.239.659/0001-00</t>
+        </is>
+      </c>
+      <c r="M75" s="4" t="inlineStr">
+        <is>
+          <t>5475</t>
+        </is>
+      </c>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="O75" s="4" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="P75" s="4" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="Q75" s="4" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R75" s="4" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="S75" s="4" t="inlineStr">
+        <is>
+          <t>4000.0</t>
+        </is>
+      </c>
+      <c r="T75" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="U75" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="V75" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
+      <c r="W75" s="4" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="X75" s="4" t="inlineStr">
+        <is>
+          <t>Capital Protegido</t>
+        </is>
+      </c>
+      <c r="Y75" s="4" t="inlineStr">
+        <is>
+          <t>Fechado para captação</t>
+        </is>
+      </c>
+      <c r="Z75" s="4" t="inlineStr">
+        <is>
+          <t>LONGO PRAZO</t>
+        </is>
+      </c>
+      <c r="AA75" s="4" t="inlineStr">
+        <is>
+          <t>GERAL</t>
+        </is>
+      </c>
+      <c r="AB75" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC75" s="4" t="inlineStr">
+        <is>
+          <t>17h00</t>
+        </is>
+      </c>
+      <c r="AD75" s="4" t="inlineStr">
+        <is>
+          <t>Sim · Automatico · 100%</t>
+        </is>
+      </c>
+      <c r="AE75" s="4" t="inlineStr">
+        <is>
+          <t>AUTOMATICO</t>
+        </is>
+      </c>
+      <c r="AF75" s="4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG75" s="4" t="inlineStr">
+        <is>
+          <t>["GOV"]</t>
+        </is>
+      </c>
+      <c r="AH75" s="4" t="inlineStr">
+        <is>
+          <t>["GOV"]</t>
+        </is>
+      </c>
+      <c r="AI75" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AJ75" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AK75" s="4" t="inlineStr">
+        <is>
+          <t>2027-10-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="AL75" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AM75" s="4" t="inlineStr">
+        <is>
+          <t>CAIXA CAPITAL PROTEGIDO IBOVESPA CÍCLICO I FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO - RESPOSANBILIDAD</t>
+        </is>
+      </c>
+      <c r="AN75" s="4" t="inlineStr">
+        <is>
+          <t>Fundo com prazo de carência para aplicação e resgate, conforme Regulamento. Durante a carência, não é permitida a realização de aplicações ou resgates.
+Nova operação estruturada com inicio em 02/SET/2025 e termino em 01/OUT/2027. 
+Fundo Fechado a para aplicações a partir de 02/09/2025 (inclusive)</t>
+        </is>
+      </c>
+      <c r="AO75" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5475.pdf</t>
+        </is>
+      </c>
+      <c r="AP75" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5475.pdf</t>
+        </is>
+      </c>
+      <c r="AQ75" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5475.pdf</t>
+        </is>
+      </c>
+      <c r="AR75" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5475.pdf</t>
+        </is>
+      </c>
+      <c r="AS75" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5475.pdf</t>
+        </is>
+      </c>
+      <c r="AT75" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5475.pdf</t>
+        </is>
+      </c>
+      <c r="AU75" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5475.pdf</t>
+        </is>
+      </c>
+      <c r="AV75" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5475-SUMARIO.pdf</t>
+        </is>
+      </c>
+      <c r="AW75" s="4" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>MULTIMERCADO</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>CAIXA CAPITAL PROTEGIDO CÍCLICO III FIC FIF MM LP - RESP LTDA</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>10/01/2022</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>1,53082000</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>-0,004</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>-1,18</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>2,52</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>18,97</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>14,421</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>PF | PJ | RPPS</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fic-capital-protegido-ciclico-iii-multimercado-lp/Paginas/default.aspx</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>44.683.343/0001-73</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>6608</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>4000.0</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>D+02 (du)</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>Capital Protegido</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>Fechado para captação</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>LONGO PRAZO</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>GERAL</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>16h00</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>Sim · Automatico · 100%</t>
+        </is>
+      </c>
+      <c r="AE76" s="2" t="inlineStr">
+        <is>
+          <t>AUTOMATICO</t>
+        </is>
+      </c>
+      <c r="AF76" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG76" s="2" t="inlineStr">
+        <is>
+          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
+        </is>
+      </c>
+      <c r="AH76" s="2" t="inlineStr">
+        <is>
+          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
+        </is>
+      </c>
+      <c r="AI76" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AJ76" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AK76" s="2" t="inlineStr">
+        <is>
+          <t>2028-07-07T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="AL76" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AM76" s="2" t="inlineStr">
+        <is>
+          <t>CAIXA CAPITAL PROTEGIDO CÍCLICO III FIC DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESP LIMITADA</t>
+        </is>
+      </c>
+      <c r="AN76" s="2" t="inlineStr">
+        <is>
+          <t>Fundo com prazo de carência para aplicação e resgate, conforme Regulamento. Durante a carência, não é permitida a realização de aplicações ou resgates.                                                                  Período de Captação 02/03/2026 à 24/04/2026
+Início da Operação Estruturada: 27/04/2026
+Fim da Operação Estruturada: 03/07/2028</t>
+        </is>
+      </c>
+      <c r="AO76" s="2" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6608.pdf</t>
+        </is>
+      </c>
+      <c r="AP76" s="2" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6608.pdf</t>
+        </is>
+      </c>
+      <c r="AQ76" s="2" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6608.pdf</t>
+        </is>
+      </c>
+      <c r="AR76" s="2" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_6608.pdf</t>
+        </is>
+      </c>
+      <c r="AS76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6608.pdf</t>
+        </is>
+      </c>
+      <c r="AT76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6608.pdf</t>
+        </is>
+      </c>
+      <c r="AU76" s="2" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6608.pdf</t>
+        </is>
+      </c>
+      <c r="AV76" s="2" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/6608-SUMARIO.pdf</t>
+        </is>
+      </c>
+      <c r="AW76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>MULTIMERCADO</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>CAIXA FIC FIF CAPITAL PROTEGIDO CESTA AGRO MM</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>04/07/2022</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>1,38037000</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>0,47</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>1,78</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>6,77</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>70,737</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>GOV | PF | PJ | RPPS</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa_fic_fim_cap_protegido_cesta_agro/Paginas/default.aspx</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>42.229.068/0001-97</t>
+        </is>
+      </c>
+      <c r="M77" s="4" t="inlineStr">
+        <is>
+          <t>6621</t>
+        </is>
+      </c>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="O77" s="4" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="P77" s="4" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="Q77" s="4" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R77" s="4" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="S77" s="4" t="inlineStr">
+        <is>
+          <t>4000.0</t>
+        </is>
+      </c>
+      <c r="T77" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="U77" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="V77" s="4" t="inlineStr">
+        <is>
+          <t>D+02 (du)</t>
+        </is>
+      </c>
+      <c r="W77" s="4" t="inlineStr">
+        <is>
+          <t>OUTROS</t>
+        </is>
+      </c>
+      <c r="X77" s="4" t="inlineStr">
+        <is>
+          <t>Capital Protegido</t>
+        </is>
+      </c>
+      <c r="Y77" s="4" t="inlineStr">
+        <is>
+          <t>Fechado para captação</t>
+        </is>
+      </c>
+      <c r="Z77" s="4" t="inlineStr">
+        <is>
+          <t>LONGO PRAZO</t>
+        </is>
+      </c>
+      <c r="AA77" s="4" t="inlineStr">
+        <is>
+          <t>GERAL</t>
+        </is>
+      </c>
+      <c r="AB77" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC77" s="4" t="inlineStr">
+        <is>
+          <t>16h00</t>
+        </is>
+      </c>
+      <c r="AD77" s="4" t="inlineStr">
+        <is>
+          <t>Sim · Automatico · 100%</t>
+        </is>
+      </c>
+      <c r="AE77" s="4" t="inlineStr">
+        <is>
+          <t>AUTOMATICO</t>
+        </is>
+      </c>
+      <c r="AF77" s="4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG77" s="4" t="inlineStr">
+        <is>
+          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
+        </is>
+      </c>
+      <c r="AH77" s="4" t="inlineStr">
+        <is>
+          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
+        </is>
+      </c>
+      <c r="AI77" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AJ77" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AK77" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="AL77" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AM77" s="4" t="inlineStr">
+        <is>
+          <t>CAIXA CAPITAL PROTEGIDO CESTA AGRO FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESPONSABIL</t>
+        </is>
+      </c>
+      <c r="AN77" s="4" t="inlineStr">
+        <is>
+          <t>Fundo com prazo de carência para aplicação e resgate, conforme Regulamento. Durante a carência, não é permitida a realização de aplicações ou resgates.
+Nova Operação Estruturada:
+Dia 07/10/2024 -&gt; Reabertura para Resgates e Aplicações do fundo;
+Dia 25/10/2024 -&gt; Fechamento para Aplicações e Resgates
+Dia 29/10/2024 -&gt; Início da nova operação estruturada de Cesta Agro.</t>
+        </is>
+      </c>
+      <c r="AO77" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6621.pdf</t>
+        </is>
+      </c>
+      <c r="AP77" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6621.pdf</t>
+        </is>
+      </c>
+      <c r="AQ77" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6621.pdf</t>
+        </is>
+      </c>
+      <c r="AR77" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_6621.pdf</t>
+        </is>
+      </c>
+      <c r="AS77" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6621.pdf</t>
+        </is>
+      </c>
+      <c r="AT77" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6621.pdf</t>
+        </is>
+      </c>
+      <c r="AU77" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6621.pdf</t>
+        </is>
+      </c>
+      <c r="AV77" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/6621-SUMARIO.pdf</t>
+        </is>
+      </c>
+      <c r="AW77" s="4" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>MULTIMERCADO</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>CAIXA FIC FIM CAPITAL PROTEGIDO CICLICO II LP - RL</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>18/07/2022</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>1,47074800</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>-2,08</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>1,70</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>13,23</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>190,698</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>GOV | PF | PJ | RPPS</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fim-cap-protegido-ciclico-ii</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
           <t>45.443.651/0001-94</t>
         </is>
       </c>
-      <c r="M75" s="4" t="inlineStr">
+      <c r="M78" s="2" t="inlineStr">
         <is>
           <t>6623</t>
         </is>
       </c>
-      <c r="N75" s="4" t="inlineStr">
+      <c r="N78" s="2" t="inlineStr">
         <is>
           <t>Conservador</t>
         </is>
       </c>
-      <c r="O75" s="4" t="inlineStr">
+      <c r="O78" s="2" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="P75" s="4" t="inlineStr">
+      <c r="P78" s="2" t="inlineStr">
         <is>
           <t>5000.0</t>
         </is>
       </c>
-      <c r="Q75" s="4" t="inlineStr">
+      <c r="Q78" s="2" t="inlineStr">
         <is>
           <t>500.0</t>
         </is>
       </c>
-      <c r="R75" s="4" t="inlineStr">
+      <c r="R78" s="2" t="inlineStr">
         <is>
           <t>500.0</t>
         </is>
       </c>
-      <c r="S75" s="4" t="inlineStr">
+      <c r="S78" s="2" t="inlineStr">
         <is>
           <t>4000.0</t>
         </is>
       </c>
-      <c r="T75" s="4" t="inlineStr">
+      <c r="T78" s="2" t="inlineStr">
         <is>
           <t>D+0 (du)</t>
         </is>
       </c>
-      <c r="U75" s="4" t="inlineStr">
+      <c r="U78" s="2" t="inlineStr">
         <is>
           <t>D+0 (du)</t>
         </is>
       </c>
-      <c r="V75" s="4" t="inlineStr">
+      <c r="V78" s="2" t="inlineStr">
         <is>
           <t>D+02 (du)</t>
         </is>
       </c>
-      <c r="W75" s="4" t="inlineStr">
+      <c r="W78" s="2" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="X75" s="4" t="inlineStr">
+      <c r="X78" s="2" t="inlineStr">
         <is>
           <t>Capital Protegido</t>
         </is>
       </c>
-      <c r="Y75" s="4" t="inlineStr">
+      <c r="Y78" s="2" t="inlineStr">
         <is>
           <t>Fechado para captação</t>
         </is>
       </c>
-      <c r="Z75" s="4" t="inlineStr">
+      <c r="Z78" s="2" t="inlineStr">
         <is>
           <t>LONGO PRAZO</t>
         </is>
       </c>
-      <c r="AA75" s="4" t="inlineStr">
+      <c r="AA78" s="2" t="inlineStr">
         <is>
           <t>GERAL</t>
         </is>
       </c>
-      <c r="AB75" s="4" t="inlineStr">
+      <c r="AB78" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="AC75" s="4" t="inlineStr">
+      <c r="AC78" s="2" t="inlineStr">
         <is>
           <t>16h00</t>
         </is>
       </c>
-      <c r="AD75" s="4" t="inlineStr">
+      <c r="AD78" s="2" t="inlineStr">
         <is>
           <t>Sim · Automatico · 100%</t>
         </is>
       </c>
-      <c r="AE75" s="4" t="inlineStr">
+      <c r="AE78" s="2" t="inlineStr">
         <is>
           <t>AUTOMATICO</t>
         </is>
       </c>
-      <c r="AF75" s="4" t="inlineStr">
+      <c r="AF78" s="2" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AG75" s="4" t="inlineStr">
+      <c r="AG78" s="2" t="inlineStr">
         <is>
           <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
         </is>
       </c>
-      <c r="AH75" s="4" t="inlineStr">
+      <c r="AH78" s="2" t="inlineStr">
         <is>
           <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
         </is>
       </c>
-      <c r="AI75" s="4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AJ75" s="4" t="inlineStr">
+      <c r="AI78" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AJ78" s="2" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="AK75" s="4" t="inlineStr">
+      <c r="AK78" s="2" t="inlineStr">
         <is>
           <t>2026-07-01T00:00:00Z</t>
         </is>
       </c>
-      <c r="AL75" s="4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AM75" s="4" t="inlineStr">
+      <c r="AL78" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AM78" s="2" t="inlineStr">
         <is>
           <t>CAIXA CAPITAL PROTEGIDO CICLICO II FIC DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
-      <c r="AN75" s="4" t="inlineStr">
+      <c r="AN78" s="2" t="inlineStr">
         <is>
           <t>Fundo com prazo de carência para aplicação e resgate, conforme Regulamento. Durante a carência, não é permitida a realização de aplicações ou resgates.
 Fechado para Aplicações e Resgates a partir de 26/08/2024 
@@ -17983,745 +18584,6 @@
 Fim da Operação Estruturada - 01/07/2026</t>
         </is>
       </c>
-      <c r="AO75" s="4" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6623.pdf</t>
-        </is>
-      </c>
-      <c r="AP75" s="4" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6623.pdf</t>
-        </is>
-      </c>
-      <c r="AQ75" s="4" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6623.pdf</t>
-        </is>
-      </c>
-      <c r="AR75" s="4" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_6623.pdf</t>
-        </is>
-      </c>
-      <c r="AS75" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6623.pdf</t>
-        </is>
-      </c>
-      <c r="AT75" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6623.pdf</t>
-        </is>
-      </c>
-      <c r="AU75" s="4" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6623.pdf</t>
-        </is>
-      </c>
-      <c r="AV75" s="4" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/6623-SUMARIO.pdf</t>
-        </is>
-      </c>
-      <c r="AW75" s="4" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>MULTIMERCADO</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>CAIXA CAPITAL PROTEGIDO CÍCLICO III FIC FIF MM LP - RESP LTDA</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>10/01/2022</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>PF | PJ | RPPS</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fic-capital-protegido-ciclico-iii-multimercado-lp/Paginas/default.aspx</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>44.683.343/0001-73</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>6608</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>Conservador</t>
-        </is>
-      </c>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="P76" s="2" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="Q76" s="2" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
-      </c>
-      <c r="R76" s="2" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
-      </c>
-      <c r="S76" s="2" t="inlineStr">
-        <is>
-          <t>4000.0</t>
-        </is>
-      </c>
-      <c r="T76" s="2" t="inlineStr">
-        <is>
-          <t>D+0 (du)</t>
-        </is>
-      </c>
-      <c r="U76" s="2" t="inlineStr">
-        <is>
-          <t>D+0 (du)</t>
-        </is>
-      </c>
-      <c r="V76" s="2" t="inlineStr">
-        <is>
-          <t>D+02 (du)</t>
-        </is>
-      </c>
-      <c r="W76" s="2" t="inlineStr">
-        <is>
-          <t>NÃO SE APLICA</t>
-        </is>
-      </c>
-      <c r="X76" s="2" t="inlineStr">
-        <is>
-          <t>Capital Protegido</t>
-        </is>
-      </c>
-      <c r="Y76" s="2" t="inlineStr">
-        <is>
-          <t>Fechado para captação</t>
-        </is>
-      </c>
-      <c r="Z76" s="2" t="inlineStr">
-        <is>
-          <t>LONGO PRAZO</t>
-        </is>
-      </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>GERAL</t>
-        </is>
-      </c>
-      <c r="AB76" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr">
-        <is>
-          <t>16h00</t>
-        </is>
-      </c>
-      <c r="AD76" s="2" t="inlineStr">
-        <is>
-          <t>Sim · Automatico · 100%</t>
-        </is>
-      </c>
-      <c r="AE76" s="2" t="inlineStr">
-        <is>
-          <t>AUTOMATICO</t>
-        </is>
-      </c>
-      <c r="AF76" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG76" s="2" t="inlineStr">
-        <is>
-          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
-        </is>
-      </c>
-      <c r="AH76" s="2" t="inlineStr">
-        <is>
-          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
-        </is>
-      </c>
-      <c r="AI76" s="2" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AJ76" s="2" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AK76" s="2" t="inlineStr">
-        <is>
-          <t>2028-07-07T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="AL76" s="2" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AM76" s="2" t="inlineStr">
-        <is>
-          <t>CAIXA CAPITAL PROTEGIDO CÍCLICO III FIC DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESP LIMITADA</t>
-        </is>
-      </c>
-      <c r="AN76" s="2" t="inlineStr">
-        <is>
-          <t>Fundo com prazo de carência para aplicação e resgate, conforme Regulamento. Durante a carência, não é permitida a realização de aplicações ou resgates.                                                                  Período de Captação 02/03/2026 à 24/04/2026
-Início da Operação Estruturada: 27/04/2026
-Fim da Operação Estruturada: 03/07/2028</t>
-        </is>
-      </c>
-      <c r="AO76" s="2" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6608.pdf</t>
-        </is>
-      </c>
-      <c r="AP76" s="2" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6608.pdf</t>
-        </is>
-      </c>
-      <c r="AQ76" s="2" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6608.pdf</t>
-        </is>
-      </c>
-      <c r="AR76" s="2" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_6608.pdf</t>
-        </is>
-      </c>
-      <c r="AS76" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6608.pdf</t>
-        </is>
-      </c>
-      <c r="AT76" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6608.pdf</t>
-        </is>
-      </c>
-      <c r="AU76" s="2" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6608.pdf</t>
-        </is>
-      </c>
-      <c r="AV76" s="2" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/6608-SUMARIO.pdf</t>
-        </is>
-      </c>
-      <c r="AW76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>MULTIMERCADO</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>CAIXA FIC FIF CAPITAL PROTEGIDO CESTA AGRO MM</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>04/07/2022</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>GOV | PF | PJ | RPPS</t>
-        </is>
-      </c>
-      <c r="K77" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa_fic_fim_cap_protegido_cesta_agro/Paginas/default.aspx</t>
-        </is>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>42.229.068/0001-97</t>
-        </is>
-      </c>
-      <c r="M77" s="4" t="inlineStr">
-        <is>
-          <t>6621</t>
-        </is>
-      </c>
-      <c r="N77" s="4" t="inlineStr">
-        <is>
-          <t>Conservador</t>
-        </is>
-      </c>
-      <c r="O77" s="4" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="P77" s="4" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="Q77" s="4" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
-      </c>
-      <c r="R77" s="4" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
-      </c>
-      <c r="S77" s="4" t="inlineStr">
-        <is>
-          <t>4000.0</t>
-        </is>
-      </c>
-      <c r="T77" s="4" t="inlineStr">
-        <is>
-          <t>D+0 (du)</t>
-        </is>
-      </c>
-      <c r="U77" s="4" t="inlineStr">
-        <is>
-          <t>D+0 (du)</t>
-        </is>
-      </c>
-      <c r="V77" s="4" t="inlineStr">
-        <is>
-          <t>D+02 (du)</t>
-        </is>
-      </c>
-      <c r="W77" s="4" t="inlineStr">
-        <is>
-          <t>OUTROS</t>
-        </is>
-      </c>
-      <c r="X77" s="4" t="inlineStr">
-        <is>
-          <t>Capital Protegido</t>
-        </is>
-      </c>
-      <c r="Y77" s="4" t="inlineStr">
-        <is>
-          <t>Fechado para captação</t>
-        </is>
-      </c>
-      <c r="Z77" s="4" t="inlineStr">
-        <is>
-          <t>LONGO PRAZO</t>
-        </is>
-      </c>
-      <c r="AA77" s="4" t="inlineStr">
-        <is>
-          <t>GERAL</t>
-        </is>
-      </c>
-      <c r="AB77" s="4" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC77" s="4" t="inlineStr">
-        <is>
-          <t>16h00</t>
-        </is>
-      </c>
-      <c r="AD77" s="4" t="inlineStr">
-        <is>
-          <t>Sim · Automatico · 100%</t>
-        </is>
-      </c>
-      <c r="AE77" s="4" t="inlineStr">
-        <is>
-          <t>AUTOMATICO</t>
-        </is>
-      </c>
-      <c r="AF77" s="4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG77" s="4" t="inlineStr">
-        <is>
-          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
-        </is>
-      </c>
-      <c r="AH77" s="4" t="inlineStr">
-        <is>
-          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
-        </is>
-      </c>
-      <c r="AI77" s="4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AJ77" s="4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AK77" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-01T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="AL77" s="4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AM77" s="4" t="inlineStr">
-        <is>
-          <t>CAIXA CAPITAL PROTEGIDO CESTA AGRO FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESPONSABIL</t>
-        </is>
-      </c>
-      <c r="AN77" s="4" t="inlineStr">
-        <is>
-          <t>Fundo com prazo de carência para aplicação e resgate, conforme Regulamento. Durante a carência, não é permitida a realização de aplicações ou resgates.
-Nova Operação Estruturada:
-Dia 07/10/2024 -&gt; Reabertura para Resgates e Aplicações do fundo;
-Dia 25/10/2024 -&gt; Fechamento para Aplicações e Resgates
-Dia 29/10/2024 -&gt; Início da nova operação estruturada de Cesta Agro.</t>
-        </is>
-      </c>
-      <c r="AO77" s="4" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6621.pdf</t>
-        </is>
-      </c>
-      <c r="AP77" s="4" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6621.pdf</t>
-        </is>
-      </c>
-      <c r="AQ77" s="4" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6621.pdf</t>
-        </is>
-      </c>
-      <c r="AR77" s="4" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_6621.pdf</t>
-        </is>
-      </c>
-      <c r="AS77" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6621.pdf</t>
-        </is>
-      </c>
-      <c r="AT77" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6621.pdf</t>
-        </is>
-      </c>
-      <c r="AU77" s="4" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6621.pdf</t>
-        </is>
-      </c>
-      <c r="AV77" s="4" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/6621-SUMARIO.pdf</t>
-        </is>
-      </c>
-      <c r="AW77" s="4" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>MULTIMERCADO</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>CAIXA FIC FIM CAPITAL PROTEGIDO CICLICO II LP - RL</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>18/07/2022</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>GOV | PF | PJ | RPPS</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fic-capital-protegido-ciclico-ii-multimercado-lp/Paginas/default.aspx</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>45.443.651/0001-94</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>6623</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>Conservador</t>
-        </is>
-      </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="P78" s="2" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
-      </c>
-      <c r="R78" s="2" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
-      </c>
-      <c r="S78" s="2" t="inlineStr">
-        <is>
-          <t>4000.0</t>
-        </is>
-      </c>
-      <c r="T78" s="2" t="inlineStr">
-        <is>
-          <t>D+0 (du)</t>
-        </is>
-      </c>
-      <c r="U78" s="2" t="inlineStr">
-        <is>
-          <t>D+0 (du)</t>
-        </is>
-      </c>
-      <c r="V78" s="2" t="inlineStr">
-        <is>
-          <t>D+02 (du)</t>
-        </is>
-      </c>
-      <c r="W78" s="2" t="inlineStr">
-        <is>
-          <t>NÃO SE APLICA</t>
-        </is>
-      </c>
-      <c r="X78" s="2" t="inlineStr">
-        <is>
-          <t>Capital Protegido</t>
-        </is>
-      </c>
-      <c r="Y78" s="2" t="inlineStr">
-        <is>
-          <t>Fechado para captação</t>
-        </is>
-      </c>
-      <c r="Z78" s="2" t="inlineStr">
-        <is>
-          <t>LONGO PRAZO</t>
-        </is>
-      </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>GERAL</t>
-        </is>
-      </c>
-      <c r="AB78" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC78" s="2" t="inlineStr">
-        <is>
-          <t>16h00</t>
-        </is>
-      </c>
-      <c r="AD78" s="2" t="inlineStr">
-        <is>
-          <t>Sim · Automatico · 100%</t>
-        </is>
-      </c>
-      <c r="AE78" s="2" t="inlineStr">
-        <is>
-          <t>AUTOMATICO</t>
-        </is>
-      </c>
-      <c r="AF78" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG78" s="2" t="inlineStr">
-        <is>
-          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
-        </is>
-      </c>
-      <c r="AH78" s="2" t="inlineStr">
-        <is>
-          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
-        </is>
-      </c>
-      <c r="AI78" s="2" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AJ78" s="2" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AK78" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="AL78" s="2" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AM78" s="2" t="inlineStr">
-        <is>
-          <t>CAIXA CAPITAL PROTEGIDO CICLICO II FIC DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
-        </is>
-      </c>
-      <c r="AN78" s="2" t="inlineStr">
-        <is>
-          <t>Fundo com prazo de carência para aplicação e resgate, conforme Regulamento. Durante a carência, não é permitida a realização de aplicações ou resgates.
-Fechado para Aplicações e Resgates a partir de 26/08/2024 
--------
-Início da Operação Estruturada - 27/08/2024
-Fim da Operação Estruturada - 01/07/2026</t>
-        </is>
-      </c>
       <c r="AO78" s="2" t="inlineStr">
         <is>
           <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6623.pdf</t>
@@ -18782,32 +18644,32 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,78558600</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>-0,002</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>0,28</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>1,07</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>10,23</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>175,417</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -19042,7 +18904,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>896,026</t>
+          <t>895,915</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -19281,7 +19143,7 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>746,101</t>
+          <t>746,100</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -19491,32 +19353,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>6,77731300</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>-0,004</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>-0,89</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>5,37</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>15,35</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>127,999</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -19726,32 +19588,32 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,43079100</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>0,28</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>3,85</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>15,06</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>283,344</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -19966,32 +19828,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,35003000</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>2,03</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>5,18</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>5,12</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13,174</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -20230,7 +20092,7 @@
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>95,784</t>
+          <t>95,734</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -20708,7 +20570,7 @@
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>13,069</t>
+          <t>13,064</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -20723,12 +20585,12 @@
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>15.154.410/0001-64</t>
+          <t>01.525.057/0001-77</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>53</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -20738,7 +20600,7 @@
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
@@ -20801,7 +20663,11 @@
           <t>GERAL</t>
         </is>
       </c>
-      <c r="AB87" s="4" t="inlineStr"/>
+      <c r="AB87" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AC87" s="4" t="inlineStr">
         <is>
           <t>17h00</t>
@@ -20850,52 +20716,52 @@
       </c>
       <c r="AM87" s="4" t="inlineStr">
         <is>
-          <t>CAIXA E-FUNDO IBOVESPA FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO EM AÇÕES - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA IBOVESPA FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO EM AÇÕES - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AN87" s="4" t="inlineStr">
         <is>
-          <t>As movimentações neste Fundo são realizadas exclusivamente pelo Internet Banking. A contagem para conversão de cotas e pagamento do resgate é feita em dias úteis, conforme estabelecido no Regulamento do Fundo. Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).</t>
+          <t>A contagem para conversão de cotas e pagamento do resgate é feita em dias úteis, conforme estabelecido no Regulamento do Fundo.</t>
         </is>
       </c>
       <c r="AO87" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5832.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0053.pdf</t>
         </is>
       </c>
       <c r="AP87" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5832.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0053.pdf</t>
         </is>
       </c>
       <c r="AQ87" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5832.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0053.pdf</t>
         </is>
       </c>
       <c r="AR87" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5832.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_0053.pdf</t>
         </is>
       </c>
       <c r="AS87" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5832.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_53.pdf</t>
         </is>
       </c>
       <c r="AT87" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5832.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_53.pdf</t>
         </is>
       </c>
       <c r="AU87" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5832.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_0053.pdf</t>
         </is>
       </c>
       <c r="AV87" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5832-SUMARIO.pdf</t>
+          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/0053-SUMARIO.pdf</t>
         </is>
       </c>
       <c r="AW87" s="4" t="inlineStr"/>
@@ -21171,7 +21037,7 @@
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>273,136</t>
+          <t>272,946</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -21410,7 +21276,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>436,541</t>
+          <t>436,520</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -21649,7 +21515,7 @@
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>55,778</t>
+          <t>55,755</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -22127,7 +21993,7 @@
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>76,204</t>
+          <t>76,177</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -22580,32 +22446,32 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,24755100</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>-0,021</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>-1,82</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>-3,07</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>5,30</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>282,085</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -22844,7 +22710,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>111,700</t>
+          <t>111,654</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -23083,7 +22949,7 @@
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>124,715</t>
+          <t>124,658</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -23322,7 +23188,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>48,402</t>
+          <t>48,392</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -23565,7 +23431,7 @@
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>117,088</t>
+          <t>116,758</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -23804,7 +23670,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>39,901</t>
+          <t>39,899</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -24043,7 +23909,7 @@
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>629,705</t>
+          <t>629,401</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -24282,7 +24148,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>466,941</t>
+          <t>466,540</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -24764,7 +24630,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>29,338</t>
+          <t>29,329</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -25003,7 +24869,7 @@
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>1,723</t>
+          <t>1,718</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -25465,7 +25331,7 @@
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>35,003</t>
+          <t>34,828</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -25704,7 +25570,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>834,076</t>
+          <t>832,919</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -26652,7 +26518,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>268,165</t>
+          <t>268,052</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -26870,32 +26736,32 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>986,43017800</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>-1,30</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>0,61</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>15,27</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -27109,32 +26975,32 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.483,47485600</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>-0,002</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>-0,78</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>-0,82</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>9,76</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21,383</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -27344,7 +27210,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>167,07500900</t>
+          <t>167,07500868</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -27608,7 +27474,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>4,925</t>
+          <t>4,919</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -27844,7 +27710,7 @@
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>1.596,589</t>
+          <t>1.596,064</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -28076,7 +27942,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>674,368</t>
+          <t>674,266</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -28299,7 +28165,7 @@
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>746,566</t>
+          <t>746,473</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -28522,7 +28388,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>111,660</t>
+          <t>111,578</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -28982,7 +28848,7 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>581,621</t>
+          <t>581,297</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -29210,7 +29076,7 @@
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>448,559</t>
+          <t>448,447</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -29433,7 +29299,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>667,305</t>
+          <t>666,123</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -29898,7 +29764,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>273,172</t>
+          <t>255,689</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -30616,7 +30482,7 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>19,404</t>
+          <t>19,403</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -30857,7 +30723,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>94,279</t>
+          <t>94,276</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -31100,7 +30966,7 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>8.116,732</t>
+          <t>7.983,447</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -31338,7 +31204,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>16.099,200</t>
+          <t>16.099,143</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -31577,7 +31443,7 @@
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>3.007,320</t>
+          <t>3.007,317</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -31791,7 +31657,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1,55391800</t>
+          <t>1,55391842</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -32275,7 +32141,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>3.962,335</t>
+          <t>3.962,334</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -32725,7 +32591,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>13.781,689</t>
+          <t>13.547,600</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -32963,7 +32829,7 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>13.293,626</t>
+          <t>13.293,188</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -33202,7 +33068,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.515,620</t>
+          <t>3.515,607</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -33676,7 +33542,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>32.821,865</t>
+          <t>32.798,152</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -33912,7 +33778,7 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>2.831,498</t>
+          <t>2.798,318</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
@@ -34150,7 +34016,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>16.487,897</t>
+          <t>16.648,650</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -35112,7 +34978,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>460,633</t>
+          <t>459,420</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -35839,7 +35705,7 @@
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>1.730,392</t>
+          <t>1.730,370</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
@@ -37390,7 +37256,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>13.113,026</t>
+          <t>13.113,024</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -37405,12 +37271,12 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>05.164.356/0001-84</t>
+          <t>03.737.206/0001-97</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -37465,7 +37331,7 @@
       </c>
       <c r="X158" s="2" t="inlineStr">
         <is>
-          <t>RF 100% TPF - Longo Prazo</t>
+          <t>RF DI até 49% Crédito Privado</t>
         </is>
       </c>
       <c r="Y158" s="2" t="inlineStr">
@@ -37536,57 +37402,58 @@
       </c>
       <c r="AM158" s="2" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA BRASIL FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA REFERENCIADO DI LONGO PRAZO - RESP LIMITADA</t>
         </is>
       </c>
       <c r="AN158" s="2" t="inlineStr">
         <is>
-          <t>Para aplicação no fundo é necessário o cadastramento prévio de cotistas, conforme descrito no FI657. O procedimento de inclusão da conta deverá ser realizado sempre que houver qualquer aplicação, mesmo para os clientes que já realizaram o cadsatramento anteriormente.</t>
+          <t>1. Para aplicação por meio de conta operação 003, é necessário o cadastramento prévio de cotistas, conforme descrito no item Adesão, do FI612.
+2. O procedimento de inclusão da conta deverá ser realizado sempre que houver qualquer aplicação por meio de conta operação 003, mesmo para os clientes que já realizaram o cadastramento anteriormente.</t>
         </is>
       </c>
       <c r="AO158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5462.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5404.pdf</t>
         </is>
       </c>
       <c r="AP158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5462.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5404.pdf</t>
         </is>
       </c>
       <c r="AQ158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5462.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5404.pdf</t>
         </is>
       </c>
       <c r="AR158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5462.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5404.pdf</t>
         </is>
       </c>
       <c r="AS158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5462.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5404.pdf</t>
         </is>
       </c>
       <c r="AT158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5462.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5404.pdf</t>
         </is>
       </c>
       <c r="AU158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5462.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5404.pdf</t>
         </is>
       </c>
       <c r="AV158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5462-SUMARIO.pdf</t>
+          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5404-SUMARIO.pdf</t>
         </is>
       </c>
       <c r="AW158" s="2" t="inlineStr">
         <is>
-          <t>https://web.microsoftstream.com/video/91aaf70b-85c2-4cf1-b537-e42b3bd894ec?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
+          <t>https://web.microsoftstream.com/video/f88f1fc7-aac3-44df-a2a5-ce3ac05edfb3?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
     </row>
@@ -38107,7 +37974,7 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>1.568,519</t>
+          <t>1.541,491</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
@@ -38344,7 +38211,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>24.067,652</t>
+          <t>24.067,648</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -38910,7 +38777,7 @@
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>282,305</t>
+          <t>282,301</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
@@ -39363,7 +39230,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>11,11490200</t>
+          <t>11,11490221</t>
         </is>
       </c>
       <c r="E167" s="6" t="inlineStr">
@@ -40076,7 +39943,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>3,39992000</t>
+          <t>3,39991961</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr">
@@ -40307,7 +40174,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>2,45068700</t>
+          <t>2,45068727</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -822,43 +822,185 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-renda-fixa-simples-lp/</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
-      <c r="Z2" s="2" t="inlineStr"/>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr"/>
-      <c r="AD2" s="2" t="inlineStr"/>
-      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>22.791.329/0001-50</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5980</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>SELIC</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>RF Simples até 49% Crédito Privado</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>Aberto para captação</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>LONGO PRAZO</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>GERAL</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>17h00</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
       <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>CAIXA E-SIMPLES FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AN2" s="2" t="inlineStr">
+        <is>
+          <t>Fundo com movimentação exclusiva pelo IBC/APP.
+OBS: O Fundo possui a funcionalidade de Resgate Automático em caso de adesão pelo cotista, o gerente deverá proceder à contratação no SIART. Para ativar a funcionalidade de Resgate Automático, acessar o SIART -&gt; Movimentação Automática -&gt; Marcar
+As regras da funcionalidade de Movimentação Automática estão descritas no MN TE099.</t>
+        </is>
+      </c>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5980.pdf</t>
+        </is>
+      </c>
+      <c r="AP2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5980.pdf</t>
+        </is>
+      </c>
+      <c r="AQ2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5980.pdf</t>
+        </is>
+      </c>
+      <c r="AR2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5980.pdf</t>
+        </is>
+      </c>
+      <c r="AS2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5980.pdf</t>
+        </is>
+      </c>
+      <c r="AT2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5980.pdf</t>
+        </is>
+      </c>
+      <c r="AU2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5980.pdf</t>
+        </is>
+      </c>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5980-SUMARIO.pdf</t>
+        </is>
+      </c>
       <c r="AW2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -13613,44 +13755,192 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fi-multimercado-rv30-longo-prazo</t>
         </is>
       </c>
-      <c r="L57" s="4" t="inlineStr"/>
-      <c r="M57" s="4" t="inlineStr"/>
-      <c r="N57" s="4" t="inlineStr"/>
-      <c r="O57" s="4" t="inlineStr"/>
-      <c r="P57" s="4" t="inlineStr"/>
-      <c r="Q57" s="4" t="inlineStr"/>
-      <c r="R57" s="4" t="inlineStr"/>
-      <c r="S57" s="4" t="inlineStr"/>
-      <c r="T57" s="4" t="inlineStr"/>
-      <c r="U57" s="4" t="inlineStr"/>
-      <c r="V57" s="4" t="inlineStr"/>
-      <c r="W57" s="4" t="inlineStr"/>
-      <c r="X57" s="4" t="inlineStr"/>
-      <c r="Y57" s="4" t="inlineStr"/>
-      <c r="Z57" s="4" t="inlineStr"/>
-      <c r="AA57" s="4" t="inlineStr"/>
-      <c r="AB57" s="4" t="inlineStr"/>
-      <c r="AC57" s="4" t="inlineStr"/>
-      <c r="AD57" s="4" t="inlineStr"/>
-      <c r="AE57" s="4" t="inlineStr"/>
-      <c r="AF57" s="4" t="inlineStr"/>
-      <c r="AG57" s="4" t="inlineStr"/>
-      <c r="AH57" s="4" t="inlineStr"/>
-      <c r="AI57" s="4" t="inlineStr"/>
-      <c r="AJ57" s="4" t="inlineStr"/>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>03.737.188/0001-43</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P57" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Q57" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="R57" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="S57" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="T57" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="U57" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="V57" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
+      <c r="W57" s="4" t="inlineStr">
+        <is>
+          <t>70% CDI + 30% IBOV</t>
+        </is>
+      </c>
+      <c r="X57" s="4" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+      <c r="Y57" s="4" t="inlineStr">
+        <is>
+          <t>Aberto para captação</t>
+        </is>
+      </c>
+      <c r="Z57" s="4" t="inlineStr">
+        <is>
+          <t>LONGO PRAZO</t>
+        </is>
+      </c>
+      <c r="AA57" s="4" t="inlineStr">
+        <is>
+          <t>GERAL</t>
+        </is>
+      </c>
+      <c r="AB57" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC57" s="4" t="inlineStr">
+        <is>
+          <t>16h00</t>
+        </is>
+      </c>
+      <c r="AD57" s="4" t="inlineStr">
+        <is>
+          <t>Sim · Automatico · 100%</t>
+        </is>
+      </c>
+      <c r="AE57" s="4" t="inlineStr">
+        <is>
+          <t>AUTOMATICO</t>
+        </is>
+      </c>
+      <c r="AF57" s="4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG57" s="4" t="inlineStr">
+        <is>
+          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
+        </is>
+      </c>
+      <c r="AH57" s="4" t="inlineStr">
+        <is>
+          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
+        </is>
+      </c>
+      <c r="AI57" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AJ57" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="AK57" s="4" t="inlineStr"/>
-      <c r="AL57" s="4" t="inlineStr"/>
-      <c r="AM57" s="4" t="inlineStr"/>
-      <c r="AN57" s="4" t="inlineStr"/>
-      <c r="AO57" s="4" t="inlineStr"/>
-      <c r="AP57" s="4" t="inlineStr"/>
-      <c r="AQ57" s="4" t="inlineStr"/>
-      <c r="AR57" s="4" t="inlineStr"/>
-      <c r="AS57" s="4" t="inlineStr"/>
-      <c r="AT57" s="4" t="inlineStr"/>
-      <c r="AU57" s="4" t="inlineStr"/>
-      <c r="AV57" s="4" t="inlineStr"/>
-      <c r="AW57" s="4" t="inlineStr"/>
+      <c r="AL57" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AM57" s="4" t="inlineStr">
+        <is>
+          <t>CAIXA RV 30 FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AN57" s="4" t="inlineStr">
+        <is>
+          <t>A contagem para conversão de cotas e pagamento do resgate é feita em dias úteis, conforme estabelecido no Regulamento do Fundo. Este Fundo está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).</t>
+        </is>
+      </c>
+      <c r="AO57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0082.pdf</t>
+        </is>
+      </c>
+      <c r="AP57" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0082.pdf</t>
+        </is>
+      </c>
+      <c r="AQ57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0082.pdf</t>
+        </is>
+      </c>
+      <c r="AR57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_0082.pdf</t>
+        </is>
+      </c>
+      <c r="AS57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_82.pdf</t>
+        </is>
+      </c>
+      <c r="AT57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_82.pdf</t>
+        </is>
+      </c>
+      <c r="AU57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_0082.pdf</t>
+        </is>
+      </c>
+      <c r="AV57" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/0082-SUMARIO.pdf</t>
+        </is>
+      </c>
+      <c r="AW57" s="4" t="inlineStr">
+        <is>
+          <t>https://web.microsoftstream.com/video/86aa0100-d5af-4db2-9f67-441255924e4e?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -17224,15 +17514,19 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="K73" s="4" t="inlineStr"/>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/fundos-investimento/multimercado/estrategia-livre-mm-lp/Paginas/default.aspx</t>
+        </is>
+      </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>35.536.472/0001-48</t>
+          <t>34.660.333/0001-69</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -17242,7 +17536,7 @@
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
@@ -17330,8 +17624,16 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="AG73" s="4" t="inlineStr"/>
-      <c r="AH73" s="4" t="inlineStr"/>
+      <c r="AG73" s="4" t="inlineStr">
+        <is>
+          <t>["Pessoa Física", "Private"]</t>
+        </is>
+      </c>
+      <c r="AH73" s="4" t="inlineStr">
+        <is>
+          <t>["Pessoa Física", "Private"]</t>
+        </is>
+      </c>
       <c r="AI73" s="4" t="inlineStr">
         <is>
           <t>Não</t>
@@ -17350,52 +17652,48 @@
       </c>
       <c r="AM73" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FUNCIONÁRIOS ESTRATÉGIA LIVRE FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESPONSABI</t>
-        </is>
-      </c>
-      <c r="AN73" s="4" t="inlineStr">
-        <is>
-          <t>Fundo destinado a Funcionários e aposentados da Caixa Econômica Federal. Disponível para aplicação somente via conta corrente marcada como conta-salário empregado CAIXA.</t>
-        </is>
-      </c>
+          <t>CAIXA ESTRATÉGIA LIVRE FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESPONSABILIDADE LIMITA</t>
+        </is>
+      </c>
+      <c r="AN73" s="4" t="inlineStr"/>
       <c r="AO73" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6479.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6440.pdf</t>
         </is>
       </c>
       <c r="AP73" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6479.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6440.pdf</t>
         </is>
       </c>
       <c r="AQ73" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6479.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6440.pdf</t>
         </is>
       </c>
       <c r="AR73" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6479.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6440.pdf</t>
         </is>
       </c>
       <c r="AS73" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6479.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6440.pdf</t>
         </is>
       </c>
       <c r="AT73" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6479.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6440.pdf</t>
         </is>
       </c>
       <c r="AU73" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6479.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6440.pdf</t>
         </is>
       </c>
       <c r="AV73" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/6479-SUMARIO.pdf</t>
+          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/6440-SUMARIO.pdf</t>
         </is>
       </c>
       <c r="AW73" s="4" t="inlineStr"/>

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,26442300</t>
+          <t>2,26546800</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -794,22 +794,22 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>5,43</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>12,79</t>
+          <t>12,78</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>405,891</t>
+          <t>428,376</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,50331500</t>
+          <t>5,50583200</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>5,32</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.599,761</t>
+          <t>6.566,890</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,77871600</t>
+          <t>2,77998700</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>5,32</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>971,966</t>
+          <t>950,158</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>3,33555600</t>
+          <t>3,33725300</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>5,86</t>
+          <t>5,91</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>11,671</t>
+          <t>11,680</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -1735,22 +1735,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,49026300</t>
+          <t>3,49206700</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>5,98</t>
+          <t>6,03</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>119,868</t>
+          <t>119,831</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1977,32 +1977,32 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1.838,17745300</t>
+          <t>1.839,19494400</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>6,07</t>
+          <t>6,13</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>14,61</t>
+          <t>14,60</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>96,673</t>
+          <t>96,728</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -2216,22 +2216,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,71248000</t>
+          <t>9,71720500</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>5,58</t>
+          <t>5,63</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>582,976</t>
+          <t>583,300</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2455,32 +2455,32 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3,35909700</t>
+          <t>3,36083500</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>5,94</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>14,18</t>
+          <t>14,17</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>62,638</t>
+          <t>62,749</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,99984900</t>
+          <t>3,00147000</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>6,20</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1.665,645</t>
+          <t>1.664,699</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2925,32 +2925,32 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>19,76386800</t>
+          <t>19,81575100</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>0,273</t>
+          <t>0,262</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>-0,30</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>3,38</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>10,85</t>
+          <t>11,00</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>119,263</t>
+          <t>119,579</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -3168,17 +3168,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,47058700</t>
+          <t>13,47143300</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>0,171</t>
+          <t>0,006</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>-0,17</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>9,94</t>
+          <t>9,75</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,602</t>
+          <t>27,606</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>09.548.729/0001-71</t>
+          <t>03.218.183/0001-04</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>87</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>IPCA+6%</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="AM12" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FOCO ÍNDICE DE PREÇOS FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESP LIMITADA</t>
+          <t>CAIXA CAPITAL ÍNDICE DE PREÇOS FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESP LIMITADA</t>
         </is>
       </c>
       <c r="AN12" s="2" t="inlineStr">
@@ -3349,47 +3349,47 @@
       </c>
       <c r="AO12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5414.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0087.pdf</t>
         </is>
       </c>
       <c r="AP12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5414.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0087.pdf</t>
         </is>
       </c>
       <c r="AQ12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5414.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0087.pdf</t>
         </is>
       </c>
       <c r="AR12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5414.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_87.pdf</t>
         </is>
       </c>
       <c r="AS12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5414.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_87.pdf</t>
         </is>
       </c>
       <c r="AT12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5414.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_87.pdf</t>
         </is>
       </c>
       <c r="AU12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5414.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_0087.pdf</t>
         </is>
       </c>
       <c r="AV12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5414-SUMARIO.pdf</t>
+          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/0087-SUMARIO.pdf</t>
         </is>
       </c>
       <c r="AW12" s="2" t="inlineStr">
         <is>
-          <t>https://web.microsoftstream.com/video/a5ab94de-1f04-4f00-87d2-ffa0c6babbaf?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
+          <t>https://web.microsoftstream.com/video/32d65536-1de1-4f2f-a9b8-0fbb0d9347fc?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
     </row>
@@ -3411,22 +3411,22 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>46,19197300</t>
+          <t>46,21438300</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>5,57</t>
+          <t>5,62</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>40,531</t>
+          <t>40,543</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -3651,22 +3651,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20,23025600</t>
+          <t>20,23970500</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,594</t>
+          <t>64,600</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3890,32 +3890,32 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>3,14012900</t>
+          <t>3,14046200</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>0,158</t>
+          <t>0,010</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>5,72</t>
+          <t>5,73</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>11,19</t>
+          <t>10,99</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>78,270</t>
+          <t>78,279</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -4133,32 +4133,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14,96460000</t>
+          <t>14,97191000</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>5,60</t>
+          <t>5,66</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>13,36</t>
+          <t>13,35</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,763</t>
+          <t>27,754</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4372,22 +4372,22 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>3,00192300</t>
+          <t>3,00334500</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>5,49</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>1,627</t>
+          <t>1,628</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -4607,32 +4607,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,29859200</t>
+          <t>3,30647800</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>0,263</t>
+          <t>0,239</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>-0,48</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>3,49</t>
+          <t>3,74</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>11,43</t>
+          <t>11,55</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>135,106</t>
+          <t>135,267</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4850,22 +4850,22 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,04271100</t>
+          <t>3,04433100</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>6,21</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1.763,912</t>
+          <t>1.764,996</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -5081,22 +5081,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32,81327100</t>
+          <t>32,82974200</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>5,76</t>
+          <t>5,81</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2.192,107</t>
+          <t>2.200,355</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5320,22 +5320,22 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,30797600</t>
+          <t>3,30963900</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>5,82</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>13,051</t>
+          <t>13,013</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -5564,32 +5564,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3,34396800</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>0,329</t>
+          <t>3,33890600</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>-0,151</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>4,92</t>
+          <t>4,76</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>10,18</t>
+          <t>9,82</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,618</t>
+          <t>65,492</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,32 +5803,32 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>19,05358700</t>
+          <t>19,06333300</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>5,92</t>
+          <t>5,97</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>14,13</t>
+          <t>14,12</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>950,541</t>
+          <t>950,760</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,11213849</t>
+          <t>1,11472938</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -6050,14 +6050,14 @@
           <t>-0,001</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>-0,20</t>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>0,02</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>3,10</t>
+          <t>3,34</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>205,303</t>
+          <t>205,712</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1,24146100</t>
+          <t>1,24224000</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -6287,22 +6287,22 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>5,99</t>
+          <t>6,06</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>14,53</t>
+          <t>14,54</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>71,379</t>
+          <t>71,426</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -6508,22 +6508,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1.834,37329900</t>
+          <t>1.835,39037000</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>6,21</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>175,488</t>
+          <t>175,646</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6747,32 +6747,32 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1,20397200</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>0,129</t>
+          <t>1,20388200</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>-0,007</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>7,13</t>
+          <t>7,12</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>13,75</t>
+          <t>13,51</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>40,001</t>
+          <t>39,998</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -6986,22 +6986,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,04048600</t>
+          <t>1,04102900</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>-0,001</t>
+          <t>-0,002</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>6,11</t>
+          <t>6,16</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,972</t>
+          <t>21,989</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,17181800</t>
+          <t>1,17252500</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -7219,22 +7219,22 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>5,59</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>13,98</t>
+          <t>13,99</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>66,553</t>
+          <t>66,585</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,07566699</t>
+          <t>1,07737058</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -7450,12 +7450,12 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>4,09</t>
+          <t>4,26</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>305,785</t>
+          <t>306,272</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7894,22 +7894,22 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>5,14588400</t>
+          <t>5,14870200</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>6,14</t>
+          <t>6,19</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>851,782</t>
+          <t>851,850</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8133,22 +8133,22 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>4,95138600</t>
+          <t>4,95402500</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>6,14</t>
+          <t>6,20</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.270,389</t>
+          <t>3.272,057</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>29,27848900</t>
+          <t>29,29263900</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>5,57</t>
+          <t>5,62</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,112</t>
+          <t>21,122</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8599,22 +8599,22 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>30,64862400</t>
+          <t>30,66461000</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>6,03</t>
+          <t>6,09</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>3.109,338</t>
+          <t>3.108,270</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -8834,32 +8834,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1.771,92412100</t>
+          <t>1.773,03457500</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0,088</t>
+          <t>0,062</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>13,31</t>
+          <t>13,29</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>123,161</t>
+          <t>122,919</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>3,22644100</t>
+          <t>3,22814100</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>6,17</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -9094,7 +9094,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>586,364</t>
+          <t>587,335</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -9308,32 +9308,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>6,19605500</t>
+          <t>6,19923200</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>5,93</t>
+          <t>5,98</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>14,17</t>
+          <t>14,16</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>121,534</t>
+          <t>121,592</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9548,22 +9548,22 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1,27095400</t>
+          <t>1,27164400</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>6,31</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>391,366</t>
+          <t>391,375</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -9787,32 +9787,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>10,60781400</t>
+          <t>10,61342400</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>6,12</t>
+          <t>6,17</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>14,63</t>
+          <t>14,62</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2.369,324</t>
+          <t>2.370,668</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10026,22 +10026,22 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>5,52453600</t>
+          <t>5,52743200</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>6,22</t>
+          <t>6,27</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>545,807</t>
+          <t>545,693</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -10266,22 +10266,22 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3,57293100</t>
+          <t>3,57486400</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>6,23</t>
+          <t>6,29</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15.579,204</t>
+          <t>15.576,511</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>200000.0</t>
+          <t>50000.0</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>20000.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
@@ -10442,7 +10442,12 @@
       </c>
       <c r="AN42" s="2" t="inlineStr">
         <is>
-          <t>*Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).</t>
+          <t>*Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).
+Fundo em Campanha período 16/06/2026 à 30/06/2026
+Redução de Tickets
+Aplicação